--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -809,8 +809,854 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Menkes tegaskan perbaikan layanan usai kasus pasien BPJS viral</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:38:17 +0700</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kesehatan Budi Gunadi Sadikin menanggapi kasus pasien BPJS Kesehatan yang menjadi sorotan di media ...</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681784/menkes-tegaskan-perbaikan-layanan-usai-kasus-pasien-bpjs-viral</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_MENKES-TEGASKAN-PERBAIKAN-LAYANAN.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Menkes dan Kepala BGN tanggapi keracunan MBG di Jayapura dan Semarang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:13:21 +0700</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kesehatan Budi Gunadi Sadikin dan Kepala Badan Gizi Nasional (BGN) Sudaryono menanggapi kasus ...</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681775/menkes-dan-kepala-bgn-tanggapi-keracunan-mbg-di-jayapura-dan-semarang</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENKES-DAN-KEPALA-BGN-TANGGAPI-KERACUNAN-MBG-DI-JAYAPURA-DAN-SEMARANG.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Undana luncurkan website desa di Sumba Timur cegah korupsi Dana Desa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:12:26 +0700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tim Pengabdian kepada Masyarakat (PKM) Universitas Nusa Cendana (Undana) meluncurkan website resmi Desa Mburukulu, ...</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681780/undana-luncurkan-website-desa-di-sumba-timur-cegah-korupsi-dana-desa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/Hukum-Undana.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UT siap menuju World Class University lewat pengukuhan 6 profesor baru</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:09:03 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Universitas Terbuka (UT) menyatakan siap menuju World Class University melalui pengukuhan enam orang guru besar atau ...</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681776/ut-siap-menuju-world-class-university-lewat-pengukuhan-6-profesor-baru</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_145852.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KP2MI rancang Program SMK Go Global tingkatkan brain circulation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:04:07 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kementerian Pelindungan Pekerja Migran Indonesia (KP2MI) berupaya agar implementasi Program SMK Go Global dapat ...</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681773/kp2mi-rancang-program-smk-go-global-tingkatkan-brain-circulation</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000257554.jpg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Menteri Kebudayaan siapkan Museum Musik Indonesia di Bandung</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:59:03 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Menteri Kebudayaan Fadli Zon mengatakan pihaknya tengah menyiapkan Museum Musik Indonesia di Kota Bandung, Jawa Barat, ...</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681772/menteri-kebudayaan-siapkan-museum-musik-indonesia-di-bandung</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0391.jpeg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Akademisi nilai intelijen keuangan, MLA kunci bongkar sindikat daring</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:59:02 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Guru Besar Hukum Laut Internasional Universitas Indonesia Arie Afriansyah menilai intelijen keuangan dan bantuan hukum ...</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681768/akademisi-nilai-intelijen-keuangan-mla-kunci-bongkar-sindikat-daring</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/24/WhatsApp-Image-2025-06-24-at-8.53.56-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Film SOLATA angkat realitas pendidikan dan nasionalisme di pelosok</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:54:18 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Film SOLATA yang artinya dalam bahasa Toraja adalah "Teman sebagai keluarga yang kita pilih" mengangkat ...</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681767/film-solata-angkat-realitas-pendidikan-dan-nasionalisme-di-pelosok</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001569922.jpg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ungu adopsi konsep MV lamanya di MV "Utara-Selatan"</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Grup musik Ungu kembali mengadopsi konsep pertunjukan panggung dalam video musik (MV) terbaru mereka berjudul ...</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681763/ungu-adopsi-konsep-mv-lamanya-di-mv-utara-selatan</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_145547.jpg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gubernur Sumut bawa anggota DPRD lihat langsung pembangunan di Nias</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:43:26 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution membawa sejumlah anggota DPRD Sumut melihat langsung, dan sekaligus ...</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681759/gubernur-sumut-bawa-anggota-dprd-lihat-langsung-pembangunan-di-nias</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001032398.jpg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bogor dukung percepatan pembangunan Tol Desari hingga Salabenda</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:38:31 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Bogor, Jawa Barat, mendukung percepatan pembangunan Jalan Tol Depok-Antasari (Desari) hingga ...</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681755/bogor-dukung-percepatan-pembangunan-tol-desari-hingga-salabenda</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1003317882.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BPBD Garut pantau daerah pesisir untuk cek dampak gempa Pangandaran</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:30:12 +0700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Kabupaten Garut, Jawa Barat memantau daerah, terutama pesisir pantai untuk ...</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681751/bpbd-garut-pantau-daerah-pesisir-untuk-cek-dampak-gempa-pangandaran</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260805_235729.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Menbud apresiasi kontribusi Is Haryanto bagi musik Indonesia</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:27:07 +0700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Menteri Kebudayaan Fadli Zon mengapresiasi kontribusi musisi Is Haryanto terhadap perkembangan musik Indonesia dalam ...</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681747/menbud-apresiasi-kontribusi-is-haryanto-bagi-musik-indonesia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0402.jpeg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MTI: Audit independen perkuat keselamatan transportasi laut</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:18:42 +0700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Masyarakat Transportasi Indonesia (MTI) mendorong audit keselamatan independen untuk memperkuat sistem transportasi ...</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681743/mti-audit-independen-perkuat-keselamatan-transportasi-laut</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/91F0BE4F-DCB0-4CA3-AB88-28A1FE654A87.jpeg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Iran Klaim Sepakat dengan Oman Kelola Bersama Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 02:01:54 +0700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Iran dan Oman sepakat mengelola rute kapal di Selat Hormuz. Kesepakatan ini diharapkan dapat meningkatkan keamanan jalur pelayaran meski tantangan masih ada.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606236/iran-klaim-sepakat-dengan-oman-kelola-bersama-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/18/perang-as-iran-berakhir-selat-hormuz-segera-dibuka-1781798442960_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Analisis BMKG soal Gempa M 5,2 di Pangandaran Terasa hingga Sukabumi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:25:03 +0700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 5,2 mengguncang Pangandaran, Jawa Barat, pada Rabu malam. BMKG menyatakan tidak ada potensi tsunami dan mengimbau masyarakat tetap tenang.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606234/analisis-bmkg-soal-gempa-m-5-2-di-pangandaran-terasa-hingga-sukabumi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rudal Rusia Bombardir Kyiv Ukraina, 17 Orang Tewas dan 40 Terluka</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:00:11 +0700</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Serangan rudal Rusia di Kyiv menewaskan 17 orang dan melukai puluhan lainnya. Ukraina mendesak pengiriman lebih banyak rudal pencegat untuk melindungi warganya.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606223/rudal-rusia-bombardir-kyiv-ukraina-17-orang-tewas-dan-40-terluka</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/rusia-kembali-serang-kyiv-sedikitnya-15-orang-tewas-1785922609538_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Austria-Slovakia Catat Rekor Suhu Panas Tertinggi 41 Derajat Celsius</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:15:03 +0700</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Austria dan Slovakia mencatat suhu tertinggi 41 derajat Celsius akibat gelombang panas ekstrem. Perubahan iklim memperparah kekeringan di Eropa.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606217/austria-slovakia-catat-rekor-suhu-panas-tertinggi-41-derajat-celsius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/03/bingkai-sepekan-gelombang-panas-ekstrem-terjang-eropa-warga-diminta-waspada-1783086200616_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -1655,8 +1655,102 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Madrid dan Leipzig Sepakati Transfer Diomande, Nilainya Segini</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 02:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Real Madrid akhirnya mencapai kata sepakat dengan RB Leipzig soal transfer Yan Diomande. Winger Pantai Gading itu selangkah lagi berseragam putih-putih.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8606221/madrid-dan-leipzig-sepakati-transfer-diomande-nilainya-segini</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/yan-diomande-1785952593058_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tanpa Penonton, Final Piala Presiden Tetap Dijaga Ketat Aparat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Muhammad Robbani</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Organizing Committee (OC) Piala Presiden 2026 Arya Sinulingga ungkap alasan final tanpa penonton. Tanpa penonton, laga tetap dijaga ketat aparat.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606219/tanpa-penonton-final-piala-presiden-tetap-dijaga-ketat-aparat</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1749,8 +1749,714 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Arsenal sepakat datangkan Bruno Guimaraes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:52:58 +0700</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Juara Liga Inggris Arsenal dilaporkan mencapai kesepakatan untuk mendatangkan gelandang Newcastle United Bruno ...</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681809/arsenal-sepakat-datangkan-bruno-guimaraes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/05/19/2023-05-18T204216Z_664206330_UP1EJ5I1LIETK_RTRMADP_3_SOCCER-ENGLAND-NEW-BRH-REPORT.jpg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mohamed Salah gabung Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:47:52 +0700</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mohamed Salah bergabung dengan klub Turki Trabzonspor setelah didatangkan dari Liverpool dalam status bebas ...</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681808/mohamed-salah-gabung-trabzonspor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/04/XxjpseE000147_20260704_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Newcastle tunjuk Matthias Jaissle sebagai pelatih kepala baru</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:43:37 +0700</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Newcastle United  menunjuk Matthias Jaissle sebagai pelatih kepala baru menggantikan Eddie Howe yang mundur ...</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681807/newcastle-tunjuk-matthias-jaissle-sebagai-pelatih-kepala-baru</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/11/12/ilustrasi-newcastle.jpg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Perputaran ekonomi Piala Presiden 2026 capai Rp1,5 miliar</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:37:14 +0700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ketua Organizing Committee (OC) Piala Presiden 2026 Tsamara Amany mengungkapkan total perputaran ekonomi turnamen ...</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681804/perputaran-ekonomi-piala-presiden-2026-capai-rp15-miliar</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0002.jpg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Luis Figo desak Presiden FIFA Gianni Infantino mundur</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:30:38 +0700</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Gelandang legendaris Portugal, Luis Figo, mendesak Presiden FIFA Gianni Infantino mundur.
+"Hari ini, saya ...</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681803/luis-figo-desak-presiden-fifa-gianni-infantino-mundur</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/12/IMG-20260712-WA0131.jpg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Undana bentuk tim investigasi soal kasus mahasiswi depresi</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ANTARA - Universitas Nusa Cendana membentuk tim investigasi sebagai tindak lanjut atas kasus yang menimpa mahasiswi ...</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681787/undana-bentuk-tim-investigasi-soal-kasus-mahasiswi-depresi</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_UNDANA-BENTUK-TIM-INVESTIGASI.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Zhergova antar Juventus taklukkan Chelsea 1-0</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:26:06 +0700</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Edon Zhergova mengantarkan Juventus menaklukkan Chelsea 1-0 pada pertandingan persahabatan di Stadion Kai Tak Sports ...</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681799/zhergova-antar-juventus-taklukkan-chelsea-1-0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/10/30/1667073098700.jpg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Derby Milano di Perth berakhir imbang 1-1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:20:11 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Derby Milano antara AC Milan dan Inter Milan berakhir imbang 1-1 pada pertandingan persahabatan di Stadion Optus, ...</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681796/derby-milano-di-perth-berakhir-imbang-1-1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/2026.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Manchester City tekuk K-League All Stars 3-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:15:21 +0700</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Manchester City mengandaskan tim K-League All Stars dengan  3-1 pada pertandingan persahabatan di Stadion Seoul ...</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681792/manchester-city-tekuk-k-league-all-stars-3-1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/semenyo.jpg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Diupah Rp 100 Ribu, Pemulung di Makassar Bantu Angkut Kabel BTS Hasil Curian</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:00:16 +0700</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Reinhard Soplantila</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Polisi menangkap SA, pria 38 tahun, yang terlibat pencurian kabel BTS di Makassar. Ia mengaku dibayar Rp 100 ribu untuk membantu mengangkut barang curian.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606265/diupah-rp-100-ribu-pemulung-di-makassar-bantu-angkut-kabel-bts-hasil-curian</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-menangkap-pria-berinisial-sa-terkait-kasus-pencurian-kabel-dan-perlengkapan-menara-bts-1785935325035_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pemerintah Nigeria Bebaskan 308 Korban Penculikan Bandit-Kelompok Jihadis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:33:36 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Pemerintah Nigeria berhasil membebaskan 308 warga yang diculik, termasuk 163 dari Desa Woro. Penculikan ini menjadi krisis besar di negara tersebut.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606261/pemerintah-nigeria-bebaskan-308-korban-penculikan-bandit-kelompok-jihadis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/21/personel-militer-nigeria-berpatroli-di-lokasi-serangan-militan-1763722354741_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AS Cabut Sanksi Maskapai Irak yang Terkait Garda Revolusi Iran</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 03:55:57 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AS mencabut sanksi terhadap maskapai Fly Baghdad setelah peninjauan. Namun, sanksi terhadap pemiliknya tetap berlaku. Perubahan operasional jadi faktor utama.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606259/as-cabut-sanksi-maskapai-irak-yang-terkait-garda-revolusi-iran</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/14/ilustrasi-pesawat_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gempa M 5,4 Guncang Boven Digoel Papua</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 03:08:50 +0700</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Farih Maulana Sidik</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Gempa bumi magnitudo 5,4 mengguncang Kabupaten Boven Digoel, Papua Selatan, pada kedalaman 57 km. BMKG menginformasikan gempa terjadi pukul 02.46 WIB.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606256/gempa-m-5-4-guncang-boven-digoel-papua</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bocah di Jambi Tewas Diterkam Buaya Saat Mandi di Sungai</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 03:00:31 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Dimas Sanjaya</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Seorang bocah 11 tahun, M Dzaki, tewas diterkam buaya saat mandi di sungai di Jambi. Temannya, Aldi, mengalami luka dan dirawat.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606255/bocah-di-jambi-tewas-diterkam-buaya-saat-mandi-di-sungai</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/petugas-saat-mengevakuasi-bocah-yang-tewas-diterkam-buaya-1785899635913_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pasutri di Bandung Kompak Jadi Jambret, Motifnya Masalah Ekonomi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 02:33:33 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Wisma Putra</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pasangan suami-istri di Bandung ditangkap setelah menjambret handphone anak di bawah umur. Motifnya diduga karena masalah ekonomi. Terancam 9 tahun penjara.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606249/pasutri-di-bandung-kompak-jadi-jambret-motifnya-masalah-ekonomi</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/13/366624f0-eb8f-4197-9ef1-fab9055cc0dc_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:I43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -2455,8 +2455,756 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Darwinbox Luncurkan Cortex, Platform HCM AI-Native Terbaru</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:42:06 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>- Darwinbox adalah platform Human Capital Management yang terkemuka di dunia dan melayani lebih dari 1.400 perusahaan ...</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681844/darwinbox-luncurkan-cortex-platform-hcm-ai-native-terbaru</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/03/23/Logo-BusinessWire-800x600.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Bolehkah beras merah dicampur beras putih? Ini penjelasannya</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:41:47 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Mencampur beras merah dan beras putih saat memasak nasi masih menjadi kebiasaan sebagian masyarakat yang ingin ...</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681840/bolehkah-beras-merah-dicampur-beras-putih-ini-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/11/21/pexels-polina-tankilevitch-4110253.jpg</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>DKI kemarin, rekayasa lalin terkait MRT hingga jumlah penduduk miskin</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:38:20 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sejumlah berita seputar Jakarta pada Rabu (5/8) menarik untuk disimak kembali hari ini, mulai dari rekayasa lalu lintas ...</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681839/dki-kemarin-rekayasa-lalin-terkait-mrt-hingga-jumlah-penduduk-miskin</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_2392.jpeg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kenapa makan ubi bikin kentut? Ini penyebabnya menurut ahli gizi</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:33:01 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Makan ubi sering dikaitkan dengan meningkatnya frekuensi buang angin atau kentut. Anggapan tersebut ternyata memiliki ...</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681835/kenapa-makan-ubi-bikin-kentut-ini-penyebabnya-menurut-ahli-gizi</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/366068.jpg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Vaksin HPV untuk siswa laki-laki</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan (Kemenkes) memperluas vaksinasi human papillomavirus (HPV) pada 2026 dengan menyasar siswa ...</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5681831/vaksin-hpv-untuk-siswa-laki-laki</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/20260806-Vaksin-HPV-untuk-siswa-laki-laki.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sudah tidur 8 jam tapi masih lelah? Ini 8 tanda kualitas tidur buruk</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:27:38 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Banyak orang menganggap tidur selama tujuh hingga delapan jam sudah cukup untuk menjaga kesehatan. Padahal, durasi ...</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681829/sudah-tidur-8-jam-tapi-masih-lelah-ini-8-tanda-kualitas-tidur-buruk</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/03/tidur.jpg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sulit tidur? Coba 7 minuman alami yang bisa membantu cepat terlelap</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:22:00 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Tidur yang nyenyak menjadi salah satu kunci untuk menjaga kesehatan tubuh dan pikiran. Sayangnya, banyak orang masih ...</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681828/sulit-tidur-coba-7-minuman-alami-yang-bisa-membantu-cepat-terlelap</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/11/D1381D2E-B040-47E1-8DE3-1CD98B238FE5.jpeg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jipang Menyala, kreasi lampu hias semarakkan HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:20:11 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ANTARA - Warga Desa Jipang, Kecamatan Karanglewas, Kabupaten Banyumas, Jawa Tengah, memeriahkan HUT ke-81 Kemerdekaan ...</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681791/jipang-menyala-kreasi-lampu-hias-semarakkan-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AYM_JIPANG-MENYALA-KREASI-LAMPU-HIAS.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Everton datangkan Christian Norgaard dari Arsenal</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:10:16 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Everton mendatangkan gelandang Christian Norgaard dari  Arsenal dalam skema transfer penuh dalam kontrak ...</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681824/everton-datangkan-christian-norgaard-dari-arsenal</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/f4176e00-910b-11f1-9e05-9b214625883c.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sebagian Jakarta bakal cerah berawan pada Kamis pagi</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:06:32 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi Klimatologi dan Geofisika (BMKG) memprakirakan wilayah Jakarta Barat, Jakarta Pusat, Jakarta Selatan, ...</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681820/sebagian-jakarta-bakal-cerah-berawan-pada-kamis-pagi</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/19/IMG_20260719_000858.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Xsolla, GDAP, dan DTI-EMB Umumkan Kemitraan Strategis untuk Mempercepat Pertumbuhan Industri Game di Filipina</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:03:19 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>- Xsolla, sebuah perusahaan perdagangan game video global terkemuka, pada hari ini mengumumkan penandatanganan Nota ...</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681817/xsolla-gdap-dan-dti-emb-umumkan-kemitraan-strategis-untuk-mempercepat-pertumbuhan-industri-game-di-filipina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cara hilangkan bau sepatu yang membandel, ampuh dengan bahan sederhana</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:59:32 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bau apek pada sepatu sering muncul akibat kelembapan, keringat, serta pertumbuhan bakteri dan jamur yang terperangkap ...</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681816/cara-hilangkan-bau-sepatu-yang-membandel-ampuh-dengan-bahan-sederhana</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/06/Festival-Sentra-Industri-Di-Bandung-060726-rai-3.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BPS catat jumlah penduduk miskin di Sumsel turun 28 ribu orang</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:54:26 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat jumlah penduduk miskin di Sumatera Selatan per Maret 2026 mencapai 869.970 orang ...</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681813/bps-catat-jumlah-penduduk-miskin-di-sumsel-turun-28-ribu-orang</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/a12529b8-8a2b-4d12-a36d-de767436b64d.jpeg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>8 manfaat beras merah untuk kesehatan, bantu jaga gula darah</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:45:06 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Beras merah menjadi salah satu pilihan sumber karbohidrat yang semakin diminati masyarakat karena memiliki kandungan ...</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681845/8-manfaat-beras-merah-untuk-kesehatan-bantu-jaga-gula-darah</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/20/pembukaan-jatiluwih-festival-2026-bali-200626-nhw-5.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bereskan Utang, Kemenkeu Ambil Alih 60% Saham Kereta Cepat September</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan (Kemenkeu) mengambil seluruh saham PT Pilar Sinergi BUMN Indonesia (PSBI) di PT Kereta Cepat Indonesia China (KCIC).</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606067/bereskan-utang-kemenkeu-ambil-alih-60-saham-kereta-cepat-september</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/15/mobilitas-penumpang-whoosh-diprediksi-meningkat-saat-lebaran-1773573347987_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pajak Toko Online Ditunda karena Ekonomi Belum Lari Kencang</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan (Kemenkeu) menunda penerapan pajak e-commerce yang sebelumnya dijadwalkan mulai berlaku 1 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606042/pajak-toko-online-ditunda-karena-ekonomi-belum-lari-kencang</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/01/14/ecf367f7-0e3e-4422-a3a4-1f35143e24a6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I43"/>
+  <autoFilter ref="A1:I59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -3203,8 +3203,3486 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AS akan syaratkan deposit hingga Rp4,46 M untuk visa calon imigran</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:16:48 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Pemerintahan Presiden Amerika Serikat Donald Trump berencana memungut deposit keamanan sebesar 100.000-250.000 dolar AS ...</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681917/as-akan-syaratkan-deposit-hingga-rp446-m-untuk-visa-calon-imigran</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/05/31/visa-and-passport.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Menkes ungkap temuan bakteri pada kasus keracunan MBG Papua &amp; Semarang</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:09:54 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Menteri Kesehatan (Menkes) Budi Gunadi Sadikin mengatakan pihaknya menindaklanjuti temuan bakteri E. coli dalam ...</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681913/menkes-ungkap-temuan-bakteri-pada-kasus-keracunan-mbg-papua-semarang</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/11/10/budi-gunadi.jpg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hiroshima peringati 81 tahun bom atom di tengah ketegangan global</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:04:09 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Kota Hiroshima di Jepang, Kamis, memperingati 81 tahun serangan bom atom oleh Amerika Serikat di kota tersebut, di ...</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681909/hiroshima-peringati-81-tahun-bom-atom-di-tengah-ketegangan-global</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/17/ilustrasi-peringatan-bom-atom-Jepang.jpg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BGN: Insiden keamanan pangan di Papua akibat SPPG masak terlalu awal</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:01:10 +0700</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) mengungkap insiden keamanan pangan dalam Program Makan Bergizi Gratis (MBG) di Papua akibat ...</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681907/bgn-insiden-keamanan-pangan-di-papua-akibat-sppg-masak-terlalu-awal</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/194258.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kemenekraf perkuat SDM pelaku ekraf Sumedang lewat digitalisasi</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:59:03 +0700</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Kementerian Ekonomi Kreatif (Kemenekraf) memperkuat kualitas sumber daya manusia (SDM) ekonomi kreatif di Kabupaten ...</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681904/kemenekraf-perkuat-sdm-pelaku-ekraf-sumedang-lewat-digitalisasi</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000591757.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BMKG: Cuaca RI didominasi cerah berawan hingga berawan tebal hari ini</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:52:46 +0700</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mengatakan cuaca di sebagian besar wilayah Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681901/bmkg-cuaca-ri-didominasi-cerah-berawan-hingga-berawan-tebal-hari-ini</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/IMG_20260727_000026.jpg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>10 gejala diabetes yang sering diabaikan, jangan sampai terlambat</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:40:33 +0700</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Diabetes merupakan salah satu penyakit kronis yang jumlah penderitanya terus meningkat di berbagai negara, termasuk ...</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681897/10-gejala-diabetes-yang-sering-diabaikan-jangan-sampai-terlambat</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/IMG-20260707-WA0022.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10 cara mengatasi sedih setelah putus cinta, bantu move on lebih cepat</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:37:07 +0700</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Putus cinta merupakan pengalaman yang hampir pernah dialami setiap orang. Berakhirnya sebuah hubungan tidak hanya ...</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681893/10-cara-mengatasi-sedih-setelah-putus-cinta-bantu-move-on-lebih-cepat</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/05/27/girl-863686_1280.jpg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>9 tanda anak mengalami kesulitan belajar yang wajib diwaspadai</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:33:03 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Setiap anak memiliki kemampuan dan kecepatan belajar yang berbeda-beda. Ada yang cepat memahami pelajaran, tetapi ada ...</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681892/9-tanda-anak-mengalami-kesulitan-belajar-yang-wajib-diwaspadai</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/25/rumah-baca-di-kampung-sarawandori-serui-2675749.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cara aman melihat gerhana Matahari total tanpa merusak mata</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:29:34 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Fenomena gerhana Matahari total akan kembali terjadi pada Rabu, 12 Agustus 2026. Peristiwa astronomi ini diprediksi ...</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681888/cara-aman-melihat-gerhana-matahari-total-tanpa-merusak-mata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/20/antarafoto-gerhana-matahari-sebagian-di-bekasi-20042023-par-2.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Petugas gabungan angkut lapak PKL liar di Kembangan Jakbar</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:29:10 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Petugas gabungan Pemerintah Kota Jakarta Barat (Jakbar) mengangkut tujuh lapak pedagang kaki lima (PKL) liar di kawasan ...</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681885/petugas-gabungan-angkut-lapak-pkl-liar-di-kembangan-jakbar</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_070621.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HKI: Pengembangan kawasan industri di Madura buat pusat ekonomi baru</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:25:43 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Himpunan Kawasan Industri (HKI) Indonesia meyakini pengembangan Kawasan Industri Wiraraja Madura di Kabupaten ...</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681884/hki-pengembangan-kawasan-industri-di-madura-buat-pusat-ekonomi-baru</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-06-12-at-14.36.36-1-_edit_366879319671620.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10 penyakit yang bisa dipicu polusi udara, dari asma hingga stroke</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:25:24 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Polusi udara menjadi salah satu masalah kesehatan masyarakat yang semakin mengkhawatirkan, terutama di kota-kota besar ...</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681881/10-penyakit-yang-bisa-dipicu-polusi-udara-dari-asma-hingga-stroke</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/02/Penggunaan-Masker-Untuk-Cegah-Dampak-Polusi-Jakarta-240823-app-4.jpg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kelurahan di Jakbar gelar lomba busana bahan daur ulang rayakan HUT RI</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:22:20 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kelurahan Kemanggisan, Kecamatan Palmerah, Kota Jakarta Barat (Jakbar), menggelar lomba busana kreatif berbahan daur ...</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681877/kelurahan-di-jakbar-gelar-lomba-busana-bahan-daur-ulang-rayakan-hut-ri</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/18/IMG-20230318-WA0004_5.jpg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Bagaimana gerhana Matahari total terjadi? Ini penjelasan ilmiahnya</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:22:04 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Gerhana matahari total menjadi salah satu fenomena astronomi yang paling dinantikan karena hanya terjadi pada waktu dan ...</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681875/bagaimana-gerhana-matahari-total-terjadi-ini-penjelasan-ilmiahnya</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/04/20/antarafoto-gerhana-matahari-kendari-200324-jjn-2.jpg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Bolehkah menyiram rem cakram yang panas? Ini penjelasannya</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:18:18 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Kebiasaan menyiram air pada rem cakram yang sedang panas masih sering dilakukan sebagian pengendara dengan alasan agar ...</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5681873/bolehkah-menyiram-rem-cakram-yang-panas-ini-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/04/12/IMG20200412104947.jpg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Apa itu hiperpigmentasi? Kenali penyebab, ciri, dan cara mengatasinya</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:14:32 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Hiperpigmentasi kulit menjadi salah satu masalah kulit yang cukup sering dialami masyarakat. Kondisi ini ditandai ...</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681871/apa-itu-hiperpigmentasi-kenali-penyebab-ciri-dan-cara-mengatasinya</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/12/Kulit.jpg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Udara Jakarta terburuk ketiga di dunia pada Kamis pagi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:09:30 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kualitas udara Jakarta pada Kamis pagi berdasarkan data situs pemantau kualitas udara IQAir pada pukul 06.00 WIB ...</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681869/udara-jakarta-terburuk-ketiga-di-dunia-pada-kamis-pagi</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/06/13/Screenshot_2023-06-13-18-20-39-47_40deb401b9ffe8e1df2f1cc5ba480b12.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Transisi mobilitas berkelanjutan hingga promosi wastra Indonesia</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:03:11 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Kanal hiburan, gaya hidup, tekno, dan otomotif ANTARA menyiarkan pemberitaan mulai dari pentingnya kolaborasi ...</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681867/transisi-mobilitas-berkelanjutan-hingga-promosi-wastra-indonesia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/WhatsApp-Image-2026-08-04-at-05.45.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Multiplier Raih Pendanaan Seri B senilai $35 Juta untuk Membangun Model Baru Layanan Profesional</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:42 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>- Multiplier, perusahaan teknologi yang mengakuisisi perusahaan-perusahaan layanan profesional premium serta membangun ...</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681865/multiplier-raih-pendanaan-seri-b-senilai-35-juta-untuk-membangun-model-baru-layanan-profesional</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/03/23/Logo-BusinessWire-800x600.jpg</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Kamis, gerai Samsat Keliling tersedia di 14 wilayah Jadetabek</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:06 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Direktorat Lalu Lintas Polda Metro Jaya menyediakan layanan Sistem Administrasi Manunggal Satu Atap (Samsat) Keliling ...</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681863/kamis-gerai-samsat-keliling-tersedia-di-14-wilayah-jadetabek</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/02/22/IMG_20240222_080648.jpg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kapan ganti oli gardan motor matic? Ini jarak tempuh yang disarankan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:56:11 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Oli gardan menjadi salah satu komponen penting pada motor matic yang sering terlupakan dalam perawatan rutin. Padahal, ...</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5681860/kapan-ganti-oli-gardan-motor-matic-ini-jarak-tempuh-yang-disarankan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/03/17/Layanan-servis-dan-ganti-oli-gratis-di-Tangerang-1732025-pma-7.jpeg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Menjaga anak dari pengadilan publik</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:55:22 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Setiap kali sebuah video tentang anak viral di media sosial, perhatian publik biasanya langsung tersedot pada siapa ...</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681856/menjaga-anak-dari-pengadilan-publik</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Sunardi-saat-bermain-dengan-anaknya-2.jpg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Layanan SIM Keliling tersedia di lima lokasi Jakarta pada Kamis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:54:29 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Direktorat Lalu Lintas Polda Metro Jaya membuka layanan Surat Izin Mengemudi (SIM) Keliling di lima lokasi di ...</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681853/layanan-sim-keliling-tersedia-di-lima-lokasi-jakarta-pada-kamis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/07/28/PhotoGrid_1595891798067.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Jangan berlebihan, ini 5 efek samping makan beras merah bagi kesehatan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:50:35 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Beras merah dikenal sebagai salah satu sumber karbohidrat yang lebih sehat karena kaya serat, vitamin, mineral, dan ...</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681849/jangan-berlebihan-ini-5-efek-samping-makan-beras-merah-bagi-kesehatan</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/05/19/IMG-20210519-WA0078.jpg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Kriminal kemarin, praperadilan Febrie hingga jaringan produksi narkoba</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:46:24 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Sejumlah peristiwa terkait kriminal dan keamanan terjadi di Jakarta pada Rabu (5/8), mulai dari praperadilan ...</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5681847/kriminal-kemarin-praperadilan-febrie-hingga-jaringan-produksi-narkoba</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_20260805_194756.jpg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Netanyahu Bertekad Cegah Iran Punya Senjata Nuklir</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:16:44 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Wilda Hayatun Nufus</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Benjamin Netanyahu mengisyaratkan kemungkinan mengambil tindakan militer di tengah proses negosiasi kesepakatan antara Iran dengan Amerika Serikat (AS).</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606353/netanyahu-bertekad-cegah-iran-punya-senjata-nuklir</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/pm-israel-benjamin-netanyahu-1779163940748_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sadisnya Saepul Mutilasi Pria Kenalan di Medsos</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:09:13 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Misteri mayat mutilasi di Depok terungkap. Korban K (51) dibunuh oleh kenalan media sosial, Saepul (26), setelah cekcok. Pelaku ditangkap polisi.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606355/sadisnya-saepul-mutilasi-pria-kenalan-di-medsos</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pemkot Tangsel Dorong Angka Partisipasi Sekolah Lewat Penguatan PAUD</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:08:03 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Tangerang Selatan memperkuat sarana PAUD untuk tingkatkan partisipasi sekolah. Anggaran Rp4 miliar dialokasikan demi pendidikan berkualitas.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606344/pemkot-tangsel-dorong-angka-partisipasi-sekolah-lewat-penguatan-paud</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/wali-kota-tangerang-selatan-benyamin-davnie-1785978456517.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tak Perlu Putar Jauh, Dua JPO di Rasuna Said Bakal Terhubung</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:00:49 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Pemprov DKI akan menghubungkan dua JPO di Jalan HR Rasuna Said untuk memperkuat konektivitas serta memudahkan mobilitas pejalan kaki.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/foto-news/d-8605699/tak-perlu-putar-jauh-dua-jpo-di-rasuna-said-bakal-terhubung</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/tak-perlu-putar-jauh-dua-jpo-di-rasuna-said-bakal-terhubung-1785923553687_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>128 Ribu Orang Ikut War Tiket Upacara HUT RI di Hari Pertama, Ada dari LN</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:54:48 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Antusiasme masyarakat untuk mendaftar sebagai peserta Upacara HUT RI ke-81 di hari pertama dibuka mencapai 128.331 pendaftar dari 36 provinsi dan luar negeri.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606338/128-ribu-orang-ikut-war-tiket-upacara-hut-ri-di-hari-pertama-ada-dari-ln</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ilustrasi-upacara-hut-ri-di-istana-1785898929673_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Waka Komisi III DPR Dorong Perampasan Aset Koruptor daripada Hukuman Mati</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:51:34 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Kalau dihukum mati, uangnya nggak balik, kata Sahroni.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606336/waka-komisi-iii-dpr-dorong-perampasan-aset-koruptor-daripada-hukuman-mati</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/wakil-ketua-komisi-iii-dpr-ahmad-sahroni-1785822730689_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MUI Dorong Hukum Mati Koruptor, Yusril Sebut Sudah Diatur Undang-Undang</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:42:40 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Menteri Yusril merespons MUI yang dorong hukuman mati bagi koruptor. Ia menekankan pentingnya keadilan dan etika dalam penegakan hukum di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606327/mui-dorong-hukum-mati-koruptor-yusril-sebut-sudah-diatur-undang-undang</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/19/menko-kumham-imipas-yusril-ihza-mahendra-1779175464746_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bansos PKH Triwulan III Tersalurkan ke 7 Juta KPM dan Sembako 12 Juta KPM</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:42:27 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial salurkan Bansos PKH dan sembako untuk lebih dari 18 juta KPM. Menteri Gus Ipul menjelaskan proses dan update data penerima.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606325/bansos-pkh-triwulan-iii-tersalurkan-ke-7-juta-kpm-dan-sembako-12-juta-kpm</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/mensos-saifullah-yusuf-1785976918126_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cerita Relawan Berjibaku 2 Jam Siapkan Pemakaman Wanita Bobot 300 Kg di Sragen</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:42:22 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Tim detikJateng</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Tim relawan bercerita mempersiapkan alat beberapa jam sebelum pemakaman wanita asal Sragen berbobot 300 kilogram berinisial I (39) dilaksanakan.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606324/cerita-relawan-berjibaku-2-jam-siapkan-pemakaman-wanita-bobot-300-kg-di-sragen</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pemakaman-wanita-berbobot-300-kg-di-sragen-1785844745612_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pemkot Tangsel Gencarkan Edukasi Kesehatan untuk Ibu Hamil</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:34:32 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Tangerang Selatan mengedukasi ibu hamil dan tenaga kesehatan untuk meningkatkan kesehatan selama kehamilan.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606320/pemkot-tangsel-gencarkan-edukasi-kesehatan-untuk-ibu-hamil</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pemkot-tangsel-1785976448359_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Trump Menepis Kabar Amunisi AS Menipis</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:33:07 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Presiden Trump membantah kabar AS kehabisan amunisi di tengah perang dengan Iran. Ia menegaskan pasokan amunisi masih mencukupi dan produksi meningkat.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606317/trump-menepis-kabar-amunisi-as-menipis</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/trump-ultimatum-iran-damai-atau-penyerahan-total-1785838566479_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Beras Premium Produksi BULOG Kini Jangkau Retail Modern</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:27:20 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Perum BULOG memperluas distribusi beras premium ke retail modern di Indonesia untuk memudahkan akses masyarakat. Stok beras aman dan harga terjangkau.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606314/beras-premium-produksi-bulog-kini-jangkau-retail-modern</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/beras-premium-produksi-bulog-1785976010978_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Legislator PD Tak Setuju MUI: Hukuman Mati Bukan Solusi Berantas Korupsi</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:22:24 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Benny K Harman dari F-Demokrat menolak hukuman mati bagi koruptor, mengusulkan KPK sebagai lembaga independen untuk pemberantasan korupsi dan perampasan aset.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606312/legislator-pd-tak-setuju-mui-hukuman-mati-bukan-solusi-berantas-korupsi</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/25/ketua-fraksi-partai-demokrat-mpr-ri-benny-k-harman-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Respons Walkot Solo Usai Digugat Penjual Miras di Lokananta karena Kena Razia</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:17:02 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Tara Wahyu NV</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Respons Walkot Solo usai digugat penjual minuman keras di Lokananta karena kena razia.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606309/respons-walkot-solo-usai-digugat-penjual-miras-di-lokananta-karena-kena-razia</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/pemkot-solo-1785144402288_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mardani PKS Respons Golkar dan PDIP: Oposisi dan Koalisi Sama Mulianya</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:13:07 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>PDIP dan Golkar saling berbalas pernyataan tentang oposisi dan koalisi. Mardani PKS menegaskan kedua posisi mulia jika untuk kepentingan rakyat.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606307/mardani-pks-respons-golkar-dan-pdip-oposisi-dan-koalisi-sama-mulianya</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/21/mardani-ali-sera_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Cerita di Balik 'Bencongan' Jadi Nama Kelurahan</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:02:46 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Kelurahan Bencongan di Tangerang memiliki nama unik dengan sejarah menarik. Ini cerita di balik nama unik kelurahan tersebut.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606304/cerita-di-balik-bencongan-jadi-nama-kelurahan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kelurahan-bencongan-di-tangerang-1785918374256_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ILF &amp;amp; IGT Expo 2026 Resmi Dibuka, Hadirkan Inovasi Industri Manufaktur</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:47:52 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Brand Studio</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ILF &amp; IGT Expo 2026 hadir di JIExpo Kemayoran! Diikuti 210 pelaku industri dari 14 negara dengan beragam solusi manufaktur tekstil dan kulit terkini.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/detik-tv/d-8606288/ilf-igt-expo-2026-resmi-dibuka-hadirkan-inovasi-industri-manufaktur</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/indoleather-1785973659891_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Legislator Sayangkan Nakes Hina Pasien BPJS, Desak Sanksi Tegas</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:46:48 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Anggota Komisi IX DPR, Ashabul Kahfi, menyesalkan dugaan nakes menghina pasien BPJS. Ia mendesak sanksi tegas dan evaluasi pelayanan kesehatan yang transparan.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606287/legislator-sayangkan-nakes-hina-pasien-bpjs-desak-sanksi-tegas</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/08/ketua-komisi-viii-dpr-ashabul-kahfi_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IndoHealthcare Expo 2026 Hadirkan Teknologi Kesehatan dari 9 Negara!</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:46:42 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Brand Studio</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>IndoHealthcare Gakeslab Expo 2026 hadir di JIExpo Kemayoran! Edisi ke-16 ini menghadirkan inovasi alat kesehatan dan teknologi medis dari 9 negara.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/detik-tv/d-8606285/indohealthcare-expo-2026-hadirkan-teknologi-kesehatan-dari-9-negara</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/indohealth-expo-2026-1785973369643_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IndoBeauty Expo 2026, Inovasi dan Tren Kecantikan Terbaru</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:45:26 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Brand Studio</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>IndoBeauty Expo 2026 hadir di JIExpo Kemayoran! Temukan inovasi skincare, kosmetik, teknologi kecantikan, workshop, talkshow, dan kompetisi.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/detik-tv/d-8606284/indobeauty-expo-2026-inovasi-dan-tren-kecantikan-terbaru</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/indobeauty-expo-2026-1785973429088_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Horor Tabrakan 2 Truk hingga Sopir Kejepit di Bogor</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:32:10 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Kecelakaan mengerikan melibatkan dua unit truk terjadi di Kabupaten Bogor. Kerasnya tabrakan sempat membuat pengemudi sopir terjepit di ruang kemudi.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606282/horor-tabrakan-2-truk-hingga-sopir-kejepit-di-bogor</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kecelakaan-truk-di-gunungputri-dok-istimewa-1785901663803_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Komisi I DPR Minta RI Desak Netanyahu Setop Serang Gaza: Manfaatkan BoP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:15:58 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi I DPR, Dave Laksono, mendesak pemerintah Indonesia untuk mendesak PM Israel Netanyahu menghentikan serangan di Gaza melalui Board of Peace.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606280/komisi-i-dpr-minta-ri-desak-netanyahu-setop-serang-gaza-manfaatkan-bop</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/24/dave-laksono-anggidetikcom_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Kecaman dari Senayan ke Nakes yang Hina Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:01:40 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Dugaan nakes menghina pasien BPJS, Yurizal Tri Chaerawan, menuai kecaman DPR. Legislator mendesak Kemenkes investigasi dan sanksi bagi nakes yang tak berempati.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606278/kecaman-dari-senayan-ke-nakes-yang-hina-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/06/16/631af7b6-8185-4e8f-b57f-547b351038f7_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Indonesia Makin Padat, Penduduk Bertambah 1,8 Juta Jiwa</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:00:48 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Gilang Faturahman</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Jumlah penduduk Indonesia bertambah sekitar 1,8 juta jiwa dalam enam bulan. Populasi kini mencapai 290,1 juta jiwa berdasarkan data Dukcapil.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/foto-news/d-8605837/indonesia-makin-padat-penduduk-bertambah-1-8-juta-jiwa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/indonesia-makin-padat-penduduk-bertambah-18-juta-jiwa-1785927224335_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MAKI Dukung MUI: Koruptor Harus Dihukum Mati dan Dirampas Asetnya</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:33:04 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>MUI dorong hukuman mati bagi koruptor, didukung MAKI. Korupsi dianggap merusak generasi. Perampasan aset juga jadi solusi untuk menakut-nakuti koruptor.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606275/maki-dukung-mui-koruptor-harus-dihukum-mati-dan-dirampas-asetnya</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/24/koordinator-maki-boyamin-adrialdetikcom-1766571327560_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gempa M 5,8 Guncang Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:21:29 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>fas</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Gempa bumi magnitudo 5,8 mengguncang Kabupaten Kepulauan Sangihe, Sulawesi Utara, pada kedalaman 10 km. BMKG menyatakan tidak berpotensi tsunami.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606274/gempa-m-5-8-guncang-kepulauan-sangihe</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/27/ilustrasi-gempa_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>AS Kembalikan Pungutan Tarif Impor Trump Rp 1.790 T</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:15:49 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Amerika Serikat (AS) akan mengembalikan US$ 100 miliar atau Rp 1.790 triliun (kurs Rp 17.900) dari bea masuk yang diinisiasi Presiden Donald Trump.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606334/as-kembalikan-pungutan-tarif-impor-trump-rp-1-790-t</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sekolah Rakyat Garapan Brantas Abipraya di Bandung Mulai Beroperasi</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:05:56 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Fara Difa Alfeni</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Sekolah Rakyat Terintegrasi 4 di Kabupaten Bandung resmi beroperasi dengan 560 siswa. Didesain modern, sekolah ini mendukung akses pendidikan berkualitas.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8606343/sekolah-rakyat-garapan-brantas-abipraya-di-bandung-mulai-beroperasi</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kondisi-bangunan-sekolah-rakyat-terintegrasi-srt-4-kabupaten-bandung-1785928400979.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BPS: Ekonomi Tumbuh 5,29%, Penduduk Miskin Turun Jadi 22,93 Juta Orang</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mengumumkan ekonomi Indonesia berhasil tumbuh 5,29% kuartal II-2026.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606206/bps-ekonomi-tumbuh-5-29-penduduk-miskin-turun-jadi-22-93-juta-orang</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/05/27/bangkit-dari-pandemi-ekonomi-ri-kuartal-ii-2021-diramal-tembus-7-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Izin Tambang Berakhir 2041, Ini Alasan Freeport Perpanjang Lebih Awal</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:52:32 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia mengajukan perpanjangan IUPK untuk tambang Grasberg. Ini penting untuk keberlanjutan operasi dan dampak ekonomi jangka panjang.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8606337/izin-tambang-berakhir-2041-ini-alasan-freeport-perpanjang-lebih-awal</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ilustrasi-tambang-freeport-1785977535094_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BPS Ungkap Jumlah Pengangguran Turun, Ini Datanya</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat jumlah pengangguran di Indonesia per Mei 2026 turun 24 ribu dibanding Februari 2026.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606104/bps-ungkap-jumlah-pengangguran-turun-ini-datanya</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/ribuan-lowongan-dibuka-job-fair-kendal-2026-diserbu-pencari-kerja-1784695060618_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pameran Produk Kulit dan Garmen Internasional Digelar di JIExpo Kemayoran</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:13:37 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Krista Exhibitions Group membuka ILF dan IGT Expo 2026 di Jakarta, mempertemukan 210 peserta dari 14 negara untuk inovasi dan peluang bisnis.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606308/pameran-produk-kulit-dan-garmen-internasional-digelar-di-jiexpo-kemayoran</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/krista-exhibitions-group-1785975194877_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Penyelundupan Harley Bekas dari China Terbongkar!</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Bea Cukai menggagalkan penyelundupan 5 unit sepeda motor Harley-Davidson bekas terurai dan 20 unit frame (rangka) bekas di Pelabuhan Tanjung Priok.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606192/penyelundupan-harley-bekas-dari-china-terbongkar</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/modus-misdeclaration-terbongkar-harley-davidson-bekas-ilegal-disita-bea-cukai-1785903653788_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Milan Vs Inter: Hasil Uji Coba Bukan Hal Penting untuk Chivu</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Putra Rusdi K</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Pelatih Inter Milan,Cristian Chivu, menilai hasil bukan yang utama di laga uji coba. Ia tetap puas meski timnya gagal menang melawan AC Milan.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8606322/milan-vs-inter-hasil-uji-coba-bukan-hal-penting-untuk-chivu</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/19/cristian-chivu-1781884812961_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Amorim: Milan Masih Punya PR di Penguasaan Bola</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Putra Rusdi K</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Pelatih AC Milan, Ruben Amorim, menilai timnya tak cukup baik dalam penguasaan bola. Amorim yang baru menukangi Milan punya pekerjaan rumah memperbaiki itu.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8606254/amorim-milan-masih-punya-pr-di-penguasaan-bola</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/29/2288116407-1785324182386_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Mohamed Salah Tiba di Turki, Siap Gabung Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:53 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Mohamed Salah tiba di Turki dan menyita perhatian publik. Bintang asal Mesir itu dikabarkan segera menandatangani kontrak bersama Trabzonspor.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8605993/mohamed-salah-tiba-di-turki-siap-gabung-trabzonspor</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mohamed-salah-tiba-di-turki-siap-gabung-trabzonspor-1785933827411_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Salah Pakai Nomor 10 di Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Mohamed Salah begitu spesial untuk Trabzonspor. Klub berjuluk Badai Laut Hitam itu sampai rela memberikan jersey nomor 10 untuk Salah.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606233/salah-pakai-nomor-10-di-trabzonspor</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mohamed-salah-1785947980160_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Matthias Jaissle Jadi Manajer Baru Newcastle</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:30:35 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Newcastle United sudah mendapat pengganti Eddie Howe. The Magpies resmi menunjuk Matthias Jaissle sebagai manajer baru.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8606253/matthias-jaissle-jadi-manajer-baru-newcastle</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/mathias-jaissle-1785959585763_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Akhirnya Newcastle dan Arsenal Sepakati Harga Bruno Guimaraes</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Adhi Prasetya</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Newcastle United akhirnya bersedia melepas Bruno Guimaraes ke Arsenal. Gelandang asal Brasil itu tinggal menjalani tes medis.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606231/akhirnya-newcastle-dan-arsenal-sepakati-harga-bruno-guimaraes</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/26/bruno-guimaraes-1782492285195_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Madrid Naikkan Tawaran Kontrak, Vinicius Mau Terima Gak Nih?</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:30:10 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Real Madrid memang tidak mau kehilangan Vinicius Junior. El Real bahkan sudah menaikkan tawaran kontrak baru Vinicius, diterima gak nih?</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8606247/madrid-naikkan-tawaran-kontrak-vinicius-mau-terima-gak-nih</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/vinicius-junior-1785957793822_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Hasil Uji Coba: Arsenal Dikalahkan Real Betis 1-3</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:05:52 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Putra Rusdi K</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Arsenal kalah 1-3 dari Real Betis pada laga uji coba. Empat gol yang lahir di laga ini semuanya tercipta di babak pertama.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606269/hasil-uji-coba-arsenal-dikalahkan-real-betis-1-3</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/2289228762-1785967497682_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sebagai Anggota KONI, ORADO Dipercaya Gelar Piala Panglima TNI</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:59:53 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Randy Prasatya</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Olahraga Domino Nasional (PB ORADO) ditunjuk sebagai penyelenggara turnamen. Penunjukan itu dilakukan setelah ORADO menjadi anggota resmi KONI.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sport-lain/d-8606264/sebagai-anggota-koni-orado-dipercaya-gelar-piala-panglima-tni</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/orado-1785967060955_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Rajawali Junior League 2026 Wadah Kompetisi Pesepakbola Muda</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:45:02 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Muhammad Robbani</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Rajawali Junior League (RJL) 2026 akan digelar akhir bulan ini. Kompetisi ini akan menjadi wadah pesepakbola muda menunjukkan kebolehannya.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606262/rajawali-junior-league-2026-wadah-kompetisi-pesepakbola-muda</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/rajawali-junior-league-1785966184113_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Melihat Mudryk Merumput Lagi usai 20 Bulan Menanti</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:30:25 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Adhi Prasetya</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Winger Chelsea Mykhailo Mudryk akhirnya kembali merumput usai sanksi larangan bermainnya resmi berakhir pekan lalu. Penantian sekitar 20 bulan terbayar lunas.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606222/melihat-mudryk-merumput-lagi-usai-20-bulan-menanti</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mykhailo-mudryk-1785944989830_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tanpa Penonton, Final Piala Presiden 2026 Tetap Dijaga Ketat Aparat</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Muhammad Robbani</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Organizing Committee (OC) Piala Presiden 2026 Arya Sinulingga ungkap alasan final tanpa penonton. Tanpa penonton, laga tetap dijaga ketat aparat.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606219/tanpa-penonton-final-piala-presiden-2026-tetap-dijaga-ketat-aparat</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/ilustrasi-logo-piala-presiden-2026-1783328492093_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UFO Tabrak Pesawat di Jerman Usai Temuan Drone Bawa Bom</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:29:53 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>UFO menabrak pesawat kargo di Jerman. Insiden ini terjadi setelah penemuan drone berpeledak di bandara.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/06/082858870/ufo-tabrak-pesawat-di-jerman-usai-temuan-drone-bawa-bom</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/cyrcKtn8_2nM4erlhhMh4yt3fjI=/0x114:2000x1447/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/08/06/6a73e2965bbfe.jpg</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sensus Ekonomi 2026 dan Perangkap Pendapatan Menengah</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:29:54 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Yang patut dikhawatirkan bukan fakta Vietnam telah menyalip Indonesia, tapi ancaman perangkap pendapatan menengah dan risiko menua sebelum kaya.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/06/080500026/sensus-ekonomi-2026-dan-perangkap-pendapatan-menengah</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/KyIafYblO1lujHaD9wtHO-GBbdM=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/07/17/6a59c113dfafe.jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Raul Fernandez Bertahan di Trackhouse Aprilia hingga MotoGP 2028</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:29:55 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Raul Fernandez resmi memperpanjang kontrak bersama Trackhouse Aprilia hingga MotoGP 2028 usai tampil konsisten sepanjang musim 2026.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://otomotif.kompas.com/read/2026/08/06/074200415/raul-fernandez-bertahan-di-trackhouse-aprilia-hingga-motogp-2028</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/TJDyg5EO3nluHXdfB71uRBNjiNE=/0x447:1498x1446/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2025/10/19/68f4fdacd7730.jpeg</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I59"/>
+  <autoFilter ref="A1:I133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$257</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -6681,8 +6681,5838 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Trump akui masih ingin capai kesepakatan dengan Iran</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:49:40 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump mengatakan masih ingin mencapai kesepakatan dengan Iran.
+"Saya lebih ...</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682160/trump-akui-masih-ingin-capai-kesepakatan-dengan-iran</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/thumbs_b_c_2263c951fe4876ab38332a738c829d57-1.jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Menlu Yordania: Israel akibatkan konflik di Timteng jadi konflik agama</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:48:01 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Menteri Luar Negeri Yordania Ayman Safadi menyebut rezim zionis Israel sebagai pihak yang mendorong konflik di Timur ...</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682159/menlu-yordania-israel-akibatkan-konflik-di-timteng-jadi-konflik-agama</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/05/18/Masjid.jpg</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ekonom: Merah Putih Bond berpotensi memperdalam pasar keuangan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:47:18 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ekonom Institute for Development of Economics and Finance (INDEF) M Rizal Taufikurahman menilai Merah Putih Bond ...</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682157/ekonom-merah-putih-bond-berpotensi-memperdalam-pasar-keuangan</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/08/20260108_141804_Chrome.jpg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Iran sebut capai kata mufakat dengan Oman soal pelayaran Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:43:03 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Iran dan Oman telah mencapai kesepakatan melalui dialog mengenai pelayaran aman di Selat Hormuz dan tengah ...</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682153/iran-sebut-capai-kata-mufakat-dengan-oman-soal-pelayaran-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/thumbs_b_c_5eaff112ebc17e5f36674374d164683f.jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AFPI sebut masih ada gap kredit Rp1.650 triliun di Indonesia</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:41:31 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Asosiasi Fintech Pendanaan Bersama Indonesia (AFPI) melaporkan masih terdapat kesenjangan pembiayaan (credit gap) ...</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682152/afpi-sebut-masih-ada-gap-kredit-rp1650-triliun-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/ec362622-5b56-4a5e-9b64-51cb44135bac.jpeg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Legislator sebut perubahan iklim ancam ketahanan pembangunan nasional</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:40:14 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi IV DPR RI Alex Indra Lukman mengatakan perubahan iklim harus dipandang sebagai ancaman terhadap ...</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682148/legislator-sebut-perubahan-iklim-ancam-ketahanan-pembangunan-nasional</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/dampak-banjir-bandang-di-padang-1or0t-dom.jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Kemendiktisaintek hadirkan kategori disabilitas di Pilmapres 2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:39:10 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Tinggi, Sains, dan Teknologi (Kemdiktisaintek) mendorong adanya inklusivitas pada ajang ...</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682144/kemendiktisaintek-hadirkan-kategori-disabilitas-di-pilmapres-2026</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000470705.jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Indonesia desak dunia bersatu lawan pelanggaran Israel di Yerusalem</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:37:10 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Indonesia mendesak agar komunitas internasional tidak diam atas tindakan rezim zionis Israel yang semakin merongrong ...</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682143/indonesia-desak-dunia-bersatu-lawan-pelanggaran-israel-di-yerusalem</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/17859820416a73ec5919255_WhatsApp_Image_2026_08_06_at_08_57_29_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Zulhas: KDKMP harus jadi motor ekonomi desa berbasis potensi lokal</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:36:19 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator (Menko) Bidang Pangan Zulkifli Hasan (Zulhas) mengatakan Koperasi Desa/Kelurahan Merah Putih ...</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682139/zulhas-kdkmp-harus-jadi-motor-ekonomi-desa-berbasis-potensi-lokal</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000177838.jpg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>DJP: Penundaan pajak "marketplace" demi jaga daya beli masyarakat</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:34:46 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pajak (DJP) Kementerian Keuangan menyatakan penundaan implementasi pemungutan Pajak Penghasilan ...</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682136/djp-penundaan-pajak-marketplace-demi-jaga-daya-beli-masyarakat</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/31/1000435544.jpg</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Kemenhut perkuat diplomasi dorong RI jadi pemimpin kehutanan global</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:30:23 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) RI memperkuat diplomasi publik dan negosiasi internasional sebagai strategi ...</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682135/kemenhut-perkuat-diplomasi-dorong-ri-jadi-pemimpin-kehutanan-global</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/a1e7f8d1-849d-4429-8b57-c1fbf39363cb.jpeg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Mitrade Raih Gelar "AI Broker of the Year 2026", Hadirkan MitradeGPT Versi Terbaru di Asia</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:30:21 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Broker CFD Mitrade meraih gelar "AI Broker of the Year 2026" dari Global Business ...</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682131/mitrade-raih-gelar-ai-broker-of-the-year-2026-hadirkan-mitradegpt-versi-terbaru-di-asia</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/22/Mitrade-logo.jpg</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Menteri Bahlil: Realisasi PNBP ESDM capai Rp138,4 triliun</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:29:28 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan realisasi Penerimaan Negara Bukan Pajak ...</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682129/menteri-bahlil-realisasi-pnbp-esdm-capai-rp1384-triliun</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_7523_1.jpg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Kementan targetkan budi daya PMAAS capai 1 juta hektare pada 2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:24:39 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian (Kementan) menargetkan budi daya pertanian dengan penerapan budi daya padi berbasis mekanisasi ...</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682128/kementan-targetkan-budi-daya-pmaas-capai-1-juta-hektare-pada-2026</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/pmaas.jpg</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Djakarta International Theater Platform 2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:24:26 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Seniman Indonesia Yudi Ahmad Tajudin (kanan) bersama seniman Thailand Sasapin Siriwanij (kiri) mementaskan Horizon pada ...</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5682127/djakarta-international-theater-platform-2026</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Djakarta-International-Theater-Platform-2026-050826-RRY-4.jpg</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Bappenas: Praktik baik SDGs sederhana dapat beri perubahan penting</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:23:10 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Kepala Sekretariat Nasional Sustainable Development Goals (SDGs) Kementerian Perencanaan Pembangunan Nasional/Badan ...</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682123/bappenas-praktik-baik-sdgs-sederhana-dapat-beri-perubahan-penting</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/25/WhatsApp-Image-2026-06-25-at-15.27.58.jpeg</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Baznas-Kemensos kolaborasi tingkatkan pendidikan warga prasejahtera</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:22:56 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Badan Amil Zakat Nasional (Baznas) RI dan Kementerian Sosial (Kemensos) memperkuat sinergi dalam meningkatkan kualitas ...</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682120/baznas-kemensos-kolaborasi-tingkatkan-pendidikan-warga-prasejahtera</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000470686.jpg</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>12 ribu pengunjung datangi anjungan Baic di GIIAS dalam lima hari awal</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:22:23 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Memasuki hari kelima penyelenggaraan pameran Gaikindo Indonesia International Auto Show (GIIAS) 2026, produsen ...</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682116/12-ribu-pengunjung-datangi-anjungan-baic-di-giias-dalam-lima-hari-awal</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Copy-of-WZ_08664.jpg</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BPBD Jatim kerahkan drone water spray, padamkan karhutla di Bromo</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Badan Penanggulangan Bencana Daerah (BPBD) Jawa Timur (Jatim) mengerahkan drone water spray dan juga truk pemadam ...</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682113/bpbd-jatim-kerahkan-drone-water-spray-padamkan-karhutla-di-bromo</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/273248.jpg</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Bapanas: Harga gabah tertinggi delapan tahun jaga inflasi beras</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:14:30 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Badan Pangan Nasional (Bapanas) menyatakan kenaikan harga gabah ke level tertinggi dalam delapan tahun terakhir mampu ...</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682109/bapanas-harga-gabah-tertinggi-delapan-tahun-jaga-inflasi-beras</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/AABBF981-C853-4BF9-B8E3-B0757C6B7287.jpeg</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Garda Prabowo usul visa kerja PMI Turki dikelola Kedubes</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:13:21 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Organisasi masyarakat Gerakan Rakyat Dukung dan Bela (Garda) Prabowo mengusulkan pengurusan visa kerja pekerja migran ...</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682105/garda-prabowo-usul-visa-kerja-pmi-turki-dikelola-kedubes</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000472702.jpg</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Cari rumah dan kendaraan lebih mudah, BRI Consumer Expo 2026 Goes to PIK2 hadir dengan beragam promo</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:10:44 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – Membeli rumah atau kendaraan merupakan keputusan finansial yang membutuhkan banyak ...</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682104/cari-rumah-dan-kendaraan-lebih-mudah-bri-consumer-expo-2026-goes-to-pik2-hadir-dengan-beragam-promo</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/BRI-Consumer-Expo-PIK-2.jpg</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Kemnaker perkuat pelatihan dan penempatan kerja bagi disabilitas</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:09:39 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) terus memperkuat akses kerja bagi penyandang disabilitas melalui peningkatan ...</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682103/kemnaker-perkuat-pelatihan-dan-penempatan-kerja-bagi-disabilitas</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/ecf9e925-932f-48d7-93ed-34fb92dff7d5.jpeg</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Dari literasi teks ke literasi multimodal</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:04:03 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Seorang guru meminta murid-muridnya menjelaskan dampak perubahan iklim. Dua puluh tahun lalu, kemungkinan besar mereka ...</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682100/dari-literasi-teks-ke-literasi-multimodal</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/ilustrasi_literasi_multimodal.jpg</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Kepala BGN: Kepatuhan SOP kunci keamanan pangan Program MBG</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:03:28 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengatakan kepatuhan terhadap Standar Operasional Prosedur (SOP) di seluruh ...</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682096/kepala-bgn-kepatuhan-sop-kunci-keamanan-pangan-program-mbg</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/upscalemedia-transformed-8.jpeg</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pemkot Jakpus siapkan pembinaan UMKM usai penertiban di Karet Tengsin</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:02:38 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Administrasi Jakarta Pusat (Jakpus) menyiapkan pembinaan usaha bagi sebagian pedagang yang ...</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682092/pemkot-jakpus-siapkan-pembinaan-umkm-usai-penertiban-di-karet-tengsin</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000832391.jpg</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Pertamina apresiasi dedikasi kru kapal lintasi Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:02:32 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Direktur Utama PT Pertamina International Shipping Surya Tri Harto menyampaikan apresiasi setinggi-tingginya kepada ...</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682088/pertamina-apresiasi-dedikasi-kru-kapal-lintasi-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/26/gamsunoro-251024-pus-8.jpg</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Sedang Wonosari dan selang warna-warni</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:59:24 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Di balik perbukitan Imogiri, Kabupaten Bantul, Daerah Istimewa Yogyakarta, terdapat sebuah tempat bernama Dusun ...</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682087/sedang-wonosari-dan-selang-warna-warni</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000003745.jpg</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Kemenhut kerahkan operasi terpadu atasi karhutla savana Gunung Bromo</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:58:42 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) terus mengerahkan operasi terpadu untuk melindungi kawasan konservasi saat kebakaran ...</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682085/kemenhut-kerahkan-operasi-terpadu-atasi-karhutla-savana-gunung-bromo</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001294364.jpg</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Iran dukung setiap keputusan Palestina dalam negosiasi</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:56:21 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Iran akan mendukung setiap keputusan yang dibuat para pemimpin Palestina selama proses negosiasi, kata Presiden Iran ...</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682081/iran-dukung-setiap-keputusan-palestina-dalam-negosiasi</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_9e02544a49301ebaae68b6daa93a9192.jpg</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Pemkot Jakpus tertibkan 95 bangunan di atas saluran PHB Karet Tengsin</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:55:11 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Pusat (Jakpus) menertibkan 95 bangunan semi permanen yang berdiri di atas saluran ...</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682077/pemkot-jakpus-tertibkan-95-bangunan-di-atas-saluran-phb-karet-tengsin</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000832392.jpg</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Simak daftar harga emas Galeri24-Antam-UBS di Pegadaian pada Kamis</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:53:51 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Harga emas di laman Pegadaian dikutip dari Jakarta, Kamis, pukul 10.38 WIB, menunjukkan harga emas jenama Galeri24, ...</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682075/simak-daftar-harga-emas-galeri24-antam-ubs-di-pegadaian-pada-kamis</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/29/bazar-emas-pegadaian-di-palu-2718734.jpg</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Prabowo undang BRIN paparkan riset pangan dan energi</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:51:00 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengundang para peneliti Badan Riset dan Inovasi Nasional (BRIN) untuk memaparkan hasil riset ...</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682071/prabowo-undang-brin-paparkan-riset-pangan-dan-energi</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/WhatsApp-Image-2026-07-30-at-19.50.13-1-2.jpeg</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Mendag dorong perlindungan kekayaan intelektual produk unggulan RI</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:50:52 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Menteri Perdagangan (Kemendag) Budi Santoso menegaskan Indonesia perlu memperkuat perlindungan kekayaan intelektual ...</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682067/mendag-dorong-perlindungan-kekayaan-intelektual-produk-unggulan-ri</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0973.jpeg</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Isuzu tampilkan inovasi digital Road Sweeper di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:50:09 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>PT Isuzu Astra Motor Indonesia (IAMI) memanfaatkan pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) ...</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682065/isuzu-tampilkan-inovasi-digital-road-sweeper-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Photo-2-Isuzu-GIGA-FVR-Road-Sweeper.jpg</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ekonomi kemarin, permintaan SUN hingga bantuan daerah Rp20,5 triliun</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:49:17 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Berbagai peristiwa ekonomi diberitakan Kantor Berita ANTARA pada Rabu (5/8), mulai dari permintaan Surat Utang Negara ...</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682063/ekonomi-kemarin-permintaan-sun-hingga-bantuan-daerah-rp205-triliun</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/IMG_0942.jpeg</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Polisi tanggapi dugaan penyekapan ART di Kelapa Gading Jakut</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:48:59 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Polsek Kelapa Gading menindaklanjuti laporan dugaan penyekapan yang dilakukan kepada pelapor seorang wanita berinisial ...</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682061/polisi-tanggapi-dugaan-penyekapan-art-di-kelapa-gading-jakut</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2016/05/2016050420140608Ilustrasi_wanita_korban_pemerkosaan.jpg</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>UNISOC Lyric Audio: Mengubah Pengalaman Mendengarkan Audio</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:47:58 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Peran teknologi audio kini jauh melampaui fungsi dasarnya sebagai media komunikasi suara. Mulai dari panggilan ...</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682057/unisoc-lyric-audio-mengubah-pengalaman-mendengarkan-audio</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/UNISOC-AI-Ultrasonic.jpg</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Yusril sebut hukuman mati koruptor sudah diatur dalam Undang-Undang</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:42:47 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Hukum, HAM, Imigrasi, dan Pemasyarakatan Yusril Ihza Mahendra menyatakan hukuman mati ...</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682055/yusril-sebut-hukuman-mati-koruptor-sudah-diatur-dalam-undang-undang</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/1000444717.jpg</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>71 Lapak BSI hadir di pasar rakyat guna dekatkan layanan syariah</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:42:44 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PT Bank Syariah Indonesia (Persero) Tbk menghadirkan 71 Layanan Pasar dan Pengusaha UMKM (Lapak) BSI di berbagai pasar ...</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682052/71-lapak-bsi-hadir-di-pasar-rakyat-guna-dekatkan-layanan-syariah</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/bsi-19.jpg</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Hard Rock Cafe dan Coca-Cola® Meluncurkan Kompetisi Musik Hard Rock Rising untuk Musisi Pendatang Baru</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:40:41 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Hard Rock Cafe dan Coca-Cola hari ini meluncurkan Hard Rock Rising. Kompetisi musik ini hadir di 34 negara dan 64 ...</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682048/hard-rock-cafe-dan-coca-cola-meluncurkan-kompetisi-musik-hard-rock-rising-untuk-musisi-pendatang-baru</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Hard-Rock-Cafe-dan-Coca-Cola.jpg</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Dirut Bulog siapkan pengalihan sebagian CBP jadi beras premium</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:37:51 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Direktur Utama Perum Bulog Ahmad Rizal Ramdhani menyatakan, pihaknya menyiapkan pengalihan sebagian Cadangan Beras ...</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682045/dirut-bulog-siapkan-pengalihan-sebagian-cbp-jadi-beras-premium</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/3AA8161D-3346-4A31-B51E-42399E1732FF.jpeg</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Menekraf: Diaspora jadi mitra strategis perluas ekraf ke internasional</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:31:29 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Menteri Ekonomi Kreatif/Kepala Badan Ekonomi Kreatif (Ekraf), Teuku Riefky Harsya mengatakan jejaring diaspora ...</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682041/menekraf-diaspora-jadi-mitra-strategis-perluas-ekraf-ke-internasional</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000591384.jpg</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Laporan Cision Peringatkan Merek tentang 'Jebakan Fragmentasi Data' yang Merugikan</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:28:01 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Cision, pemimpin global dalam intelijen konsumen dan media, hari ini merilis The Data Fragmentation Trap: Why ...</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682039/laporan-cision-peringatkan-merek-tentang-jebakan-fragmentasi-data-yang-merugikan</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/10/logo-Cision.jpg</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Kepala BGN beri batas waktu SPPG urus SLHS hingga 10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:27:08 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>nya tidak dilanjutkan," ujar Sudaryono.
+Kepala BGN menyebutkan hingga kini dirinya telah mencopot 137 kepala ...</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682036/kepala-bgn-beri-batas-waktu-sppg-urus-slhs-hingga-10-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0002_2.jpg</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Ketum PBNU: Konsep Saadatuna, syarah pembentukan umat terbaik</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:16:58 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Ketua Umum Pengurus Besar Nahdlatul Ulama (PBNU) Yahya Cholil Staquf menjelaskan konsep Saadatuna sebagai syarah atas ...</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682035/ketum-pbnu-konsep-saadatuna-syarah-pembentukan-umat-terbaik</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000176768_1.jpg</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Bupati TTU harap keadilan bagi keluarga Dokter Icha</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:16:19 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>ANTARA - Misa peringatan 40 hari wafatnya dr. Eliza Princila Utami Pakaenoni atau dr. Icha berlangsung khusyuk di ...</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5681988/bupati-ttu-harap-keadilan-bagi-keluarga-dokter-icha</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BUPATI-TTU-HARAP-KEADILAN-BAGI-KELUARGA-DOKTER-ICHA.jpg</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Perangkat keamanan berbasis digital jadi senjata terhindar kejahatan</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:13:28 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Meningkatnya kasus pencurian kendaraan bermotor, aksi vandalisme, hingga tabrak lari yang kerap terjadi di area parkir ...</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682032/perangkat-keamanan-berbasis-digital-jadi-senjata-terhindar-kejahatan</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-09.24.52.jpeg</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Perjalanan KuCoin Selama Sembilan Tahun Terakhir Mencerminkan Transformasi dari Bursa Kripto Menjadi Infrastruktur Aset Digital</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:13:12 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Setelah industri aset digital memasuki fase yang semakin maju, peran bursa kripto kini tidak lagi sebatas ...</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682029/perjalanan-kucoin-selama-sembilan-tahun-terakhir-mencerminkan-transformasi-dari-bursa-kripto-menjadi-infrastruktur-aset-digital</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CoinGecko-Research-KuCoin.jpg</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pemerintah siapkan OMC percepat pemadaman karhutla di Gunung Bromo</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:06:42 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Pemerintah melalui Badan Nasional Penanggulangan Bencana (BNPB) menyiapkan skenario Operasi Modifikasi Cuaca (OMC) ...</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682025/pemerintah-siapkan-omc-percepat-pemadaman-karhutla-di-gunung-bromo</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/penutupan-sebagian-akses-wisata-bromo-2834203.jpg</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Polisi Selidiki Temuan Senjata Api dan Air Gun di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:55:32 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Selatan menyelidiki temuan senjata, termasuk air gun dan senjata api, di sekolah swasta di Pondok Pinang. Penyelidikan masih berlangsung.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606664/polisi-selidiki-temuan-senjata-api-dan-air-gun-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/04/26/ilustrasi-senjata-api-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ART di Jakut Telepon ke 110, Ngaku Disekap dan Dimintai Uang</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:51:34 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Wanita yang bekerja sebagai ART di perumahan Kelapa Gading, Jakut diduga disekap dan dimintai sejumlah uang. Korban lalu lapor ke call center Polri 110.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606661/art-di-jakut-telepon-ke-110-ngaku-disekap-dan-dimintai-uang</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/05/01/d2a01ba7-8a31-4376-ad70-b2158d2f4413_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>8 Siswa SMA Unggulan CT ARSA Jadi Mahasiswa ITB 2026, Bertambah Dibanding 2025</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:50:25 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Nur Khansa Ranawati</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Sebanyak delapan siswa SMA Unggulan CT ARSA Foundation berhasil diterima sebagai mahasiswa baru program sarjana ITB tahun akademik 2026/2027.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606660/8-siswa-sma-unggulan-ct-arsa-jadi-mahasiswa-itb-2026-bertambah-dibanding-2025</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/8-alumni-sma-unggulan-ct-arsa-foundation-bersama-rektor-itb-tatacipta-dirgantara-dan-general-manager-ct-arsa-foundation-haeran-1785916574453_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Adik Kandung Jadi Saksi Sidang Kasus Korupsi, Eks Ketua Ombudsman Keberatan</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:45:55 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Adik kandung mantan Ketua Ombudsman RI Hery Susanto bernama Edi Sugandi dihadirkan jaksa sebagai saksi dalam persidangan kasus korupsi.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606651/adik-kandung-jadi-saksi-sidang-kasus-korupsi-eks-ketua-ombudsman-keberatan</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sidang-eks-ketua-ombudsman-muliadetikcom-1785991541340_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Asosiasi Sepak Bola Korsel Digeledah Polisi Terkait Pelatih Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:40:39 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Kantor asosiasi sepak bola nasional Korsel digeledah polisi pada Kamis (6/8) terkait penyelidikan terhadap penunjukan pelatih timnas Korsel selama Piala Dunia.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606633/asosiasi-sepak-bola-korsel-digeledah-polisi-terkait-pelatih-piala-dunia</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kantor-asosiasi-sepak-bola-nasional-korsel-kfa-di-seoul-1785991198253_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Saepul Pemutilasi Pria di Depok Jadi Tersangka, Terancam Hukuman Mati</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:33:35 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Polisi menangkap Saepul, pelaku pembunuhan dan mutilasi pria K di Depok. Saepul terancam hukuman mati atas perencanaan kejahatan ini.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606625/saepul-pemutilasi-pria-di-depok-jadi-tersangka-terancam-hukuman-mati</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Penyu Hendak Melahirkan Mati Terbelah di Kaltim, Seluruh Telurnya Diambil Pelaku</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:31:33 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Riani Rahayu</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Seekor penyu betina yang hendak bertelur mati terbelah di pesisir Kabupaten Berau, Kaltim. Seluruh telur yang masih ada di dalam tubuh penyu itu hilang.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606620/penyu-hendak-melahirkan-mati-terbelah-di-kaltim-seluruh-telurnya-diambil-pelaku</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/penyu-ditemukan-mati-mengenaskan-di-pesisir-berau-1785936713273_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sopir Demo, Angkot Kosong Ditinggal Berjejer di Dekat Stasiun Tebet</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari, Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Sekitar 150 sopir Mikrolet M44 demo di Balai Kota DKI Jakarta, menuntut evaluasi rute JakLingko 48A yang dinilai merugikan pendapatan mereka.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606609/sopir-demo-angkot-kosong-ditinggal-berjejer-di-dekat-stasiun-tebet</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sopir-angkot-demo-di-balai-kota-jakarta-brigitta-beliadetikcom-1785990567413_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>KPK Panggil Rudy Tanoesoedibjo Tersangka Kasus Korupsi Bansos Tahun 2020</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:23:34 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>KPK memanggil Komisaris Utama PT Dosni Roha Logistik, Bambang Rudijanto Tanoesoedibjo (BRT) atau Rudy Tanoe.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606593/kpk-panggil-rudy-tanoesoedibjo-tersangka-kasus-korupsi-bansos-tahun-2020</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/14/bambang-rudijanto-tanoesoedibjo-azhar-detikcom_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Saepul Pemutilasi Pria di Depok Gabung Grup Sesama Jenis, Rencanakan Bunuh Korban</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:22:25 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Polisi ungkap Seapul pemutilasi pria di Depok gabung grup sesama jenis. Pelaku berkenalan lewat media sosial Hornet.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606592/saepul-pemutilasi-pria-di-depok-gabung-grup-sesama-jenis-rencanakan-bunuh-korban</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Detik-detik Pabrik Miras Ilegal di Bogor Digerebek, Pelaku Tak Berkutik</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:21:07 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Polsek Cileungsi mengungkap detik-detik penggerebekan pabrik produksi minuman keras (miras) oplosan di Sukaraja, Kabupaten Bogor, Jawa Barat.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606589/detik-detik-pabrik-miras-ilegal-di-bogor-digerebek-pelaku-tak-berkutik</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polsek-cileungsi-mengungkap-detik-detik-penggerebekan-pabrik-produksi-minuman-keras-miras-oplosan-di-sukaraja-kabupaten-bogor--1785990000852_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Polda Metro Hormati Putusan PN Jaksel Tak Terima Praperadilan Ketiga Roy Suryo</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:14:58 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya merespons putusan hakim Pengadilan Negeri Jakarta Selatan (PN Jaksel) yang tidak menerima gugatan praperadilan ketiga Roy Suryo.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606584/polda-metro-hormati-putusan-pn-jaksel-tak-terima-praperadilan-ketiga-roy-suryo</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kabidkum-polda-metro-jaya-kombes-abrianto-pardede-ondangdetikcom-1785989597430_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Kronologi Warga Terobos Asap Karhutla di Ketapang Berujung Tewas Terbakar</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:11:44 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Seorang warga bernama Taufik Hidayat (26) tewas akibat kebakaran hutan dan lahan (karhutla) di Kabupaten Ketapang, Kalimantan Barat.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606577/kronologi-warga-terobos-asap-karhutla-di-ketapang-berujung-tewas-terbakar</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/evakuasi-taufik-seorang-pekerja-yang-tewas-terjebak-karhutla-dok-istimewa-1785914057235_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Warga Protes Proyek Trotoar Jl Pemuda Depok Terlalu Lebar: Jalan Jadi Sempit</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:04:47 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Proyek trotoar di Depok menuai keluhan warga. Lebarnya trotoar membuat jalan semakin sempit.</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606565/warga-protes-proyek-trotoar-jl-pemuda-depok-terlalu-lebar-jalan-jadi-sempit</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/proyek-trotoar-di-jalan-pramuka-depok-1785988778760_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sungai Cileungsi Tercemar, Air Bekasi Menghitam dan Berbusa</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:00:11 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Sungai Cileungsi hingga Kali Bekasi diduga tercemar limbah. Air berubah hitam dan berbusa terlihat di kawasan Margahayu, Kota Bekasi.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/foto-news/d-8606081/sungai-cileungsi-tercemar-air-bekasi-menghitam-dan-berbusa</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sungai-cileungsi-tercemar-air-bekasi-menghitam-dan-berbusa-1785937959484_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Nasabah Dirampok Kawanan Bersajam di Cibitung, Rp 30 Juta Raib</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:58:58 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Perampokan bersenjata tajam terjadi di Cibitung, Bekasi, saat nasabah baru pulang dari bank. Korban kehilangan uang Rp 30 juta dan mengalami luka.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606558/nasabah-dirampok-kawanan-bersajam-di-cibitung-rp-30-juta-raib</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/06/24/f76d026c-9771-46e8-9200-8840de04f3ab_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Malaysia Tanggapi Penangkapan 3 Wanita Asal Sabah terkait Narkotika di Soetta</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:56:42 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Kepolisian Malaysia menanggapi penangkapan tiga wanita berkewarganegaraan Malaysia di Bandara Internasional Soekarno-Hatta, Indonesia, terkait narkotika.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606557/malaysia-tanggapi-penangkapan-3-wanita-asal-sabah-terkait-narkotika-di-soetta</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/petugas-bea-cukai-1767173975737_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Polres Tangsel Musnahkan 46 Juta Butir Obat Keras Sitaan dari Gudang di Jaktim</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:54:39 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Polres Tangsel mengungkap peredaran obat keras ilegal sebanyak 46 juta butir yang disita dari gudang diJaktim. Puluhan juta obat keras itu dimusnahkan.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606555/polres-tangsel-musnahkan-46-juta-butir-obat-keras-sitaan-dari-gudang-di-jaktim</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polres-tangsel-mengungkap-peredaran-obat-keras-ilegal-sebanyak-46-juta-butir-yang-disita-dari-gudang-dijaktim-puluhan-juta-oba-1785988341990_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Kecelakaan Bus ALS Tewaskan 19 Orang, 2 Bos Perusahaan Jadi Tersangka</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:50:46 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>M Rizky Pratama</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Polisi menetapkan dua orang sebagai tersangka dalam kecelakaan antara bus ALS dan truk tangki BBM di Musi Rawas Utara, Sumsel, yang menewaskan 19 orang.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606548/kecelakaan-bus-als-tewaskan-19-orang-2-bos-perusahaan-jadi-tersangka</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/07/polisi-melakukan-olah-tkp-bus-als-terbakar-usai-tabrakan-dengan-truk-tangki-1778132371983_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pramono Ungkap Indeks Pembangunan Manusia Jakarta Teratas: Bukti Makin Baik</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:49:29 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Pramono mengungkapkan IPM Jakarta nomor 1. Hal itu mencerminkan Jakarta makin baik.</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606546/pramono-ungkap-indeks-pembangunan-manusia-jakarta-teratas-bukti-makin-baik</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pramono-anung-brigitta-beliadetikcom-1785988095617_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Anggota DPR Sentil Nakes yang Hina Pasien BPJS: Tak Boleh Diskriminasi</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:48:47 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Legislator mengkritik nakes yang menghina pasien BPJS. Minta evaluasi etika pelayanan kesehatan.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606545/anggota-dpr-sentil-nakes-yang-hina-pasien-bpjs-tak-boleh-diskriminasi</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/19/anggota-komisi-ix-dpr-nurhadi-1758262062453_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Anggota BPK Tegaskan Peran Imigrasi Seleksi WNA Masuk RI, Tak Cuma soal PNBP</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:46:51 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>BPK RI membeberkan peran kebijakan bebas visa dari Dirjen Imigrasi Kemenimipas sebagai penyaring WNA yang masuk ke Tanah Air.</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606542/anggota-bpk-tegaskan-peran-imigrasi-seleksi-wna-masuk-ri-tak-cuma-soal-pnbp</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/direktur-jenderal-imigrasi-hendarsam-marantoko-1785987475220_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Suami di Jambi Tewas Dihajar Warga Usai Bunuh Istrinya Sendiri</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:45:58 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Dimas Sanjaya</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Pria berinisial AR (35) tewas dihajar warga. Peristiwa itu terjadi setelah AR membunuh istrinya, D (29), di Sarolangun, Jambi.</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606540/suami-di-jambi-tewas-dihajar-warga-usai-bunuh-istrinya-sendiri</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-melakukan-olah-tkp-pembunuhan-di-sarolangun-jambi-1785929685872_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Pramono Apresiasi Petugas TransJ Bantu Disabilitas Nyeberang di Jakpus</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:40:18 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Pramusapa Transjakarta viral bantu penumpang disabilitas menuju Stasiun MRT. Gubernur DKI Pramono Anung mengapresiasi.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606532/pramono-apresiasi-petugas-transj-bantu-disabilitas-nyeberang-di-jakpus</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/gubernur-dki-jakarta-pramono-anung-1785987586592_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Hakim Tak Terima Praperadilan Ketiga Roy Suryo</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:34:01 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Hakim Pengadilan Negeri Jakarta Selatan tak menerima gugatan praperadilan ketiga yang diajukan oleh Roy Suryo.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606515/hakim-tak-terima-praperadilan-ketiga-roy-suryo</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sidang-praperadilan-roy-suryo-rumondangdetikcom-1785987232013_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Polisi Amankan 16 Pelajar di Bogor Mau Tawuran, Sajam Disita</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:26:38 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Polisi menggagalkan tawuran pelajar di Cibinong, Bogor. Sebanyak 16 pelajar ditangkap.</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606507/polisi-amankan-16-pelajar-di-bogor-mau-tawuran-sajam-disita</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tawuran-1785986743722_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Polres Jakbar Musnahkan Narkoba Rp 119 Miliar, Selamatkan 3,5 Juta Jiwa</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:19:43 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakbar memusnahkan narkoba senilai Rp 119 miliar dan menetapkan tujuh tersangka. Pengungkapan ini bukti keseriusan Polri dalam memerangi narkotika.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606500/polres-jakbar-musnahkan-narkoba-rp-119-miliar-selamatkan-3-5-juta-jiwa</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polres-metro-jakarta-barat-memusnahkan-bahan-baku-narkoba-rp-119-miliar-1785986320741_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Viral Hina Pasien BPJS 'Ruang Jenazah Kosong', Dokter RSUD di NTT Minta Maaf</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:14:45 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Tim detikBali</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Dokter Benny Sihombing meminta maaf setelah komentarnya menghina pasien BPJS viral. Ia siap bertanggung jawab atas konsekuensi hukum dan etik.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606494/viral-hina-pasien-bpjs-ruang-jenazah-kosong-dokter-rsud-di-ntt-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/beni-christian-sihombing-dokter-rsud-ruteng-yang-berkomentar-jahat-di-threads-yurizaltrich-tangkapan-layar-bennychrstn-1785907200397_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Prabowo Undang Peneliti BRIN ke Istana Siang Ini</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:14:29 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengundang sejumlah peneliti BRIN ke Istana siang ini. Prabowo akan mendengarkan pemaparan hasil penelitian BRIN.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606493/prabowo-undang-peneliti-brin-ke-istana-siang-ini</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/presiden-prabowo-subianto-1785491824191_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Trump Akui Lebih Pilih Deal dengan Iran: Saya Tak Ingin Bunuh Orang</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:13:28 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Trump lebih memilih kesepakatan dengan Iran daripada tindakan militer. Namun dia memperingatkan bahwa aksi militer tetap menjadi opsi jika diplomasi gagal.</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606492/trump-akui-lebih-pilih-deal-dengan-iran-saya-tak-ingin-bunuh-orang</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/presiden-as-donald-trump-1783563356572_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>BPJS, Antrean, dan Empati yang Memudar</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:03:35 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Sudrajat</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Ketika kepekaan kemanusiaan mulai memudar, yang sedang diuji bukan hanya sistem kesehatan, melainkan juga wajah peradaban kita.</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/kolom/d-8606484/bpjs-antrean-dan-empati-yang-memudar</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/14/ilustrasi-rumah-sakit_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Cegah Kejahatan Digital, Polda Sumsel Bekali 150 Personel Pemahaman AI</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:02:20 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Fara Difa Alfeni</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Kapolda Sumsel Irjen Pol. Sandi Nugroho membuka Training of Trainer 'Paham AI' untuk edukasi pelajar tentang pemanfaatan AI yang aman dan etis.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8606481/cegah-kejahatan-digital-polda-sumsel-bekali-150-personel-pemahaman-ai</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polda-sumsel-1785985311189_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Krisis Air Mengintai, Dua Sumber Air di Grobogan Terus Menyusut</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:00:06 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Krisis air bersih mengintai Desa Sugihmanik, Grobogan. Dalam lima tahun terakhir, dua sumber air terus menyusut saat musim kemarau.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/foto-news/d-8605735/krisis-air-mengintai-dua-sumber-air-di-grobogan-terus-menyusut</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/krisis-air-mengintai-dua-sumber-air-di-grobogan-terus-menyusut-1785924395141_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Faktor Musiman Dongkrak Pertumbuhan Ekonomi 5,29%</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:51:49 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Said Abdullah</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>BPS melaporkan pertumbuhan ekonomi Indonesia 5,29% (yoy) di tengah tantangan global. Sektor akomodasi dan listrik tumbuh pesat.</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/kolom/d-8606470/faktor-musiman-dongkrak-pertumbuhan-ekonomi-5-29</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/03/said-abdullah-1764743504515_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Bawa Kabur Istri Orang, Pria di Samarinda Diikat di Tiang Listrik</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:48:59 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Muhammad Budi Kurniawan</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Video pria di Samarinda, S alias Z (46), diikat di tiang listrik viral. Belakangan diketahui S membawa kabur perempuan berinisial R (33) yang telah bersuami.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606467/bawa-kabur-istri-orang-pria-di-samarinda-diikat-di-tiang-listrik</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pria-di-samarinda-diikat-di-tiang-listrik-1785910387166_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Wamensos Pantau Pembangunan Sekolah Rakyat Probolinggo-Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:45:17 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Proses pembangunan Sekolah Rakyat permanen terus berlangsung di Kuansing, Polewali Mandar, dan Probolinggo, menjamin pendidikan gratis bagi anak prasejahtera.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606464/wamensos-pantau-pembangunan-sekolah-rakyat-probolinggo-polewali-mandar</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kemensos-1785984298888_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Polda Metro Tangkap Pengedar Narkoba di Jakbar, Ganja 4 Kg Disita</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:44:56 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Ditresnarkoba Polda Metro Jaya menggagalkan transaksi ganja di Palmerah, Jakarta. Pelaku berinisial J (24) ditangkap dengan barang bukti 4 kg ganja.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606463/polda-metro-tangkap-pengedar-narkoba-di-jakbar-ganja-4-kg-disita</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ditresnarkoba-polda-metro-jaya-mengungkap-peredaran-ganja-4-kilogram-di-jakbar-1785984275969_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Siasat Pengemis di Kudus Raup Rp 540 Ribu/Hari: Maksa hingga Tarik Baju</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:17:46 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Tim detikJateng</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Pengemis perempuan berinisial J (40) di kawasan Menara Kudus bisa membawa uang tunai hingga Rp 540 ribu sehari. Cara dia mendapatkannya ternyata meresahkan.</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606430/siasat-pengemis-di-kudus-raup-rp-540-ribu-hari-maksa-hingga-tarik-baju</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/pengemis-meresahkan-1785912739239_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>6 Kereta Api Berhenti Darurat Saat Gempa M 5,2 Guncang Pangandaran</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:58:41 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 5,2 mengguncang Pangandaran, Jawa Barat. KAI Daop 2 sempat menghentikan enam perjalanan kereta untuk memastikan keselamatan penumpang.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606397/6-kereta-api-berhenti-darurat-saat-gempa-m-5-2-guncang-pangandaran</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kereta-serayu-yang-berhenti-darurat-di-stasiun-cipendeuy-antaraho-daop-2-bandung-1785981469556_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Mampukah Trump Tekan Israel Agar Terima Rencana Damai Gaza?</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:42:57 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Deutsche Welle (DW)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Trump disebut akan sangat kecewa jika Israel menolak rencana perdamaian baru yang diumumkan pekan lalu. Seberapa gencar AS mendorong Israel untuk menerimanya?</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/dw/d-8606375/mampukah-trump-tekan-israel-agar-terima-rencana-damai-gaza</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/mampukah-trump-tekan-israel-agar-terima-rencana-damai-gaza-1785980577069.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Parah! Trotoar di Jalan Alternatif Sentul Sering Dilewati Pemotor sampai Rusak</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:39:46 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Trotoar di Jalan Alternatif Sentul, Bogor, sering dilewati motor sampai rusak.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606372/parah-trotoar-di-jalan-alternatif-sentul-sering-dilewati-pemotor-sampai-rusak</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/trotoar-di-jalan-alternatif-sentul-bogor-sering-dilewati-motor-sampai-rusak-rizkydetikcom-1785980261197_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Obligasi Daerah Rp5,2 T, Kenneth DPRD DKI: Harus Berdampak Nyata bagi Warga Jakarta</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:25:04 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Mega Putra Ratya</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta, Pramono Anung, rencanakan penerbitan obligasi daerah Rp5,2 triliun untuk pembiayaan pembangunan, di tengah pemangkasan anggaran pusat.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606360/obligasi-daerah-rp5-2-t-kenneth-dprd-dki-harus-berdampak-nyata-bagi-warga-jakarta</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/obligasi-daerah-rp52-t-kenneth-dprd-dki-harus-berdampak-nyata-bagi-warga-jakarta-1785979416761.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Lagi Ditunda, Pajak Toko Online Mau Diterapkan 1 November!</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:52:00 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan (Kemenkeu) resmi menunda pemungutan Pajak Penghasilan (PPh) Pasal 22 oleh marketplace sampai dengan 31 Oktober 2026.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606663/lagi-ditunda-pajak-toko-online-mau-diterapkan-1-november</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/11/ilustrasi-pajak_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Mendag Ungkap Biang Kerok Neraca Perdagangan RI Defisit 2 Bulan</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:44:29 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Menteri Perdagangan Budi Santoso menyampaikan defisit neraca perdagangan bukan disebabkan dari pelemahan ekspor.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606646/mendag-ungkap-biang-kerok-neraca-perdagangan-ri-defisit-2-bulan</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/06/transaksi-program-belanja-nasional-2025-tembus-rp39378-triliun-1770360987663_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Harga Indeks Biodiesel Agustus 2026 Naik Jadi Rp 14.924/Liter</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:32:39 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM menetapkan harga biodiesel Agustus 2026 sebesar Rp 14.924 per liter, naik dari Juli. Harga bioetanol ditetapkan Rp 11.695 per liter.</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8606624/harga-indeks-biodiesel-agustus-2026-naik-jadi-rp-14-924-liter</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/07/indonesia-gaspol-energi-hijau-b50-ditargetkan-berlaku-mulai-juli-1780832294509_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Ekosistem Perdagangan Karbon Mau Dibenahi, Ini Bocorannya</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:20:17 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Kementerian Kehutanan (Kemenhut) akan membenahi ekosistem perdagangan karbon di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/ekonomi-hijau/d-8606587/ekosistem-perdagangan-karbon-mau-dibenahi-ini-bocorannya</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/05/30/kredit-karbon-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Catat! Ini Rekayasa Lalu Lintas Imbas Proyek Stasiun MRT Glodok dan Kota</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:15:10 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>PT MRT Jakarta akan menerapkan rekayasa lalu lintas mulai Agustus 2026 untuk pembangunan MRT Fase 2A CP203, mencakup Stasiun Glodok dan Kota.</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8606585/catat-ini-rekayasa-lalu-lintas-imbas-proyek-stasiun-mrt-glodok-dan-kota</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/28/terowongan-penghubung-stasiun-mrt-kota-glodok-selesai-dibangun_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Pelabuhan Merak-Ketapang Ditata Ulang, Pengawasan Diperketat</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:07:13 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>PT ASDP Indonesia Ferry (Persero) resmi menerapkan program sterilisasi pelabuhan pada enam pelabuhan utama.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8606567/pelabuhan-merak-ketapang-ditata-ulang-pengawasan-diperketat</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/10/libur-sekolah-makin-hemat-tarif-penyeberangan-dipangkas-hingga-100-persen-1781099546351_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RI Gandeng China Kembangkan Kawasan Industri di Madura</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:32:36 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Kerja sama ini dianggap langkah penting untuk memperluas investasi kedua negara sekaligus mendorong kawasan industri modern di Bangkalan, Madura.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8606514/ri-gandeng-china-kembangkan-kawasan-industri-di-madura</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/13/menko-perekonomian-airlangga-hartarto-1783940653691_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Danantara Buka Seleksi Mitra Proyek Pengolahan Sampah Jadi Listrik</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:18:02 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>PT Danantara Investment Management membuka pendaftaran penyedia untuk proyek Waste-to-Energy di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8606498/danantara-buka-seleksi-mitra-proyek-pengolahan-sampah-jadi-listrik</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/05/pembangunan-fasilitas-pengolahan-sampah-jadi-energi-listrik-di-burangkeng-molor-1772709082219_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Lompat Rp 50.000 per Gram!</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:52:14 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Harga emas Antam hari ini naik Rp 50.000 per gram menjadi Rp 2.679.000. Buyback juga meningkat hingga Rp 90.000, kini Rp 2.490.000 per gram.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606472/harga-emas-antam-lompat-rp-50-000-per-gram</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/21/harga-emas-antam-meroket-hari-ini-nyaris-rp-25-juta-per-gram-1761021329954_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Agrinas Palma Cetak Laba Rp 890 M</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:50:13 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>PT Agrinas Palma Nusantara (Persero) mencatatkan laba bersih sebesar Rp 890 miliar.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606469/agrinas-palma-cetak-laba-rp-890-m</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/09/direktur-utama-agrinas-palma-nusantara-mohammad-abdul-ghani-1783581361002_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Air Pegunungan Dieng Jadi Pasokan Listrik Jawa-Bali Lewat PLTA Garung</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:29:52 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Fadhly Fauzi Rachman</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>PLTA Garung di Dieng memanfaatkan air pegunungan untuk menghasilkan 26,4 MW listrik, mendukung sistem Jawa-Bali dan pemberdayaan masyarakat lokal.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8606476/air-pegunungan-dieng-jadi-pasokan-listrik-jawa-bali-lewat-plta-garung</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/plta-garung-1785985104634_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Dolar AS Melemah ke Rp 17.912</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:20:48 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Nilai tukar dolar AS berada pada level Rp 17.912 atau turun sebesar 21 poin (0,12%).</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8606435/dolar-as-melemah-ke-rp-17-912</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/dolar-as-tekuk-rupiah-ke-rp-17978-1784523338213_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>IHSG Dibuka Tancap Gas Menguat ke 6.300</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:18:01 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) pagi ini dibuka menguat. IHSG langsung meroket ke zona hijau ketikan perdagangan dibuka pada level 6.300-an.</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8606432/ihsg-dibuka-tancap-gas-menguat-ke-6-300</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Petani Kediri Panen Bantuan, Ratusan Mesin Pertanian Siap Tingkatkan Produktivitas</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:00:20 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Petani Kediri mendapat 216 unit mesin pertanian bantuan pemerintah untuk meningkatkan produktivitas, mulai dari pengolahan lahan hingga panen.</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8605947/petani-kediri-panen-bantuan-ratusan-mesin-pertanian-siap-tingkatkan-produktivitas</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/petani-kediri-panen-bantuan-ratusan-mesin-pertanian-siap-tingkatkan-produktivitas-1785931225447_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Simak Rekomendasi Saham Saat IHSG Menguat</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:58:40 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>IHSG naik 0,50%. FORE percepat ekspansi, AMRT catat kinerja semester I-2026, sementara MARK membagikan dividen interim.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8606396/simak-rekomendasi-saham-saat-ihsg-menguat</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bursa-dan-valas-1785981105-1785981105349.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Skema Buka-Tutup Jadi Jalan Tengah Akses Bendungan Lahor</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:38:07 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Penutupan akses jalan di atas Bendungan Lahor, Kabupaten Malang, Jawa Timur sejak 1 Agustus 2026 menuai protes warga.</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8606370/skema-buka-tutup-jadi-jalan-tengah-akses-bendungan-lahor</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/skema-buka-tutup-jadi-jalan-tengah-akses-bendungan-lahor-1785982091611_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Kemenhub Bakal Panggil Operator KM Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:30:09 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan bakal memanggil PT Atosim Lampung Pelayaran, operator KM Mutiara Sentosa II yang terbakar di Perairan Madura, Jawa Timur.</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606339/kemenhub-bakal-panggil-operator-km-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/km-mutiara-sentosa-2-terbakar-ratusan-penumpang-dievakuasi-dari-laut-madura-1785671535501_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Arsenal Vs Betis: The Gunners Kalah karena Salah Sendiri</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Putra Rusdi K</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Manajer Arsenal,Mikel Arteta, sangat kecewa timnya kalah dari Real Betis. Ia menilai The Gunners kalah karena salah sendiri.</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606433/arsenal-vs-betis-the-gunners-kalah-karena-salah-sendiri</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/2289228762-1785967497682_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Marc Marquez Waspadai MotoGP Inggris, Silverstone Bisa Jadi Ujian Terberat!</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:30:05 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Kris FW</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Marc Marquez mewaspadai MotoGP Inggris 2026 di Silverstone. Pebalap Ducati itu menyebut lintasan tersebut sangat menguras fisik.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8606579/marc-marquez-waspadai-motogp-inggris-silverstone-bisa-jadi-ujian-terberat</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/09/moto-prix-mas-testing-1770621581437_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Figo Desak Infantino Mundur</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Luis Figo tidak senang dengan manuver Presiden FIFA Gianni Infantino belakangan ini. Legenda Timnas Portugal itu mendesak Infantino untuk mundur.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606429/figo-desak-infantino-mundur</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/luis-figo-gianni-infantino-1785977216138_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Norgaard Pindah ke Everton usai Jarang Main di Arsenal</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:00:20 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Adhi Prasetya</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Christian Norgaard memutuskan pindah ke Everton meski baru setahun bergabung dengan Arsenal. Ia ingin bermain lebih sering.</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606426/norgaard-pindah-ke-everton-usai-jarang-main-di-arsenal</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/25/carabao-cup-1758757374560_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Singapura Vs Indonesia: Rekor Buruk Garuda di Kandang Singa</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:40:45 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Putra Rusdi K</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia dibayangi rekor buruk di kandang Singapura saat bermain di Piala AFF. Tim Garuda hanya sekali menang di kandang Singa.</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606392/singapura-vs-indonesia-rekor-buruk-garuda-di-kandang-singa</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/12/29/indonesia-vs-thailand-final-piala-aff-2020_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Juventus Solid Redam Chelsea</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:20:40 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Putra Rusdi K</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Pelatih Juventus, Luciano Spalletti, memuji timnya yang bermain solid saat melawan Chelsea. Si Nyonya Tua menang usai mampu meredam tekanan The Blues.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8606391/juventus-solid-redam-chelsea</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/uji-coba-1785936703617_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Arteta Jadi  Manajer Paling Senior di Liga Inggris</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:00:25 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Inilah lima manajer dengan masa kerja paling lama di Premier League musim 2026/27 mendatang. Mikel Arteta paling senior!</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8605882/arteta-jadi-manajer-paling-senior-di-liga-inggris</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/25/mikel-arteta-1779653213116.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Karena Munoz Cocok dengan Gaya Main Iraola</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Victor Munoz tak pikir panjang untuk menerima tawaran Liverpool. Sebab, Munoz merasa gaya main sang manajer Andoni Iraola cocok dengannya.</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606380/karena-munoz-cocok-dengan-gaya-main-iraola</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/victor-munoz-1785980514524_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Asaba Indonesia Tampil Lagi di Ajang Basket Veteran ASEAN</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:33:01 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Tim basket veteran putra Asaba Indonesia kembali tampil di ajang Asean Veteran Basketball bulan ini. Asaba bertekad membawa pulang gelar juara.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/basket/d-8606442/asaba-indonesia-tampil-lagi-di-ajang-basket-veteran-asean</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/asaba-basketball-1785983557610_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Modric Ungkap Alasan Utama Milan Gagal Lolos ke Liga Champions</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:20:30 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Adhi Prasetya</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Gelandang AC Milan Luka Modric mengungkap alasan utama timnya gagal lolos ke Liga Champions musim depan meski konsisten di tiga besar hampir sepanjang musim.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8606381/modric-ungkap-alasan-utama-milan-gagal-lolos-ke-liga-champions</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/luka-modric-1785950179765_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Peralta Belum Bisa Main Penuh di Final Piala Presiden 2026</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:00:25 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Muhammad Robbani</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Mariano Peralta bertekad untuk ikut membantu Persib Bandung di final Piala Presiden 2026. Meski belum dalam kondisi prima, ia siap jika diturunkan.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606357/peralta-belum-bisa-main-penuh-di-final-piala-presiden-2026</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/latihan-mariano-peralta-bersama-skuad-persib-bandung-di-lapangan-pendamping-gbla-kamis-3072026-1785405696499_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Infantino Mengaku Salah, tapi 'Tetap Didukung' Sebagai Presiden FIFA</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:30:10 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Adhi Prasetya</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>FIFA meminta maaf karena meluncurkan proposal untuk menjual saham Piala Dunia. Mereka juga mengklaim Gianni Infantino masih didukung sebagai presiden.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606335/infantino-mengaku-salah-tapi-tetap-didukung-sebagai-presiden-fifa</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/25/presiden-federasi-sepak-bola-internasional-fifa-gianni-infantino-1758751598826_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>KPK Panggil Rudy Tanoe Sebagai Saksi Kasus Penyaluran Beras Bansos</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:04:27 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>KPK panggil Bambang Rudijanto Tanoesoedibjo, Dirut PT Dosni Roha Logistik, sebagai saksi kasus korupsi bansos beras yang rugikan negara Rp 200 Miliar.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/06/12033081/kpk-panggil-rudy-tanoe-sebagai-saksi-kasus-penyaluran-beras-bansos</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/sPMPszMcYwafRiduAvif57ywLiA=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/06/30/6a43aecc7cd73.jpeg</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Steam Diskon Semua Game Need for Speed, Harga mulai Rp 20.000-an</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:04:29 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Steam menggelar diskon besar-besaran untuk seluruh seri Need for Speed hingga 13 Agustus. Beberapa judul kini bisa dibeli mulai Rp 23.900.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://tekno.kompas.com/read/2026/08/06/11460057/steam-diskon-semua-game-need-for-speed-harga-mulai-rp-20.000-an</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RQv8kaYBXIDfpem5c6qWlsAEJH4=/152x0:759x405/1200x675/filters:watermark(data/photo/2026/01/30/697c816a7af9e.png,0,-0,1)/data/photo/2025/07/14/68746422aa276.jpg</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ketika Amerika Serikat Membayangi Diplomasi Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:04:29 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Negosiasi Iran–Oman mengenai Selat Hormuz tidak dapat dipahami hanya sebagai isu bilateral.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/06/113200370/ketika-amerika-serikat-membayangi-diplomasi-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/kpyrSW4PWLojSI2jazN76ep2_ec=/0x0:2000x1333/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2026/05/30/6a1ab1b0b4883.jpg</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I133"/>
+  <autoFilter ref="A1:I257"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$257</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$330</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I257"/>
+  <dimension ref="A1:I330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12511,8 +12511,3439 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Bapanas pastikan pasokan bawang putih aman dan terjaga</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:33:39 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Badan Pangan Nasional (Bapanas) memastikan pasokan bawang putih nasional tetap aman dan terjaga melalui penguatan ...</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682304/bapanas-pastikan-pasokan-bawang-putih-aman-dan-terjaga</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/FDA4BAED-1158-445D-9FD7-7209B487040C.jpeg</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Banggar DPR nilai faktor musiman dongkrak ekonomi RI tumbuh 5,2 persen</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:33:25 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Badan Anggaran Dewan Perwakilan Rakyat (Banggar DPR) RI menilai faktor musiman mendongkrak perekonomian RI tumbuh 5,2 ...</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682303/banggar-dpr-nilai-faktor-musiman-dongkrak-ekonomi-ri-tumbuh-52-persen</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/01/Said-Abdullah-1.jpg</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Personel Gulkarmat Jaksel padamkan kebakaran di SDN 04 Srengseng Sawah</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:32:38 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Sebanyak 60 personel Suku Dinas Penanggulangan Kebakaran dan Penyelamatan (Gulkarmat) Jakarta Selatan (Jaksel) ...</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682300/personel-gulkarmat-jaksel-padamkan-kebakaran-di-sdn-04-srengseng-sawah</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001014476.jpg</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Hakim federal AS izinkan Trump akhiri perlindungan 350 warga Haiti</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:29:46 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Hakim federal Amerika Serikat (AS) berkedudukan di Washington D.C. mengabulkan keputusan pemerintahan Presiden Donald ...</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682297/hakim-federal-as-izinkan-trump-akhiri-perlindungan-350-warga-haiti</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000013_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>OnePlus meredup di pasar global, distribusi dihentikan di pasar AS</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:27:35 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Jenama ponsel pintar, OnePlus, tampak makin kehilangan eksistensinya di pasar global setelah baru-baru ini secara resmi ...</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682295/oneplus-meredup-di-pasar-global-distribusi-dihentikan-di-pasar-as</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/InShot_20260806_130451713.jpg</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Menaker dorong perkuat STEM guna hapus kesenjangan skill tenaga kerja</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:26:10 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli mendorong penguatan pendidikan Sains, Teknologi, Rekayasa, dan Matematika ...</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682292/menaker-dorong-perkuat-stem-guna-hapus-kesenjangan-skill-tenaga-kerja</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000470811.jpg</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Komisi IX ingatkan nakes jaga etika bermedia sosial</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:24:33 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Anggota Komisi IX DPR RI Asep Rommy Romaya mengingatkan tenaga kesehatan (nakes) untuk menjaga etika dalam bermedia ...</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682289/komisi-ix-ingatkan-nakes-jaga-etika-bermedia-sosial</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/WhatsApp-Image-2026-06-09-at-14.50.10.jpeg</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>BI: Transaksi QRIS capai 12,55 miliar pada semester I 2026</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:23:46 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) mencatat volume transaksi digital Quick Response Code Indonesian Standard atau QRIS menembus 12,55 ...</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682285/bi-transaksi-qris-capai-1255-miliar-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_134312.jpg</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Lima alutsista baru TNI AU dikerahkan dalam latihan gabungan TNI</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:20:48 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Lima alat utama sistem senjata (alutsista) milik TNI AU diturunkan untuk mengikuti latihan gabungan TNI terintegrasi ...</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682283/lima-alutsista-baru-tni-au-dikerahkan-dalam-latihan-gabungan-tni</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001560157.jpg</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Potret peluncuran Satelit Lampung-1 di Shandong</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:20:41 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Roket pengangkut Jielong-3 Y12 lepas landas dari perairan lepas pantai Kota Haiyang, Provinsi Shandong, China timur, ...</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682279/potret-peluncuran-satelit-lampung-1-di-shandong</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000033_20260805_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>BPS rilis Indeks Kepuasan Layanan Haji Indonesia 2026 capai 83,28 poin</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:18:15 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) merilis hasil Indeks Kepuasan Layanan Haji Indonesia (IKLHI) tahun 1447 Hijriah/2026 Masehi ...</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682276/bps-rilis-indeks-kepuasan-layanan-haji-indonesia-2026-capai-8328-poin</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000176812.jpg</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Penggunaan Air KAI Turun 22,16 Persen, ATWP LRT Jabodebek Perkuat Daur Ulang Air</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:15:37 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) mencatat penggunaan air sebesar 716,30 megaliter sepanjang 2025. Jumlah tersebut ...</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682272/penggunaan-air-kai-turun-2216-persen-atwp-lrt-jabodebek-perkuat-daur-ulang-air</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-12.19.53.jpeg</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Ekspedisi Rupiah Berdaulat 2026 sambangi Papua</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Ekspedisi Rupiah Berdaulat (ERB) menjangkau Papua pada 4-10 Agustus 2026 untuk memastikan masyarakat di wilayah ...</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5682263/ekspedisi-rupiah-berdaulat-2026-sambangi-papua</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/20260806-Ekspedisi-Rupiah-Berdaulat-2026-sambangi-Papua.jpg</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>BRIN paparkan 12 klaster inovasi kepada Presiden Prabowo</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:14:49 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Sebanyak 150 peneliti Badan Riset dan Inovasi Nasional (BRIN) memaparkan hasil riset dan inovasi dalam 12 klaster ...</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682268/brin-paparkan-12-klaster-inovasi-kepada-presiden-prabowo</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034735.jpg</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Polisi dalami dugaan hubungan sesama jenis dalam kasus mutilasi di Depok</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:09:26 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya mendalami dugaan adanya hubungan sesama jenis antara tersangka SA alias Saepullah dengan korban dalam ...</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682267/polisi-dalami-dugaan-hubungan-sesama-jenis-dalam-kasus-mutilasi-di-depok</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Anthropic bentuk tim pengembangan chip untuk AI Claude</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:04:28 +0700</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Perusahaan kecerdasan artifisial (AI) Anthropic membentuk tim khusus untuk mengembangkan chip AI buatan sendiri untuk ...</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682260/anthropic-bentuk-tim-pengembangan-chip-untuk-ai-claude</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/InShot_20260506_133536251.jpg</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>210,47 Juta Pelanggan Commuter Line Jabodetabek Perkuat Produktivitas dan Mobilitas Rendah Karbon</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:01:55 +0700</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) melayani 210.468.029 pelanggan Commuter Line Jabodetabek sepanjang ...</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682256/21047-juta-pelanggan-commuter-line-jabodetabek-perkuat-produktivitas-dan-mobilitas-rendah-karbon</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-12.09.05.jpg</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Mendukbangga minta SPPG aktif salurkan MBG 3B di Babel</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:01:20 +0700</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kependudukan dan Pembangunan Keluarga (Mendukbangga) / Kepala Badan Kependudukan dan Keluarga ...</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682220/mendukbangga-minta-sppg-aktif-salurkan-mbg-3b-di-babel</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENDUKBANGGA-MINTA-SPPG-AKTIF-SALURKAN-MBG-3B-DI-BABEL.jpg</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Sekolah Rakyat Medan: Membangun karakter demi masa depan siswa</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:00:59 +0700</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Para siswa dari berbagai jenjang pendidikan tampak menyimak materi dalam program Taruna Mengajar di Sekolah Rakyat ...</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682255/sekolah-rakyat-medan-membangun-karakter-demi-masa-depan-siswa</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0034-2.jpg</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>KPK panggil anggota DPRD Kaltim di kasus Rita Widyasari</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:00:12 +0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) memanggil anggota DPRD Kalimantan Timur Sarkowi V. Zahry sebagai saksi dalam ...</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682253/kpk-panggil-anggota-dprd-kaltim-di-kasus-rita-widyasari</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_7484.jpg</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Dishub DKI uji coba penutupan perputaran arah di RS Fatmawati Raya</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:57:01 +0700</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Dinas Perhubungan (Dishub) DKI Jakarta melakukan uji coba penutupan perputaran arah (U-turn) di Jalan RS Fatmawati ...</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682252/dishub-dki-uji-coba-penutupan-perputaran-arah-di-rs-fatmawati-raya</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001014312.jpg</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>PAN: Usulan Pilkada tanpa wakil sudah jadi diskusi lintas fraksi</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:55:59 +0700</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Umum Partai Amanat Nasional (PAN) Saleh Partaonan Daulay menilai usulan pemilihan kepala daerah (Pilkada) ...</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682251/pan-usulan-pilkada-tanpa-wakil-sudah-jadi-diskusi-lintas-fraksi</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/24/1001249216.jpg</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Sergio Castel ungkap target bersama Persik Kediri</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:55:46 +0700</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Penyerang anyar Sergio Castel mengungkapkan targetnya telah menerima tawaran bergabung bersama klub BRI Super League ...</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682247/sergio-castel-ungkap-target-bersama-persik-kediri</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/10/persib-bandung-kalahkan-persija-jakarta-2787353.jpg</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Kuasa hukum: Praperadilan Febrie bukan hindari proses hukum</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:54:32 +0700</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Tim kuasa hukum mantan Jaksa Agung Muda Tindak Pidana Khusus (Jampidsus) Febrie Adriansyah menyatakan permohonan ...</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682243/kuasa-hukum-praperadilan-febrie-bukan-hindari-proses-hukum</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/febrie-adriansyah-ajukan-praperadilan-ke-pn-jaksel-2835015.jpg</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SpaceX berencana buat Starlink jadi opsel di AS</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:51:06 +0700</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Perusahaan antariksa yang dimiliki pebisnis Elon Musk, SpaceX, membagikan rencana barunya untuk masuk ke dalam industri ...</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682241/spacex-berencana-buat-starlink-jadi-opsel-di-as</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/09/IMG-20241208-WA0015_1.jpg</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Gulkarmat Jaktim evakuasi musang yang jatuh dari plafon rumah warga</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:50:38 +0700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Petugas Suku Dinas Penanggulangan Kebakaran dan Penyelamatan (Gulkarmat) Jakarta Timur (Jaktim) mengevakuasi seekor ...</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682240/gulkarmat-jaktim-evakuasi-musang-yang-jatuh-dari-plafon-rumah-warga</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/InShot_20260806_115833896.jpg</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Komisioner Uni Eropa: Penyelundup bertanggung jawab atas tragedi Ceuta</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:46:44 +0700</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Komisioner Uni Eropa (EU) untuk Urusan Dalam Negeri dan Migrasi Magnus Brunner meyakini bahwa penyelundup manusia ...</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682237/komisioner-uni-eropa-penyelundup-bertanggung-jawab-atas-tragedi-ceuta</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Spanyol-Migran-memasuki-Ceuta.jpg</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Bandara utama Venezuela kembali Layani penerbangan kargo pascagempa</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:45:28 +0700</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Bandar Udara (Bandara) Internasional Simon Bolivar, bandara utama yang melayani ibu kota Venezuela, Caracas, kembali ...</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682235/bandara-utama-venezuela-kembali-layani-penerbangan-kargo-pascagempa</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000009_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>128.331 warga daftar undangan upacara HUT Ke-81 RI di Istana</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:45:26 +0700</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Sebanyak 128.331 pendaftar dari 36 provinsi di Indonesia dan 14 negara mengikuti pendaftaran undangan Upacara ...</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682231/128331-warga-daftar-undangan-upacara-hut-ke-81-ri-di-istana</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/prasetyo-hadi_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>KAI Layani 1,57 Juta Ton Angkutan BBM hingga Juli 2026, Jaga Kelancaran Rantai Pasok Energi Nasional</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:43:01 +0700</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) melayani angkutan bahan bakar minyak atau BBM sebanyak 1.570.911 ton selama ...</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682227/kai-layani-157-juta-ton-angkutan-bbm-hingga-juli-2026-jaga-kelancaran-rantai-pasok-energi-nasional</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-12.05.34.jpeg</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Kapolda-Pangdam perkuat sinergi lewat kunjungan ke Mako Brimob</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:41:50 +0700</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Kapolda Metro Jaya Komjen Pol. Asep Edi Suheri bersama Pangdam Jaya Letjen TNI Deddy Suryadi memperkuat sinergi ...</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682225/kapolda-pangdam-perkuat-sinergi-lewat-kunjungan-ke-mako-brimob</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Polda-Pangdam.jpg</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>PSS Sleman gelar peluncuran tim di Stadion Maguwoharjo</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:40:06 +0700</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Klub Promosi BRI Super League PSS Sleman akan menggelar peluncuran tim untuk menghadapi kompetisi 2026/2027 di Stadion ...</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682221/pss-sleman-gelar-peluncuran-tim-di-stadion-maguwoharjo</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/04/23/IMG_5232-scaled-e1619170570649-1024x745.jpg</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Minecraft akan dirilis untuk Nintendo Switch 2 pada 27 Oktober</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:37:53 +0700</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Gim Minecraft akan hadir di konsol Nintendo Switch 2 pada 27 Oktober 2026 dengan peningkatan kualitas visual ...</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682219/minecraft-akan-dirilis-untuk-nintendo-switch-2-pada-27-oktober</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Homepage_Discover-our-games_MC-Vanilla-KeyArt_864x864.jpg</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Kepala Bapanas pastikan pengawasan beras fortifikasi diperketat</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:32:09 +0700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pangan Nasional (Bapanas) sekaligus Menteri Pertanian Andi Amran Sulaiman memastikan pengawasan beras ...</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682216/kepala-bapanas-pastikan-pengawasan-beras-fortifikasi-diperketat</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/8813B57A-20AF-421A-B253-891224E6867C.jpeg</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>6 investasi TPT ciptakan hampir 10 ribu lapangan kerja</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:29:38 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Sekretaris Jenderal Asosiasi Garment dan Textile Indonesia (AGTI) Rizal Tanzil Rakhman mengatakan investasi pada enam ...</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682213/6-investasi-tpt-ciptakan-hampir-10-ribu-lapangan-kerja</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/14/antarafoto-kinerja-industri-manufaktur-tahun-2024-150124-ysw-2.jpg</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Wamenpar dorong investasi industri rekreasi lewat Fun Asia Expo 2026</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:28:47 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Pariwisata Ni Luh Puspa mengatakan penyelenggaraan Fun Asia Expo 2026 menjadi upaya untuk mendorong ...</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682211/wamenpar-dorong-investasi-industri-rekreasi-lewat-fun-asia-expo-2026</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-05-at-21.41.39.jpeg</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Hiroshima serukan hapus senjata nuklir pada peringatan 81 thn bom atom</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:27:55 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Hiroshima pada Kamis menyerukan penghapusan senjata nuklir oleh para pemimpin dunia di tengah meningkatnya ...</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682207/hiroshima-serukan-hapus-senjata-nuklir-pada-peringatan-81-thn-bom-atom</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/ilustrasi-peringatan-bom-atom-Jepang.jpg</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Koalisi Pejalan Kaki minta JPO kawasan UI hingga Pasar Minggu direnovasi</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:27:20 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Koalisi Pejalan Kaki meminta pemerintah agar merenovasi jembatan penyeberangan orang (JPO) Stasiun Universitas ...</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682205/koalisi-pejalan-kaki-minta-jpo-kawasan-ui-hingga-pasar-minggu-direnovasi</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001014293.jpg</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>OJK minta pindar perkuat tata kelola demi jaga kepercayaan publik</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:22:41 +0700</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) meminta industri pinjaman daring (pindar) memperkuat tata kelola dan manajemen risiko guna ...</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682203/ojk-minta-pindar-perkuat-tata-kelola-demi-jaga-kepercayaan-publik</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/c756d23e-0e38-4da7-a296-05d8e08704f4.jpeg</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>PWI nilai pers punya peran strategis untuk memerangi pinjol ilegal</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:22:28 +0700</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Ketua Umum Persatuan Wartawan Indonesia (PWI) Pusat Akhmad Munir menilai pers memiliki peran strategis dalam ...</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682199/pwi-nilai-pers-punya-peran-strategis-untuk-memerangi-pinjol-ilegal</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/f54d1eff-1fa0-484e-aa29-cf7df6459230.jpeg</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Huawei Nova 16 SE meluncur dengan layar OLED dan baterai 8.500 mAh</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:20:30 +0700</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Huawei resmi menghidupkan kembali lini ponsel Nova SE setelah absen lebih dari dua tahun dengan meluncurkan Huawei Nova ...</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682197/huawei-nova-16-se-meluncur-dengan-layar-oled-dan-baterai-8500-mah</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Huawei-Nova-16-SE.jpg</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Tinjau SPPG Pangkalpinang, Mendukbangga pastikan kualitas MBG 3B</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:18:57 +0700</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Menteri Kependudukan dan Pembangunan Keluarga (Mendukbangga) Wihaji meninjau Satuan Pelayanan Pemenuhan Gizi (SPPG) di ...</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682195/tinjau-sppg-pangkalpinang-mendukbangga-pastikan-kualitas-mbg-3b</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/mendukbangga.jpg</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Waktu terbaik naik pesawat bersama anak agar nyaman dan minim jet lag</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:16:37 +0700</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Waktu keberangkatan pesawat dapat memengaruhi kenyamanan anak selama perjalanan sekaligus membantu mengurangi risiko ...</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682193/waktu-terbaik-naik-pesawat-bersama-anak-agar-nyaman-dan-minim-jet-lag</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2013/09/20130902pengasuh-anak-dalam-pesawat.jpg</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Menteri PPN buka Indonesia's Sustainable Development Goals Award 2026</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:15:22 +0700</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682191/menteri-ppn-buka-indonesias-sustainable-development-goals-award-2026</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/PPN-Judol.jpeg</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Operasi kereta Daop 2 kemabli normal pascagempa walau telat 9-60 menit</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:15:20 +0700</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>PT KAI Daerah Operasi (Daop) 2 Bandung mengungkapkan perjalanan kereta api telah kembali beroperasi normal ...</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682187/operasi-kereta-daop-2-kemabli-normal-pascagempa-walau-telat-9-60-menit</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1002080940.jpg</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>KPK panggil Rudy Tanoe sebagai saksi kasus penyaluran bansos beras</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:14:06 +0700</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) memanggil Komisaris Utama PT Dosni Roha Logistik sekaligus Direktur Utama PT Dosni ...</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682185/kpk-panggil-rudy-tanoe-sebagai-saksi-kasus-penyaluran-bansos-beras</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/12/14/Screenshot_20231214_140224_Video-Player.jpg</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen telusuri dugaan penyalahgunaan Dapodik murid</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:12:19 +0700</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah (Kemendikdasmen) tengah melakukan verifikasi dan penelusuran terhadap dugaan ...</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682181/kemendikdasmen-telusuri-dugaan-penyalahgunaan-dapodik-murid</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/25/pendidikan.jpg</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>KSOP Sampit keluarkan maklumat pelayaran waspada kabut asap karhutla</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:12:14 +0700</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Kantor Kesyahbandaran dan Otoritas Pelabuhan (KSOP) Kelas III Sampit, Kabupaten Kotawaringin Timur (Kotim), Kalimantan ...</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682180/ksop-sampit-keluarkan-maklumat-pelayaran-waspada-kabut-asap-karhutla</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001725985.jpg</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Indonesia tekankan kepatuhan pada hukum laut dalam konflik bersenjata</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:10:27 +0700</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Indonesia mendorong kepatuhan terhadap hukum lingkungan laut serta menyoroti perlunya pedoman teknis mengenai perlakuan ...</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682176/indonesia-tekankan-kepatuhan-pada-hukum-laut-dalam-konflik-bersenjata</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Kemlu-RI-Naval-Warfare-Workstream-ICRC-06082026_1.jpg</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Membangun Masa Depan Riset dan Teknologi, Pembangunan Gedung L-SSIT Universitas Udayana Capai Progres 47,11%</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:10:21 +0700</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Pembangunan Gedung Laboratorium Smart System and Integrated Technologies (L-SSIT) Universitas Udayana, Bali terus ...</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682175/membangun-masa-depan-riset-dan-teknologi-pembangunan-gedung-l-ssit-universitas-udayana-capai-progres-4711</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Pembangunan-Gedung-L-SSIT.jpg</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>OJK didorong siapkan mitigasi risiko kredit macet industri pindar</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:05:25 +0700</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Konsultan dan Perencana Keuangan Elvi Diana mendorong Otoritas Jasa Keuangan (OJK) menyiapkan langkah mitigasi terhadap ...</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682173/ojk-didorong-siapkan-mitigasi-risiko-kredit-macet-industri-pindar</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/30/IMG_0468.jpeg</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Cinta Indonesia, Dubes Palestina Akan Gelar Perayaan HUT RI di Kedubes</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:32:50 +0700</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Duta Besar Palestina, Al-Sattiri, mengumumkan perayaan HUT ke-79 RI sebagai ungkapan terima kasih rakyat Palestina. Gubernur DKI Jakarta mendukung acara ini.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606839/cinta-indonesia-dubes-palestina-akan-gelar-perayaan-hut-ri-di-kedubes</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pramono-bersama-dubes-palestina-brigitta-belia-permata-saridetikcom-1785997942304_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>150 Peneliti BRIN Bakal Paparkan Hasil Riset Pangan hingga Nuklir ke Prabowo</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:32:06 +0700</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Kepala Badan Riset dan Inovasi Nasional (BRIN) Arif Satria membawa 150 orang peneliti ke Istana, Jakarta.</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606837/150-peneliti-brin-bakal-paparkan-hasil-riset-pangan-hingga-nuklir-ke-prabowo</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kepala-brin-arif-satria-evadetikcom-1785997911603_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Presiden Iran Ungkap Komunikasi dengan Mojtaba Khamenei 'Sangat Sulit'</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:27:08 +0700</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Presiden Iran Masoud Pezeshkian mengungkapkan bahwa komunikasi dengan pemimpin tertinggi negaranya, Mojtaba Khamenei, sangat sulit pada saat ini.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606829/presiden-iran-ungkap-komunikasi-dengan-mojtaba-khamenei-sangat-sulit</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/11/pemimpin-tertinggi-iran-mojtaba-khamenei-1775906157579_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Bamsoet Ingatkan Industri Kesehatan Harus Adaptif Hadapi Tantangan Global</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:18:43 +0700</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Bamsoet soroti tantangan industri rumah sakit di tengah ketidakpastian ekonomi. Siloam Hospitals menunjukkan pertumbuhan positif dan inovasi layanan kesehatan.</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606810/bamsoet-ingatkan-industri-kesehatan-harus-adaptif-hadapi-tantangan-global</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bamsoet-1785997067503_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Istri di Bogor Bakar Baju Suami hingga Rumah Terbakar, Dipicu Cekcok</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:07:22 +0700</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Kebakaran rumah di Menteng Asri, Bogor, dipicu istri yang membakar baju suami saat bertengkar. Kerugian mencapai Rp 150 juta.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606787/istri-di-bogor-bakar-baju-suami-hingga-rumah-terbakar-dipicu-cekcok</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kebakaran-rumah-di-bogor-dipicu-istri-bakar-baju-suami-1785996380774_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Pengedar Ribuan Tramadol dan Hexymer Dibekuk di Tangerang, Pemasok Diburu</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:52:13 +0700</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Polres Metro Tangerang Kota mengungkap peredaran obat keras ilegal, menangkap tersangka YG dengan ribuan butir tramadol dan hexymer.</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606762/pengedar-ribuan-tramadol-dan-hexymer-dibekuk-di-tangerang-pemasok-diburu</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Kobra di Karanganyar Telan Pisau hingga Perut Terbelah, Diduga Stres</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:48:58 +0700</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Agil Trisetiawan Putra</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Seekor ular kobra ditemukan dalam kondisi menelan pisau dapur di rumah warga Desa Sroyo, Kecamatan Jaten, Kabupaten Karanganyar.</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606756/kobra-di-karanganyar-telan-pisau-hingga-perut-terbelah-diduga-stres</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ular-kobra-menelan-pisau-di-desa-sroyo-jaten-karanganyar-tanpa-watermark-1785911516116_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Polres Serang Kirim 64 Truk Tangki Air Atasi Kekeringan di 6 Kecamatan</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:48:44 +0700</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Polres Serang mengirim 64 tangki air untuk membantu warga di daerah terdampak kekeringan.</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606754/polres-serang-kirim-64-truk-tangki-air-atasi-kekeringan-di-6-kecamatan</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polres-serang-mengirim-64-tangki-air-untuk-membantu-warga-di-daerah-terdampak-kekeringan-1785995228316_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Buron Kasus Pembunuhan Sekdin PRKP Bangkalan Diduga Gondol Emas 1 Kg</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:44:25 +0700</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Suparno</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Buron kasus kematian Sekdin PRKP Bangkalan, Erlan, diduga mencuri perhiasan emas 1 kg dan uang tunai ratusan juta. Keluarga korban melaporkan kehilangan.</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606748/buron-kasus-pembunuhan-sekdin-prkp-bangkalan-diduga-gondol-emas-1-kg</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/07/pembunuhan-sekdin-prkp-bangkalan-1783403824762_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Netanyahu Tegaskan Tolak Kesepakatan Gaza Usulan Trump</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:43:46 +0700</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Netanyahu menegaskan penolakannya terhadap kesepakatan perdamaian Gaza yang diusulkan sekutu dekatnya, Presiden AS Donald Trump.</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606747/netanyahu-tegaskan-tolak-kesepakatan-gaza-usulan-trump</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/26/pm-israel-benjamin-netanyahu-1756180921129_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Perkuat Sinergi TNI-Polri, Kapolda Metro dan Pangdam Jaya Kunjungi Dankorbrimob Polri</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:33:56 +0700</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Kapolda Metro Jaya dan Pangdam Jaya kunjungi Markas Korps Brimob untuk memperkuat sinergi TNI-Polri dalam menjaga keamanan Jakarta dan dukung agenda nasional.</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606739/perkuat-sinergi-tni-polri-kapolda-metro-dan-pangdam-jaya-kunjungi-dankorbrimob-polri</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kapolda-metro-jaya-dan-pangdam-jaya-mengunjungi-dankorbrimob-polri-dalam-rangka-memperkuat-soliditas-dan-sinergi-tni-polri-1785994408613_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>SDN di Srengseng Jaksel Kebakaran: Pelajar Dievakuasi, Api Berangsur Mati</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:28:19 +0700</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Bangunan SDN di Srengseng Sawah, Jagakarsa, Jakarta Selatan, dilanda kebakaran. Pelajar di sekolah tersebut sudah dievakuasi.</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606722/sdn-di-srengseng-jaksel-kebakaran-pelajar-dievakuasi-api-berangsur-mati</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/01/07/1ec4fbfe-119d-4c1c-b3e0-e50685a1e1bb_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>PK Ditolak, Bos Smelter Tetap Dihukum 18 Tahun Bui di Kasus Korupsi Rp 300 T</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:26:41 +0700</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Mahkamah Agung (MA) menolak peninjauan kembali (PK) yang diajukan terpidana kasus korupsi pengelolaan timah bernama Tamron.</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606719/pk-ditolak-bos-smelter-tetap-dihukum-18-tahun-bui-di-kasus-korupsi-rp-300-t</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/01/26/aed271bd-0523-49d3-a57f-ee5dd7541d42_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SD di Cibaduyut Digembok Ahli Waris, Hampir Seribu Siswa Terpaksa Pulang</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:20:57 +0700</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Rifat Alhamidi</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Sebanyak 945 siswa SDN 026 Bojongloa, Kota Bandung, tak bisa belajar seperti biasa. Pasalnya, lingkungan sekolah itu disegel oleh ahli waris.</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606702/sd-di-cibaduyut-digembok-ahli-waris-hampir-seribu-siswa-terpaksa-pulang</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pembelajaran-sdn-026-bojongloa-dihentikan-setelah-sempat-disegel-ahli-waris-1785991246958_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Legislator PKB Usul Pilkada Tanpa Wakil, PAN: Usulan Bagus dan Simpatik</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:07:39 +0700</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Usulan ini bagus dan simpatik. Sudah banyak diperbincangkan di lintas fraksi, kata Saleh.</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606676/legislator-pkb-usul-pilkada-tanpa-wakil-pan-usulan-bagus-dan-simpatik</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/10/saleh-daulay_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>SDN di Srengseng Sawah Jaksel Kebakaran</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:04:32 +0700</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Bangunan sekolah dasar negeri (SDN) di Srengseng Sawah, Jagakarsa, Jaksel dilanda kebakaran. Petugas damkar berjibaku memadamkan api.</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606674/sdn-di-srengseng-sawah-jaksel-kebakaran</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/23/aba98b4b-9134-44d4-bc2c-056cf42d0c43_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Kenalkan, Sofia Anak Buruh Lulusan SMA CT ARSA yang Tembus ITB</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:01:15 +0700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Nur Khansa Ranawati</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Bagi Sofi Aulia Syarifa (19), melanjutkan pendidikan hingga kuliah pernah terasa seperti mimpi. Kini, SMA Plus CT ARSA Sukoharjo itu resmi jadi mahasiswa ITB.</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606666/kenalkan-sofia-anak-buruh-lulusan-sma-ct-arsa-yang-tembus-itb</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/sofi-aulia-syarifa-lulusan-sma-plus-ct-arsa-yang-tembus-itb-1785923838256_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Penyu Hendak Bertelur Mati Terbelah di Kaltim, Seluruh Telurnya Diambil Pelaku</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:31:33 +0700</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Riani Rahayu</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Seekor penyu betina yang hendak bertelur mati terbelah di pesisir Kabupaten Berau, Kaltim. Seluruh telur yang masih ada di dalam tubuh penyu itu hilang.</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606620/penyu-hendak-bertelur-mati-terbelah-di-kaltim-seluruh-telurnya-diambil-pelaku</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/penyu-ditemukan-mati-mengenaskan-di-pesisir-berau-1785936713273_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Roy Suryo Kalah Lagi di Praperadilan Ketiga</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:34:01 +0700</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Hakim Pengadilan Negeri Jakarta Selatan tak menerima gugatan praperadilan ketiga yang diajukan oleh Roy Suryo.</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606515/roy-suryo-kalah-lagi-di-praperadilan-ketiga</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sidang-praperadilan-roy-suryo-rumondangdetikcom-1785987232013_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Kemenhan Rotasi 14 Pejabat Tinggi, Sekretaris Bacadnas Berganti</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:43:27 +0700</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Kemenhan merotasi 14 pejabat pimpinan tinggi, termasuk posisi Sekretaris Bacadnas yang kini dijabat Mayjen TNI (Mar) Freddy Ardianzah.</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/06/13424791/kemenhan-rotasi-14-pejabat-tinggi-sekretaris-bacadnas-berganti</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/1tcSy0VFMv_5jsqfG3Us-zZzC4I=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a742928e8f6f.jpg</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Terungkap Motif Penebangan 10 Pohon di Cihapit, Diduga demi Sewa Videotron</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:43:30 +0700</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Petinggi subkontraktor diduga memerintahkan penebangan 10 pohon di Cihapit karena berencana menyewa videotron yang pandangannya terhalang.</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/06/133000978/terungkap-motif-penebangan-10-pohon-di-cihapit-diduga-demi-sewa-videotron</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/u_bm11Ybowq4LB5HrbaMY629JB8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a72e08497f56.jpg</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 Sukses Mengorbit, Mengapa Pemprov Belum Bisa Langsung Manfaatkan Datanya?</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:43:31 +0700</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Meski telah sukses diluncurkan ke orbit, data Satelit Lampung-1 masih harus melalui proses verifikasi dan pengolahan bersama BRIN sebelum digunakan.</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/131123978/satelit-lampung-1-sukses-mengorbit-mengapa-pemprov-belum-bisa-langsung</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/lt-GVFMNLaiVoB0qgnwsx5KS_Uw=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a741c7c0f5ae.jpg</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I257"/>
+  <autoFilter ref="A1:I330"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$330</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$376</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I330"/>
+  <dimension ref="A1:I376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15942,8 +15942,2170 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Beijing ditetapkan sebagai ibu kota arsitektur dunia UNESCO-UIA 2029</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:01:16 +0700</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Beijing ditetapkan sebagai Ibu Kota Arsitektur Dunia UNESCO-UIA (International Union of Architects) 2029, demikian ...</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682343/beijing-ditetapkan-sebagai-ibu-kota-arsitektur-dunia-unesco-uia-2029</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000012_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>AS cabut sanksi maskapai Irak, bantah longgarkan sanksi Iran</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:59:47 +0700</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Departemen Keuangan Amerika Serikat (AS) mencabut sanksi untuk maskapai penerbangan asal Irak, Fly Baghdad, beserta dua ...</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682341/as-cabut-sanksi-maskapai-irak-bantah-longgarkan-sanksi-iran</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000008_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Pemprov DKI perkuat pendidikan anak sejak usia dini</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:58:33 +0700</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta terus berupaya memperkuat pendidikan sejak usia dini sebagai bagian dari ...</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682340/pemprov-dki-perkuat-pendidikan-anak-sejak-usia-dini</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000315491.jpg</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Menko Airlangga: Investasi sudah lebih merata di semester I 2026</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:56:01 +0700</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator (Menko) Bidang Perekonomian Airlangga Hartarto mengatakan kegiatan investasi sudah menunjukkan ...</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682336/menko-airlangga-investasi-sudah-lebih-merata-di-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0438.jpeg</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Dishub Cilegon tertibkan parkir liar kendaraan di JLS</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:52:47 +0700</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Perhubungan Kota Cilegon bersama Satlantas Polres Cilegon, Kamis (6/8), melaksanakan penertiban parkir ...</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682307/dishub-cilegon-tertibkan-parkir-liar-kendaraan-di-jls</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DISHUB-CILEGON-TERTIBKAN-PARKIR-LIAR-KENDARAAN-DI-JLS.jpg</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>BPS rilis IKLHI 2026, Menhaj: Alhamdulillah, pelayanan haji luar biasa</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:51:26 +0700</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Menteri Haji dan Umrah (Menhaj) Mochammad Irfan Yusuf menyebut capaian Indeks Kepuasan Layanan Haji Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682333/bps-rilis-iklhi-2026-menhaj-alhamdulillah-pelayanan-haji-luar-biasa</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000176834.jpg</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>TNI AU pertajam kemampuan personel di bidang intelijen</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:47:34 +0700</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>TNI AU berupaya memperkuat kemampuan personelnya dalam bidang intelijen dengan menggelar Pelatihan Kepala Satuan ...</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682332/tni-au-pertajam-kemampuan-personel-di-bidang-intelijen</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001560248.jpg</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>"Desa Batu" di China Utara pikat wisatawan saat liburan musim panas</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:46:24 +0700</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Dikenal sebagai "desa batu", Desa Xijingyu di Distrik Jizhou, Kota Tianjin, China utara, terkenal dengan ...</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682328/desa-batu-di-china-utara-pikat-wisatawan-saat-liburan-musim-panas</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000005_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Sidang putusan praperadilan ketiga Roy Suryo</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:46:04 +0700</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Hakim tunggal I Ketut Darpawan memimpin jalannya sidang putusan praperadilan ketiga yang diajukan oleh tersangka kasus ...</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5682324/sidang-putusan-praperadilan-ketiga-roy-suryo</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Sidang-putusan-praperadilan-ketiga-Roy-Suryo-06082026-ab-1.jpg</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Wisatawan mancanegara menjajal pencapaian iptek China di Shenzhen</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:43:03 +0700</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Seiring penerapan mendalam dari pencapaian industri-industri emerging, banyak wisatawan mancanegara memilih wisata ilmu ...</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682320/wisatawan-mancanegara-menjajal-pencapaian-iptek-china-di-shenzhen</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000007_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Myanmar lestarikan 6.105 bangunan berusia seabad lebih</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:43:02 +0700</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Pemerintah Myanmar melestarikan 6.105 bangunan yang berusia lebih dari 100 tahun dengan menetapkannya sebagai cagar ...</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682317/myanmar-lestarikan-6105-bangunan-berusia-seabad-lebih</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000010_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Pemprov DKI tegaskan dukung hak rakyat Palestina</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:42:21 +0700</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta menegaskan sikap mendukung hak rakyat Palestina untuk hidup dalam perdamaian, ...</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682315/pemprov-dki-tegaskan-dukung-hak-rakyat-palestina</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_2404.jpeg</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Menko IPK minta konsolidasi BUMN bisa dukung kawasan industri</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:40:18 +0700</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Infrastruktur dan Pembangunan Kewilayahan (Menko IPK) Agus Harimurti Yudhoyono (AHY) meminta ...</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682312/menko-ipk-minta-konsolidasi-bumn-bisa-dukung-kawasan-industri</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_5281.jpeg</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>BRIN pamerkan 150–200 produk inovasi kepada Presiden</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:39:30 +0700</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memamerkan sekitar 150–200 produk inovasi dari 12 klaster riset kepada ...</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682311/brin-pamerkan-150-200-produk-inovasi-kepada-presiden</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034738.jpg</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>POSSI: Kejuaraan Asia 2026 jadi momentum populerkan hoki bawah air</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:39:02 +0700</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Persatuan Olahraga Selam Seluruh Indonesia (PB POSSI) menjadikan Kejuaraan Asia Hoki Bawah Air CMAS 2026 ...</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682309/possi-kejuaraan-asia-2026-jadi-momentum-populerkan-hoki-bawah-air</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/16/WhatsApp-Image-2025-11-15-at-18.51.38.jpeg</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Mendukbangga manfatkan ruang ramah anak, tekan gangguan mental remaja</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:35:34 +0700</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Menteri Kependudukan dan Pembangunan Keluarga (Mendukbangga) Wihaji mengintensifkan ruang ramah anak guna menjaga ...</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682308/mendukbangga-manfatkan-ruang-ramah-anak-tekan-gangguan-mental-remaja</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/mendukbangga2.jpg</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Kobra Telan Pisau di Karanganyar karena Stres? Ini Penjelasan Pakar UGM</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:05:41 +0700</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Tim detikJateng</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Pakar satwa UGM mengatakan ular memang bisa stres pada kondisi tertentu. Namun pada kasus ular kobra menelan pisau di Karanganyar, pakar punya pandangan lain.</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606905/kobra-telan-pisau-di-karanganyar-karena-stres-ini-penjelasan-pakar-ugm</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ular-kobra-menelan-pisau-di-desa-sroyo-jaten-karanganyar-tanpa-watermark-1785911516116_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BRIN Bawa Sepatu Buatan Sendiri Saat Temui Prabowo, Mau Diproduksi Massal</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:04:30 +0700</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Kepala Badan Riset dan Inovasi Nasional (BRIN) Arif Satria memamerkan sepatu buatan lembaganya saat hendak menemui Presiden Prabowo Subianto.</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606902/brin-bawa-sepatu-buatan-sendiri-saat-temui-prabowo-mau-diproduksi-massal</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sepatu-buatan-brin-evadetikcom-1785999841494_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Warga Bilang Pemotor Melintas di Trotoar Jl Sentul karena Putaran Balik Jauh</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:00:47 +0700</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Warga mengatakan pemotor melintas di trotoar Jalan Alternatif Sentul karena putaran balik jauh.</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606897/warga-bilang-pemotor-melintas-di-trotoar-jl-sentul-karena-putaran-balik-jauh</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/trotoar-di-jalan-alternatif-sentul-bogor-sering-dilewati-motor-sampai-rusak-rizkydetikcom-1785980261197_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Pria di Jakbar Kehilangan Motor Saat First Meet Wanita Kenalan Medsos</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:58:31 +0700</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Seorang pria menjadi korban curanmor di Kembangan, Jakbar. Sepeda motor pria itu diduga dibawa wanita saat pertemuan pertama (first meet) mereka.</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606895/pria-di-jakbar-kehilangan-motor-saat-first-meet-wanita-kenalan-medsos</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/seorang-pria-menjadi-korban-curanmor-di-kembangan-jakbar-sepeda-motor-pria-itu-diduga-dibawa-wanita-saat-pertemuan-pertama-fir-1785999460503_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Di Sekolah Pemilu Hijau, Kapolda Riau Dorong Green Policing untuk Green Election</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:54:29 +0700</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Kapolda Riau Irjen Herry Heryawan dukung Sekolah Pemilu Hijau KPU Riau. Ia menekankan pentingnya kolaborasi untuk demokrasi berkelanjutan.</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/melindungi-tuah-marwah/d-8606887/di-sekolah-pemilu-hijau-kapolda-riau-dorong-green-policing-untuk-green-election</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kapolda-riau-irjen-pol-herry-heryawan-menghadiri-peluncuran-sekolah-pemilu-hijau-di-kpu-riau-1785999184772_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Pemotor Tewas Usai Tabrak Trotoar di Jalan Juanda Depok</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:53:55 +0700</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Seorang pengendara motor berusia 29 tahun meninggal setelah kecelakaan tunggal menabrak trotoar di Jalan Juanda, Depok.</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606885/pemotor-tewas-usai-tabrak-trotoar-di-jalan-juanda-depok</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tkp-kecelakaan-pemotor-tewas-usai-tabrak-trotoar-di-depok-1785999184753_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Kepala BGN Ungkap Kasus Keracunan MBG di Jayapura gegara Masak Terlalu Cepat</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:52:57 +0700</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>ANTARA</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Sejumlah siswa di Depapre, Papua, diduga keracunan setelah mengonsumsi MBG. BGN menyebut penyebabnya karena SPPG masak terlalu awal.</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606883/kepala-bgn-ungkap-kasus-keracunan-mbg-di-jayapura-gegara-masak-terlalu-cepat</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kepala-bgn-sudaryono-1785937585412_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Ide Pilkada Tanpa Wakil, NasDem Singgung Banyak Kepala Daerah Kena OTT</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:52:55 +0700</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>NasDem menanggapi usulan pilkada tanpa wakil. Ia menekankan pentingnya kolaborasi antara kepala daerah dan wakil dalam pemerintahan.</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606882/ide-pilkada-tanpa-wakil-nasdem-singgung-banyak-kepala-daerah-kena-ott</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/14/kapoksi-komisi-ii-dpr-fraksi-nasdem-ujang-bey-1765691178496_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Detik-detik Nasabah di Cibitung Dirampok: Dibacok lalu Duit Rp 30 Juta Dicuri</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:47:21 +0700</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Seorang nasabah bank di Cibitung dirampok oleh komplotan bersenjata tajam, kehilangan Rp 30 juta. Polisi masih menyelidiki kasus ini.</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606870/detik-detik-nasabah-di-cibitung-dirampok-dibacok-lalu-duit-rp-30-juta-dicuri</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/06/24/f76d026c-9771-46e8-9200-8840de04f3ab_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Muzani Pastikan Sidang Tahunan MPR Digelar 14 Agustus, Ini Susunan Agendanya</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:47:06 +0700</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI, Ahmad Muzani, mengumumkan Sidang Tahunan MPR 2026 pada 14 Agustus. Agenda mencakup pidato kenegaraan dan laporan kinerja lembaga negara.</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606869/muzani-pastikan-sidang-tahunan-mpr-digelar-14-agustus-ini-susunan-agendanya</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/mpr-1785998788494_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Airlangga Ungkap Respons China soal Utang Kereta Cepat Ditanggung Kemenkeu</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:55:51 +0700</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>China disebut merespons baik upaya penyelesaian utang Whoosh yang akan dilakukan Indonesia.</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8606891/airlangga-ungkap-respons-china-soal-utang-kereta-cepat-ditanggung-kemenkeu</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/05/momen-airlangga-pamer-ekonomi-ri-tumbuh-lebih-tinggi-dari-as-china-1777977745953_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Alarm dari Kadin! Ekspor Nikel RI Terancam Hilang 5 Juta Ton</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:48:29 +0700</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Kadin Indonesia mengungkap dampak pemangkasan kuota nikel menjadi 260-270 juta ton, berpotensi hilangnya ekspor 3,5-5 juta ton. Kadin dorong kepastian RKAB.</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8606876/alarm-dari-kadin-ekspor-nikel-ri-terancam-hilang-5-juta-ton</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/21/nikel-indonesia-1753066004291_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>JHT hingga Pesangon Mulai Dibahas Pemerintah Jadi Alasan Buruh Batal Demo</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:28:40 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Presiden KSPI Said Iqbal memastikan tidak ada aksi buruh besar-besaran pada Agustus-September 2026.</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606831/jht-hingga-pesangon-mulai-dibahas-pemerintah-jadi-alasan-buruh-batal-demo</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/15/buruh-demo-dpr-keluhkan-kecilnya-kenaikan-ump-1768461540644_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Istana Buka Suara soal Utang Kereta Cepat Ditanggung Kementerian Keuangan</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:23:56 +0700</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Pihak istana buka suara soal penyelesaian utang Kereta Cepat Jakarta Bandung atau Whoosh yang akan diambil alih Kementerian Keuangan.</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8606826/istana-buka-suara-soal-utang-kereta-cepat-ditanggung-kementerian-keuangan</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/mensesneg-prasetyo-hadi-1784627991720_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Viral Dua JPO Rasuna Said Bikin Bingung, Konektivitas Antarmoda Jadi Sorotan</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:00:57 +0700</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Gilang Faturahman</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Dua JPO di Jalan H.R. Rasuna Said berdiri berdampingan, tetapi tak saling terhubung. Kondisi ini membuat sebagian pengguna transportasi umum harus memutar.</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8606610/viral-dua-jpo-rasuna-said-bikin-bingung-konektivitas-antarmoda-jadi-sorotan</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/konektivitas-jpo-rasuna-said-disorot-efisiensi-mobilitas-kawasan-bisnis-jadi-sorotan-1785989995354.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>IHSG Tertahan di Level 6.351</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:57:47 +0700</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) berakhir stagnan pada penutupan perdagangan sesi I hari ini, Kamis (6/8/2026).</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8606773/ihsg-tertahan-di-level-6-351</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/28/bei-terapkan-trading-halt-imbas-ihsg-anjlok-1769587530913_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Mendagri Ungkap 79 Pemda Butuh Tambahan Rp 14 T buat Bayar Pegawai</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:33:45 +0700</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Tito Karnavian mengungkapkan pihaknya memetakan ada 79 pemerintah daerah yang butuh tambahan dana alokasi umum dari pemerintah pusat.</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606717/mendagri-ungkap-79-pemda-butuh-tambahan-rp-14-t-buat-bayar-pegawai</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mendagri-wanti-wanti-kepala-daerah-jaga-integritas-demi-cegah-korupsi-1785894664987_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Rekening Raksasa Migas Iran Dibekukan Gegara Terlilit Utang Rp 304 T</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:30:04 +0700</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Rekening bank milik National Iranian Oil Company (NIOC) dibekukan oleh Bank of Industry and Mine milik pemerintah akibat utang yang terus membengkak.</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8606716/rekening-raksasa-migas-iran-dibekukan-gegara-terlilit-utang-rp-304-t</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/02/04/b21a4c0d-dca4-41fb-9380-5413e56fdc4e_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Said Iqbal Pastikan Tak Ada Demo Besar Buruh di Agustus-September</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:23:59 +0700</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Said Iqbal, Presiden KSPI, memastikan tidak ada aksi buruh besar di Agustus-September 2026. Meski demikian, ada empat tuntutan yang tetap diperjuangkan.</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606707/said-iqbal-pastikan-tak-ada-demo-besar-buruh-di-agustus-september</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/06/penasihat-khusus-presiden-bidang-ketenagakerjaan-dan-kesejahteraan-buruh-yang-juga-presiden-kspi-said-iqbal-1783315153767_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Sejarah di Liga Inggris! Manajer Baru Terbanyak dalam Semusim</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:00:20 +0700</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Liga Inggris musim 2026/27 catatkan sejarah. Itu adalah manajer baru terbanyak dalam semusim, ada sembilan lho!</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606771/sejarah-di-liga-inggris-manajer-baru-terbanyak-dalam-semusim</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/14/andoni-iraola-1784017083641.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Singapura Vs Indonesia: Skuad Garuda Harus Lebih Kreatif</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:40:10 +0700</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia akan dijamu oleh Timnas Singapura dalam laga krusial di ajang Piala AFF 2026. Skuad Garuda dituntut untuk bermain lebih kreatif.</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606685/singapura-vs-indonesia-skuad-garuda-harus-lebih-kreatif</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/garuda-dihajar-vietnam-0-3-mimpi-semifinal-kini-di-ujung-tanduk-1785773513300_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Kejuaraan Dunia di India: Alwi Farhan Fokus Main, Nggak Pikirin Venue</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Mercy Raya</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Alwi Farhan siap menghadapi tantangan besar Kejuaraan Dunia Bulutangkis yang digelar di India pada pertengahan Agustus ini.Alwi nggak mau pikirin venue.</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8606811/kejuaraan-dunia-di-india-alwi-farhan-fokus-main-nggak-pikirin-venue</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/alwi-farhan-1784694498208.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Real Madrid Mundur Beli Enzo Fernandez</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:20:30 +0700</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Beberapa bulan terakhir, Madrid rumornya mau beli Enzo Fernandez dari Chelsea. Namun sejauh ini, belum ada tawaran resmi yang masuk. Diyakini El Real mundur.</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8606682/real-madrid-mundur-beli-enzo-fernandez</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/enzo-fernandez-1784675213849.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Pesepakbola Thailand Meninggal Tersambar Petir di Lapangan</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:00:20 +0700</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Kabar duka dari Thailand. Pesepakbola di Liga 3 meninggal dunia akibat tersambar petir saat main di lapangan.</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/gila-bola/d-8606684/pesepakbola-thailand-meninggal-tersambar-petir-di-lapangan</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/08/ilustrasi-petir-1746676660826.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Arsenal Lebih Antusias Sambut Musim Baru, Berambisi Bikin Dinasti</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:40:40 +0700</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Okdwitya Karina Sari</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Setelah mengakhiri puasa panjang gelar Liga Inggris, Arsenal menatap musim 2026/2027 dengan lebih antusias. Arsenal punya ambisi menciptakan dinasti.</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606583/arsenal-lebih-antusias-sambut-musim-baru-berambisi-bikin-dinasti</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/31/arsenal-1780241719681_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Head to Head Singapura Vs Indonesia: Garuda Unggul Atas The Lions</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Timnas Singapura akan berhadapan dengan Timnas Indonesia pada laga pamungkas Grup A Piala AFF 2026. Berikut catatan head to head kedua tim.</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606628/head-to-head-singapura-vs-indonesia-garuda-unggul-atas-the-lions</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2018/11/09/ec0d1cd6-783b-4065-9b32-d41de7dc761c_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Van Dijk Bantu Leoni Lalui Masa-masa Sulit</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:00:35 +0700</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Mohammad Resha Pratama</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Tahun pertama sebagai pemain Liverpool tidaklah menyenangkan untuk Giovanni Leoni. Beruntung ada Virgil van Dijk yang menyemangati Leoni.</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606431/van-dijk-bantu-leoni-lalui-masa-masa-sulit</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/giovanni-leoni-1785978207990_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>7 Kebiasaan Sepele yang Ternyata Bisa Merusak Kesehatan</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:13:56 +0700</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Beberapa kebiasaan yang terasa sepele dan tidak berbahaya nyatanya bisa berdampak buruk bagi kesehatan fisik dan mental dalam jangka panjang.</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>https://lifestyle.kompas.com/read/2026/08/06/141219720/7-kebiasaan-sepele-yang-ternyata-bisa-merusak-kesehatan</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/VxA_U17_Rqx0PKrJhw1giDHFFDA=/0x0:5145x3430/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2025/09/05/68ba673443b91.jpg</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Tak Peduli Mau Dihukum Mati, Eks PM Bangladesh Tetap Ingin Pulang</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:13:57 +0700</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Eks PM Bangladesh yang digulingkan, Sheikh Hasina berencana untuk kembali ke negaranya dari pengasingan di India pada Desember.</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/06/140000570/tak-peduli-mau-dihukum-mati-eks-pm-bangladesh-tetap-ingin-pulang</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/KqBi27DSy7i_XwV7Y5kK0f_RZ6Q=/79x22:1024x652/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2024/08/05/66b0a34b78a2d.jpg</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>BGN Beri "Deadline" SPPG Penuhi SLHS, Paling Lambat 10 Agustus</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:13:58 +0700</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Kepala BGN memberi batas waktu hingga 10 Agustus 2026 bagi SPPG urus SLHS. Dapur yang tak penuhi standar akan ditutup permanen, kepala SPPG terancam dicopot.</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/06/13415551/bgn-beri-deadline-sppg-penuhi-slhs-paling-lambat-10-agustus</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/uXjDD9HgmL4W1tIqWolErz4__0I=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/29/6a69bd228d42b.jpeg</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I330"/>
+  <autoFilter ref="A1:I376"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$389</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I376"/>
+  <dimension ref="A1:I389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18104,8 +18104,619 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Benarkah kalori nasi merah lebih rendah dari nasi putih? Ini faktanya</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:25:42 +0700</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Anggapan bahwa nasi merah memiliki kalori lebih rendah dibandingkan nasi putih masih sering muncul, terutama di ...</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682388/benarkah-kalori-nasi-merah-lebih-rendah-dari-nasi-putih-ini-faktanya</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/07/02/DE121E3F-3DEF-4311-BACA-81FD21AB6D3F.jpeg</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Netanyahu Isyaratkan Siap Serang Iran Sendirian Tanpa AS</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:25:17 +0700</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Netanyahu mengisyaratkan bahwa Israel dapat mengambil tindakan militer sepihak terhadap Iran, tanpa keterlibatan sekutu dekatnya AS.</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8606961/netanyahu-isyaratkan-siap-serang-iran-sendirian-tanpa-as</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/10/16/pm-israel-benjamin-netanyahu_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Kebakaran Gunung Bromo Belum Padam, Drone Water Spray dan Heli Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:24:47 +0700</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>M Rofiq</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Petugas menggunakan helikopter dan drone water spray untuk padamkan kebakaran hutan di Gunung Bromo. Kebakaran mulai terkendali.</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606960/kebakaran-gunung-bromo-belum-padam-drone-water-spray-dan-heli-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/proses-pemadaman-kebakaran-gunung-bromo-menggunakan-drone-water-spray-dan-heli-1785994028539_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Kapolda Riau: Green Policing Siap Menjadi Fondasi Menuju Green Election</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:22:16 +0700</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Kapolda Riau Irjen Herry Heryawan luncurkan Sekolah Pemilu Hijau, mengintegrasikan Green Policing untuk mendukung Green Election dan demokrasi berkelanjutan.</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/melindungi-tuah-marwah/d-8606947/kapolda-riau-green-policing-siap-menjadi-fondasi-menuju-green-election</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kapolda-riau-irjen-pol-herry-heryawan-menghadiri-peluncuran-sekolah-pemilu-hijau-di-kpu-riau-1785999184630_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Kebakaran di SDN Srengseng Jaksel Bersumber dari Gudang Buku</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:18:03 +0700</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Kebakaran di SDN di Srengseng Sawah, Jagakarsa, Jakarta Selatan telah padam. Kebakaran terjadi di gudang penyimpanan buku.</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606938/kebakaran-di-sdn-srengseng-jaksel-bersumber-dari-gudang-buku</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kebakaran-di-sdn-di-srengseng-sawah-jagakarsa-jakarta-selatan-telah-padam-kebakaran-terjadi-di-gudang-penyimpanan-buku-dok-dam-1786000554778_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Purbaya Bakal Salurkan Rp 20 T Bantu Pemda Bayar Gaji ASN</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:27:17 +0700</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan akan segera menyalurkan Rp 20,5 triliun kepada 490 pemerintah daerah untuk menjaga stabilitas keuangan daerah.</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606970/purbaya-bakal-salurkan-rp-20-t-bantu-pemda-bayar-gaji-asn</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/toko-online-lega-pemerintah-tunda-pajak-final-05-persen-1785929270093_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Pamer Teknologi Penyimpanan Gas, Bisa Pangkas Impor-Hemat Devisa</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:18:48 +0700</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Ratusan peneliti Badan Riset dan Inovasi Nasional (BRIN) merapat ke Istana Kepresidenan, Jakarta Pusat.</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8606939/kepala-brin-pamer-teknologi-penyimpanan-gas-bisa-pangkas-impor-hemat-devisa</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kepala-brin-arif-satria-evadetikcom-1785997911603_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Pajak Toko Online Ditunda, Asosiasi e-Commerce Siap Ikuti Aturan</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:01:15 +0700</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Asosiasi E-commerce Indonesia (idEA) menanggapi keputusan pemerintah menunda penerapan pemungutan Pajak Penghasilan (PPh) Pasal 22 oleh marketplace.</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606898/pajak-toko-online-ditunda-asosiasi-e-commerce-siap-ikuti-aturan</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/24/ilustrasi-belanja-online-1771906901925_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Penjual Ikan Cupang Andalkan Live Streaming untuk Dongkrak Penjualan</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:00:13 +0700</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Andhika Prasetia</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Bisnis ikan cupang beradaptasi dengan pemasaran digital melalui live streaming. Strategi ini membantu menjaga penjualan di tengah perubahan tren pasar.</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8606596/penjual-ikan-cupang-andalkan-live-streaming-untuk-dongkrak-penjualan</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/penjual-ikan-cupang-andalkan-live-streaming-untuk-dongkrak-penjualan-1785989845605_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Mo Salah Pindah ke Turki, Diejek Bos Klub Arab Saudi</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:20:15 +0700</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Okdwitya Karina Sari</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Mohamed Salah segera diresmikan sebagai pemain baru klub Turki, Trabzonspor. Bos Al Kholood, Ben Harburg, mengejek kepindahan Mo Salah itu.</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606774/mo-salah-pindah-ke-turki-diejek-bos-klub-arab-saudi</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mohamed-salah-tiba-di-turki-siap-gabung-trabzonspor-1785933827411_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Alasan dan Penyebab Ruang Bahagia Cabut Gugatan terhadap Pemkot Solo</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:42:37 +0700</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Dalam sidang ini, pihak penggugat melalui kuasa hukumnya Asy' Adi Rouf kembali memohon untuk mencabut gugatan.</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/144210978/alasan-dan-penyebab-ruang-bahagia-cabut-gugatan-terhadap-pemkot-solo</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/UCkPHDXydNdPh5ppo5H-rM6uBrY=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/22/6a60ec53669f6.jpg</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Latihan di Beijing, Kunci Sukses Operasi Jantung LVAD Tanpa Perdarahan</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:42:37 +0700</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Tim dokter RSCM sempat terbang ke Beijing dan berlatih pada jantung babi sebelum sukses memasang LVAD tanpa perdarahan.</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>https://health.kompas.com/read/26H06142900268/latihan-di-beijing-kunci-sukses-operasi-jantung-lvad-tanpa-perdarahan</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/7eZpjBt-SmtKmcjwpV0fmldWL6w=/0x0:1280x853/1200x675/filters:watermark(data/photo/2026/01/30/697c819f9c086.png,0,-0,1)/data/photo/2026/08/05/6a7341b04fde6.jpeg</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Duduk Perkara Sekda Konawe Selatan Jadi Tersangka: Sempat Digerebek, Adik Terluka</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:42:38 +0700</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Duduk perkara Sekda Konawe Selatan jadi tersangka usai penggerebekan. Polisi ungkap kronologi insiden yang membuat adiknya terluka.</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/141358778/duduk-perkara-sekda-konawe-selatan-jadi-tersangka-sempat-digerebek-adik</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/wVZMC3im5NaV2QYn6qjXdAVk_p8=/217x34:1466x659/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a728e8559478.png</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I376"/>
+  <autoFilter ref="A1:I389"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$389</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$486</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I389"/>
+  <dimension ref="A1:I486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18715,8 +18715,4567 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Timnas 3x3 putri tampil di Singapore Series untuk persiapan AG 2026</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:50:13 +0700</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Timnas bola basket 3x3 putri Indonesia bersiap tampil untuk mengikuti FIBA 3x3 Women's Series Singapura 2026 pada ...</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682527/timnas-3x3-putri-tampil-di-singapore-series-untuk-persiapan-ag-2026</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/04/1000368703.jpg</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Polres Lumajang buat sekat bakar antisipasi karhutla TNBTS meluas</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:49:33 +0700</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Kepolisian Resor (Polres) Lumajang membuat sekat bakar darurat untuk mengantisipasi kebakaran hutan dan lahan ...</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682525/polres-lumajang-buat-sekat-bakar-antisipasi-karhutla-tnbts-meluas</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-15.20.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Undian Kejuaraan Dunia 2026: Alwi Farhan berpotensi jumpa Shi Yu Qi</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:47:33 +0700</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Tunggal putra Indonesia Alwi Farhan berpotensi menghadapi unggulan pertama sekaligus juara bertahan asal China Shi Yu ...</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682524/undian-kejuaraan-dunia-2026-alwi-farhan-berpotensi-jumpa-shi-yu-qi</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/22/alwi-farhan-china-open.jpeg</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Konsultan: Eropa minati properti residensial dan komersial Indonesia</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:46:15 +0700</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Konsultan properti Knight Frank Indonesia menilai para pelaku usaha dari Uni Eropa atau EU meminati properti ...</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682523/konsultan-eropa-minati-properti-residensial-dan-komersial-indonesia</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1035.jpg</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Wapres Gibran tinjau langsung perkembangan pemulihan pascabencana di Aceh</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:43:51 +0700</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Wakil Presiden Gibran Rakabuming Raka mendengar penjelasan dari petugas Kementerian PU terkait pembangunan jembatan ...</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5682521/wapres-gibran-tinjau-langsung-perkembangan-pemulihan-pascabencana-di-aceh</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Kunker-Wapres-Gibran-ke-Aceh-060826-Rmd-4.jpg</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Korsel izinkan hak cipta untuk lagu yang dibuat dengan bantuan AI</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:43:34 +0700</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Korea Selatan akan mengizinkan pencipta untuk mendaftarkan hak cipta atas lagu yang dibuat dengan bantuan AI, asalkan ...</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682519/korsel-izinkan-hak-cipta-untuk-lagu-yang-dibuat-dengan-bantuan-ai</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/27/Bendera-Korea-Selatan_1.jpg</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Ketidakseimbangan bakteri baik usus picu gangguan perilaku anak</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:42:57 +0700</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Direktur Medical and Scientific Affairs, Danone Indonesia Dr. dr. Ray Wagiu Basrowi, MKK, FRSPH menyampaikan bahwa ...</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682515/ketidakseimbangan-bakteri-baik-usus-picu-gangguan-perilaku-anak</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/963bf01c-2c38-4cc2-914d-f1f457781e4e.jpeg</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ESDM catat tambahan PNBP Rp20,98 miliar dari penegakan hukum</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:38:28 +0700</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Kementerian Energi dan Sumber Daya Mineral (ESDM) mencatat penambahan Penerimaan Negara Bukan Pajak (PNBP) sebesar ...</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682512/esdm-catat-tambahan-pnbp-rp2098-miliar-dari-penegakan-hukum</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/realisasi-devisa-ekspor-batu-bara-2825587.jpg</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Kepala BGN: 1.700 SPPG di daerah stunting tinggi siap beroperasi</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:38:15 +0700</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menyebut 1.700 Satuan Pelayanan Pemenuhan Gizi (SPPG) di daerah dengan angka ...</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682508/kepala-bgn-1700-sppg-di-daerah-stunting-tinggi-siap-beroperasi</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/195031.jpg</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Bareskrim asistensi kasus penyelundupan 50 ton pasir timah di Belitung</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:32:33 +0700</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Direktorat Tindak Pidana Tertentu (Dittipidter) Bareskrim Polri menyatakan pihaknya akan mengasistensi penanganan kasus ...</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682507/bareskrim-asistensi-kasus-penyelundupan-50-ton-pasir-timah-di-belitung</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000087351.jpg</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Bappenas-Kemenbud kolaborasi kembangkan talenta seni budaya Indonesia</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:32:02 +0700</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Kementerian Perencanaan Pembangunan Nasional (PPN)/Badan Perencanaan Pembangunan Nasional (Bappenas) berkolaborasi ...</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682503/bappenas-kemenbud-kolaborasi-kembangkan-talenta-seni-budaya-indonesia</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-09.15.14-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Pemerintah luncurkan Satu Data ZIS-DSKL perkuat integrasi data zakat</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:29:53 +0700</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Pemerintah melalui Kementerian Perencanaan Pembangunan Nasional/Badan Perencanaan Pembangunan Nasional (PPN/Bappenas), ...</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682495/pemerintah-luncurkan-satu-data-zis-dskl-perkuat-integrasi-data-zakat</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000176881.jpg</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Kemensos tangguhkan 1,49 juta penerima bansos terindikasi judi online</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:29:38 +0700</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial menangguhkan sebanyak 1.494.652 Keluarga Penerima Manfaat (KPM) Program Sembako yang terindikasi ...</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682491/kemensos-tangguhkan-149-juta-penerima-bansos-terindikasi-judi-online</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0004_1.jpg</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Zulhas: Ponpes dengan 1.000 lebih siswa asrama bisa bangun dapur MBG</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:28:46 +0700</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Pangan Zulkifli Hasan (Zulhas) mengatakan pemerintah mengizinkan pondok pesantren (ponpes) ...</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682488/zulhas-ponpes-dengan-1000-lebih-siswa-asrama-bisa-bangun-dapur-mbg</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1E58581C-EB92-45A1-8253-849D0457835A.jpeg</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Menlu kawasan Pasifik berkumpul di Fiji jelang KTT</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:25:48 +0700</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Para menteri luar negeri dari 18 negara anggota Forum Kepulauan Pasifik (Pacific Islands Forum/PIF) berkumpul di Fiji ...</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682484/menlu-kawasan-pasifik-berkumpul-di-fiji-jelang-ktt</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2017/07/20170714pasifik.jpg</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>KemenHAM susun Perpres kepatuhan pelaku usaha dan HAM</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:25:14 +0700</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Kementerian Hak Asasi Manusia (KemenHAM) menyusun Rancangan Peraturan Presiden tentang Penilaian Kepatuhan Pelaku Usaha ...</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682483/kemenham-susun-perpres-kepatuhan-pelaku-usaha-dan-ham</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001221960.jpg</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>PSSI dukung penuh Gianni Infantino lanjutkan kepemimpinan di FIFA</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:24:56 +0700</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Persatuan Sepak Bola Seluruh Indonesia (PSSI) memberikan dukungan penuh terhadap Gianni Infantino untuk melanjutkan ...</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682481/pssi-dukung-penuh-gianni-infantino-lanjutkan-kepemimpinan-di-fifa</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/12/1000282681.jpg</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Legislator minta Polri semakin masif tindak judol pascatemuan PPATK</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Anggota Komisi III DPR RI Abdullah meminta Polri semakin masif menindak pelaku judi daring (judol) usai Pusat Pelaporan ...</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682480/legislator-minta-polri-semakin-masif-tindak-judol-pascatemuan-ppatk</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/09/Anggota_Komisi_III_DPR_RI_Abdullah_Foto_Dep_Alma20260409135732.jpeg</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Propam Jambi selidiki dugaan penipuan rekrutmen Polri Rp7,81 miliar</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:18:39 +0700</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Bidang Profesi dan Pengamanan (Bidpropam) Polda Jambi menyelidiki dugaan penipuan dalam rekrutmen Bintara Polri Tahun ...</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682479/propam-jambi-selidiki-dugaan-penipuan-rekrutmen-polri-rp781-miliar</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/369945.jpg</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Sri Mulyani Indrawati kembali duduki jabatan di Bank Dunia</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:17:29 +0700</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Bank Dunia menunjuk mantan Menteri Keuangan RI Sri Mulyani Indrawati sebagai Ketua Independen Asosiasi Pengembangan ...</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682473/sri-mulyani-indrawati-kembali-duduki-jabatan-di-bank-dunia</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/26/foto-terbaik-2025-2696596.jpg</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Kedubes Prancis resmikan Residensi Rimbaud perkuat pertukaran penulis</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:15:26 +0700</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Kedutaan Besar Prancis di Indonesia meluncurkan Residensi Rimbaud, program residensi sastra bilateral resiprokal ...</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682472/kedubes-prancis-resmikan-residensi-rimbaud-perkuat-pertukaran-penulis</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/28/Prancis.jpg</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Kemensos salurkan bansos triwulan III: PKH 7 juta KPM sembako 12 juta</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:10:44 +0700</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial mengakselerasi penyaluran bantuan sosial (bansos) Program Keluarga Harapan (PKH) dan Bantuan Pangan ...</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682471/kemensos-salurkan-bansos-triwulan-iii-pkh-7-juta-kpm-sembako-12-juta</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0004_1.jpg</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Nikita Bier resmi tinggalkan jabatan Kepala Produk di X</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:08:44 +0700</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Platform jejaring sosial, X, kembali harus kehilangan sosok pimpinan karena Nikita Bier yang sebelumnya dipercaya ...</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682468/nikita-bier-resmi-tinggalkan-jabatan-kepala-produk-di-x</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/07/30/WhatsApp-Image-2023-07-30-at-13.56.35.jpeg</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Prabowo terima paparan 15 stan riset unggulan BRIN</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:08:23 +0700</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menerima paparan hasil riset strategis Badan Riset dan Inovasi Nasional (BRIN) yang ...</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682465/prabowo-terima-paparan-15-stan-riset-unggulan-brin</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/IMG_3564.jpeg</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Wapres tinjau pemulihan infrastruktur pascabencana pembangunan di Aceh</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:06:27 +0700</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Wakil Presiden (Wapres) Gibran Rakabuming meninjau proses pemulihan infrastruktur dan layanan dasar pascabencana di ...</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682463/wapres-tinjau-pemulihan-infrastruktur-pascabencana-pembangunan-di-aceh</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/wapres-6.jpeg</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>DPR: Bantuan Rp20,5 triliun jaga fiskal 490 pemerintah daerah</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:00:03 +0700</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Anggota Komisi II DPR RI Rycko Menoza menyatakan rencana alokasi bantuan sebesar Rp20,5 triliun kepada 490 pemerintah ...</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682461/dpr-bantuan-rp205-triliun-jaga-fiskal-490-pemerintah-daerah</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/658f46bf-b25d-4563-90a3-9afd4efea3c6.jpeg</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Festival Raimuti 2026 di Manokwari</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:56:24 +0700</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Peserta mengikuti lomba perahu pada Festival Raimuti 2026 di Dermaga H Rahman Mansim, Manokwari, Papua Barat, Kamis ...</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5682457/festival-raimuti-2026-di-manokwari</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Festival-Raimuti-2026-di-Manokwari-682026-ci-4.jpg</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Presiden Iran sebut komunikasi dengan Motjaba Khamenei sangat sulit</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:55:25 +0700</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Presiden Iran Masoud Pezeshkian pada Rabu mengatakan bahwa komunikasi dengan Pemimpin Tertinggi Iran, Mojtaba Khamenei, ...</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682453/presiden-iran-sebut-komunikasi-dengan-motjaba-khamenei-sangat-sulit</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/thumbs_b_c_ed45147544be714dcdaa6c8ff91040f9.jpg</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Presiden Myanmar kunjungi Thailand guna peroleh legitimasi politik</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:53:41 +0700</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Presiden Myanmar Min Aung Hlaing pada Kamis melakukan kunjungan resmi ke Thailand selama dua hari, dan menurut pihak ...</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682449/presiden-myanmar-kunjungi-thailand-guna-peroleh-legitimasi-politik</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/10/XxjpbeE000254_20260410_PEPFN0A001A.jpg</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Toyota arahkan TEY-14 hasilkan aksi nyata dukung dekarbonisasi RI</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:53:05 +0700</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Toyota Indonesia mengarahkan penyelenggaraan Toyota Eco Youth (TEY) ke-14 tidak lagi sekadar menjadi kompetisi inovasi ...</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682447/toyota-arahkan-tey-14-hasilkan-aksi-nyata-dukung-dekarbonisasi-ri</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000177905.jpg</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Menpora inginkan muaythai Indonesia kejar emas di SEA Games 2027</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:48:41 +0700</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Menteri Pemuda dan Olahraga Erick Thohir menginginkan cabang olahraga muaythai Indonesia mampu meraih medali emas pada ...</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682445/menpora-inginkan-muaythai-indonesia-kejar-emas-di-sea-games-2027</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/17140b43-667b-44fd-916f-73ea39b039f1.jpeg</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Kejati pastikan tempuh banding terkait vonis bebas tiga anggota dewan</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:46:53 +0700</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Juru Bicara Kejaksaan Tinggi Nusa Tenggara Barat Harun Al Rasyid memastikan jaksa penuntut umum akan menempuh upaya ...</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682441/kejati-pastikan-tempuh-banding-terkait-vonis-bebas-tiga-anggota-dewan</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/sidang-putusan-gratifikasi-dprd-ntb.jpg</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Legislator: Identitas tunggal penting wujudkan pemilu berkualitas</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:44:28 +0700</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Anggota DPR RI Rycko Menoza mengatakan penerapan sistem identitas tunggal (single identity) menjadi salah satu langkah ...</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682439/legislator-identitas-tunggal-penting-wujudkan-pemilu-berkualitas</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/PHOTO-2026-08-06-11-21-27.jpg</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Bulog DKI-Banten masifkan pendistribusian beras premium ke toko retail</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:44:05 +0700</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Perusahaan Umum (Perum) Badan Urusan Logistik (Bulog) Kanwil DKI Jakarta dan Banten memasifkan pendistribusian ...</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682435/bulog-dki-banten-masifkan-pendistribusian-beras-premium-ke-toko-retail</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-13.33.24.jpeg</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen: Revitalisasi tembus pulau terluar setelah 21 tahun</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:43:15 +0700</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Dasar dan Menengah (Kemendikdasmen) berhasil memperbaiki sarana dan prasarana layanan pendidikan ...</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682433/kemendikdasmen-revitalisasi-tembus-pulau-terluar-setelah-21-tahun</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000228793.jpg</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Jatim jajaki kerja sama industri-teknologi dengan perkapalan Tiongkok</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:42:53 +0700</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jawa Timur menjajaki kerja sama sektor industri dan teknologi perkapalan dengan Republik Rakyat ...</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682429/jatim-jajaki-kerja-sama-industri-teknologi-dengan-perkapalan-tiongkok</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1329502.jpg</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Bareskrim respons kabar Anton Timbang hadiri pertemuan di Istana</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:42:14 +0700</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Direktorat Tindak Pidana Tertentu (Dittipidter) Bareskrim Polri merespons kabar tersangka kasus dugaan tersangka ...</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682425/bareskrim-respons-kabar-anton-timbang-hadiri-pertemuan-di-istana</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000087344.jpg</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Pertumbuhan pasar asuransi energi didorong ekspansi proyek migas</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:41:36 +0700</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>PT Asuransi Tugu Pratama Indonesia (Tugu Insurance) mencatat pasar asuransi energi nasional mengalami pertumbuhan ...</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682421/pertumbuhan-pasar-asuransi-energi-didorong-ekspansi-proyek-migas</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000454785.jpg</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>UOB Perkuat Bisnis Wealth Management melalui Kemitraan Distribusi Strategis dengan Allianz Global Investors</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:41:14 +0700</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>UOB Group menjalin kemitraan strategis dengan Allianz Global Investors (AGI). Melalui kemitraan ini, AGI akan ...</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682419/uob-perkuat-bisnis-wealth-management-melalui-kemitraan-distribusi-strategis-dengan-allianz-global-investors</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/UOB-x-Allianz-Global-Investors.jpg</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Disnakertrans Cianjur: Penempatan pekerja migran tekan pengangguran</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:41:09 +0700</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Dinas Tenaga Kerja dan Transmigrasi (Disnakertrans) Kabupaten Cianjur, Jawa Barat, mencatat program penempatan pekerja ...</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682415/disnakertrans-cianjur-penempatan-pekerja-migran-tekan-pengangguran</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/deni-ls.jpg</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Mendukbangga tinjau keluarga berisiko stunting di Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:36:17 +0700</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Menteri Kependudukan dan Pembangunan Keluarga (Mendukbangga) Republik Indonesia, Wihaji meninjau Keluarga Berisiko ...</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682411/mendukbangga-tinjau-keluarga-berisiko-stunting-di-pangkalpinang</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/mendukbangga3.jpg</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>WFP peringatkan El Nino berisiko perparah kerawanan pangan di Afrika</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:35:55 +0700</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Program Pangan Dunia (WFP) PBB pada Selasa (4/8) memperingatkan bahwa lebih dari 18 juta orang di seluruh Afrika Timur ...</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682408/wfp-peringatkan-el-nino-berisiko-perparah-kerawanan-pangan-di-afrika</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/07/24/XY37QCAE5VJUZO33FXDBHJYIO4_1.jpg</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Menbud sebut tradisi lisan bagian dari program pemajuan kebudayaan</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:32:42 +0700</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Menteri Kebudayaan Fadli Zon mengatakan bahwa tradisi lisan merupakan salah satu dari sepuluh obyek dari program ...</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682405/menbud-sebut-tradisi-lisan-bagian-dari-program-pemajuan-kebudayaan</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/05/Dongeng-akhir-pekan-untuk-mengisi-libur-sekolah-di-Bogor-050726-Arf-1.jpg</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Pemerintah fokus tingkatkan investasi dan pariwisata di Q3-2026</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:32:07 +0700</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator (Menko) Bidang Perekonomian Airlangga Hartarto mengatakan pemerintah fokus untuk meningkatkan ...</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682404/pemerintah-fokus-tingkatkan-investasi-dan-pariwisata-di-q3-2026</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0441.jpeg</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Pemprov Maluku percepat penetapan kompensasi Blok Masela</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:29:20 +0700</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Maluku mempercepat penilaian dan penetapan kompensasi bagi masyarakat terdampak Proyek Strategis ...</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682403/pemprov-maluku-percepat-penetapan-kompensasi-blok-masela</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-10.29.25.jpeg</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Disbudpar Cianjur: Realisasi PAD sektor pariwisata capai 61 persen</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:28:51 +0700</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Dinas Kebudayaan dan Pariwisata (Disbudpar) Kabupaten Cianjur, Jawa Barat, mencatat realisasi Pendapatan Asli Daerah ...</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682399/disbudpar-cianjur-realisasi-pad-sektor-pariwisata-capai-61-persen</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/kadis-yudha.jpg</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>BRIN buat inovasi sepatu lokal harga Rp75 Ribu untuk Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:27:10 +0700</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) mengembangkan inovasi sepatu berbahan karet produksi lokal yang dibanderol ...</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682395/brin-buat-inovasi-sepatu-lokal-harga-rp75-ribu-untuk-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034744.jpg</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>BRIN paparkan teknologi alternatif pengganti LPG ke Prabowo</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:27:02 +0700</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) akan memaparkan teknologi adsorbed natural gas (ANG) sebagai salah satu ...</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682392/brin-paparkan-teknologi-alternatif-pengganti-lpg-ke-prabowo</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034746.jpg</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Ma'ruf Amin luncurkan buku dihadiri sejumlah bakal calon Ketum PBNU</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Wakil Presiden ke-13 RI Ma’ruf Amin meluncurkan buku berjudul Fikroh, Manhaj, dan Harakah Nahdhiyyah dalam ...</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682384/maruf-amin-luncurkan-buku-dihadiri-sejumlah-bakal-calon-ketum-pbnu</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000176845.jpg</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Kepala BGN Ungkap Penyebab Keracunan MBG di Papua: Masaknya Kecepetan</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:57:00 +0700</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengungkap penyebab banyaknya kasus keracunan dari program Makan Bergizi Gratis (MBG) di Papua.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607145/kepala-bgn-ungkap-penyebab-keracunan-mbg-di-papua-masaknya-kecepetan</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kepala-badan-gizi-nasional-bgn-1786006514265_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Peserta Sidang Tahunan MPR 2026 Bakal Pakai PSL, Bukan Baju Adat</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:51:08 +0700</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Eddy Soeparno mengungkapkan peserta sidang tahunan 2026 akan mengenakan pakaian sipil lengkap (PSL). Sidang digelar 14 Agustus.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607138/peserta-sidang-tahunan-mpr-2026-bakal-pakai-psl-bukan-baju-adat</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/15/momen-pidato-perdana-prabowo-di-sidang-tahunan-mpr-1755233887571_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>MPR Kaji 3 Opsi Payung Hukum PPHN, Lewat Amandemen UUD atau Tap MPR</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:48:12 +0700</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Eddy Soeparno mengungkapkan tiga opsi hukum untuk menetapkan PPHN. Termasuk amendemen UUD, TAP MPR, atau pembuatan undang-undang.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607133/mpr-kaji-3-opsi-payung-hukum-pphn-lewat-amandemen-uud-atau-tap-mpr</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/eddy-soeparno-1786005656335_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Polisi Sisir Kali Licin Cari Potongan Kaki Korban Mutilasi di Depok</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:48:01 +0700</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Tim Resmob Polda Metro Jaya mencari potongan kaki korban mutilasi di Kali Licin, Depok. Tersangka Saepul mengaku membuangnya di lokasi tersebut.</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607132/polisi-sisir-kali-licin-cari-potongan-kaki-korban-mutilasi-di-depok</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polisi-sisir-kali-licin-depok-mencari-potongan-kaki-korban-mutilasi-1786006025311_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>BRIN Pamerkan Robot hingga Kendaraan Otonom, Mensesneg: Tanda Indonesia Mampu</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menerima audiensi para peneliti dari Badan Riset dan Inovasi Nasional (BRIN) di Istana.</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607106/brin-pamerkan-robot-hingga-kendaraan-otonom-mensesneg-tanda-indonesia-mampu</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/brin-pamerkan-sejumlah-produk-di-istana-evadetikcom-1786005595142_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Lomba Foto LRT Hadirkan Hadiah Menarik, Ini Syaratnya</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:33:09 +0700</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>LRT Jabodebek menggelar Lomba Foto dengan hadiah menarik. Peserta dapat mengirimkan foto sesuai tema dan syarat yang ditentukan. Ikuti dan menangkan!</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607096/lomba-foto-lrt-hadirkan-hadiah-menarik-ini-syaratnya</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/lrt-jabodebek-1786005153603_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Mensesneg: Tak Ada Surpres Pergantian Kapolri</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:31:07 +0700</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi menegaskan tidak ada surat presiden (surpres) terkait pergantian Kapolri Jenderal Listyo Sigit Prabowo.</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607089/mensesneg-tak-ada-surpres-pergantian-kapolri</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/mensesneg-prasetyo-hadi-1784627991634_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Demo Selesai, Sopir Angkot M44 Kembali Beroperasi dari Stasiun Tebet</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Sopir mikrolet M44 selesai demo di Balai Kota DKI Jakarta dan kembali beroperasi. Mereka menuntut evaluasi trayek JakLingko 48A yang berdampak pada pendapatan.</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607086/demo-selesai-sopir-angkot-m44-kembali-beroperasi-dari-stasiun-tebet</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sopir-angkot-m44-kembali-beroperasi-dari-stasiun-tebet-usai-demo-1786004988741_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Disparekraf DKI Dorong Sport Tourism Lewat Jakarta Watersport Festival</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:27:09 +0700</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Jakarta Watersport Festival di Danau Sunter hadirkan olahraga air, hiburan, dan edukasi. Festival ini dorong kunjungan wisatawan dan dukung UMKM.</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607082/disparekraf-dki-dorong-sport-tourism-lewat-jakarta-watersport-festival</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/disparekraf-dki-dorong-sport-tourism-lewat-jakarta-watersport-festival-1786004753222_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Polisi Cokok 2 Pengedar di Jakbar, Sita Ribuan Tramadol hingga Vape Narkoba</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:26:29 +0700</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Polsek Kembangan menangkap dua pengedar narkoba, RRF dan MS, di Cengkareng dan Grogol Petamburan. Barang bukti termasuk sabu dan vape berisi etomidate.</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607081/polisi-cokok-2-pengedar-di-jakbar-sita-ribuan-tramadol-hingga-vape-narkoba</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polsek-kembangan-menangkap-dua-pengedar-narkoba-menyita-ribuan-tramadol-hingga-vape-etomidate-dan-sabu-1786004767626_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>DLH Siapkan Sanksi Perusahaan yang Diduga Bikin Air Kali Bekasi Hitam Bak Oli</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:25:21 +0700</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>DLH Kabupaten Bogor menyiapkan sanksi ke sejumlah perusahaan yang diduga membuat Kali Bekasi tercemar.</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607080/dlh-siapkan-sanksi-perusahaan-yang-diduga-bikin-air-kali-bekasi-hitam-bak-oli</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/video-air-kali-bekasi-berwarna-hitam-mirip-oli-bekas-viral-di-media-sosial-medsos-kualitas-air-tersebut-menurun-karena-ada-dug-1785929406139_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>22 Penumpang Ditolak Masuk Pesawat di Thailand Gegara Kejar Seleb</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:23:40 +0700</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Sebanyak 22 penumpang asal China dilarang masuk ke dalam pesawat maskapai Thai Airways menyusul insiden di Bandara Suvarnabhumi, Thailand.</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8607077/22-penumpang-ditolak-masuk-pesawat-di-thailand-gegara-kejar-seleb</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ilustrasi-bandara-suvarnabhumi-1786004576201_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Kepala BGN Luruskan soal 13 Ribu SPPG, Begini Penjelasannya</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:21:49 +0700</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono menepis narasi yang menyebut pihaknya seolah-olah segera membuka 13 ribu dapur baru. Sudaryono menyebut SPPG akan dirilis secara bertahap.</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607075/kepala-bgn-luruskan-soal-13-ribu-sppg-begini-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>BNN Tekankan Resiliensi Generasi Muda Hadapi Ancaman Narkotika</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:20:25 +0700</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Kepala BNN Suyudi Ario Seto menekankan pentingnya resiliensi generasi muda dalam menolak narkotika. Acara di UNMA membahas dampak penyalahgunaan narkoba.</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607072/bnn-tekankan-resiliensi-generasi-muda-hadapi-ancaman-narkotika</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bnn-1786004345632_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Polisi: Saepul Rencanakan Bunuh Pria di Depok demi Kuasai Harta Korban</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:16:26 +0700</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Saepul (26) ditangkap setelah membunuh dan memutilasi K (51) di Depok. Ia berencana mencuri motor korban. Terancam hukuman mati.</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607056/polisi-saepul-rencanakan-bunuh-pria-di-depok-demi-kuasai-harta-korban</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/polisi-mengecek-temuan-mayat-mutilasi-di-tanah-kosong-pancoran-mas-kota-depok-1785896612343_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Pemprov Jateng &amp;amp; Kaltim Jalin Kerja Sama, Potensi Ekonomi Capai Rp 20,2 T</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:12:26 +0700</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Jateng dan Kaltim jalin kerja sama dengan potensi ekonomi Rp 20,2 triliun. Fokus pada perdagangan, industri, dan proyek IKN untuk pembangunan berkelanjutan.</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/bangun-indonesia/d-8607044/pemprov-jateng-kaltim-jalin-kerja-sama-potensi-ekonomi-capai-rp-20-2-t</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pemprov-jateng-kaltim-jalin-kerja-sama-potensi-ekonomi-capai-rp-202-t-1786003912828_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>DPD Soroti Dinamika Pusat-Daerah Lewat Buku, Ini Pesan Muzani</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:12:24 +0700</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Fara Difa Alfeni</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Dedi Iskandar menyerahkan buku DPD RI di Tengah Dinamika Kedaerahan kepada Ketua MPR RI. Buku ini mengulas peran DPD RI dalam sistem ketatanegaraan.</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607043/dpd-soroti-dinamika-pusat-daerah-lewat-buku-ini-pesan-muzani</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/mpr-1786002762003_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Prabowo Rapat Bareng Panglima TNI, Bahas Progres Jembatan hingga Listrik Desa</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:06:16 +0700</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menggelar rapat dengan Panglima TNI Jenderal TNI Agus Subiyanto dan jajarannya.</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607029/prabowo-rapat-bareng-panglima-tni-bahas-progres-jembatan-hingga-listrik-desa</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/prabowo-rapat-dengan-jajaran-pimpinan-tni-dok-setkab-1786003558651_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Melawan Perampok Bersajam, Nasabah di Cibitung Terluka di Tangan</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:04:42 +0700</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Seorang nasabah bank di Cibitung menjadi korban perampokan bersenjata, kehilangan Rp 30 juta dan terluka. Polisi masih memburu pelaku dan menyelidiki kasus ini.</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607027/melawan-perampok-bersajam-nasabah-di-cibitung-terluka-di-tangan</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/02/23/267bfe58-78ed-42ba-bbc5-e2e07b1df3b1_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Penertiban Bangunan Liar di Tanah Abang Pulihkan Fungsi Drainase</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:00:35 +0700</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Ari Saputra</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Pemkot Jakarta Pusat menertibkan bangunan semi permanen di atas saluran air di Tanah Abang. Langkah ini untuk menata kawasan dan memulihkan fungsi drainase.</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/foto-news/d-8606815/penertiban-bangunan-liar-di-tanah-abang-pulihkan-fungsi-drainase</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/normalisasi-drainase-95-bangunan-di-atas-saluran-phb-ditertibkan-1785996772444.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Menko Zulhas dan BGN Fokus SPPG di 3T, Targetkan Selesai Minggu Ini</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:59:35 +0700</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Menko Pangan Zulkifli Hasan targetkan penyelesaian SPPG untuk makan bergizi gratis di daerah 3T, termasuk Papua, NTT, dan Maluku, dalam minggu ini.</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607020/menko-zulhas-dan-bgn-fokus-sppg-di-3t-targetkan-selesai-minggu-ini</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/menko-pangan-zulhas-hingga-kepala-bgn-sudaryono-menyampaikan-perkembangan-evaluasi-mbg-taufiqdetikcom-1786003142815_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Ahmad Muzani Pastikan MPR Matangkan Formulasi Hukum PPHN</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:53:42 +0700</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>MPR RI mematangkan Pokok-Pokok Haluan Negara (PPHN) sebagai pedoman nasional. Ahmad Muzani menekankan pentingnya konsensus untuk legitimasi PPHN.</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607003/ahmad-muzani-pastikan-mpr-matangkan-formulasi-hukum-pphn</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/mpr-1786002762084_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Kapolda Banten Ajak Warga Bikin Bak Tampung Air Hujan untuk Cadangan Kemarau</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:51:45 +0700</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Kapolda Banten Irjen Hengki mengusulkan pembangunan bak penampungan air hujan untuk atasi kekeringan.</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607000/kapolda-banten-ajak-warga-bikin-bak-tampung-air-hujan-untuk-cadangan-kemarau</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kapolda-banten-1786002601261_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Zulhas Umumkan Ponpes Boleh Bikin SPPG, Ini Kriteria dan Syaratnya</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:51:35 +0700</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Zulhas mengumumkan pondok pesantren (ponpes) boleh membangun dapur Satuan Pelayanan Pemenuhan Gizi (SPPG) program Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606999/zulhas-umumkan-ponpes-boleh-bikin-sppg-ini-kriteria-dan-syaratnya</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/jumpa-pers-mengenai-perbaikan-tata-kelola-program-makan-bergizi-gratis-taufiqdetikcom-1786002575542_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>BNN Hadiri Kuliah Umum Nasional di Universitas Majalengka</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:47:22 +0700</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>BNN menggelar Kuliah Umum di UNMA untuk tingkatkan literasi generasi muda terhadap ancaman narkotika. Fokus pada kesehatan dan karakter demi Indonesia Emas 2045</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606991/bnn-hadiri-kuliah-umum-nasional-di-universitas-majalengka</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bnn-1786002372782_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Penampakan Senjata Api di Sekolah Jaksel, Kini Diusut Polisi</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:46:28 +0700</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Penemuan senjata api di sekolah swasta Pondok Pinang, Jakarta Selatan, menggegerkan. Polisi sedang menyelidiki kepemilikan dan kronologi penemuan tersebut.</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606990/penampakan-senjata-api-di-sekolah-jaksel-kini-diusut-polisi</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-sejumlah-senjata-api-di-salah-satu-ruangan-yayasan-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786002238709_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Legislator Desak Usut Akar Masalah Terkait Nakes Diduga Hina Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:33:06 +0700</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Anggota DPR Edy Wuryanto menyoroti dugaan nakes menghina pasien BPJS. Ia meminta evaluasi pelayanan kesehatan dan etika komunikasi tenaga medis di media sosial.</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8606978/legislator-desak-usut-akar-masalah-terkait-nakes-diduga-hina-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/02/anggota-komisi-ix-dpr-ri-fraksi-pdip-edy-wuryanto-dok-istimewa-1746123691922_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XII DPR Dukung Perpres Atur Timah Masyarakat di Belitung</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:55:58 +0700</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XII DPR Bambang Patijaya mendukung Pemerintah Pusat untuk menerbitkan Perpres sebagai legalitas timah masyarakat di Pulau Belitung.</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607142/ketua-komisi-xii-dpr-dukung-perpres-atur-timah-masyarakat-di-belitung</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/03/04/ketua-komisi-xii-dpr-bambang-patijaya-1741099742550_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Penerima MBG Berpotensi Berkurang Imbas Temuan 6 Juta Data Ganda</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:51:48 +0700</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) mengungkapkan adanya potensi penurunan jumlah penerima program Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607140/penerima-mbg-berpotensi-berkurang-imbas-temuan-6-juta-data-ganda</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/kepala-bgn-sudaryono-1784715793188_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Danantara Dapat Tawaran Kempit Saham Bandara Madinah</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:48:45 +0700</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>CEO Danantara Rosan Roeslani mengatakan pihaknya mendapatkan tawaran besar dari pemerintah Arab Saudi.</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8607136/danantara-dapat-tawaran-kempit-saham-bandara-madinah</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/ilustrasi-kantor-danantara-1784212600266_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Menperin Ungkap Pembiayaan buat Startup Turun hingga Rp 6,09 Triliun</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:41:56 +0700</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Kementerian Perindustrian (Kemenperin) mencatat adanya penurunan pendanaan bagi startup nasional sepanjang tahun 2025.</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607095/menperin-ungkap-pembiayaan-buat-startup-turun-hingga-rp-6-09-triliun</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/menteri-perindustrian-menperin-agus-gumiwang-kartasasmita-1786005067652_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Bos BGN Luruskan Isu 13 Ribu Dapur MBG Segera Dibuka</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:37:13 +0700</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono meluruskan terkait kabar 13.000 Satuan Pelayanan Pemenuhan Gizi (SPPG) akan segera dibuka.</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607099/bos-bgn-luruskan-isu-13-ribu-dapur-mbg-segera-dibuka</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Kadin Minta Hilirisasi Jangan Cuma Jadi Mainan Konglomerat dan Asing</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:31:53 +0700</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Kadin Indonesia minta pemerintah beri ruang bagi pengusaha lokal dalam hilirisasi energi dan mineral.</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607092/kadin-minta-hilirisasi-jangan-cuma-jadi-mainan-konglomerat-dan-asing</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/15/pembangunan-pabrik-di-kek-batang-pacu-pertumbuhan-investasi-nasional-1776264402935_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Pembangunan Tol Laut Teluk Jakarta Diharapkan Percepat Arus Logistik Nasional</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:30:24 +0700</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Pradita Utama</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Pembangunan jalan akses pelabuhan di Teluk Jakarta ditargetkan mempercepat arus logistik sekaligus meningkatkan konektivitas pelabuhan. Begini progresnya.</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8607004/pembangunan-tol-laut-teluk-jakarta-diharapkan-percepat-arus-logistik-nasional</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pembangunan-tol-laut-teluk-jakarta-diharapkan-percepat-arus-logistik-nasional-1786001253115_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>RI Berpeluang Jadi Raja Industri Protein Asia Tenggara</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:06:53 +0700</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>RI Berpeluang Jadi Raja Industri Protein Asia Tenggara, Sebesar Ini Potensinya</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607030/ri-berpeluang-jadi-raja-industri-protein-asia-tenggara</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/04/09/meningkatnya-permintaan-telur-ayam-untuk-lebaran_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Janji Bulog Jaga Kualitas Beras Usai Dapat Margin Fee 7%</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:58:52 +0700</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Bulog memastikan tambahan margin tersebut akan dikembalikan kepada masyarakat melalui peningkatan kualitas pelayanan dan mutu beras.</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607018/janji-bulog-jaga-kualitas-beras-usai-dapat-margin-fee-7</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/29/bulog-tegaskan-tetap-serap-gabah-hasil-panen-petani-sepanjang-tahun-1782706837728_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Menanti Inklusifitas Angka Pertumbuhan Ekonomi</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:43:52 +0700</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>20detik Signature</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Apa strategi yang perlu disiapkan agar pertumbuhan itu lebih inklusif?</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606866/menanti-inklusifitas-angka-pertumbuhan-ekonomi</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/detiksore6-agustus-2026-1785998741725_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Pemerintah Selidiki Beras Fortifikasi Mahal, Klaim Gizi Bakal Diuji!</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:38:40 +0700</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Pemerintah mendalami peredaran beras fortifikasi yang dijual dengan harga jauh lebih tinggi dibandingkan beras medium dan premium.</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606982/pemerintah-selidiki-beras-fortifikasi-mahal-klaim-gizi-bakal-diuji</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/27/kenaikan-harga-beras-1756283170846_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Said Iqbal Ungkap Alasan Buruh Batal Demo di Agustus</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:28:40 +0700</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Presiden KSPI Said Iqbal memastikan tidak ada aksi buruh besar-besaran pada Agustus-September 2026.</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606831/said-iqbal-ungkap-alasan-buruh-batal-demo-di-agustus</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/15/buruh-demo-dpr-keluhkan-kecilnya-kenaikan-ump-1768461540644_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Singapura Vs Indonesia: Saatnya Garuda Menang di Kandang Singa</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:40:40 +0700</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia sedang sulit menang di kandang Timnas Singapura. Kini, Garuda harus memperbaiki catatan itu demi tiket ke semifinal Piala AFF 2026.</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606852/singapura-vs-indonesia-saatnya-garuda-menang-di-kandang-singa</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/12/23/singapura-vs-indonesia_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Lanny/Ester Awalnya Sering Tabrakan, Kini Siap Debut sebagai Pasangan Baru</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:30:35 +0700</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Mercy Raya</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Jelang debut sebagai pasangan ganda putri, Lanny Tria Mayasari dan Ester Nurumi Tri Wardoyo mengaku sempat sering bertabrakan saat latihan.</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8607069/lanny-ester-awalnya-sering-tabrakan-kini-siap-debut-sebagai-pasangan-baru</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/lanny-tria-mayasari-ester-nurumi-tri-wardoyo-1786004143150_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Gianni Infantino Masih Aman Posisinya Sebagai Presiden FIFA</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:20:35 +0700</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Gianni Infantino masih aman posisinya sebagai Presiden FIFA. Gianni percaya dirinya bisa lanjutkan periode keempat di pemilihan 2027 nanti.</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/bola-dunia/d-8606863/gianni-infantino-masih-aman-posisinya-sebagai-presiden-fifa</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/23/gianni-infantino-1784793685990.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Awas Menyesal Nanti Menyesal, Vinicius!</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:00:35 +0700</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Okdwitya Karina Sari</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Mantan bintang sekaligus direktur Real Madrid Predrag Mijatovic memperingatkan Vinicius Junior. Masa depan Vinicius lagi dipertanyakan menyusul rumor Arsenal.</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8606861/awas-menyesal-nanti-menyesal-vinicius</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/08/vinicius-junior-1775599794726_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Maraknya Tragedi Pesepakbola Tersambar Petir, Ada dari Indonesia</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:40:30 +0700</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Beberapa tahun terakhir, tercatat tragedi pesepakbola-pesepakbola di dunia yang meninggal dunia karena tersambar petir. Ada dari Indonesia juga.</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/gila-bola/d-8606782/maraknya-tragedi-pesepakbola-tersambar-petir-ada-dari-indonesia</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/04/ilustrasi-hujan-petir-1762239904688.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Bawa Nama Negara, Alwi Farhan Enggan Pilih-pilih Turnamen</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Mercy Raya</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Alwi Farhan menegaskan akan tampil maksimal di Kejuaraan Dunia, China Masters, dan Asian Games 2026. Ia tak mau pilih-pilih turnamen.</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/raket/d-8606909/bawa-nama-negara-alwi-farhan-enggan-pilih-pilih-turnamen</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/alwi-farhan-1784194208649_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Tugu Insurance Raup Laba Bersih Rp 480,29 Miliar, Naik 76,87 Persen Per Semester I 2026</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:04:02 +0700</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Sejalan dengan itu, laba per saham (EPS) tercatat sebesar Rp 135, meningkat dari Rp 76 pada semester I-2025.</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/06/160346326/tugu-insurance-raup-laba-bersih-rp-48029-miliar-naik-7687-persen-per-semester</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/mbhBt5LU72-ZhS7UoDUurNBCkBs=/14x0:671x438/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2025/11/01/6905f64557748.jpeg</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Penampakan Sepatu Lokal Rp 80.000 yang Mau Dipesan Prabowo</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:04:04 +0700</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Arif Satria pamer sepatu lokal BRIN di Istana. Sepatu ini terbuat dari karet, harga Rp 80.000, dan dipesan juga oleh Presiden Prabowo.</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/06/15505431/penampakan-sepatu-lokal-rp-80000-yang-mau-dipesan-prabowo</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RY8Sg6zLorYT1FJhOUh9l0lfYM4=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a744924700a2.jpg</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap Warga Cimahi Pembuat Video AI Manipulasi Gambar Presiden Prabowo, Sebar Konten Provokatif</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:04:05 +0700</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Polda Jabar tangkap FG, warga Cimahi, karena manipulasi gambar Presiden Prabowo Subianto pakai AI di medsos dengan narasi provokatif.</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/06/153446578/polisi-tangkap-warga-cimahi-pembuat-video-ai-manipulasi-gambar-presiden</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/2u3Px-Lvy1c23FTkxGzd77N4Gco=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a744125a1976.jpg</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I389"/>
+  <autoFilter ref="A1:I486"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$486</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$527</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I486"/>
+  <dimension ref="A1:I527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23274,8 +23274,1935 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Menaker ajak perguruan tinggi selaraskan kurikulum dengan industri</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:22:09 +0700</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli mengajak institusi pendidikan tinggi di seluruh Indonesia untuk semakin ...</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682591/menaker-ajak-perguruan-tinggi-selaraskan-kurikulum-dengan-industri</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_153622.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>OJK: Industri keuangan syariah bergerak ke arah yang lebih baik</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:21:27 +0700</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Komisioner Otoritas Jasa Keuangan (OJK) Friderica Widyasari Dewi mengatakan industri keuangan syariah ...</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682588/ojk-industri-keuangan-syariah-bergerak-ke-arah-yang-lebih-baik</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/22/bsi-3.jpg</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Gubernur Koster tetapkan lima kawasan rendah emisi di Bali</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:20:44 +0700</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Gubernur Bali Wayan Koster menetapkan proyek lima kawasan rendah emisi di Pulau Dewata yang tengah dipersiapkan sebagai ...</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682585/gubernur-koster-tetapkan-lima-kawasan-rendah-emisi-di-bali</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/70b440c1-582c-4718-a926-2d9a6b247016.jpeg</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Pemerintah monitor industri rentan PHK dan penciptaan lapangan kerja</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:20:20 +0700</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator (Menko) Bidang Perekonomian Airlangga Hartarto memastikan pemerintah terus memonitor ...</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682583/pemerintah-monitor-industri-rentan-phk-dan-penciptaan-lapangan-kerja</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0441.jpeg</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Uruguay sebut krisis Argentina-Brasil "kabar buruk" bagi Mercosur</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:16:33 +0700</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Menteri Luar Negeri Uruguay Mario Lubetkin pada Rabu (5/8) mengatakan bahwa krisis diplomatik antara Argentina dan ...</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682576/uruguay-sebut-krisis-argentina-brasil-kabar-buruk-bagi-mercosur</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2016/06/20160626Mercosur.jpg</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Mensesneg membantah isu Surpres penggantian Kapolri</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:15:03 +0700</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Menseneg) Prasetyo Hadi membantah isu mengenai penggantian Kapolri, dan ...</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682572/mensesneg-membantah-isu-surpres-penggantian-kapolri</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/sesneg.jpg</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Perkaya kualitas ajar, Menaker usul dosen cuti guna magang di industri</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:13:35 +0700</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli mengusulkan gagasan inovatif kepada pimpinan perguruan tinggi untuk ...</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682569/perkaya-kualitas-ajar-menaker-usul-dosen-cuti-guna-magang-di-industri</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_154922.jpg.jpeg</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Selandia Baru luncurkan mata pelajaran baru berbasis industri</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:13:02 +0700</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Selandia Baru pada Kamis (6/8) meluncurkan serangkaian mata pelajaran baru yang berbasis industri di tingkat sekolah ...</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682565/selandia-baru-luncurkan-mata-pelajaran-baru-berbasis-industri</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000020_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>TNBTS: "Drone water spray" dimaksimalkan tangani kebakaran di Bromo</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:13:01 +0700</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Balai Besar Taman Nasional Bromo Tengger Semeru (TNBTS) menyatakan pemadaman kebakaran di kawasan Gunung Bromo ...</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682561/tnbts-drone-water-spray-dimaksimalkan-tanganikebakaran-di-bromo</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001402670.jpg</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Gulkarmat Jakpus bentuk Redkar di Senen percepat penanganan kebakaran</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:12:50 +0700</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Suku Dinas Penanggulangan Kebakaran dan Penyelamatan (Gulkarmat) Jakarta Pusat membentuk Relawan Pemadam Kebakaran ...</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682560/gulkarmat-jakpus-bentuk-redkar-di-senen-percepat-penanganan-kebakaran</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/15/jakarta-fire-safety-challenge-2025-2623293.jpg</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>PBB sebut operasi militer Israel ganggu kehidupan warga sipil di Gaza</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:12:19 +0700</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Operasi militer Israel di Jalur Gaza mengganggu kehidupan warga sipil, merusak tempat penampungan, serta meningkatkan ...</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682559/pbb-sebut-operasi-militer-israel-ganggu-kehidupan-warga-sipil-di-gaza</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000004_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>JATAM gugat Gubernur Sulteng soal limbah tailing di PTUN</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:10:54 +0700</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Jaringan Advokasi Tambang (JATAM) Sulawesi Tengah menggugat Gubernur Sulawesi Tengah ke Pengadilan Tata Usaha Negara ...</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682555/jatam-gugat-gubernur-sulteng-soal-limbah-tailing-di-ptun</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-16.14.33.jpeg</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Prabowo terima laporan capaian program TNI dukung pembangunan</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:10:48 +0700</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menerima laporan perkembangan berbagai program strategis TNI yang mendukung pemerataan ...</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682553/prabowo-terima-laporan-capaian-program-tni-dukung-pembangunan</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034773.jpg</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Wuling pamer dua model PHEV di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:10:46 +0700</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Memanfaatkan pameran otomotif Gaikindo Indonesia International Auto Show (GIIAS) 2026, Wuling motor (Wuling) ...</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682551/wuling-pamer-dua-model-phev-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000503134.jpg</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Pemkot Jaktim gencarkan skrining TBC lewat CKG, sasar 77 ribu warga</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:08:29 +0700</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Timur mulai menggencarkan program skrining Tuberkulosis (TBC) yang terintegrasi ...</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682548/pemkot-jaktim-gencarkan-skrining-tbc-lewat-ckg-sasar-77-ribu-warga</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/InShot_20260806_153422556.jpg</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>IESR sebut Program PLTS 100 GW dukung pertumbuhan ekonomi</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:05:42 +0700</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Institute for Essential Services Reform (IESR) menyatakan program pembangunan pembangkit listrik tenaga surya (PLTS) ...</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682545/iesr-sebut-program-plts-100-gw-dukung-pertumbuhan-ekonomi</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_151807.jpg</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Pemprov Papua siap fasilitasi identifikasi jenazah korban PD II</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:05:33 +0700</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Papua menyatakan kesiapan memfasilitasi proses identifikasi kerangka jenazah korban ...</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682543/pemprov-papua-siap-fasilitasi-identifikasi-jenazah-korban-pd-ii</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1002069916.jpg</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Houthi klaim serangan rudal terhadap kapal minyak Saudi di Teluk Aden</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:05:28 +0700</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Kelompok Houthi Yaman pada Rabu (5/8) menyatakan telah menargetkan sebuah kapal tanker minyak Arab Saudi dengan rudal ...</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682541/houthi-klaim-serangan-rudal-terhadap-kapal-minyak-saudi-di-teluk-aden</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/28/ilustrasi-rudal-Iran.jpg</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>BP BUMN-Danantara kawal ketat transformasi PT Pos Indonesia</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:04:41 +0700</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>BP BUMN dan Danantara melakukan monitoring rutin sebagai upaya mengawal proses transformasi PT Pos Indonesia agar ...</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682540/bp-bumn-danantara-kawal-ketat-transformasi-pt-pos-indonesia</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/WhatsApp-Image-2026-07-29-at-16.12.46.jpeg</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Pemerintah Aceh gencarkan BIAS 2026, tingkatkan kekebalan komunitas</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:04:14 +0700</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Aceh mulai menggencarkan Bulan Imunisasi Anak Sekolah (BIAS) 2026 sepanjang Agustus. Penanggung ...</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682499/pemerintah-aceh-gencarkan-bias-2026-tingkatkan-kekebalan-komunitas</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-06-151427.jpg</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Kemenkes: 1 juta yang semula sehat terdeteksi hipertensi di CKG 2026</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:02:38 +0700</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan dalam Cek Kesehatan Gratis (CKG) 2026 mendeteksi sekitar satu juta kasus baru hipertensi dari ...</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682536/kemenkes-1-juta-yang-semula-sehat-terdeteksi-hipertensi-di-ckg-2026</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-19.09.09.jpeg</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Wamensos cek progres pembangunan SR Probolinggo hingga Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:02:01 +0700</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Sosial Agus Jabo mengecek progres pembangunan Sekolah Rakyat di Probolinggo, Kuantan Singingi, dan ...</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682535/wamensos-cek-progres-pembangunan-sr-probolinggo-hingga-polewali-mandar</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000176885.jpg</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Legenda bulu tangkis akui wilayah timur masih kurang turnamen</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:59:07 +0700</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Legenda bulu tangkis Indonesia Richard Mainaky mengatakan bibit atlet bulu tangkis di wilayah Timur Indonesia itu cukup ...</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682532/legenda-bulu-tangkis-akui-wilayah-timur-masih-kurang-turnamen</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/ImgResizer_Crop_1786005381193.jpg</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Kementerian PKP dan BPS perkuat data terkait bantuan perumahan</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Kementerian Perumahan dan Kawasan Permukiman (PKP) menggandeng Badan Pusat Statistik (BPS) untuk memperkuat tata ...</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682529/kementerian-pkp-dan-bps-perkuat-data-terkait-bantuan-perumahan</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1037.jpg</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Potongan Kaki Korban Mutilasi Dicari, Saepul Ikut Dibawa ke Kali</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:22:01 +0700</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Tim Resmob Polda Metro Jaya melakukan penyisiran di Kali Licin, Depok, untuk mencari potongan kaki korban mutilasi. Tersangka Saepul hadir di lokasi.</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607221/potongan-kaki-korban-mutilasi-dicari-saepul-ikut-dibawa-ke-kali</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polisi-melakukan-penyisiran-di-kali-licin-depok-untuk-mencari-potongan-kaki-korban-mutilasi-1786008041635_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Disdik Jaksel Siapkan Opsi PJJ Usai Kebakaran di SDN 04 Srengseng Sawah</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:15:59 +0700</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Sudindik Wilayah I Jaksel menyiapkan skema pembelajaran hybrid bagi siswa pascakebakaran di SDN 04 Srengseng Sawah. PJJ disiapkan bagi siswa yang trauma.</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607200/disdik-jaksel-siapkan-opsi-pjj-usai-kebakaran-di-sdn-04-srengseng-sawah</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sudindik-wilayah-i-jaksel-menyiapkan-skema-pembelajaran-hybrid-bagi-siswa-usai-kebakaran-yang-terjadi-di-sdn-04-srengseng-sawa-1786007697351_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Legislator Gerindra Dorong UMKM Palembang Lindungi Merek Usaha</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:12:23 +0700</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Partai Gerindra dorong UMKM Palembang untuk daftarkan merek dagang. Perlindungan hukum penting untuk daya saing dan keberlangsungan usaha.</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607184/legislator-gerindra-dorong-umkm-palembang-lindungi-merek-usaha</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/legislator-gerindra-kartika-sandra-desi-dorong-umkm-palembang-lindungi-merek-usaha-1786007525842.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Saksi Akui Tagihan PNBP Turun Rp 28 M Usai Beri Rp 1 M ke Eks Ketua Ombudsman</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:07:40 +0700</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Jaksa menghadirkan Tjia Peng Tjoan selaku Direktur PT Dinamika Sejahtera Mandiri sebagai saksi dalam sidang kasus suap mantan Ketua Ombudsman Hery Susanto.</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607168/saksi-akui-tagihan-pnbp-turun-rp-28-m-usai-beri-rp-1-m-ke-eks-ketua-ombudsman</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sidang-eks-ketua-ombudsman-muliadetikcom-1785991541340_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Wamendagri Bima Arya Dorong DPRD Wujudkan Pembangunan Berkeadilan Ekologis</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:06:13 +0700</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Wamendagri menekankan peran strategis DPRD dalam pembangunan berkeadilan ekologis. Legislator diharapkan optimalkan fungsi legislasi dan pengawasan.</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607165/wamendagri-bima-arya-dorong-dprd-wujudkan-pembangunan-berkeadilan-ekologis</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/wamendagri-bima-arya-dorong-dprd-wujudkan-pembangunan-berkeadilan-ekologis-1786007086451_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Polres OKI Genjot Kualitas Layanan Lewat Forum Konsultasi Publik Mandiri</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:05:18 +0700</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Polres OKI gelar Forum Konsultasi Publik 2026 untuk meningkatkan pelayanan publik. Kegiatan ini libatkan masyarakat &amp; berbagai elemen untuk evaluasi dan masukan</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/nyago-bumi-sriwijaya/d-8607162/polres-oki-genjot-kualitas-layanan-lewat-forum-konsultasi-publik-mandiri</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polda-sumsel-1786006975157.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Ketum TP PKK Ajak Pelajar Biak Kenali Potensi Bahari untuk Cintai Tanah Air</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:03:47 +0700</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Ketua TP PKK Tri Tito Karnavian ajak pelajar Biak cintai Tanah Air melalui pendidikan karakter dan potensi bahari. Dukung program pemerintah untuk pendidikan.</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607160/ketum-tp-pkk-ajak-pelajar-biak-kenali-potensi-bahari-untuk-cintai-tanah-air</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ketum-tp-pkk-ajak-pelajar-biak-kenali-potensi-bahari-untuk-cintai-tanah-air-1786007009183.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Korea Utara Tembakkan Proyektil Diduga Rudal Balistik, Jatuh ke Lautan</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:01:08 +0700</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Korut terdeteksi menembakkan proyektil tak teridentifikasi pada Kamis (6/8) waktu setempat. Proyektil itu jatuh ke lautan di sebelah timur Semenanjung Korea.</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8607152/korea-utara-tembakkan-proyektil-diduga-rudal-balistik-jatuh-ke-lautan</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/27/korut-mengklaim-sukses-menguji-coba-rudal-yang-membawa-banyak-hulu-ledak-sekaligus_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>MPR Kaji 3 Opsi Payung Hukum PPHN, Lewat Amendemen UUD atau Tap MPR</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:48:12 +0700</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Eddy Soeparno mengungkapkan tiga opsi hukum untuk menetapkan PPHN. Termasuk amendemen UUD, Tap MPR, atau pembuatan undang-undang.</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607133/mpr-kaji-3-opsi-payung-hukum-pphn-lewat-amendemen-uud-atau-tap-mpr</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/eddy-soeparno-1786005656335_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>337 Saham Turun, IHSG Ditutup Melemah ke 6.343</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:23:56 +0700</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) ditutup melemah pada perdagangan hari ini. Pada penutupan pasar, IHSG tercatat di level 6.300.</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8607228/337-saham-turun-ihsg-ditutup-melemah-ke-6-343</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/18/ihsg-anjlok-ke-zona-merah-bursa-saham-melemah-tajam-1779098741262_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Negara Raup Rp 20,9 M dari Lelang Batu Bara Sitaan</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:23:35 +0700</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM berhasil lelang 76.742 MT batu bara sitaan, menghasilkan PNBP Rp 20,9 miliar. Penegakan hukum dan pengelolaan aset negara diperkuat.</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607227/negara-raup-rp-20-9-m-dari-lelang-batu-bara-sitaan</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/realisasi-devisa-ekspor-batu-bara-1784643932277_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Startup RI Urutan 6 Terbanyak di Dunia, tapi Mutunya Peringkat 45</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:14:12 +0700</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Menteri Perindustrian (Menperin), Agus Gumiwang Kartasasmita, menyebut Indonesia menjadi negara dengan jumlah startup terbesar ke enam dunia.</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607187/startup-ri-urutan-6-terbanyak-di-dunia-tapi-mutunya-peringkat-45</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/08/ilustrasi-startup-atau-start-up_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Jembatan Kereta Api Jember Jalani Uji Beban Pascaperbaikan</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:00:45 +0700</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Tripa Ramadhan</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Jembatan kereta api di Jember jalani uji kekuatan usai perbaikan. Pengujian menggunakan dua lokomotif dilakukan untuk memastikan keselamatan perjalanan kereta.</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8606568/jembatan-kereta-api-jember-jalani-uji-beban-pascaperbaikan</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/jembatan-kereta-api-jember-jalani-uji-beban-pascaperbaikan-1785989027280_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Mo Salah Pergi, Siapa yang Serba Nomor 1 di Liverpool Nanti?</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:00:10 +0700</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Mohamed Salah dan Liverpool berpisah. Sejak kedatangan Salah, dirinya jadi pemain nomor 1 untuk urusan menjebol gawang lawan. Siapa yang bisa gantikannya?</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/foto-sepakbola/d-8606962/mo-salah-pergi-siapa-yang-serba-nomor-1-di-liverpool-nanti</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/mohamed-salah-1785943966122.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Viral Pengunjung Madiun Umbul Square Kecewa, Bayar Tiket Rp 20.000 Cuma Lihat Sedikit Satwa</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:34:46 +0700</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Video kekecewaan pengunjung Madiun Umbul Square viral karena bayar Rp 20.000 tapi lihat sedikit satwa. Ini kata Madiun Umbul Square dan BBKSDA Jatim</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/06/163415578/viral-pengunjung-madiun-umbul-square-kecewa-bayar-tiket-rp-20000-cuma-lihat</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/FRrWW69_C5OGEF4AD6DkUIqt4hs=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a743dbb0fd13.jpg</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Gubernur Kalsel Tagih Janji PLN Soal Pemadaman Listrik Berakhir Awal Agustus, Ternyata Molor</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:34:48 +0700</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Gubernur Kalsel menagih janji PLN terkait pemadaman listrik bergilir yang sebelumnya akan berakhir pada awal agustus. Ternyata molor.</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/161139378/gubernur-kalsel-tagih-janji-pln-soal-pemadaman-listrik-berakhir-awal</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/kq5cOLdimH3-4Pps8A5sESt7kFc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/04/09/69d6e042e82e0.jpeg</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Jadi Tersangka, Kabag Keuangan Setwan Ponorogo Diberhentikan Sementara dari PNS, Gaji 50 Persen</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:34:50 +0700</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Kabag Keuangan Setwan Ponorogo diberhentikan sementara dari statusnya sebagai PNS setelah ditetapkan menjadi tersangka korupsi</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/06/155645778/jadi-tersangka-kabag-keuangan-setwan-ponorogo-diberhentikan-sementara-dari</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/_gWtM5mJDhF_q9c6SCOILYLS7XE=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/05/6a73255eca5c8.jpg</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I486"/>
+  <autoFilter ref="A1:I527"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$527</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$612</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I527"/>
+  <dimension ref="A1:I612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -25201,8 +25201,4003 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Menperin: Penerima insentif EV untuk produk bernilai tambah tinggi</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:48:16 +0700</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Menteri Perindustrian (Menperin) Agus Gumiwang Kartasasmita menyatakan penerima insentif kendaraan listrik atau ...</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682667/menperin-penerima-insentif-ev-untuk-produk-bernilai-tambah-tinggi</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-16.27.54_edit_302164035168473.jpg</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Presiden undang 150 peneliti BRIN berdialog, unjuk inovasi di Istana</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:27:27 +0700</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto mengundang para peneliti dari Badan Riset dan Inovasi Nasional atau BRIN untuk ...</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682580/presiden-undang-150-peneliti-brin-berdialog-unjuk-inovasi-di-istana</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PRESIDEN-UNDANG-150-PENELITI-BRIN-BERDIALOG-UNJUK-INOVASI-DI-ISTANA_1.jpg</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Cara membersihkan noda kasur membandel dengan bahan alami</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:11:19 +0700</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Noda pada kasur seperti bekas keringat, ompol, makanan, hingga bercak membandel dapat mengganggu kenyamanan tidur jika ...</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682716/cara-membersihkan-noda-kasur-membandel-dengan-bahan-alami</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/10/12/pexels-teona-swift-6850588.jpg</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Kenali tanda dan cara ampuh mengendalikan kutu busuk rumah</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:40:41 +0700</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Kutu kasur atau kutu busuk menjadi salah satu masalah rumah tangga yang dapat mengganggu kenyamanan tidur. Serangga ...</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682648/kenali-tanda-dan-cara-ampuh-mengendalikan-kutu-busuk-rumah</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2013/08/20130825Vi-Spring-bed.jpg</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Bangun harmoni rumah tangga: Tips komunikasi dan kepercayaan</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:35:43 +0700</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Membangun rumah tangga yang harmonis dan bahagia menjadi impian hampir setiap pasangan. Namun, hubungan yang langgeng ...</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682639/bangun-harmoni-rumah-tangga-tips-komunikasi-dan-kepercayaan</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/11/Ilustrasi-Pasangan-memasak-bersama2-freepik.jpg</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Trump Ribut dengan Menhan AS, Merasa Disesatkan Soal Pasokan Amunisi</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:04:31 +0700</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Novi Christiastuti</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Trump dilaporkan berselisih dengan Menhan AS Pete Hegseth dalam rapat kabinet terbaru, karena dia merasa disesatkan mengenai pasokan amunisi AS.</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/internasional/d-8607340/trump-ribut-dengan-menhan-as-merasa-disesatkan-soal-pasokan-amunisi</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/trump-duduk-di-antara-menlu-as-marco-rubio-kiri-dan-menhan-as-pete-hegseth-kanan-saat-rapat-kabinet-di-camp-david-maryland-pad-1786010274849_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Kepala BGN Ungkap Temuan Data Ganda Penerima MBG, Bakal Lakukan Penyisiran</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:59:53 +0700</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono ungkap data ganda penerima Makan Bergizi Gratis. BGN akan melakukan penyisiran data penerima dan berpotensi berkurang hingga 6 juta orang.</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607330/kepala-bgn-ungkap-temuan-data-ganda-penerima-mbg-bakal-lakukan-penyisiran</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Wihaji Tinjau Keluarga Berisiko Stunting di Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:59:31 +0700</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>sls</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Wihaji Tinjau Keluarga Berisiko Stunting di Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/adv-nhl-detikcom/d-8607328/wihaji-tinjau-keluarga-berisiko-stunting-di-bangka-tengah</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/adv-1786010308779.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Sopir Angkot M44 Demo, Warga Ngeluh Antre Panjang Jaklingko di Stasiun Tebet</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:58:09 +0700</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Sopir mikrolet M44 mogok beroperasi akibat demo di Balai Kota, menyebabkan antrean Jaklingko di Stasiun Tebet semakin panjang.</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607316/sopir-angkot-m44-demo-warga-ngeluh-antre-panjang-jaklingko-di-stasiun-tebet</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/antrean-jaklingko-di-stasiun-tebet-jadi-lebih-panjang-gegara-sopir-angkot-m44-mogok-narik-adhfar-aulia-syuhadadetikcom-1786010263995_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Polisi Segera Rekonstruksi Kasus Wanita Dibunuh lalu Dibuang di Tol Bogor</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:57:58 +0700</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Kasus pembunuhan wanita di Bogor memasuki tahap baru. Berkas perkara diserahkan ke kejaksaan dan rekonstruksi segera digelar.</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607314/polisi-segera-rekonstruksi-kasus-wanita-dibunuh-lalu-dibuang-di-tol-bogor</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pelaku-pembunuhan-wanita-di-bogor-m-febryan-mf-alias-ambon-26-1786010231002_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Kapolda Riau Ajak Mahasiswa Jadi Pelopor Demokrasi Green Campaign</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:53:29 +0700</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Kapolda Riau Irjen Herry Heryawan mengajak mahasiswa jadi pelopor Green Campaign dan agen perubahan untuk mewujudkan pemilu ramah lingkungan.</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/melindungi-tuah-marwah/d-8607302/kapolda-riau-ajak-mahasiswa-jadi-pelopor-demokrasi-green-campaign</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kapolda-riau-irjen-pol-herry-heryawan-menghadiri-peluncuran-sekolah-pemilu-hijau-di-kpu-riau-1785999184908_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Kebakaran di Bromo Meluas hingga 51 Hektare, Ini Titik Awalnya</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:51:50 +0700</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Muhammad Aminudin</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda 51 hektare lahan di kawasan Taman Nasional Bromo Tengger Semeru. Balai Besar TNBTS mengungkap lokasi awal titik api.</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607279/kebakaran-di-bromo-meluas-hingga-51-hektare-ini-titik-awalnya</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/kebakaran-di-bromo-sulit-dipadamkan-1785919757064_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Selain Senpi, Ada Sabu-30 CD Porno di Ruang Eks Ketua Yayasan Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:48:20 +0700</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Ratusan senjata ditemukan di ruangan mantan ketua yayasan sekolah swasta di Jaksel. Selain senjata, ada narkoba hingga CD porno yang ditemukan di ruangan itu.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607275/selain-senpi-ada-sabu-30-cd-porno-di-ruang-eks-ketua-yayasan-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-sejumlah-senjata-api-di-salah-satu-ruangan-yayasan-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786002238709_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Marbut di Purwakarta Tewas Dibacok Tetangga Saat Hendak Azan</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:45:58 +0700</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Dian Firmansyah</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Pria berinisial AS, marbut Masjid Al-Muhajirin, tewas dibacok tetangga saat hendak azan. Polisi amankan senjata tajam sebagai barang bukti.</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607273/marbut-di-purwakarta-tewas-dibacok-tetangga-saat-hendak-azan</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/polisi-melakukan-olah-tkp-pembunuhan-marbot-di-purwakarta-kamis-682026-1786006580475_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Mendagri Lantik Pejabat Baru, Soroti Pentingnya Penyegaran Organisasi</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:32:22 +0700</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian melantik pejabat baru di Kemendagri untuk penyegaran organisasi. Dia berharap kinerja kementerian meningkat dengan sinergi pegawai.</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607242/mendagri-lantik-pejabat-baru-soroti-pentingnya-penyegaran-organisasi</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kemendagri-1786008555214_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Senjata di Sekolah Jaksel Ditemukan di Ruang Eks Ketua Yayasan, Jumlah Ratusan</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:32:17 +0700</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>995 pucuk senjata, termasuk senjata api dan amunisi, ditemukan di ruangan mantan ketua yayasan di salah satu sekolah di Jaksel. Polisi selidiki kasus ini.</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607241/senjata-di-sekolah-jaksel-ditemukan-di-ruang-eks-ketua-yayasan-jumlah-ratusan</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-sejumlah-senjata-api-di-salah-satu-ruangan-yayasan-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786002238709_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Menkop Lakukan Peletakan Batu Pertama Pembangunan KDKMP Dekai di Yahukimo</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:31:13 +0700</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Menkop Ferry Juliantono resmikan Koperasi Desa Merah Putih di Yahukimo. Koperasi ini diharapkan tingkatkan ekonomi lokal dan optimalkan potensi SDA.</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607240/menkop-lakukan-peletakan-batu-pertama-pembangunan-kdkmp-dekai-di-yahukimo</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/menkop-lakukan-peletakan-batu-pertama-pembangunan-kdkmp-dekai-di-yahukimo-1786008650427_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>BNN Ajak Mahasiswa Jadi Garda Terdepan Pencegahan Narkotika</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:30:49 +0700</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Kepala BNN Suyudi Ario Seto mengajak mahasiswa UNMA jadi garda terdepan pencegahan narkotika. Kampus harus aman, edukatif, dan berkarakter.</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607220/bnn-ajak-mahasiswa-jadi-garda-terdepan-pencegahan-narkotika</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bnn-ajak-mahasiswa-jadi-garda-terdepan-pencegahan-narkotika-1786008062558_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Pria di Pandeglang Digerebek Warga, Diduga Penipu Modus Lowongan Kerja MBG</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:28:02 +0700</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Aris Rivaldo</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Warga Kampung Sekong menggerebek YP, terduga penipu yang menjanjikan lowongan kerja MBG. Polisi mengamankan pelaku setelah ratusan warga marah.</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607238/pria-di-pandeglang-digerebek-warga-diduga-penipu-modus-lowongan-kerja-mbg</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kapolsek-cimanuk-akp-agus-salim-arisdetik-1786008444637_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Pertamina Pastikan Stok BBM di Bali Aman</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:59:45 +0700</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga memastikan ketersediaan BBM di Bali aman untuk masyarakat dan wisatawan.</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607329/pertamina-pastikan-stok-bbm-di-bali-aman</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/22/produk-bbm-di-spbu-pertamina-1776827152590_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Bos BGN Minta MBG Jangan Dibawa Pulang, Konsumsi Tak Boleh Lebih dari 4 Jam</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:48:48 +0700</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengimbau agar para siswa tidak membawa pulang Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607277/bos-bgn-minta-mbg-jangan-dibawa-pulang-konsumsi-tak-boleh-lebih-dari-4-jam</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Pabrik di Cimahi PHK Ratusan Karyawan, Menperin Buka Suara</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:38:51 +0700</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Ia menyebut, PHK ini dilakukan menyusul penghasilan perusahaan yang terus mengalami penyusutan.</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607251/pabrik-di-cimahi-phk-ratusan-karyawan-menperin-buka-suara</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/05/menperin-agus-gumiwang-1777956661182_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Fulham Langsung Jumpa Chelsea: Arbeloa Mau Sakiti Teman Sendiri</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Okdwitya Karina Sari</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Momen istimewa menanti Alvaro Arbeloa ketika Fulham menghadapi Chelsea. Laga tersebut turut menandai adu taktik antara Arbeloa lawan teman baiknya, Xabi Alonso.</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-inggris/d-8606984/fulham-langsung-jumpa-chelsea-arbeloa-mau-sakiti-teman-sendiri</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/2277882881-1785999539930_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Singapura Vs Indonesia: Garuda Rawan Bobol di Babak I</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:40:45 +0700</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia akan melawan Timnas Singapura dalam laga lanjutan Piala AFF 2026. Skuad Garuda rawan bobol di babak pertama.</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606949/singapura-vs-indonesia-garuda-rawan-bobol-di-babak-i</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/thom-haye-1785772033762_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Apa Quartararo Masih Trauma di MotoGP Inggris?</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:30:05 +0700</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Afif Farhan</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>MotoGP Inggris 2025 lalu, motor Fabio Quartararo bermasalah ketika memimpin dan akhirnya menepi sampai sampai menangis. Apa insiden itu masih menghantui?</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/moto-gp/d-8607172/apa-quartararo-masih-trauma-di-motogp-inggris</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/25/fabio-quartararo-1748180665507.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Modric Belum Mau Pensiun karena...</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:20:45 +0700</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Novitasari Dewi Salusi</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Luka Modric memperpanjang kontrak di Milan meski sudah berusia 40 tahun. Ia lanjut main bukan karena tak mau kariernya berakhir negatif usai musim mengecewakan.</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-italia/d-8606953/modric-belum-mau-pensiun-karena</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/14/luka-modric-1771028794167_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Awas Nanti Menyesal, Vinicius!</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:00:35 +0700</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Okdwitya Karina Sari</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Mantan bintang sekaligus direktur Real Madrid Predrag Mijatovic memperingatkan Vinicius Junior. Masa depan Vinicius lagi dipertanyakan menyusul rumor Arsenal.</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-spanyol/d-8606861/awas-nanti-menyesal-vinicius</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/08/vinicius-junior-1775599794726_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>MPR Ungkap Poin-poin Penting PPHN, Opsi Amendemen UUD 1945 Menguat</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:58:23 +0700</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Eddy Soeparno mengungkap poin penting PPHN yang siap dibahas. PPHN akan menjadi pedoman pembangunan negara yang berlaku di setiap pemerintahan.</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806164522-32-1389392/mpr-ungkap-poin-poin-penting-pphn-opsi-amendemen-uud-1945-menguat</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/23/wakil-ketua-mpr-dukung-wfh-setelah-lebaran-untuk-hemat-bbm-1774242619086_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Bupati Ketapang Kalbar Buka Suara soal Korban Tewas Saat Karhutla</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:36:57 +0700</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Ketapang merenggut nyawa Taufik Hidayat (26). Bupati Alexander Wilyo menyerukan pencegahan karhutla agar tidak ada korban lagi.</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806161620-20-1389380/bupati-ketapang-kalbar-buka-suara-soal-korban-tewas-saat-karhutla</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/08/bmkg-kalbar-deteksi-206-titik-panas-1772970329606_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Penebang Pohon Depan Padel dengan Videotron di Bandung Terungkap</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:27:27 +0700</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Diduga pohon-pohon peneduh jalan dibabat demi estetika tempat padel yang ada videotron di simpang jalan Riau-Cihapit, Bandung. Dugaan keterlibatan ASN didalami.</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806131239-20-1389312/penebang-pohon-depan-padel-dengan-videotron-di-bandung-terungkap</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/02/10-pohon-peneduh-bandung-ditebang-farhan-ancam-pidanakan-bos-padel-1785656870697_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Penampakan Kebakaran Hutan 80 Hektare di Kawasan Gunung Bromo</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:22:21 +0700</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan seluas 80 hektare melanda Gunung Bromo hingga Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806160145-24-1389371/penampakan-kebakaran-hutan-80-hektare-di-kawasan-gunung-bromo</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/thumbnail-video-1786007284232_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Di Sidang, Bos Tambang Akui Beri Uang Rp1 M ke Mantan Ketua Ombudsman</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:10:22 +0700</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Direktur PT DSM, Tjia Peng Tjoan, mengakui memberi suap Rp1 miliar untuk mengatur LHP kepada Hery Susanto saat masih menjabat ketua Ombudsman.</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806153052-12-1389373/di-sidang-bos-tambang-akui-beri-uang-rp1-m-ke-mantan-ketua-ombudsman</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/16/hery-susanto-1776322729972_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Potensi Wisata Bahari, Ketum TP PKK Ajak Pelajar Biak Cintai Tanah Air</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:07:05 +0700</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Ketua TP PKK Tri Tito Karnavian mengajak pelajar Biak Numfor cintai Tanah Air melalui pendidikan karakter dan potensi bahari.</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806160232-20-1389372/potensi-wisata-bahari-ketum-tp-pkk-ajak-pelajar-biak-cintai-tanah-air</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/kegiatan-senam-sehat-masyarakat-sehat-dan-hebat-serta-sosialisasi-wawasan-kebangsaan-dan-cinta-tanah-air-di-lapangan-cenderawa-1786006889063_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Walkot Buka Suara soal Dugaan Laut di Batam Dikapling Secara Ilegal</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:59:02 +0700</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Wali Kota Batam Amsakar Achmad menanggapi dugaan pengkaplingan laut ilegal yang disinggung Menteri ATR/Kepala BPN awal pekan ini.</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806154409-20-1389359/walkot-buka-suara-soal-dugaan-laut-di-batam-dikapling-secara-ilegal</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/01/27/kapal-tanker-mt-horse-dan-mt-freya-dibawa-ke-batam_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Polri Perkuat SDM di Pusat Studi Kepolisian Universitas Palangka Raya</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:54:09 +0700</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Polri memperkuat pengembangan SDM melalui Pusat Studi Kepolisian Universitas Palangka Raya, fokus pada riset dan inovasi demi tugas kepolisian lebih efektif.</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806154508-20-1389361/polri-perkuat-sdm-di-pusat-studi-kepolisian-universitas-palangka-raya</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/universitas-palangka-raya-perkuat-sdm-polri-lewat-pusat-studi-kepolisian-1786005428607_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>MPR Sebut Sidang Tahunan 2026 Tak Gunakan Baju Adat</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:40:34 +0700</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR RI Eddy Soeparno mengumumkan Sidang Tahunan MPR tahun ini tanpa pakaian adat, peserta diwajibkan mengenakan Pakaian Sipil Lengkap.</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806153158-32-1389347/mpr-sebut-sidang-tahunan-2026-tak-gunakan-baju-adat</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/15/presiden-prabowo-meninggalkan-gedung-nusantara-1755239238930_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Prabowo Panggil Menhan, Panglima, hingga 3 Kepala Staf TNI</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:29:21 +0700</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto terima Panglima TNI dan kepala staf di Istana Merdeka, Kamis (6/8).</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806152259-32-1389342/prabowo-panggil-menhan-panglima-hingga-3-kepala-staf-tni</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/01/presiden-pimpin-upacara-peringatan-hari-lahir-pancasila-1780286427473_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>FOTO: Penertiban Bangunan di Karet Tengsin, Warga Tetap Bertahan</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:03:07 +0700</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>CNN Indonesia/Febria Adha L</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Warga tetap menjalankan aktivitas berdagang di tengah penertiban puluhan bangunan yang berdiri di atas saluran penghubung (PHB) di Jalan Abdul Jalil.</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806143845-22-1389320/foto-penertiban-bangunan-di-karet-tengsin-warga-tetap-bertahan</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/penertiban-bangunan-di-karet-tengsin-warga-bertahan-berdagang-1786001717718_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Wacana Pilkada Tanpa Wakil Kepala Daerah Mencuat di DPR</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:59:20 +0700</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Wacana pilkada tanpa wakil kepala daerah mulai mencuat di DPR, salah satunya dipicu oleh hubungan tak harmonis antara kepala daerah dan wakilnya.</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806143016-32-1389316/wacana-pilkada-tanpa-wakil-kepala-daerah-mencuat-di-dpr</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/08/25/dpr-setujui-rancangan-pkpu-tentang-pilkada-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>BRIN Produksi Sepatu Karet Rp80 Ribu, Prabowo Ikut Pesan</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:50:40 +0700</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Arif Satria memperkenalkan sepatu lokal kepada Presiden Prabowo. Sepatu harga terjangkau ini mendukung kebutuhan siswa Sekolah Rakyat.</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806143950-20-1389321/brin-produksi-sepatu-karet-rp80-ribu-prabowo-ikut-pesan</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/11/11/kepala-badan-riset-dan-inovasi-nasional-brin-arif-satria-1762856951952_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Polisi: Pelaku dan Korban Mutilasi Depok Kenalan di Aplikasi LGBT</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:39:24 +0700</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Polisi ungkap fakta baru kasus mutilasi di Depok. Pelaku berkenalan dengan korban melalui aplikasi gay dan merencanakan pencurian.</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806135603-12-1389303/polisi-pelaku-dan-korban-mutilasi-depok-kenalan-di-aplikasi-lgbt</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/01/15/dde382ab-9cab-4747-ad54-c29afe7300c5_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>RSA UGM Panggil Perawat yang Diduga Ikut Cibir Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:29:01 +0700</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Akademik UGM memanggil perawat terkait dugaan komentar tidak empati di media sosial. Proses investigasi etik sedang berlangsung.</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806141949-20-1389310/rsa-ugm-panggil-perawat-yang-diduga-ikut-cibir-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/24/ilustrasi-konsultasi-dengan-dokter_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>TNI Gelar Latihan Gabungan, Pamer Drone Kamikaze hingga Rudal C-705</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:16:51 +0700</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>TNI menggelar latihan tempur terintegrasi di Dabo Singkep, menampilkan teknologi modern dan strategi peperangan.</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806140730-20-1389301/tni-gelar-latihan-gabungan-pamer-drone-kamikaze-hingga-rudal-c-705</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/tni-pamer-drone-kamikaze-hingga-rudal-c-705-dalam-operasi-terintegrasi-1786000112437_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Polisi Selidiki Temuan Senjata Api di Yayasan Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:14:39 +0700</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Selatan menyelidiki temuan air gun dan senjata api di yayasan sekolah Pondok Pinang. Laporan polisi telah dibuat terkait kasus ini.</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806140334-12-1389300/polisi-selidiki-temuan-senjata-api-di-yayasan-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/05/25/ilustrasi-penembakan-di-sekolah-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Kebakaran SDN 04 Srengseng Sawah Jaksel, Api Berasal dari Gudang Buku</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:00:31 +0700</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Kebakaran di SDN 04 Srengseng Sawah, Jakarta Selatan, dimulai dari gudang buku. 17 mobil damkar dikerahkan untuk memadamkan api.</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806135350-20-1389295/kebakaran-sdn-04-srengseng-sawah-jaksel-api-berasal-dari-gudang-buku</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/01/01/70666114-61c6-4935-a290-b5f30fea1405_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Video Specialist Yusup Saepudin Tutup Usia, CNN Indonesia Berduka</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:57:53 +0700</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>CNN Indonesia berduka atas kepergian Yusup Saepudin, seorang Video Specialist Digital Admin yang dikenang sebagai sosok kreatif.</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806131613-20-1389282/video-specialist-yusup-saepudin-tutup-usia-cnn-indonesia-berduka</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/yusup-saepudin-1785999355979_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Sidang Perdana Praperadilan Eks Jampidsus Febrie Digelar Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:15:32 +0700</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Pengadilan Negeri Jakarta Selatan akan menggelar sidang praperadilan mantan Jaksa Agung Muda, Febrie Adriansyah, terkait kasus TPPU pada 18 dan 19 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806130512-12-1389273/sidang-perdana-praperadilan-eks-jampidsus-febrie-digelar-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/25/febrie-adriansyah-ditahan-kejagung-1784914764925_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>KPK Periksa Iskandar Sitorus dan Pegawai Bea Cukai</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:13:12 +0700</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Iskandar Sitorus diperiksa KPK sebagai saksi dalam kasus dugaan korupsi di Ditjen Bea dan Cukai.</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806125328-12-1389263/kpk-periksa-iskandar-sitorus-dan-pegawai-bea-cukai</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/12/iskandar-sitorus-di-kpk-1781255089868_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Kemensos Tangguhkan 1,49 Juta Penerima Bansos Terindikasi Judi Online</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:59:36 +0700</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Kemensos menangguhkan 1,49 juta KPM Program Sembako terindikasi judi online. Verifikasi data dilakukan untuk memastikan bantuan sosial tepat sasaran.</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806125253-20-1389262/kemensos-tangguhkan-149-juta-penerima-bansos-terindikasi-judi-online</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/07/menteri-sosial-saifullah-yusuf-1780804555472_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>KPK Kembali Panggil Rudy Tanoe di Kasus Bansos Hari Ini</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:48:13 +0700</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Komisaris Utama PT Dosni Roha Logistik Bambang Rudijanto Tanoesoedibjo kembali dipanggil KPK untuk diperiksa terkait kasus dugaan korupsi bansos.</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806123243-12-1389255/kpk-kembali-panggil-rudy-tanoe-di-kasus-bansos-hari-ini</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/11/26/50124780-d8f8-4a4c-90a7-33dcb9fa6ee9_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>SD di Srengseng Sawah Jaksel Kebakaran, 17 Mobil Damkar Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:37:10 +0700</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda sebuah sekolah dasar (SD) yang berlokasi di Jalan Srengseng Sawah, Jagakarsa, Jakarta Selatan pada Kamis (6/8) siang.</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806123509-20-1389256/sd-di-srengseng-sawah-jaksel-kebakaran-17-mobil-damkar-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/30/ilustrasi-ledakan-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Pasien BPJS yang Dicibir Dokter PPDS bukan dari RSUP Dr. Sardjito</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:31:01 +0700</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>RSUP Dr. Sardjito meluruskan informasi bahwa pasien BPJS yang menjadi objek cibiran dokter PPDS di media sosial bukan berasal dari rumah sakit tersebut.</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806122330-20-1389245/pasien-bpjs-yang-dicibir-dokter-ppds-bukan-dari-rsup-dr-sardjito</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2016/02/02/2c25c96a-2252-47b6-ab59-5c5a63928eff_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Bareskrim Bongkar Peredaran Etomidate Asal Thailand di Apartemen Pluit</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:54:15 +0700</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Total empat pelaku ditangkap dari dua lokasi berbeda dengan total barang bukti sebanyak 210 mililiter cairan etomidate.</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806114725-12-1389232/bareskrim-bongkar-peredaran-etomidate-asal-thailand-di-apartemen-pluit</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/bareskrim-bongkar-peredaran-etomidate-asal-thailand-di-apartemen-pluit-1785991322865_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>KKI Terjun Investigasi Kasus Dokter dan Nakes Cibir Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:29:41 +0700</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Konsil Kesehatan Indonesia akan investigasi komentar tidak empati tenaga kesehatan terhadap pasien BPJS di media sosial.</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806110235-20-1389221/kki-terjun-investigasi-kasus-dokter-dan-nakes-cibir-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/07/14/ilustrasi-dokter-alat-medis-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>DPD Sambangi Kediaman JK, Serahkan Undangan Sidang Tahunan MPR</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:23:46 +0700</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Jajaran DPD RI, dipimpin Sultan Baktiar, kunjungi Jusuf Kalla untuk menyerahkan undangan sidang tahunan MPR dan diskusikan pembangunan daerah.</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806102019-32-1389207/dpd-sambangi-kediaman-jk-serahkan-undangan-sidang-tahunan-mpr</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/08/18/c7c5ad55-4f84-4686-b2ab-e19c2915b1bd_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Hari Pertama, 128 Ribu Warga Ikut War Ticket HUT ke-81 RI di Istana</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:14:42 +0700</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Sebanyak 128.331 warga mengikuti war ticket Upacara HUT ke-81 RI di Istana Merdeka pada hari pertama pendaftaran, Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806103854-20-1389215/hari-pertama-128-ribu-warga-ikut-war-ticket-hut-ke-81-ri-di-istana</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/17/upacara-penurunan-bendera-di-istana-merdeka-1755428000061_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Pertimbangan Hakim Tak Terima Praperadilan Ganti Rugi Roy Suryo</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:02:11 +0700</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Hakim tunggal Pengadilan Negeri (PN) Jakarta Selatan, I Ketut Darpawan memutuskan permohonan Praperadilan Roy Suryo soal ganti rugi tidak dapat diterima.</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806104932-12-1389219/pertimbangan-hakim-tak-terima-praperadilan-ganti-rugi-roy-suryo</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/29/sidang-perdana-praperadilan-roy-suryo-1782735885629_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Mobil Polisi Kecelakaan di Bone, Seorang Balita Meninggal Dunia</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:57:02 +0700</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Mobil yang dikendarai seorang anggota Polres Bone terlibat kecelakaan. Dalam kecelakaan itu seorang balita meninggal dunia.</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806102029-20-1389208/mobil-polisi-kecelakaan-di-bone-seorang-balita-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/09/28/ba5e99b8-5d8e-49d5-bb76-aa2dd0f276f0_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Hakim Putuskan Praperadilan Ganti Rugi Roy Suryo Tak Dapat Diterima</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:31:29 +0700</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Hakim memutuskan praperadilan yang diajukan Roy Suryo soal permintaan ganti rugi tidak dapat diterima.</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806102606-12-1389210/hakim-putuskan-praperadilan-ganti-rugi-roy-suryo-tak-dapat-diterima</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/29/sidang-perdana-praperadilan-roy-suryo-1782735885843_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Diberhentikan Sementara, Febrie Adriansyah Masih Dapat Setengah Gaji</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:27:30 +0700</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung (Kejagung) mengatakan mantan Jaksa Agung Muda Bidang Tindak Pidana Khusus, Febrie Adriansyah masih menerima 50 persen gaji pokok.</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806093901-12-1389175/diberhentikan-sementara-febrie-adriansyah-masih-dapat-setengah-gaji</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/25/febrie-adriansyah-ditahan-kejagung-1784914764839_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Tiga Polisi di Anambas Ditahan, Diduga Terjerat Kasus Narkoba</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:19:53 +0700</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Tiga anggota Polres Kepulauan Anambas ditahan karena dugaan penyalahgunaan narkotika. Kapolres menegaskan tindakan tegas akan diambil sesuai hukum.</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805231015-12-1389103/tiga-polisi-di-anambas-ditahan-diduga-terjerat-kasus-narkoba</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/11/23/ilustrasi-wanita-di-borgol-dan-penjara-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>RSUP Dr Sardjito Setop Praktik Dokter PPDS yang Cibir Pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>RSUP Dr Sardjito hentikan praktik dokter PPDS Elda Putri Rahardini akibat dugaan komentar tidak empati di media sosial. Investigasi sedang berlangsung.</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806094735-20-1389178/rsup-dr-sardjito-setop-praktik-dokter-ppds-yang-cibir-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/08/08/ilustrasi-logo-threads-4_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Air Kali Bekasi Menghitam Seperti Oli Bekas, Diduga Tercemar</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:57:18 +0700</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Video air Kali Bekasi berwarna hitam viral. Pemkot Bekasi selidiki pencemaran, ambil sampel, dan pantau kualitas air.</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806092718-20-1389173/air-kali-bekasi-menghitam-seperti-oli-bekas-diduga-tercemar</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/air-kali-cileungsi-bekasi-hitam-bak-oli-1785983164801_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Penggeledahan di Tangerang Terkait Kasus Suap Restitusi Pajak Mulyono</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:43:43 +0700</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>KPK melakukan penggeledahan di wilayah Tangerang dan menyita uang dalam bentuk pecahan dolar Amerika Serikat pada Rabu, 5 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806091414-12-1389167/penggeledahan-di-tangerang-terkait-kasus-suap-restitusi-pajak-mulyono</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/10/13/ilustrasi-pajak-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Syarat Jadi Pramuka Garuda yang Disebut Bisa Masuk TNI-Polri Tanpa Tes</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:24:31 +0700</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Ketua Kwarnas Budi Waseso menyatakan pemegang sertifikat Pramuka Garuda berkesempatan mengikuti seleksi TNI-Polri tanpa tes. Berikut syarat jadi Pramuka Garuda.</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806085539-20-1389156/syarat-jadi-pramuka-garuda-yang-disebut-bisa-masuk-tni-polri-tanpa-tes</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/02/19/perlombaan-pramuka-di-batam-1739960236032_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Said Abdullah Ungkap Pertumbuhan Ekonomi Nasional Triwulan II 2026</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:23:48 +0700</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Info Politik</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Said Abdullah menyatakan syukur bahwa di antara gejolak geopolitik saat ini, pertumbuhan perekonomian nasional masih tercatat di angka 5,29 persen YoY.</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806092012-633-1389170/said-abdullah-ungkap-pertumbuhan-ekonomi-nasional-triwulan-ii-2026</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/09/arsip-istimewa-1780992005758_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>KPK Ungkap Tiga Pertemuan Raja Juli dengan Bupati Kuansing</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:13:07 +0700</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>KPK mengungkapkan setidaknya ada tiga kali pertemuan yang melibatkan Bupati Kuantan Singingi, Suhardiman Amby dengan Menteri Kehutanan RI Raja Juli Antoni.</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806085709-12-1389161/kpk-ungkap-tiga-pertemuan-raja-juli-dengan-bupati-kuansing</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/24/kpk-dalami-pertemuan-bupati-kuansing-nonaktif-dengan-menhut-raja-juli-1784868456753_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Remaja di Nabire Bakar Teman Wanita hingga Tewas, Takut Aib Terbongkar</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:49:40 +0700</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Seorang remaja di Nabire, Papua, membakar teman perempuannya hingga tewas setelah terancam hubungan mereka terungkap. Pelaku kini dikeluarkan dari sekolah.</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806081108-12-1389150/remaja-di-nabire-bakar-teman-wanita-hingga-tewas-takut-aib-terbongkar</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/08/29/5f396afc-c6fc-470e-85f4-6629311adb5d_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Operasi Ditutup, Nasib Korban KMP Mutiara yang Hilang Masih Misteri</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:40:55 +0700</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Operasi SAR pencarian korban kebakaran KMP Mutiara Sentosa II resmi ditutup, namun masih ada keluarga yang mencari sanak saudara yang hilang.</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805180205-20-1389004/operasi-ditutup-nasib-korban-kmp-mutiara-yang-hilang-masih-misteri</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/operasi-dihentikan-keluarga-cemas-sebut-sejumlah-kru-dan-penumpang-kmp-mutiara-sentosa-ii-masih-hilang-1785927949357_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Polisi Menang Praperadilan, Status Tersangka Korupsi Rp1,9 M Gugur</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:19:36 +0700</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Pengadilan Negeri Rantauprapat mengabulkan praperadilan Bripka Yasir Mukhtadi Lubis, menegaskan status tersangkanya tidak sah.</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806070738-12-1389139/polisi-menang-praperadilan-status-tersangka-korupsi-rp19-m-gugur</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/10/31/57bd5113-e11c-46b7-948b-d8a96adbc8eb_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Wamensos Cek Pembangunan Sekolah Rakyat Probolinggo-Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:08:35 +0700</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Proses pembangunan Sekolah Rakyat permanen terus berjalan di sejumlah daerah, untuk menjamin akses pendidikan gratis bagi anak-anak dari keluarga prasejahtera.</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806075211-20-1389146/wamensos-cek-pembangunan-sekolah-rakyat-probolinggo-polewali-mandar</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/wamensos-cek-progres-pembangunan-sekolah-rakyat-1785977730668_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Buwas: Sertifikat Pramuka Garuda Bisa Buat Daftar TNI-Polri Tanpa Tes</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:07:47 +0700</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Ketua Kwarnas Pramuka Budi Waseso menyatakan sertifikat Pramuka Garuda dapat digunakan sebagai salah satu syarat dalam proses rekrutmen TNI dan Polri.</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806065500-20-1389128/buwas-sertifikat-pramuka-garuda-bisa-buat-daftar-tni-polri-tanpa-tes</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/14/pramuka-gelar-perkemahan-nasional-untuk-anak-berkebutuhan-khususpramuka-gelar-perkemahan-nasional-untuk-anak-berkebutuhan-khus-1755177248344_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>FOTO: Kabut Asap Selimuti Palembang</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:55:35 +0700</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan (karhutla) yang terjadi di beberapa wilayah Sumatera Selatan, mulai berdampak pada kualitas udara di Kota Palembang.</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806064831-22-1389121/foto-kabut-asap-selimuti-palembang</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/kabut-asap-di-palembang-1785973669671_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Walkot Eri Minta Pengelola Mal Bongkar Pagar Tinggi: Surabaya Ini Aman</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:38:31 +0700</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Wali Kota Surabaya Eri Cahyadi meminta pengelola mal menurunkan pagar tinggi untuk menjaga estetika dan menciptakan rasa aman.</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806063455-20-1389118/walkot-eri-minta-pengelola-mal-bongkar-pagar-tinggi-surabaya-ini-aman</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/17/viral-sejumlah-mal-surabaya-mendadak-bangun-pagar-1784287185067_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Menko Polkam: Situasi Dalam Negeri Mantap, Dalam Kendali Kita Semua</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:32:13 +0700</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Menko Polkam Djamari Chaniago memastikan kondisi di seluruh Indonesia tetap aman dan terkendali di tengah isu Demo Agustus yang beredar di media sosial.</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806072528-32-1389141/menko-polkam-situasi-dalam-negeri-mantap-dalam-kendali-kita-semua</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kumpulkan-panglima-tni-kapolri-menko-polkam-pastikan-kondisi-aman-terkendali-1785913030381_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>KPK Sita Rp9,5 M dari Saksi Kasus Suap Restitusi Pajak KPP Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:04:17 +0700</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>KPK menyita US$530.000 dalam penyidikan kasus suap pajak di KPP Banjarmasin. Tiga tersangka ditahan, termasuk kepala KPP dan pegawai pajak.</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806064537-12-1389120/kpk-sita-rp95-m-dari-saksi-kasus-suap-restitusi-pajak-kpp-banjarmasin</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/02/05/keterangan-kpk-terkait-ott-kpp-madya-banjarmasin-1770294817540_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Ramai-Ramai Kecam Dokter dan Nakes Cibir Pasien BPJS di Medsos</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:48:19 +0700</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Sejumlah tenaga kesehatan dikritik karena komentar tidak empati di media sosial terhadap pasien BPJS. Kasus ini memicu desakan sanksi dari Kemenkes.</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806062559-20-1389115/ramai-ramai-kecam-dokter-dan-nakes-cibir-pasien-bpjs-di-medsos</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/08/08/ilustrasi-logo-threads_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Bakom-Kemendagri Turun Tangan Investigasi Makalah MBG Nobel Perdamaian</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:45:28 +0700</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Pemerintah investigasi makalah usulan program Makan Bergizi Gratis (MBG) untuk Nobel Perdamaian 2026.</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806061718-20-1389110/bakom-kemendagri-turun-tangan-investigasi-makalah-mbg-nobel-perdamaian</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/mbg-untuk-semua-1785828725627_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Tiga Titik di Bandung-Cimahi Jadi Sasaran Pembakaran Pria Berhoodie</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:58:10 +0700</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Upaya pembakaran dengan motif misterius oleh pria misterius yang memakai jaket atau sweater berhoodie hitam terjadi di Cimahi dan Bandung pada akhir pekan lalu.</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805100030-12-1388880/tiga-titik-di-bandung-cimahi-jadi-sasaran-pembakaran-pria-berhoodie</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2016/07/21/5c1ee252-aced-4456-88b2-8983c4a2fe44_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Polda Sumbar Segera Gelar Sidang Etik AKBP F Terduga Pelecehan Polwan</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 02:06:17 +0700</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Kapolda Sumbar memastikan sidang etik terhadap AKBP F, terduga pelaku pelecehan Polwan, segera digelar. Proses hukum akan dilanjutkan jika ada bukti baru.</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805192756-12-1389054/polda-sumbar-segera-gelar-sidang-etik-akbp-f-terduga-pelecehan-polwan</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/kapolda-sumbar-sidang-etik-akbp-f-terduga-pelaku-pelecehan-polwan-segera-digelar-1785932843089_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Pria di Bandung Bakar Rumah Orang Tua, Ayah Alami Luka-luka</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:12:26 +0700</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Seorang pria di Bandung, Azay Rejza, membakar rumah orang tuanya akibat sakit hati dimarahi. Ayahnya mengalami luka bakar, namun tidak ada korban jiwa.</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805171137-12-1388984/pria-di-bandung-bakar-rumah-orang-tua-ayah-alami-luka-luka</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/12/24/ilustrasi-kebakaran-pabrik_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Polisi Usut Dugaan Ancaman Bom via Informasi Elektronik Bandara Bali</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 01:06:14 +0700</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Polisi menyelidiki dugaan ancaman bom di Bandara I Gusti Ngurah Rai, Bali. Situasi keamanan tetap kondusif, dan penerbangan berjalan normal.</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805171703-12-1388992/polisi-usut-dugaan-ancaman-bom-via-informasi-elektronik-bandara-bali</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/12/bandara-bali-hentikan-operasional-selama-hari-raya-nyepi-2026-1773315870712_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Penasihat Presiden Desak Purbaya Resmikan Pajak JHT Jadi Nol Persen</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:28:12 +0700</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Pajak JHT menjadi nol persen ini merupakan satu dari empat tuntutan buruh kepada pemerintah di bulan Agustus 2026 ini.</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/06/172626826/penasihat-presiden-desak-purbaya-resmikan-pajak-jht-jadi-nol-persen</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/yIxkgINc42Rc17E95NxkCof7XWo=/337x508:4337x3175/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/06/09/6a273c718ec4a.jpg</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Advertorial</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Menkop Letakkan Batu Pertama Pembangunan KDKMP Dekai di Yahukimo</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:28:12 +0700</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Menkop Ferry Juliantono melakukan peletakan batu pertama pembangunan KDKMP Dekai di Yahukimo untuk memperkuat ekonomi masyarakat Papua Pegunungan.</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>https://biz.kompas.com/read/2026/08/06/170817428/menkop-letakkan-batu-pertama-pembangunan-kdkmp-dekai-di-yahukimo</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/zXZAle0FTSOj2C-3jgnN4wsExQ0=/0x0:1200x800/1200x675/data/photo/2026/08/06/6a745cf7236a0.jpg</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Perdagangan 593 Kg Sisik dan Kuku Trenggiling di Pontianak, 2 Orang Penjual Ditangkap</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:28:12 +0700</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Kepolisian Pontianak mengungkap dugaan perdagangan sisik dan kuku trenggiling seberat 593 Kg, menangkap dua tersangka.</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/165855878/perdagangan-593-kg-sisik-dan-kuku-trenggiling-di-pontianak-2-orang-penjual</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/ijRecBWQbWTsxqVYtIrwoJ-lxpI=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a7453e441720.jpeg</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I527"/>
+  <autoFilter ref="A1:I612"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$612</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$725</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I612"/>
+  <dimension ref="A1:I725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -29196,8 +29196,5324 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Asupan dalam menjaga mikrobiota usus seimbang untuk saluran cerna</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:37:47 +0700</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Pakar Gastroenterologi dan Nutrisi Anak, University Hospital Brussels (UZ Brussel), Belgia, Prof. Yvan Vandenplas, MD, ...</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682783/asupan-dalam-menjaga-mikrobiota-usus-seimbang-untuk-saluran-cerna</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1884a94a-6551-473d-943f-86c10ccbfc6c.jpeg</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Madani minta status siaga darurat  di Papua Selatan diperpanjang</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:19 +0700</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Lembaga nirlaba Madani Berkelanjutan meminta pemerintah menetapkan status siaga darurat di Papua Selatan diperpanjang ...</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682781/madani-minta-status-siaga-darurat-di-papua-selatan-diperpanjang</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/palangka-raya-karhutlaa-5.jpeg</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Pencurian besi hidran di Jaktim hambat pasokan air saat kebakaran</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:06 +0700</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Suku Dinas Penanggulangan Kebakaran dan Penyelamatan (Gulkarmat) Jakarta Timur menyebut pencurian besi ...</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682780/pencurian-besi-hidran-di-jaktim-hambat-pasokan-air-saat-kebakaran</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/InShot_20260806_165057824.jpg</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Polisi diminta bongkar bunker usai temuan senjata di sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:01 +0700</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Tim kuasa hukum yayasan sekolah swasta di kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan, meminta polisi ...</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682776/polisi-diminta-bongkar-bunker-usai-temuan-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001014828.jpg</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Dua wajah Kaluna di pementasan "Home Sweet Loan The Musical"</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:32:52 +0700</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Tim produksi teater musikal "Home Sweet Loan The Musical" resmi memperkenalkan Kalya Islamadina dan Chintana ...</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682772/dua-wajah-kaluna-di-pementasan-home-sweet-loan-the-musical</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_125026.jpg</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Jateng-Kaltim jajaki kerja sama dengan potensi ekonomi Rp20,2 triliun</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:32:51 +0700</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jawa Tengah dan Kalimantan Timur menjalin kerja sama berbagai sektor, dengan potensi ekonomi yang ...</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682769/jateng-kaltim-jajaki-kerja-sama-dengan-potensi-ekonomi-rp202-triliun</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1002083791.jpg</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Bappenas: SDM perlu kerja terintegrasi untuk pembangunan berkelanjutan</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:31:29 +0700</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Deputi Bidang Pangan, Sumber Daya Alam, dan Lingkungan Hidup Kementerian Perencanaan Pembangunan Nasional/Badan ...</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682764/bappenas-sdm-perlu-kerja-terintegrasi-untuk-pembangunan-berkelanjutan</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/30/Teguh-PPN.jpeg</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Kemendag: Program festival belanja jaga daya beli saat "low season"</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:27:50 +0700</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Kementerian Perdagangan (Kemendag) mengatakan program-program festival belanja menjadi salah satu upaya kolaboratif ...</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682763/kemendag-program-festival-belanja-jaga-daya-beli-saat-low-season</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_0436.jpeg</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Rutan Salemba gagalkan penyelundupan sabu dan ekstasi</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:27:10 +0700</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Petugas Rumah Tahanan (Rutan) Kelas I Salemba, Jakarta Pusat menggagalkan upaya penyelundupan barang yang diduga ...</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682759/rutan-salemba-gagalkan-penyelundupan-sabu-dan-ekstasi</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000832765.jpg</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Tradisi lulur keraton dikenalkan kembali kepada generasi muda</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:27:06 +0700</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Tradisi perawatan tubuh menggunakan lulur berbahan alami yang telah lama menjadi bagian dari budaya Keraton Yogyakarta ...</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682756/tradisi-lulur-keraton-dikenalkan-kembali-kepada-generasi-muda</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000699492.jpg</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Asaki siapkan ekspansi kapasitas produksi, investasi hingga Rp10 T</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:26:03 +0700</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Asosiasi Aneka Industri Keramik Indonesia (Asaki) menyiapkan ekspansi kapasitas produksi industri keramik nasional ...</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682755/asaki-siapkan-ekspansi-kapasitas-produksi-investasi-hingga-rp10-t</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/29/WhatsApp-Image-2026-06-23-at-21.17.09.jpeg</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>IESR: PLTS jadi solusi percepatan transisi energi terbarukan</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:25:19 +0700</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Institute for Essential Services Reform (IESR) menyatakan bahwa pembangunan pembangkit listrik tenaga surya (PLTS) ...</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682752/iesr-plts-jadi-solusi-percepatan-transisi-energi-terbarukan</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_171616.jpg</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Airlangga: pertumbuhan ekonomi positif, termasuk investasi merata</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:23:09 +0700</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Koordinator bidang Perekonomian Airlangga Hartarto menyatakan kondisi perekonomian Indonesia relatif ...</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682687/airlangga-pertumbuhan-ekonomi-positif-termasuk-investasi-merata</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-06-165001.jpg</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Produsen EV China genjot ekspansi lewat manufaktur lokal</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:23:00 +0700</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Di pelabuhan-pelabuhan utama China, berbagai kendaraan listrik (electric vehicle/EV) buatan China satu demi satu dimuat ...</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682748/produsen-ev-china-genjot-ekspansi-lewat-manufaktur-lokal</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000022_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>MPR ungkap Sidang Tahunan digelar 14 Agustus dan dimulai lebih pagi</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:22:59 +0700</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR RI Eddy Soeparno menyampaikan bahwa Sidang Tahunan MPR RI dan Sidang Bersama DPR RI-DPD RI bakal ...</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682747/mpr-ungkap-sidang-tahunan-digelar-14-agustus-dan-dimulai-lebih-pagi</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/IMG_20260721_150526.jpg</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Hino digitalisasi inspeksi kendaraan niaga lewat aplikasi</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:22:47 +0700</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>PT Hino Motors Sales Indonesia mulai menerapkan digitalisasi proses Pre-Delivery Inspection (PDI) bagi perusahaan ...</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682744/hino-digitalisasi-inspeksi-kendaraan-niaga-lewat-aplikasi</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_1954.JPG.jpeg</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Iskandar Widjaja kolaborasi dengan Niu Niu gelar konser di Indonesia</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:32 +0700</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Pemain biola internasional Iskandar Widjaja kembali ke Indonesia untuk menggelar rangkaian konser di Jakarta, Bali dan ...</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682741/iskandar-widjaja-kolaborasi-dengan-niu-niu-gelar-konser-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Iskandar-Wijaja-x-Niu-Niu-a.jpg</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Adopsi Kendaraan Listrik Tumbuh, 21.865 Pelanggan Baru Gunakan Home Charging Services PLN pada Semester I 2026</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:28 +0700</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – Seiring meningkatnya adopsi kendaraan listrik (Electric Vehicle/EV) di Indonesia, minat ...</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682737/adopsi-kendaraan-listrik-tumbuh-21865-pelanggan-baru-gunakan-home-charging-services-pln-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-17.16.25.jpeg</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Kepala BGN: MBG tidak boleh dikonsumsi lebih dari empat jam</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:28 +0700</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengingatkan Makan Bergizi Gratis (MBG) sebaiknya tidak dibawa pulang oleh ...</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682735/kepala-bgn-mbg-tidak-boleh-dikonsumsi-lebih-dari-empat-jam</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/195035.jpg</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Lonjakan wisatawan asing soroti daya tarik "China Cool"</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:19 +0700</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Ketika gelombang panas ekstrem melanda berbagai belahan dunia, semakin banyak wisatawan mancanegara yang berkunjung ke ...</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682731/lonjakan-wisatawan-asing-soroti-daya-tarik-china-cool</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000018_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Menkum tegaskan kejadian SPG GIIAS direkam tanpa izin melanggar hukum</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:00 +0700</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Menteri Hukum (Menkum) Supratman Andi Agtas menegaskan kejadian adanya sales promotion girl (SPG) atau usher di pameran ...</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682728/menkum-tegaskan-kejadian-spg-giias-direkam-tanpa-izin-melanggar-hukum</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000473216.jpg</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Prabowo lihat satu per satu hasil riset dan inovasi BRIN di Istana</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:18:17 +0700</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto berkeliling ruangan di halaman tengah Istana Kepresidenan RI, Jakarta, Kamis, selama lebih ...</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682724/prabowo-lihat-satu-per-satu-hasil-riset-dan-inovasi-brin-di-istana</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/foto-brin.jpg</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Pertamina Patra Niaga salurkan alsintan listrik ke petani Bali</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:18:01 +0700</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>PT Pertamina Patra Niaga menyalurkan bantuan alat dan mesin pertanian (alsintan) berbasis listrik kepada kelompok tani ...</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682720/pertamina-patra-niaga-salurkan-alsintan-listrik-ke-petani-bali</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000177951.jpg</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Resmi K100 Pro akan dibekali baterai 8.580 mAh dan kamera 200MP</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:14:45 +0700</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Redmi mengonfirmasi kapasitas baterai dan kemampuan kamera Redmi K100 Pro menjelang jadwal peluncurannya pada 11 ...</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682719/resmi-k100-pro-akan-dibekali-baterai-8580-mah-dan-kamera-200mp</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000309054.jpg</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Rowing Indonesia minta berangkat lebih awal ke Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:14:15 +0700</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Tim nasional dayung nomor rowing Indonesia meminta diberangkatkan lebih awal ke Jepang untuk mempersiapkan peralatan ...</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682717/rowing-indonesia-minta-berangkat-lebih-awal-ke-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/16/tim-dayung-putri-empat-orang-raih-medali-perak-2691151.jpg</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>KPU Banyumas siapkan pemilih disabilitas menuju Pemilu 2029 inklusif</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:12:23 +0700</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>ANTARA - Komisi Pemilihan Umum (KPU) Kabupaten Banyumas memberikan pendidikan politik kepada 31 siswa SLB B Yakut ...</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682664/kpu-banyumas-siapkan-pemilih-disabilitas-menuju-pemilu-2029-inklusif</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_KPU-BANYUMAS-SIAPKAN-PEMILIH-DISABILITAS-MENUJU-PEMILU-2029-INKLUSIF.jpg</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Seskab buka pertemuan perdana Prabowo dan 150 periset BRIN di Istana</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:10:17 +0700</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Sekretaris Kabinet (Seskab) Teddy Indra Wijaya membuka pertemuan perdana antara Presiden Prabowo Subianto dengan ...</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682712/seskab-buka-pertemuan-perdana-prabowo-dan-150-periset-brin-di-istana</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034812.jpg</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Sekjen PDIP ingatkan ASI eksklusif adalah kunci lawan stunting</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:10:02 +0700</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Sekretaris Jenderal DPP PDI Perjuangan, Hasto Kristiyanto, menegaskan bahwa peringatan Hari ASI Sedunia bukan ...</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682708/sekjen-pdip-ingatkan-asi-eksklusif-adalah-kunci-lawan-stunting</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000580703.jpg</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Bedah lebih dalam teknologi pada "head unit" Changan Nevo Q05</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:08:41 +0700</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Mobil listrik merek dari China  Changan Nevo Q05  dilengkapi head unit yang dirancang bukan hanya sebagai ...</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682707/bedah-lebih-dalam-teknologi-pada-headunitchangan-nevo-q05</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_1949.JPG.jpeg</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Kemkomdigi bekali forum pelajar Indonesia ciptakan ruang digital aman</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:04:57 +0700</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Kementerian Komunikasi dan Digital (Kemkomdigi) membekali Forum Pelajar Indonesia sebuah cara praktis untuk generasi ...</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682703/kemkomdigi-bekali-forum-pelajar-indonesia-ciptakan-ruang-digital-aman</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0031-1.jpg</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Manfaatkan botol plastik bekas menjadi wayang upcycle bernilai seni</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:04:42 +0700</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Apul (38) menyelesaikan pembuatan wayang upscycle di Bank Sampah Pa-Q-One, Gedongkiwo, Mantrijeron, Yogyakarta.</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5682699/manfaatkan-botol-plastik-bekas-menjadi-wayang-upcycle-bernilai-seni</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Wayang-berbahan-botol-plastik-bekas-060826-afa-8.jpg</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Kadin yakin kepastian RKAB pulihkan sektor pertambangan</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:03:30 +0700</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Umum Bidang Keanggotaan Kadin Indonesia Widiyanto Saputro meyakini kepastian kuota produksi melalui revisi ...</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682695/kadin-yakin-kepastian-rkab-pulihkan-sektor-pertambangan</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_7550.jpg</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Rowing Indonesia tanpa tambahan uji coba jelang Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:00:40 +0700</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Tim nasional dayung nomor rowing Indonesia dipastikan tanpa tambahan uji coba internasional menjelang Asian Games 2026 ...</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682691/rowing-indonesia-tanpa-tambahan-uji-coba-jelang-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/17/Dayung.jpg</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>KUD optimistis musim penangkapan ikan nelayan Cilacap membaik</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:58:38 +0700</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Ketua Koperasi Unit Desa (KUD) Mino Saroyo Cilacap Untung Jayanto optimistis musim penangkapan ikan nelayan di ...</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682689/kud-optimistis-musim-penangkapan-ikan-nelayan-cilacap-membaik</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001095541.jpg</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>AS sebut akan gunakan militer, ekonomi untuk akhiri perang dengan Iran</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:52:51 +0700</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Wakil Presiden Amerika Serikat JD Vance   mengatakan pihaknya akan menggunakan sarana militer, ekonomi, dan ...</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682685/as-sebut-akan-gunakan-militer-ekonomi-untuk-akhiri-perang-dengan-iran</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/iran.jpg</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>KEPP OKP paparkan delapan platform pembangunan Papua</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:52:43 +0700</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Ketua Komite Eksekutif Percepatan Pembangunan Otonomi Khusus Papua (KEPP OKP) Velix Wanggai memaparkan ...</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682683/kepp-okp-paparkan-delapan-platform-pembangunan-papua</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/pelatihan-pembuatan-kerajinan-gerabah-di-jayapura-2773875.jpg</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>BPBD Probolinggo: Luas savana Bromo yang terbakar capai 80 hektare</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:52:42 +0700</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Kepala Pelaksana Badan Penanggulangan Bencana Daerah (BPBD) Kabupaten Probolinggo Oemar Sjarief mengatakan luas savana ...</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682680/bpbd-probolinggo-luas-savana-bromo-yang-terbakar-capai-80-hektare</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-14.49.50.jpeg</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Spek lengkap Lepas E4 EV, harga Rp300 jutaan dan jarak tempuh 600 km</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:52:40 +0700</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Lepas E4 EV, salah satu mobil listrik yang dipamerkan di Gaikindo Indonesia International Auto Show (GIIAS) 2026 ...</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5682676/spek-lengkap-lepas-e4-ev-harga-rp300-jutaan-dan-jarak-tempuh-600-km</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_1946.JPG.jpeg</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Airlangga: RKAT Danantara direvisi menyesuaikan DSI dan DDMF</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:52:23 +0700</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Perekonomian Airlangga Hartarto mengungkapkan Rencana Kerja dan Anggaran Tahunan (RKAT) ...</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682672/airlangga-rkat-danantara-direvisi-menyesuaikan-dsi-dan-ddmf</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/tempImageTW1qM6.jpg</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Speedboat Sekatak terbakar di perairan Salimbatu, 22 penumpang selamat</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:50:05 +0700</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebuah speedboat reguler rute Tanjung Selor menuju Tarakan hangus terbakar di perairan wilayah Salimbatu, ...</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682539/speedboat-sekatak-terbakar-di-perairan-salimbatu-22-penumpang-selamat</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_SPEEDBOAT-SEKATAK-TERBAKAR-DI-PERAIRAN-SALIMBATU-22-PENUMPANG-SELAMAT.jpg</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Konsultan properti: Danantara Housing Expo inisiatif bagus pemerintah</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:48:29 +0700</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Konsultan properti, Knight Frank Indonesia mengungkapkan Danantara Housing Expo 2026 merupakan inisiatif bagus dari ...</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682668/konsultan-properti-danantara-housing-expo-inisiatif-bagus-pemerintah</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1034.jpg</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Industri pakan ternak Kaltim manfaatkan bahan baku bungkil sawit</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:46:41 +0700</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>ANTARA - Industri pakan ternak di Kalimantan Timur memanfaatkan bungkil sawit sebagai bahan baku pakan hewan. Bungkil ...</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682592/industri-pakan-ternak-kaltim-manfaatkan-bahan-baku-bungkil-sawit</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-06-161608.jpg</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Korban tewas serangan Israel di Gaza bertambah jadi 73.381 orang</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:45:31 +0700</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat serangan Israel di Jalur Gaza meningkat menjadi 73.381 orang, sementara 174.231 lainnya ...</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682661/korban-tewas-serangan-israel-di-gaza-bertambah-jadi-73381-orang</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Gaza-luluh-lantak-setelah-2-tahun-diserbu-Israel.jpg</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>AFPI sebut sebagian besar anggotanya ajukan banding atas putusan KPPU</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:44:25 +0700</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Asosiasi Fintech Pendanaan Indonesia (AFPI) menyampaikan sebagian besar anggotanya tengah mengajukan banding ke ...</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682659/afpi-sebut-sebagian-besar-anggotanya-ajukan-banding-atas-putusan-kppu</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/e8da37f5-030a-48d4-8ae8-12d333d27369.jpeg</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>KKP beri benur hingga eskavator untuk pemulihan tambak di Aceh Utara</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:44:02 +0700</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>ANTARA - Kementerian Kelautan dan Perikanan (KKP) RI  serahkan bantuan alat berat, mesin kapal, cool box dan benur ...</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682636/kkp-beri-benur-hingga-eskavator-untuk-pemulihan-tambak-di-aceh-utara</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KKP-BERI-BENUR-HINGGA-ESKAVATOR-UNTUK-PEMULIHAN-TAMBAK-DI-ACEH-UTARA.jpg</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>IHSG ditutup melemah seiring bursa saham kawasan Asia</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:43:38 +0700</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Kamis sore ditutup turun seiring dengan pelemahan ...</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682655/ihsg-ditutup-melemah-seiring-bursa-saham-kawasan-asia</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/IHSG-ditutup-melemah-ke-posisi-5.941-030626-sth-02.jpg</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Pemerintah kawal pemenuhan hak pekerja terdampak PHK di Cimahi</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:42:47 +0700</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Pemerintah memastikan akan mengawal proses pemenuhan hak pekerja terdampak pemutusan hubungan kerja (PHK) di PT Namnam ...</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682651/pemerintah-kawal-pemenuhan-hak-pekerja-terdampak-phk-di-cimahi</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/483823.jpg</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Eks pemimpin junta Myanmar kunjungi Thailand sebagai presiden</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:41:19 +0700</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>ANTARA - Mantan pemimpin junta Myanmar, Min Aung Hlaing, tiba di Bangkok pada hari Kamis (6/8) untuk kunjungan ...</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682476/eks-pemimpin-junta-myanmar-kunjungi-thailand-sebagai-presiden</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_EKS-PEMIMPIN-JUNTA-MYANMAR-KUNJUNGI-THAILAND-SEBAGAI-PRESIDEN.jpg</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Indosat-Nokia-NVIDIA Bangun Infrastruktur AI Terbesar di Asia Tenggara</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:32:38 +0700</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Indosat meluncurkan Zankore, kolaborasi dengan Ooredoo, Nokia, dan NVIDIA untuk infrastruktur AI. Proyek ini dukung pertumbuhan ekonomi digital di Asia-Pasifik.</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607398/indosat-nokia-nvidia-bangun-infrastruktur-ai-terbesar-di-asia-tenggara</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/indosat-ooredoo-hutchison-indosatmeluncurkan-zankore-by-indosat-1786011462647.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Menperin Siapkan Aturan Teknis Subsidi Kendaraan Listrik</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:24:34 +0700</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Menteri Perindustrian (Menperin), Agus Gumiwang Kartasasmita, siap menjalankan insentif bagi kendaraan berbasis listrik.</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607387/menperin-siapkan-aturan-teknis-subsidi-kendaraan-listrik</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/26/mou-menperin-menpora-1764172322626_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Piala Presiden 2026: Taklukkan Arema FC 3-1, Persija Finis Ketiga</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:22 +0700</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Lucas Aditya</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Persija Jakarta mampu memetik kemenangan 3-1 atas Arema FC dalam laga lanjutan Piala Presiden 2026. Macan Kemayoran pun finis ketiga.</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8607402/piala-presiden-2026-taklukkan-arema-fc-3-1-persija-finis-ketiga</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/piala-presiden-1785657422042_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Adhyaksa FC Promosi ke Super League, Ada 'Adhyaksa' Lain di Championship</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:15:25 +0700</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Muhammad Robbani</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Adhyaksa FC sudah promosi ke Super League sebagai Isen Mulang Kalteng FC. Tapi tetap ada nama Adhyaksa yang tampil di Championship lewat Adhyaksa F.C. Bekasi.</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>https://sport.detik.com/sepakbola/liga-indonesia/d-8606993/adhyaksa-fc-promosi-ke-super-league-ada-adhyaksa-lain-di-championship</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/23/jadi-markas-baru-adhyaksa-fc-stadion-tuah-pahoe-bersolek-istimewa-1782199090985_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Total 995 Senpi Ditemukan di Gedung Yayasan Sekolah Pondok Pinang</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:38:11 +0700</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Sebuah kantor yayasan sekolah swasta di Pondok Pinang, Jakarta, ternyata menyimpan 995 senjata api dan narkoba.</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806170949-12-1389408/total-995-senpi-ditemukan-di-gedung-yayasan-sekolah-pondok-pinang</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>MPR Ungkap Respons Prabowo Soal PPHN, Tekankan Jenis Produk Hukum</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:06 +0700</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR mengungkap arahan Presiden Prabowo terkait PPHN. Tiga opsi produk hukum dipertimbangkan, dengan fokus pada amendemen UUD dan TAP MPR.</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806172641-20-1389406/mpr-ungkap-respons-prabowo-soal-pphn-tekankan-jenis-produk-hukum</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/pimpinan-mpr-ri-menemui-presiden-di-istana-1785748046504_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Israel dan Lebanon Berunding, Tapi Perang Jalan Terus: 2 IDF Tewas, Apa Sebenarnya yang Terjadi?</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:48:11 +0700</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Respons pemerintah Israel yang kali ini lebih berhati-hati dengan tidak langsung menyalahkan Hizbullah</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7864868/israel-dan-lebanon-berunding-tapi-perang-jalan-terus-2-idf-tewas-apa-sebenarnya-yang-terjadi</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/LcBxEAfyL4kNELeUTXt6IKchv4E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ISRAEL-SERANG-LEBANON-345345rwer.jpg</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 10 SMA Kurikulum Merdeka Halaman 93 Edisi Revisi: Aktivitas 2.2</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:45:56 +0700</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban 10 SMA Kurikulum Merdeka Halaman 93 Edisi Revisi: Aktivitas 2.2.</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7864867/kunci-jawaban-ips-kelas-10-sma-kurikulum-merdeka-halaman-93-edisi-revisi-aktivitas-22</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FP7tCNrIZOkh9ZATUliZ5114wis=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pembelajaran-tatap-muka-hari-pertama-di-sd-n-1-semarapura-kangin-klungkung-bali.jpg</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Dukung Pertanian Berkelanjutan, Pertamina Salurkan 3 Traktor Listrik  ke Petani Bali</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:45:52 +0700</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Pertamina memperkuat pemberdayaan masyarakat berbasis energi bersih melalui Program Desa Energi Berdikari Uma Palak Lestari di Denpasar, Bali.</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7864866/dukung-pertanian-berkelanjutan-pertamina-salurkan-3-traktor-listrik-ke-petani-bali</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/OK0WrAazRIt04U9Lb0wDeS7EujM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Traktor-listrik-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Afgan Masih Lajang di Usia 37 Tahun, Akui Hidupnya Berantakan Tanpa 6 ART di Rumah</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:43:11 +0700</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Penyanyi Afgan mengungkapkan besarnya peran Asisten Rumah Tangga (ART) dalam menunjang aktivitas sehari-harinya.</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7864865/afgan-masih-lajang-di-usia-37-tahun-akui-hidupnya-berantakan-tanpa-6-art-di-rumah</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/rn_8SUW2k6w6xptZoe4hQg4Sfrw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Afgan-1-05082026.jpg</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Denny  Indrayana Kritik Politik Anggaran: MBG Jalan, Gaji Guru dan Dosen Masih Memprihatinkan</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:42:10 +0700</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Ia mengingatkan MK sebelumnya juga telah menegaskan pentingnya kesejahteraan guru dan dosen dalam putusan terkait program Makan Bergizi Gratis (MBG)</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864864/denny-indrayana-kritik-politik-anggaran-mbg-jalan-gaji-guru-dan-dosen-masih-memprihatinkan</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/873ucO_OljjdjoWTEnKHvODR_58=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/denny-indrayana-soal-gaji-guru.jpg</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Aleix Espargaro Prediksi 3 Kandidat Juara MotoGP 2026, Marc Marquez Jadi Ancaman Jorge Martin</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:39:10 +0700</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Prediksi Aleix Espargaro ada pertarungan Jorge Martin, Marc Marquez, dan Ai Ogura, dalam perebutan gelar juara dunia MotoGP 2026.</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7864863/aleix-espargaro-prediksi-3-kandidat-juara-motogp-2026-marc-marquez-jadi-ancaman-jorge-martin</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/WwTcMGAR_FjpP1p85zJvliY79So=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Jorge-Martin-Juara-Dunia-MotoGP-2024_20241118_125846.jpg</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Hasil Piala Presiden 2026: Persija Sabet Juara 3 setelah Gilas Arema FC 3-1, Bawa Pulang Rp2,5 M</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:38:00 +0700</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Persija Jakarta menaklukkan Arema FC 3-1 dan finis di posisi ketiga Piala Presiden 2026. Macan Kemayoran bawa pulang hadiah Rp2,5 miliar.</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864862/hasil-piala-presiden-2026-persija-sabet-juara-3-setelah-gilas-arema-fc-3-1-bawa-pulang-rp25-m</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/33o21bLP2B7moOanFXOkkIRHouI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Selebrasi-winger-Persija-Jakarta-Arlyansyah-saat-mencetak-gol-ke-gawang-Arema-FC.jpg</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Dokter-Nakes Diduga Lakukan Bullying ke Yurizal Berasal dari 10 RS: Ada yang PNS hingga Dokter Gigi</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:37:50 +0700</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>KKI menyebut dokter dan nakes yang diduga melakukan bullying terhadap Yurizal berasal dari 10 rumah sakit dan ada yang berstatus PNS.</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864861/dokter-nakes-diduga-lakukan-bullying-ke-yurizal-berasal-dari-10-rs-ada-yang-pns-hingga-dokter-gigi</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/mKiK7DSnd0Cxme8GVosRxLtbQdw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sosok-Yurizal-Tri-Chaerawan.jpg</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Joey Pelupessy Tetap Pilih Abroad, Tak Ikut Arus Pemain Naturalisasi Timnas Indonesia ke Liga 1</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:36:26 +0700</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Di tengah gempuran pemain naturalisasi Timnas Indonesia yang membela klub Liga 1, Joey Pelupessy justru tetap abroad dan bertahan di Lommel SK.</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864860/joey-pelupessy-tetap-pilih-abroad-tak-ikut-arus-pemain-naturalisasi-timnas-indonesia-ke-liga-1</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2K5xVfbjZNz6RwMK98lmOry1Qb0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lommel-SK-perpanjang-kontrak-Joey-Pelupessy.jpg</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Tak Hanya Anak-anak, Demam Berdarah juga Berisiko pada Ibu Hamil dan Lansia</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:29 +0700</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>DBD tidak hanya menyerang anak-anak. Dokter mengingatkan bayi, ibu hamil, hingga lansia juga berisiko mengalami kondisi berat.</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7864859/tak-hanya-anak-anak-demam-berdarah-juga-berisiko-pada-ibu-hamil-dan-lansia</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/R4M4PrciGyQ63CjZ2NePl0scgKo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/fogging-nyamuk-dbd-di-bugel-tangerang_20210309_204611.jpg</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Sebelum 995 Senpi Ditemukan di Bekas Ruang Kerjanya, Ketua Yayasan Sekolah Jaksel Dipecat</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:31:14 +0700</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Ketua yayasan sekolah di Jaksel dipecat sebelum ruang kerjanya dibuka. Dari ruangan itu, pihak yayasan mengaku menemukan 995 senjata.</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864858/sebelum-995-senpi-ditemukan-di-bekas-ruang-kerjanya-ketua-yayasan-sekolah-jaksel-dipecat</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c23bmk4PHY76ZCmOECtNP5j3wK4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ratusan-senjata-api-di-sekolah-swasta-Pondok-Pinang-Kebayoran-Lama-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Sinopsis Night Tales, Drama China Baru tentang Balas Dendam dan Pengkhianatan yang Bikin Penasaran</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:28:39 +0700</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Drama China Night Tales hadir dengan kisah balas dendam, romansa, dan intrik keluarga. Simak sinopsis, pemain, dan jadwal tayangnya.</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7864857/sinopsis-night-tales-drama-china-baru-tentang-balas-dendam-dan-pengkhianatan-yang-bikin-penasaran</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/741UGGMgGbJJbaYqHX_Ljju216w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Film-Bioskop-Ilustrasi.jpg</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Pakar Hukum Usul RUU Perampasan Aset Diganti Jadi Pemulihan Aset, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:28:19 +0700</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Yehezkiel Minggus Tiranda mengusulkan agar terminologi dalam Rancangan Undang-Undang (RUU) Perampasan Aset dikaji ulang.</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864856/pakar-hukum-usul-ruu-perampasan-aset-diganti-jadi-pemulihan-aset-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/24a9NWVOjFjUESBWUmQQ1m2fccY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/RDPU-RUU-peramapsan-aset-senin.jpg</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>China Siapkan Kota Bawah Tanah 400 Juta Meter Persegi: 4 Lapis Kedalaman, Target Rampung pada 2035</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:24:53 +0700</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>China rencananya akan membuat kota bawah tanah dalam empat lapisan kedalaman seluas total 400 juta meter persegi.</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7864855/china-siapkan-kota-bawah-tanah-400-juta-meter-persegi-4-lapis-kedalaman-target-rampung-pada-2035</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RqSgsL__UibIolsC5CvV87R2lUg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-kota-beijing.jpg</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Hadiri Forum di Yordania, RI Ajak Dunia Tinggalkan Cara Lama Hadapi Pelanggaran Israel di Palestina</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:22:29 +0700</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Indonesia menegaskan kekerasan yang dilakukan Israel dan berbagai pelanggaran hukum internasional di wilayah Palestina tidak boleh dibiarkan.</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864854/hadiri-forum-di-yordania-ri-ajak-dunia-tinggalkan-cara-lama-hadapi-pelanggaran-israel-di-palestina</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-14XrRcuyDlHiUJ_fjk2dZHYIM4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wamenlu-Arrmanatha-Nasir-1274.jpg</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu What If I Call - Alex Crichton: and You Pick up The Phone?</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:45 +0700</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Simak lirik lagu dan terjemahan What If I Call milik Alex Crichton dalam artikel berikut ini.</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7864853/terjemahan-lirik-lagu-what-if-i-call-alex-crichton-and-you-pick-up-the-phone</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/CL9ms16FPIIxTCUp0D3p9YN4Z0w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-upgrade-fm.jpg</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Sintya Marisca Ingin Perbaiki Diri Supaya Cepet Dapat Jodoh</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:02 +0700</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Sintya Marisca akui dirinya kini masih jomblo, berharap bisa memperbaiki diri supaya segera bertemu jodoh.</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7864852/sintya-marisca-ingin-perbaiki-diri-supaya-cepet-dapat-jodoh</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/YUNinEGuzj4-Shg00dIE4Qhal1c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sintya-Marisca-1-11092024.jpg</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Kisah Tak Harmonis Rashford dan Amorim yang akan Berjumpa Lagi, Transfer ke AC Milan?</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:19:21 +0700</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Bukan pindah ke AC Milan, pertemuan Marcus Rashford dengan Ruben Amorim sebatas laga uji coba. Apalagi keduanya miliki hubungan yang tak harmonis.</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864851/kisah-tak-harmonis-rashford-dan-amorim-yang-akan-berjumpa-lagi-transfer-ke-ac-milan</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4qEd6pQbgXKgvb0QXbnegEJefEk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/aksi-penyerang-manchester-united-marcus-rashford-saat-melawan-real-betis-di-laga-uji-coba-pramusim.jpg</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Kim Sang-sik Balas Sindiran Justin Hubner soal Piala AFF 2026: Setiap Turnamen Itu Penting!</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Kim Sang-sik menanggapi sindiran Justin Hubner soal status Piala AFF 2026. Pelatih Vietnam menegaskan setiap turnamen tetap penting bagi timnya.</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864850/kim-sang-sik-balas-sindiran-justin-hubner-soal-piala-aff-2026-setiap-turnamen-itu-penting</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Z_nlcxIY_5ls05nvwXNrSuw1_rw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/RAIH-KEMENANGAN-Pelatih-Timnas-Vietnam-Kim-Sang-sik.jpg</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Cirebon Jumat, 7 Agustus 2026: Panas Seharian, Suhu Udara Tembus 34 Derajat</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:18:00 +0700</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Menurut pantauan BMKG Jawa Barat,  prakiraan cuaca untuk wilayah Cirebon pada Jumat (7/8/2026) cerah dengan potensi terik matahari yang menyengat.</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7864849/prakiraan-cuaca-cirebon-jumat-7-agustus-2026-panas-seharian-suhu-udara-tembus-34-derajat</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RvfGnQQIZUQoOu2g3M8w6WjfNPc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-cuaca-cerah-Kota-Pontianak.jpg</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Warga RI Ternyata Masih Doyan Nonton TV, Durasinya Bisa Segini</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Masyarakat Indonesia masih setia menonton TV, dengan 70% penonton setiap hari. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806153032-37-757170/warga-ri-ternyata-masih-doyan-nonton-tv-durasinya-bisa-segini</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/masyarakat-indonesia-masih-menggunakan-tv-untuk-alat-menonton-di-tengah-dominasi-smartphone-maupun-tablet-1786005118964_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Prabowo Teringat Pesan BJ Habibie: Indonesia Punya Banyak Orang Pintar</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:38:27 +0700</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menekankan pentingnya peran orang pintar dalam pengembangan sains dan teknologi.</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806173127-37-757219/prabowo-teringat-pesan-bj-habibie-indonesia-punya-banyak-orang-pintar</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pertemuan-presiden-ri-dengan-150-periset-dari-badan-riset-dan-inovasi-nasional-6-agustus-2026-1786010089825_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Ramai-Ramai Tinggalkan Google, Langsung Bikin Pengganti Baru</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Jeff Dean, engineer terkemuka Google, mengundurkan diri setelah hampir 30 tahun. Ia mendirikan startup AI, Discovery Loop.</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806152546-37-757163/ramai-ramai-tinggalkan-google-langsung-bikin-pengganti-baru</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/14/google-reutersfrancis-mascarenhasfile-photo-1760426243251_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Elon Musk Hancur-Hancuran, Harapannya Cuma Starlink</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Saham SpaceX anjlok 12% setelah laporan keuangan publik. Investor khawatir Starlink tak mampu mendanai ekspansi AI yang mahal.</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806150344-37-757157/elon-musk-hancur-hancuran-harapannya-cuma-starlink</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/14/ceo-tesla-elon-musk-memegang-telepon-seluler-saat-tiba-untuk-menghadiri-jamuan-makan-malam-kenegaraan-bersama-presiden-as-dona-1778764359254_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>BRIN Beberkan Potensi Nuklir RI ke Prabowo, Ada Uranium 89.000 Ton!</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menerima paparan inovasi teknologi nuklir dari BRIN, termasuk potensi uranium dan pengembangan energi alternatif di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806155127-37-757177/brin-beberkan-potensi-nuklir-ri-ke-prabowo-ada-uranium-89000-ton</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pertemuan-presiden-ri-dengan-150-periset-dari-badan-riset-dan-inovasi-nasional-6-agustus-2026-1786005466292_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Serangan Besar-Besaran Guncang Amerika, Wall Street Jadi Target</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Serangan siber besar-besaran mengguncang sektor keuangan AS, menargetkan hedge fund dan perusahaan investasi besar.</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806134926-37-757126/serangan-besar-besaran-guncang-amerika-wall-street-jadi-target</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/25/seorang-pria-berjalan-di-wall-street-di-luar-bursa-saham-new-york-nyse-di-kota-new-york-as-7-april-2025-1771984988559_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>TikTok Mendadak Tutup Kantor, PHK Ratusan Karyawan di Amerika</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>TikTok mengumumkan penutupan kantor Nashville dan PHK karyawan lokal sebagai bagian dari restrukturisasi global. Simak!</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806134349-37-757123/tiktok-mendadak-tutup-kantor-phk-ratusan-karyawan-di-amerika</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/02/10/tiktok-10_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Geger Data Center Raksasa Telan Anggaran Sampai Rp 18.000 Triliun</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Lima raksasa teknologi, termasuk Microsoft dan Amazon, mengunci komitmen sewa data center senilai Rp18.000 triliun.</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806122631-37-757091/geger-data-center-raksasa-telan-anggaran-sampai-rp-18000-triliun</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/22/gedung-data-center-meta-di-mansfield-as-1779441817711_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Google Assistant Disuntik Mati di HP Android September 2026</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Google Assistant akan ditutup pada 4 September 2026. Pengguna akan beralih ke Gemini, asisten AI generasi baru.</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806124700-37-757101/google-assistant-disuntik-mati-di-hp-android-september-2026</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/14/google-reuterscarlos-jassofile-photo-1763101615136_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Top! ZEEKR Pamerkan Empat Line Up Luxury EV di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:02:17 +0700</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>ZEEKR, brand Tech Luxury dari Geely, hadir di GIIAS dengan ZEEKR 009 Grand dan ZEEKR 7X. Menawarkan kenyamanan dan teknologi canggih untuk mobilitas modern.</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806134310-37-757132/top-zeekr-pamerkan-empat-line-up-luxury-ev-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/zeekr-9x-1785999581270_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>BRIN akan Paparkan Produk Inovasi ke Prabowo, Termasuk Pengganti LPG</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:43:00 +0700</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Pemaparan itu menjadi bagian dalam pertemuan antara Presiden Prabowo Subianto dengan peneliti BRIN siang ini.</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806133449-37-757120/brin-akan-paparkan-produk-inovasi-ke-prabowo-termasuk-pengganti-lpg</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/10/14/rektor-ipb-university-prof-dr-arif-satria-memberikan-pemaparan-dalam-acara-repnas-national-conference-awarding-night-energi-ma-15_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>6.000 CEO Ungkap Fakta Tak Terduga, AI Ternyata Tak Berguna</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Studi NBER menunjukkan AI belum berdampak signifikan pada produktivitas dan ketenagakerjaan. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806123043-37-757093/6000-ceo-ungkap-fakta-tak-terduga-ai-ternyata-tak-berguna</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/07/11/ilustrasi-artificial-intelegence-ai-reutersdado-ruvicillustrationfile-photo_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Cara Aktifkan Kuota Rollover di Telkomsel-XL-Indosat agar Tak Hangus</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Operator seluler kini menawarkan paket internet dengan fitur rollover, memungkinkan sisa kuota dibawa ke periode berikutnya.</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806114405-37-757062/cara-aktifkan-kuota-rollover-di-telkomsel-xl-indosat-agar-tak-hangus</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/30/sejumlah-anak-memainkan-ponsel-mereka-sesuai-pulang-sekolah-di-jakarta-senin-3032026-pemerintah-resmi-melarang-anak-di-bawah-u-1774857452764_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Tsunami Dahsyat 40 Meter Dikira Cuma 3 Meter, 18.500 Tewas Seketika</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Bencana gempa dan tsunami Jepang 2011 berdampak tragis. Ternyata ada salah perhitungan fatal. Simak!</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806112412-37-757044/tsunami-dahsyat-40-meter-dikira-cuma-3-meter-18500-tewas-seketika</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/21/foto-udara-menujukkan-garis-pantai-tomakomai-prefektur-hokkaido-jepang-setelah-peringatan-tsunami-dikeluarkan-menyusul-gempa-b-1776728111093_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>TikTok-Disney Mendadak Gabung, Begini Dampaknya ke Pengguna</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Walt Disney dan TikTok menjalin kemitraan strategis, memungkinkan penggabungan konten pada masing-masing platform.</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806110305-37-757039/tiktok-disney-mendadak-gabung-begini-dampaknya-ke-pengguna</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/02/10/tiktok-9_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Roket Elon Musk Tabrak Bulan, Buktinya Masih Dicari</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Bagian sisa roket SpaceX diperkirakan menabrak Bulan, membentuk kawah baru. Ilmuwan menunggu foto bukti benturan yang belum terdeteksi.</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806103742-37-757022/roket-elon-musk-tabrak-bulan-buktinya-masih-dicari</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/08/20/ilustrasi-bulan_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Bukan HP, Ahli Ungkap Penyebab Titik Hitam Tampak di Mata Sendiri</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Floaters adalah bayangan hitam di mata, umumnya disebabkan oleh penuaan. Waspadai jika muncul tiba-tiba atau disertai kilatan cahaya.</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806095920-37-757007/bukan-hp-ahli-ungkap-penyebab-titik-hitam-tampak-di-mata-sendiri</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/02/20/ilustrasi-bulu-mata-palsu-untuk-avriasi-istimewa-1740048423412_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Tarif Listrik Naik Gila-gilaan Demi AI, Rakyat Kecil Bayari Orang Kaya</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>AI meningkatkan tagihan listrik di AS, dengan kenaikan biaya hingga 28% di beberapa negara bagian.</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806082749-37-756970/tarif-listrik-naik-gila-gilaan-demi-ai-rakyat-kecil-bayari-orang-kaya</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/22/gedung-data-center-meta-di-mansfield-as-1779441817711_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Dunia Dalam Bahaya, Banyak Negara Sudah Siaga Penuh</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Kekhawatiran global meningkat terhadap AI Mythos milik Anthropic, yang dianggap berpotensi menjadi senjata siber.</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806061308-37-756942/dunia-dalam-bahaya-banyak-negara-sudah-siaga-penuh</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/07/21/ilustrasi-digital-banking-jcomp-freepik-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Saking Panasnya, Unta di Afrika Tak Tahan Sampai Ada yang Mati</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Unta di Afrika menderita akibat suhu ekstrem, dengan kematian meningkat. Dokter hewan melaporkan dampak serius pada kesehatan kawanan unta.</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806062422-37-756944/saking-panasnya-unta-di-afrika-tak-tahan-sampai-ada-yang-mati</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/03/19/unta-di-padang-pasir-dok-pixabay_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Cara Cek Penerima PIP Secara Online, Bisa Dilihat dari Rumah</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Pemerintah salurkan Program Indonesia Pintar (PIP) untuk siswa kurang mampu.</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260805133240-37-756750/cara-cek-penerima-pip-secara-online-bisa-dilihat-dari-rumah</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/11/gedung-sekolah-menengah-atas-sma-negeri-33-jakarta-1765438090952_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Tundukkan Arema 3-1, Persija Tempati Posisi Ketiga Piala Presiden Elite 2026</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:50:52 +0700</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Persija Jakarta menutup kiprahnya di Piala Presiden Elite 2026 dengan positif setelah mengamankan posisi ketiga. Tim berjuluk Macan Kemayoran menaklukkan Arema FC dengan skor 3-1 pada laga...</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://news.republika.co.id/berita/tjcgss348/tundukkan-arema-31-persija-tempati-posisi-ketiga-piala-presiden-elite-2026</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260806175004-770.png</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Filantropi khazanah</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Sinergi Amil Zakat-Sinergi Foundation dan UPZDK Permata Bank Syariah Perluas Dampak Zakat</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:46:48 +0700</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Sinergi Amil Zakat (SAZ)-Sinergi Foundation bersama Unit Pengelola Zakat dan Dana Kebajikan (UPZDK) Permata Bank Syariah kembali memperkuat sinergi dalam pemanfaatan dana zakat melalui pembangunan enam...</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://khazanah.republika.co.id/berita/tjcgm0472/sinergi-amil-zakatsinergi-foundation-dan-upzdk-permata-bank-syariah-perluas-dampak-zakat</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/sepanjang-2025-sazsinergi-foundation-bersama-upzdk-permata-bank-syariah_260806174525-951.jpeg</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Nasabah Mekaar Studi Banding Gratis, PNM Buka Jalan Inovasi Usaha Ultra Mikro</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:17 +0700</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Bagi banyak usaha ultra mikro, keterbatasan bukan hanya soal modal, tetapi juga akses terhadap pengetahuan dan inspirasi untuk mengembangkan usaha. Di sinilah PT Permodalan Nasional Madani...</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcg15472/nasabah-mekaar-studi-banding-gratis-pnm-buka-jalan-inovasi-usaha-ultra-mikro</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pengalaman-belajar-langsung-menjadi-salah-satu-cara-paling-efektif_260806173235-720.jpeg</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Tata kelola</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Greenovate 2026 Cetak Talenta Ekonomi Hijau, Inovasi Mahasiswa Siap Masuk Pasar</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:31:33 +0700</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Upaya mempercepat transisi menuju ekonomi hijau dinilai tidak hanya bergantung pada investasi dan kebijakan pemerintah, tetapi juga pada lahirnya inovasi yang memiliki nilai komersial. Hal itu...</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>https://esgnow.republika.co.id/berita/tjcfwl370/greenovate-2026-cetak-talenta-ekonomi-hijau-inovasi-mahasiswa-siap-masuk-pasar</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260806173054-524.png</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Inpicture</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Wapres Gibran Serap Aspirasi Guru Saat Tinjau Revitalisasi Sekolah di Aceh</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Edwin Dwi Putranto</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, ACEH -- Wakil Presiden Gibran Rakabuming Raka meninjau pelaksanaan revitalisasi SDN 7 Jangka di Kabupaten Bireuen, Aceh, sekaligus berdialog dengan para guru untuk mendengarkan berbagai aspirasi terkait layanan pendidikan.
+Kunjungan...</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>https://visual.republika.co.id/berita/tjcceq375/wapres-gibran-serap-aspirasi-guru-saat-tinjau-revitalisasi-sekolah-di-aceh</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/008208300-1786007322-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Nasional news</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Rosan Lapor ke Presiden Perkembangan Kampung Haji di Makkah</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:29:37 +0700</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Erik Purnama Putra</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Investasi dan Hilirisasi sekaligus CEO BPI Danantara Rosan Perkasa Roeslani memberi laporan terkini kepada Presiden RI di Istana Merdeka, Jakarta Pusat, Kamis (6/8/2026). Dia mengaku, melapor terkait hasil kunjungannya ke...</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://news.republika.co.id/berita/tjcftd484/rosan-lapor-ke-presiden-perkembangan-kampung-haji-di-makkah</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/060396500-1784253244-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>News rejabar</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Pemkot Siapkan TPST Tegalega untuk Produksi Briket RDF Bernilai Tambah</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:25:53 +0700</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, BANDUNG -- Pemerintah Kota (Pemkot) Bandung berupaya melakukan operasional Tempat Pengolahan Sampah Terpadu (TPST) Tegalega agar tidak hanya menghasilkan Refuse Derived Fuel (RDF) curah.
+Diharapkan, TPST ini juga mampu...</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://rejabar.republika.co.id/berita/tjcfn5472/pemkot-siapkan-tpst-tegalega-untuk-produksi-briket-rdf-bernilai-tambah</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/diharapkan-tpst-tegalega-mampu-memproduksi-briket-rdf-yang-memiliki_260806172419-603.jpeg</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>News rejabar</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Perkuat Diseminasi Informasi, Diskominfo Kota Bandung Selaraskan Medsos Kewilayahan Bandung Kulon</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:16:57 +0700</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, BANDUNG -- Kecamatan Bandung Kulon bersama Dinas Komunikasi dan Informatika (Diskominfo) Kota Bandung menggelar kegiatan Sinkronisasi Pengelolaan Media Sosial (Medsos) Kewilayahan, Rabu,5 Agustus 2026.
+Kegiatan ini diikuti pengelola medsos...</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://rejabar.republika.co.id/berita/tjcf89472/perkuat-diseminasi-informasi-diskominfo-kota-bandung-selaraskan-medsos-kewilayahan-bandung-kulon</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/sinkronisasi-pengelolaan-medsos-kewilayahan-diselenggarakan-kecamatan-bandung-kulon-dan_260806171556-702.jpeg</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>News rejabar</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Dinas Pendidikan Kota Bandung Pastikan Hak Belajar Siswa SDN 026 Bojongloa Tetap Terjamin</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:08:00 +0700</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, BANDUNG -- Dinas Pendidikan Kota Bandung memastikan proses pembelajaran peserta didik SDN 026 Bojongloa tetap menjadi prioritas utama. Setelah sempat terjadi penggembokan gerbang sekolah oleh pihak ahli waris...</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://rejabar.republika.co.id/berita/tjcetc472/dinas-pendidikan-kota-bandung-pastikan-hak-belajar-siswa-sdn-026-bojongloa-tetap-terjamin</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/emerintah-kota-bandung-memohon-dukungan-doa-dan-partisipasi-seluruh_260806170705-637.jpeg</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Csr esg now</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>JAPFA Buka Program Beasiswa 2026, Peserta tak Hanya Dapat Dana Pendidikan</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Japfa Comfeed Indonesia Tbk (JAPFA) bersama Edu Farmers International Foundation (Edufarmers) membuka pendaftaran Beasiswa JAPFA Untuk Anak Negeri Cohort 2026. Program tersebut tidak hanya memberikan bantuan...</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://esgnow.republika.co.id/berita/tjc8ip416/japfa-buka-program-beasiswa-2026-peserta-tak-hanya-dapat-dana-pendidikan</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pt-japfa-comfeed-indonesia-tbk-japfa-bersama-edu-farmers_260806145135-559.jpeg</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Nasional news</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Ratusan Senpi Ditemukan di Sebuah Sekolah Swasta di Jakarta</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:57:53 +0700</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Andri Saubani</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Sebanyak 995 pucuk senjata api, CD video porno hingga narkoba ditemukan dalam sebuah ruangan tertutup di sekolah swasta yang berada di Pondok Pinang, Kebayoran Lama, Jakarta Selatan....</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://news.republika.co.id/berita/tjcech409/ratusan-senpi-ditemukan-di-sebuah-sekolah-swasta-di-jakarta</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/senjata-api_210610165809-123.jpeg</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Happening</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Karyawan Burger King Dipecat karena Ucapkan ‘Free Palestine’</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:55:10 +0700</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Qommarria Rostanti</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Interaksi antara karyawan dan pelanggan restoran cepat saji Burger King di Breinigsville, Pennsylvania, Amerika Serikat, menjadi perbincangan. Peristiwa ini melibatkan seorang musisi keturunan Israel-Amerika, Rami Feinstein,...</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://ameera.republika.co.id/berita/tjce7y425/karyawan-burger-king-dipecat-karena-ucapkan-free-palestine</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/karyawan-burger-king-arianna-hamilton-hamilton-dipecat-setelah-mengucapkan_260806165006-555.jpeg</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Bandung raya</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>SDN 026 Bojongloa Bandung Digembok, Disdik Siapkan Relokasi</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:54:29 +0700</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Karta Raharja Ucu</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, BANDUNG -- Dinas Pendidikan (Disdik) Kota Bandung merespons kasus penggembokan SDN 026 Bojongloa, Jalan Cibaduyut, Kota Bandung, Jawa Barat, Kamis (6/8/2026). Mereka memastikan hak belajar siswa tetap terjamin...</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://rejabar.republika.co.id/berita/tjce6t282/sdn-026-bojongloa-bandung-digembok-disdik-siapkan-relokasi</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/sdn-026-bojongloa-di-jalan-cibaduyut-kota-bandung-disegel_260806144537-471.jpeg</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Inpicture</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Bangunan Ditertibkan, Pemkot Jakpus Janjikan Pembinaan Usaha bagi Warga Terdampak</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Edwin Dwi Putranto</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Pemerintah Kota Administrasi Jakarta Pusat tidak hanya melakukan penataan kawasan melalui penertiban bangunan semipermanen di Karet Tengsin, tetapi juga menyiapkan langkah lanjutan bagi warga yang terdampak.
+Melalui program...</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://visual.republika.co.id/berita/tjcbk3375/bangunan-ditertibkan-pemkot-jakpus-janjikan-pembinaan-usaha-bagi-warga-terdampak</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/053464600-1786005862-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Teh anget</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Keamanan Siber: Ancaman Nyata dan Upaya Kolektif Membangun Ketahanan</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:39:48 +0700</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Retizen</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Keamanan Siber di Era Digital: Ancaman Nyata dan Upaya Kolektif Membangun Ketahanan
+Perkembangan teknologi digital telah membawa perubahan besar dalam berbagai aspek kehidupan manusia. Mulai dari cara kita berkomunikasi, bekerja,...</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://retizen.republika.co.id/posts/775350/keamanan-siber-ancaman-nyata-dan-upaya-kolektif-membangun-ketahanan</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/075322300-1786009188-260806162246-451jpg.jpg</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Warga Dayak Gelar Ritual Adat di Nunukan, Desak Usut Tuntas Kasus Ujaran Kebencian</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:54:14 +0700</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Warga Dayak menggelar ritual adat di Alun-alun Nunukan dan mendesak kasus unggahan ujaran kebencian diusut tuntas.</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/175332678/warga-dayak-gelar-ritual-adat-di-nunukan-desak-usut-tuntas-kasus-ujaran</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/fkpE0epsYS6cxT9-DC0Skz5B6ek=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a745d9c6eba5.jpg</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>315 SPPG Mangkrak dan Belum Dibayar, Mitra Kontraktor Tagih Utang Rp 800 Miliar ke BGN</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:54:14 +0700</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Ratusan proyek Dapur SPPG mangkrak dan terancam batal karena Badan Gizi Nasional (BGN) menunggak pembayaran hingga Rp800 miliar sejak tahun 2025.</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/06/17322751/315-sppg-mangkrak-dan-belum-dibayar-mitra-kontraktor-tagih-utang-rp-800</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/yz9LEhg_tDwuaNJ2Ro3zvXTKZuY=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a745a41f3631.jpg</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Naskah Kuno Milik Cipto Raharjo Didigitalisasi, Dinas Arsip Boyolali Dalami Tulisan Soal Batik</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:54:14 +0700</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Dinas Arsip Boyolali akan memproses digitalisasi naskah kuno milik Cipto Raharjo. Selain itu, juga mendalami tulisan tentang batik.</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/171652178/naskah-kuno-milik-cipto-raharjo-didigitalisasi-dinas-arsip-boyolali-dalami</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/rxbYAUbv1RMruZ6hJLdacax6Ng0=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a74334de3c16.jpg</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I612"/>
+  <autoFilter ref="A1:I725"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$884</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I725"/>
+  <dimension ref="A1:I884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -34512,8 +34512,7482 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Huawei Watch GT 7 debut dengan delapan warna &amp; pembaruan mode olahraga</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:58:24 +0700</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Huawei secara resmi mengenalkan jam tangan pintar terbaru dari seri GT yaitu Huawei Watch GT 7 dengan delapan pilihan ...</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682828/huawei-watch-gt-7-debut-dengan-delapan-warna-pembaruan-mode-olahraga</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/InShot_20260806_171443696.jpg</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Gudang belerang di Australia terbakar, picu evakuasi darurat</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:58:23 +0700</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Kebakaran besar melanda gudang penyimpanan belerang di Port Adelaide, Australia Selatan, Kamis, sehingga memicu ...</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682825/gudang-belerang-di-australia-terbakar-picu-evakuasi-darurat</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/04/14/australia-1.jpg</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Prabowo tegaskan penguasaan sains dan teknologi kunci kemajuan bangsa</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:58:17 +0700</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Penguasaan sains dan teknologi merupakan kunci utama bagi kemajuan suatu bangsa, kata Presiden Prabowo Subianto dalam ...</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682824/prabowo-tegaskan-penguasaan-sains-dan-teknologi-kunci-kemajuan-bangsa</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034845.jpg</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>BGN pastikan telah copot kepala SPPG di Jayapura usai keracunan MBG</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:57:16 +0700</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono memastikan telah mencopot kepala Satuan Pelayanan Pemenuhan Gizi (SPPG) usai ...</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682820/bgn-pastikan-telah-copot-kepala-sppg-di-jayapura-usai-keracunan-mbg</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/195035.jpg</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Tiga kapal nelayan terbakar Indramayu</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:56:33 +0700</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Petugas pemadam kebakaran berupaya memadamkan api yang membakar tumpukan jaring ikan di galangan kapal nelayan ...</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5682816/tiga-kapal-nelayan-terbakar-indramayu</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Kebakaran-Galangan-Kapal-Nelayan-060826-DS-6.jpg</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Kegiatan belajar di SDN Srengseng Sawah kembali normal pascakebakaran</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:55:08 +0700</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta, Pramono Anung mengatakan kegiatan belajar mengajar di SDN 04 Srengseng Sawah akan kembali normal ...</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682813/kegiatan-belajar-di-sdn-srengseng-sawah-kembali-normal-pascakebakaran</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_2435.jpeg</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Wapres pastikan pemulihan layanan dasar pascabencana Aceh dipercepat</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:55:03 +0700</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Wakil Presiden (Wapres) RI Gibran Rakabuming Raka memastikan pemerintah akan mempercepat pemulihan infrastruktur ...</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682809/wapres-pastikan-pemulihan-layanan-dasar-pascabencana-aceh-dipercepat</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/6451a655-e82b-48bb-b6ac-d53981248abd.jpg</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Delapan wakil Indonesia jadi unggulan Kejuaraan Dunia BWF 2026</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:54:36 +0700</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Sebanyak delapan dari 11 wakil Indonesia berstatus unggulan pada Kejuaraan Dunia BWF 2026 yang berlangsung di New ...</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682807/delapan-wakil-indonesia-jadi-unggulan-kejuaraan-dunia-bwf-2026</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/IMG-20260726-WA0065_1.jpg</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Baznas bagikan 15 warung kontainer ke pelaku UMKM di Ponorogo</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:51:45 +0700</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Amil Zakat Nasional (Baznas) Ponorogo membagikan 15 unit warung kontainer kepada pelaku Usaha ...</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682768/baznas-bagikan-15-warung-kontainer-ke-pelaku-umkm-di-ponorogo</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BAZNAS-BAGIKAN-15-WARUNG-KONTAINER-KE-PELAKU-UMKM-DI-PONOROGO.jpg</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>DKI beri peringatan pada tenaga kesehatan yang cibir pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:49:32 +0700</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta, Pramono Anung menginstruksikan Dinas Kesehatan untuk memberikan peringatan kepada tenaga ...</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682804/dki-beri-peringatan-pada-tenaga-kesehatan-yang-cibir-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_2429.jpeg</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Kacang pistachio bantu jaga kesehatan jantung dan gula darah</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:48:37 +0700</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Kacang pistachio mengandung serat, lemak tak jenuh, protein, vitamin, mineral, dan antioksidan yang dikaitkan dengan ...</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682801/kacang-pistachio-bantu-jaga-kesehatan-jantung-dan-gula-darah</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/12/30/collage-2022-12-30T113441.798.jpg</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>WHO desak penguatan respons wabah Ebola di Kongo</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Organisasi Kesehatan Dunia (WHO) Tedros Adhanom Ghebreyesus menegaskan perlunya memperkuat upaya ...</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682797/who-desak-penguatan-respons-wabah-ebola-di-kongo</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/25/XxjpbeE000418_20260624_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Harga energi tinggi dorong prospek bisnis asuransi migas</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:45:20 +0700</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Presiden Direktur Tugu Insurance Adi Pramana mengatakan kenaikan harga energi global dinilai tidak hanya meningkatkan ...</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682795/harga-energi-tinggi-dorong-prospek-bisnis-asuransi-migas</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000591922.jpg</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Ekonom sebut kemudahan perizinan dapat tarik investor Merah Putih Bond</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:43:28 +0700</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Ekonom Institute for Development of Economics and Finance (INDEF) Esther Sri Astuti mengatakan perlu ada kemudahan ...</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682791/ekonom-sebut-kemudahan-perizinan-dapat-tarik-investor-merah-putih-bond</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Saham-dan-oblogasi.jpg</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>KSP dukung penyelesaian Tol Harbour Road II guna lancarkan logistik</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:43:24 +0700</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Kantor Staf Presiden (KSP) mendukung penyelesaian Jalan Tol Harbour Road II (HBR II) ruas Ancol Timur-Pluit dalam ...</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682788/ksp-dukung-penyelesaian-tol-harbour-road-ii-guna-lancarkan-logistik</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_5445.jpeg</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Pemkab Kepulauan Seribu ajak pengelola resor kelola sampah dari sumber</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:43:03 +0700</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Suku Dinas Lingkungan Hidup (Sudin LH) Kabupaten Kepulauan Seribu mengajak seluruh pengelola resor dan pulau ...</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682787/pemkab-kepulauan-seribu-ajak-pengelola-resor-kelola-sampah-dari-sumber</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_4269.jpeg</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Polisi diminta bongkar bunker usai temuan senjata di sekolah swasta Jaksel</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:01 +0700</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Tim kuasa hukum yayasan sekolah swasta di kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan, meminta polisi ...</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682776/polisi-diminta-bongkar-bunker-usai-temuan-senjata-di-sekolah-swasta-jaksel</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001014828.jpg</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>4 Jam Pencarian, Potongan Kaki Korban Mutilasi di Depok Belum Ditemukan</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:39:27 +0700</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Tim Resmob Polda Metro Jaya mencari potongan kaki korban mutilasi di Kali Licin, Depok. Pencarian melibatkan anjing K9, tapi belum membuahkan hasil.</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607416/4-jam-pencarian-potongan-kaki-korban-mutilasi-di-depok-belum-ditemukan</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tkp-potongan-kaki-korban-mutilasi-berinisial-k-51-devidetikcom-1786012693412_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Pemerintah Prioritaskan Daerah 3T dan Kelompok Rentan dalam Program MBG</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:38:43 +0700</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Menko Pangan Zulkifli Hasan pimpin Rakortas Program Makan Bergizi Gratis, fokus pada wilayah 3T dan kelompok prioritas untuk percepat pelaksanaan program.</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607415/pemerintah-prioritaskan-daerah-3t-dan-kelompok-rentan-dalam-program-mbg</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kemendagri-1786012698384_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Pramono Minta Dishub Kaji Tuntutan Sopir Angkot M44 Usai Demo di Balai Kota</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:38:42 +0700</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung merespons aksi demo sopir angkot M44 yang menuntut evaluasi rute JakLingko. Dishub diminta mempelajari tuntutan tersebut.</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607414/pramono-minta-dishub-kaji-tuntutan-sopir-angkot-m44-usai-demo-di-balai-kota</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/gubernur-dki-jakarta-pramono-anung-1785925811298_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>30 Saksi Diperiksa Terkait Satpam Tewas Ditenggelamkan di Waduk Jatiluhur</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:38:13 +0700</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Bima Bagaskara</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Polda Jabar terus selidiki kematian Sumarna, satpam Waduk Jatiluhur. Lebih dari 30 saksi telah diperiksa untuk mengungkap fakta di balik kasus ini.</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607413/30-saksi-diperiksa-terkait-satpam-tewas-ditenggelamkan-di-waduk-jatiluhur</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/06/03/menjadi-pahlawan-kemanusiaan-di-perairan-10_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Nggak Kapok, Residivis Ditangkap Lagi Usai Bobol 4 Kotak Amal di Bogor</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:28:26 +0700</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Polisi menangkap pria berinisial R, residivis pencuri kotak amal di Bogor. Pelaku ditangkap setelah meresahkan masyarakat dan dijerat hukum.</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607399/nggak-kapok-residivis-ditangkap-lagi-usai-bobol-4-kotak-amal-di-bogor</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/residivis-ditangkap-lagi-usai-bobol-4-kotak-amal-di-bogor-1786011251674_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Mencuat Usulan Pilkada Tanpa Wakil, PDIP Minta Segera Bentuk Pansus</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:25:45 +0700</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Ganjar Pranowo menilai seluruh isu terkait sistem pemilu dan pilkada sebaiknya dibahas secara menyeluruh melalui panitia khusus (pansus).</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607389/mencuat-usulan-pilkada-tanpa-wakil-pdip-minta-segera-bentuk-pansus</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/10/ketua-dpp-pdip-ganjar-pranowo-1768032012186_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>BNN dan Kampus Perkuat Kolaborasi Cegah Ancaman Narkotika</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:24:31 +0700</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Rektor UNMA Dr. Otong Syuhada menekankan kolaborasi dengan BNN untuk mencegah ancaman narkotika. Kuliah Umum Nasional hadirkan edukasi bagi mahasiswa.</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607386/bnn-dan-kampus-perkuat-kolaborasi-cegah-ancaman-narkotika</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bnn-dan-kampus-perkuat-kolaborasi-cegah-ancaman-narkotika-1786011789787_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Menghilang, Bocah Difabel di Jakbar Ditemukan Tertidur dalam Kandang Anjing</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:21:51 +0700</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Bocah penyandang disabilitas di Jakbar dilaporkan hilang hingga ditemukan tertidur di kandang anjing. Momen pertemuan dengan keluarga berlangsung haru.</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607373/menghilang-bocah-difabel-di-jakbar-ditemukan-tertidur-dalam-kandang-anjing</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bocah-penyandang-disabilitas-di-jakbar-dilaporkan-hilang-hingga-ditemukan-tertidur-di-kandang-anjing-momen-pertemuan-dengan-ke-1786011159293_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Prabowo Coba Air Minum yang Diolah BRIN dari Air Laut</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:17:45 +0700</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengecek sejumlah teknologi karya Badan Riset dan Inovasi Nasional (BRIN) di Istana, Jakarta.</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607368/prabowo-coba-air-minum-yang-diolah-brin-dari-air-laut</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/prabowo-minum-air-laut-yang-sudah-diubah-jadi-air-siap-minum-oleh-brin-dok-youtube-setpres-1786011287313_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Tol Prosiwangi Seksi 1 &amp;amp; 2 Rampung, Siap Perkuat Konektivitas di Jatim</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:43:09 +0700</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>KemenPU siap operasikan Jalan Tol Probolinggo-Situbondo-Banyuwangi sepanjang 24 km. Proyek ini tingkatkan konektivitas dan dorong pertumbuhan ekonomi di Jatim.</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8607422/tol-prosiwangi-seksi-1-2-rampung-siap-perkuat-konektivitas-di-jatim</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tol-prosiwangi-seksi-1-2-rampung-1786012829511_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Naik 32,3%, ACES Catatkan Laba Rp 509,8 Miliar di Semester I 2026</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:41:49 +0700</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>PT Aspirasi Hidup Indonesia Tbk (AHI) mencatatkan kinerja keuangan solid dengan laba meningkat 33,3%. Ekspansi ritel berlanjut dengan pembukaan 10 toko baru.</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607420/naik-32-3-aces-catatkan-laba-rp-509-8-miliar-di-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/naik-323-aces-catatkan-laba-rp-5098-miliar-di-semester-1-2026-1786012878417.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Setahun Mpok Alpa Meninggal, Suami Rutin Izin ke Kamar Sebelum Keluar Rumah</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:10:18 +0700</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Aji Darmaji mengakui gak mudah begitu saja lupa dengan Mpok Alpa. Aji masih melakukan kebiasaan seperti saat Mpok Alpa masih ada.</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607355/setahun-mpok-alpa-meninggal-suami-rutin-izin-ke-kamar-sebelum-keluar-rumah</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/23/aji-darmaji-1782192632572_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Pihak Ruben Onsu soal Perbedaan Tanggal Lahir di Surat Kesehatan</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:05:45 +0700</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Keabsahan dokumen kesehatan Ruben Onsu dipertanyakan netizen karena perbedaan tanggal lahir. Kuasa hukum menegaskan tidak ada niat manipulasi.</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606889/pihak-ruben-onsu-soal-perbedaan-tanggal-lahir-di-surat-kesehatan</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ruben-onsu-dan-sarwendah-1785990958341_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Sintya Marisca Ungkap Tantangan Main di Series My Chef in Crime</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:47:54 +0700</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>prih febriani</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>My Chef in Crime, series terbaru yang dibintangi Sintya Marisca, mengisahkan chef yang jadi tersangka. Saksikan tantangan dan konspirasi mulai 14 Agustus 2026!</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/tv-news/d-8607130/sintya-marisca-ungkap-tantangan-main-di-series-my-chef-in-crime</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sintya-marisca-1786005747790_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Yeay! Elsa Japasal Main Sinetron Pertama</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:18:56 +0700</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>prih febriani</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Elsa Japasal, akrab disapa Eca Aura, debut di sinetron Ternyata Ini Cinta sebagai Luna. Ia beradaptasi dengan peran baru dan menghadapi konflik emosional.</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607068/yeay-elsa-japasal-main-sinetron-pertama</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/11/elsa-japasal-1773208242864_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Serunya Anggi Rantika Istri Oki Rengga Hiking di Pegunungan Alpstein Swiss</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:17:16 +0700</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Anggi Rantika membagikan pengalaman hiking perdana. Tak tanggung-tanggung, istri Oki Rengga Hiking itu bertualag di Pegunungan Alpstein Swiss.</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607045/serunya-anggi-rantika-istri-oki-rengga-hiking-di-pegunungan-alpstein-swiss</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/anggi-rantika-1786003221505_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Ridho Illahi Tantang-Siap Buktikan Tuduhan Intimidasi Anak</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:07:48 +0700</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Perseteruan Ridho Illahi dan Herlina Permanasari memanas. Ridho dituduh intimidasi anak Herlina, sementara ia membantah dan menantang bukti tuduhan tersebut.</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606439/ridho-illahi-tantang-siap-buktikan-tuduhan-intimidasi-anak</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/07/08/e6a37c56-7bca-481d-88db-814ff4ca43e4_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Shawn Mendes Tulis Ucapan Manis Bikin Bruna Marquezine Mewek</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:29:19 +0700</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Penyanyi Shawn Mendes akhirnya go public terkait hubungan dengan model sekaligus aktris Bruna Marquezine. Momennya bikin menyentuh karena pas ulang tahun.</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606954/shawn-mendes-tulis-ucapan-manis-bikin-bruna-marquezine-mewek</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/shawn-mendes-1786000900937_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Ruben Onsu Sebagai Debitur Klaim Gak Terima Surat Ancaman Lelang Rumah dari Bank</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:02:54 +0700</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Ruben Onsu dan Sarwendah memanas terkait ancaman lelang rumah. Pengacara Ruben mempertanyakan kenapa Ruben sebagai debitur justru gak terima surat dari bank.</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606900/ruben-onsu-sebagai-debitur-klaim-gak-terima-surat-ancaman-lelang-rumah-dari-bank</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ruben-onsu-dan-sarwendah-1785990958341_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Kylian Mbappe Liburan di Kapal, Eh Ternyata Bareng Ester Exposito</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:22:25 +0700</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Bintang sepakbola Kylian Mbappe dan aktris Ester Exposito makin mencuri perhatian publik. Keduanya tampak menikmati waktu santai bersama di atas kapal pesiar.</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606803/kylian-mbappe-liburan-di-kapal-eh-ternyata-bareng-ester-exposito</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kylian-mbappe-1785996918786_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Pihak Sarwendah Perlihatkan Bukti Ancaman Lelang Rumah dari Bank</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:08:55 +0700</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Masalah finansial Ruben Onsu dan Sarwendah terungkap. Kuasa hukum Sarwendah menunjukkan bukti ancaman lelang rumah dan gangguan dari penagih utang.</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606789/pihak-sarwendah-perlihatkan-bukti-ancaman-lelang-rumah-dari-bank</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ruben-onsu-dan-sarwendah-1785990958073_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Ridho Illahi Bawa Keluarga Andrew Andika Soal Korban Investasi</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:30:18 +0700</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Perseteruan Ridho Illahi dan Herlina Permanasari berlanjut. Ridho klaim bukan satu-satunya korban investasi, simpan bukti percakapan untuk proses hukum.</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606390/ridho-illahi-bawa-keluarga-andrew-andika-soal-korban-investasi</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/07/08/b9667085-9393-40a0-baa9-da72f5af9277_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Pengacara Ungkit Kesetiaan Sarwendah Rawat Ruben Onsu Kritis</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:02:02 +0700</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Konflik hak asuh antara Ruben Onsu dan Sarwendah memanas. Kuasa hukum Sarwendah, Chris Sam Siwu, membela karakter dan dedikasi kliennya selama pernikahan.</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606648/pengacara-ungkit-kesetiaan-sarwendah-rawat-ruben-onsu-kritis</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ruben-onsu-dan-sarwendah-1785990958140_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Enzy Storia Salting Lihat Lesung Pipi Afgan</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:30:09 +0700</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Enzy Storia dan Afgan beradu akting dalam film Agensi Rumah Tangga. Chemistry mereka alami, meski tetap profesional. Tayang 10 September di bioskop.</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606020/enzy-storia-salting-lihat-lesung-pipi-afgan</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/05/liburan-enzy-storia-di-italia-1783245036889_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Tengku Dewi Putri Happy Ponsel Hilang di Turki Akhirnya Ketemu</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:01:10 +0700</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Tengku Dewi Putri pulang liburan dari Eropa ke Indonesia tanpa ponselnya. Setelah seminggu berlalu, dia mendapat email ponselnya ketemu di Istanbul, Turki.</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606445/tengku-dewi-putri-happy-ponsel-hilang-di-turki-akhirnya-ketemu</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tengku-dewi-putri-1785982616287_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Ridho Illahi Lapor Balik Herlina Usai Bantah Intimidasi-Sebar Data Pribadi</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:31:20 +0700</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Perseteruan Ridho Illahi dan Herlina Permanasari lanjut. Ridho klarifikasi laporan dugaan wanprestasi dan bantah tuduhan intimidasi.</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606362/ridho-illahi-lapor-balik-herlina-usai-bantah-intimidasi-sebar-data-pribadi</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/06/29/artis-ftv-ridho-ilahi-ditangkap-terkait-kasus-narkoba_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Pasha Ungu Sang Trendsetter soal Tren Celana Melorot Viral</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:12:57 +0700</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Pingkan Anggraini</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Pasha Ungu reminisces about the early 2000s trend of baggy pants. He humorously reflects on how styles have changed, urging fans to embrace new looks.</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605909/pasha-ungu-sang-trendsetter-soal-tren-celana-melorot-viral</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/pasha-ungu-1784363607510_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Ridho Illahi Bicara Usai Dilaporkan Dugaan Sebar Data Pribadi-Intimidasi</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:39:57 +0700</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Ridho Illahi buka suara setelah dilaporkan ke Polda Metro Jaya. Ia menjelaskan dugaan penipuan dan intimidasi terkait investasi bisnis yang gagal.</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606356/ridho-illahi-bicara-usai-dilaporkan-dugaan-sebar-data-pribadi-intimidasi</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/06/29/ridho-illahi-trans-tv_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Gisel Gak Mau Besar Kepala soal Kedekatan dengan Gempi Jadi Panutan</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:05:34 +0700</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Gisel mengaku gak mau besar kepala soal pola asuh kepada Gempi yang banyak dijadikan panutan orang.</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606329/gisel-gak-mau-besar-kepala-soal-kedekatan-dengan-gempi-jadi-panutan</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/gisel-1785835834670_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Rieke Diah Pitaloka Akui Akting Jadi Oasis Saat Sibuk di DPR</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:38:42 +0700</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Rieke Diah Pitaloka kembali berakting di film Seni Merayu Tuhan. Ia tekankan pentingnya proses casting dan dalami karakter meski sibuk sebagai anggota DPR.</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606340/rieke-diah-pitaloka-akui-akting-jadi-oasis-saat-sibuk-di-dpr</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/rieke-diah-pitaloka-1785978111254_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Suguhan Spesial Dewa 19 di Konser Simfoni Mahayuga</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:16:48 +0700</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>prih febriani</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Dewa 19 feat Virzha akan menggelar konser Simfoni Mahayuga di TIM Jakarta pada 9 Agustus 2026, menampilkan lagu langka dan aransemen baru.</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8606354/suguhan-spesial-dewa-19-di-konser-simfoni-mahayuga</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/24/ahmad-dhani-1777010483706_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Respons Imel Putri saat Pertama Bertemu Zaskia Gotik</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:05:47 +0700</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Imel Putri memberikan pernyataan soal pertemuan pertama dengan Zaskia Gotik.</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606120/respons-imel-putri-saat-pertama-bertemu-zaskia-gotik</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/imel-putri-cahyati-dan-zaskia-gotik-1785906056841_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Let's Go! Agatha Chelsea Mulai Perjalanan sebagai Mahasiswi Harvard</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:11:22 +0700</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Selebritas Agatha Chelsea mulai perjalanan sebagai mahasiswi Harvard.</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8605250/lets-go-agatha-chelsea-mulai-perjalanan-sebagai-mahasiswi-harvard</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/agatha-chelsea-1785911522464_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Gak Tahu Selvi Kitty Selebritas, Suami: Saya Menikahi sebagai Personal</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:04:17 +0700</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Suami mengaku gak tahu Selvi Kitty adalah seorang selebritas.</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606096/gak-tahu-selvi-kitty-selebritas-suami-saya-menikahi-sebagai-personal</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/03/selvi-kitty-1783097593555_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Rizky Billar Tunggu Itikad Baik Pelaku Usai Uang Rp 3,1 M Raib</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:09:14 +0700</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Rizky Billar menunggu itikad baik terduga pelaku penggelapan Rp 3,1 miliar. Ia menuntut penyelesaian segera atau akan melapor ke polisi.</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606092/rizky-billar-tunggu-itikad-baik-pelaku-usai-uang-rp-3-1-m-raib</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/rizky-billar-1785477825510_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Bapanas Selidiki Alasan Beras Fortifikasi Dijual Mahal</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:53:45 +0700</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Bapanas mulai menyelidiki alasan harga beras fortifikasi yang dijual jauh lebih mahal dibandingkan beras medium maupun premium.</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806165944-92-1389399/bapanas-selidiki-alasan-beras-fortifikasi-dijual-mahal</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/13/stock-beras-di-pasar-induk-beras-cipinang-1768288836321_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>CEO Krealogi: Banyak Program Keberlanjutan Gagal karena Kejar Angka</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:43:33 +0700</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>CEO Krealogi Azalea Ayuningtyas menilai banyak program keberlanjutan gagal karena terlalu mengejar capaian angka  dibandingkan fokus ke dampak jangka panjang.</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806172921-92-1389407/ceo-krealogi-banyak-program-keberlanjutan-gagal-karena-kejar-angka</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/azalea-ayuningtyas-1786001833454_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Zulhas Kejar Dapur MBG di Daerah 3T Rampung Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:22:07 +0700</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Menko Pangan Zulkifli Hasan menargetkan penyelesaian pembangunan SPPG atau dapur MBG di wilayah tertinggal, terdepan, dan terluar (3T) rampung pekan ini.</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806163042-92-1389384/zulhas-kejar-dapur-mbg-di-daerah-3t-rampung-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/16/menteri-koordinator-bidang-pangan-zulkifli-hasan-1778906619843_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Menkop Groundbreaking KDKMP Dekai, Sasar Pelosok Papua Pegunungan</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:06:47 +0700</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Dengan sumber daya alam melimpah di Yahukimo, Menkop mendorong agar KDKMP dapat memberi manfaat hingga ke pelosok Papua Pegunungan.</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806165506-97-1389397/menkop-groundbreaking-kdkmp-dekai-sasar-pelosok-papua-pegunungan</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/kemenkop-1786010378325_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Kementerian UMKM Dorong CSR Jadi Bagian Bisnis Inti Perusahaan</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:56:39 +0700</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Kementerian UMKM mendorong penguatan CSR agar tidak lagi dipandang sebagai sekadar bantuan sosial, tetapi menjadi bagian bisnis inti perusahaan.</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806164408-92-1389391/kementerian-umkm-dorong-csr-jadi-bagian-bisnis-inti-perusahaan</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/plt-deputi-bidang-usaha-mikro-deputi-bidang-kewirausahaan-kementerian-umkm-m-riza-damanik-di-the-bangun-bangsa-conference-1786010108061_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Pakar Wanti-wanti Program Sosial Sulit Berdampak Tanpa Data Valid</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:42:26 +0700</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Guru Besar Trisakti Juniati Gunawan menegaskan data tidak valid menjadi tantangan terbesar dalam penerapan prinsip keberlanjutan dan pengambilan kebijakan.</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806162451-532-1389379/pakar-wanti-wanti-program-sosial-sulit-berdampak-tanpa-data-valid</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/prof-juniati-gunawan-phd-guru-besar-head-of-trisakti-sustainability-center-tsc-di-di-the-bangun-bangsa-conference-1786001195158_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>BGN Temukan Sekitar 6 Juta Data Ganda Siswa Calon Penerima MBG</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:32:42 +0700</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono mengungkap pihaknya menemukan sekitar 6 juta data ganda calon penerima program Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806155931-92-1389369/bgn-temukan-sekitar-6-juta-data-ganda-siswa-calon-penerima-mbg</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bos-bgn-ultimatum-dapur-mbg-1785936867455_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>IHSG Turun Tipis ke 6.343 Sore Ini</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:21:39 +0700</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>IHSG ditutup di level 6.343 pada perdagangan Kamis (6/8) sore. Indeks saham melemah 7,42 poin atau minus 0,12 persen dari perdagangan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806161645-92-1389375/ihsg-turun-tipis-ke-6343-sore-ini</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/04/19/ilustrasi-ihsg-saham_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>DJP Resmi Tunda Pungutan Pajak Marketplace Jadi 1 November 2026</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:13:59 +0700</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>DJP menunda penerapan pemungutan PPh Pasal 22 oleh marketplace terhadap pedagang online resmi ditunda menjadi 1 November 2026.</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806155801-532-1389368/djp-resmi-tunda-pungutan-pajak-marketplace-jadi-1-november-2026</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/01/29/17a0cca1-16cd-4090-b64a-f0191e6989d2_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Rupiah Ditutup Menguat Tipis ke Rp17.923 per Dolar AS Sore Ini</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:57:00 +0700</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah ditutup di posisi Rp17.923 per dolar AS pada Kamis (6/8), menguat 10 poin atau 0,06 persen dibandingkan penutupan perdagangan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806153602-78-1389350/rupiah-ditutup-menguat-tipis-ke-rp17923-per-dolar-as-sore-ini</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/09/05/68b24196-a62f-4419-981b-4edec1eb28eb_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Social Value Indonesia Ingatkan Dampak CSR Tak Instan</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:51:53 +0700</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Chairperson of Board Social Value Indonesia Purnomo mengingatkan dampak dari sebuah program Tanggung Jawab Sosial Perusahaan (CSR) tidak hadir secara instan.</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806154518-92-1389362/social-value-indonesia-ingatkan-dampak-csr-tak-instan</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/purnomo-chairperson-social-value-indonesia-1786001337417_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Kemenkop Dorong Investasi Kemasyarakatan Bangun Kemandirian Ekonomi</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:11:30 +0700</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Kemenkop menekankan pentingnya program community investment dari dunia usaha untuk berfokus pada kemandirian ekonomi masyarakat.</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806143233-92-1389318/kemenkop-dorong-investasi-kemasyarakatan-bangun-kemandirian-ekonomi</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/destry-anna-sari-1786001087698_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Pemerintah Tak Mau Warga Bergantung Bansos, Ini Strategi Kemenko PM</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:51:12 +0700</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Kemenko PM mendorong perubahan pendekatan pemberdayaan masyarakat yang sejalan dengan arahan presiden agar masyarakat tak terus bergantung pada bansos.</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806124636-532-1389260/pemerintah-tak-mau-warga-bergantung-bansos-ini-strategi-kemenko-pm</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/01/23/banjir-bansos-di-tahun-politik-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Istana Buka Suara soal Kemenkeu Ambil Alih Saham Kereta Cepat</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:32:24 +0700</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi menyebut skema pembayaran utang proyek kereta cepat KCIC akan diatur langsung oleh Menteri Keuangan Purbaya Yudhi Sadewa.</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806132855-532-1389285/istana-buka-suara-soal-kemenkeu-ambil-alih-saham-kereta-cepat</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/istana-buka-suara-soal-pengambilalihan-saham-kereta-cepat-oleh-kemenkeu-1785997652333_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>CEO Olahkarsa: Investasi Sosial Gagal Jika Hanya Ikuti Siklus Anggaran</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:20:08 +0700</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer (CEO) Olahkarsa Unggul Ananta menilai banyak program investasi sosial (community investment) gagal memberikan dampak berkelanjutan.</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806140424-92-1389298/ceo-olahkarsa-investasi-sosial-gagal-jika-hanya-ikuti-siklus-anggaran</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/chief-executive-officer-ceo-olahkarsa-unggul-ananta-di-the-bangun-bangsa-conference-1785999864129_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Purbaya Bantah Isu Batas Defisit APBN 3 Persen dari PDB Bakal Dihapus</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:10:11 +0700</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya membantah kabar pemerintah akan menghapus batas defisit Anggaran Pendapatan dan Belanja Negara (APBN) sebesar 3 persen dari PDB.</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806065417-532-1389127/purbaya-bantah-isu-batas-defisit-apbn-3-persen-dari-pdb-bakal-dihapus</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/06/menteri-keuangan-purbayaa-yudhi-sadewa-1780743339703_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>IBCWE Sarankan Program Inklusif untuk Perempuan Pakai Social Mapping</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:06:38 +0700</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>IBCWE menyatakan keberhasilan program investasi sosial tidak cukup diukur dari keterlibatan perempuan sebagai peserta.</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806140244-532-1389296/ibcwe-sarankan-program-inklusif-untuk-perempuan-pakai-social-mapping</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/wita-krisanti-1785999843209_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Peternak Apresiasi Mentan Tahan Harga Pakan dan Genjot Penyerapan Telur</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:51:02 +0700</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Pemerintah menahan harga pakan dan mempercepat distribusi jagung, memberi harapan bagi peternak ayam petelur, diharapkan dapat stabilkan harga telur.</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806124223-97-1389257/peternak-apresiasi-mentan-tahan-harga-pakan-genjot-penyerapan-telur</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/bnr-kementan-jul-agustus-310-1785993829203_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>BPS Bongkar Jemaah Haji RI Habiskan Rp2 T Cuma Buat Ini</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:50:25 +0700</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>BPS mencatat jemaah haji Indonesia menghabiskan hampir Rp2 triliun untuk oleh-oleh. Total pengeluaran pribadi diperkirakan mencapai Rp4,25 triliun.</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806130901-532-1389275/bps-bongkar-jemaah-haji-ri-habiskan-rp2-t-cuma-buat-ini</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/bps-belanja-haji-2026-sumbang-rp88-t-ke-ekonomi-ri-1785992604239_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Guru Besar UI: Community Investment Harus Dimulai dari Kebutuhan-Aset</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:49:14 +0700</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Guru Besar FISIP UI Isbandi Rukminto Adi menilai program community investment atau investasi sosial tidak boleh hanya berangkat dari asumsi perusahaan.</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806133755-532-1389288/guru-besar-ui-community-investment-harus-dimulai-dari-kebutuhan-aset</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/the-bangun-bangsa-coference-2026-1785989754991_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Bentoel Tinggalkan CSR Sekali Jalan, Kejar Efek Sosial Jangka Panjang</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:36:21 +0700</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Bentoel Group mengubah pendekatan program CSR yang sebelumnya bersifat satu kali (one-off) menjadi investasi sosial yang punya dampak jangka panjang.</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806130909-92-1389276/bentoel-tinggalkan-csr-sekali-jalan-kejar-efek-sosial-jangka-panjang</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/dian-widyanarti-1786000262028_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Said Iqbal soal Rencana Demo Besar-besaran Buruh: Itu Tidak Benar</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:25:07 +0700</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Presiden KSPI sekaligus Presiden Partai Buruh Said Iqbal menegaskan tidak ada rencana aksi demonstrasi besar-besaran buruh sepanjang Agustus-September 2026.</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806125900-92-1389265/said-iqbal-soal-rencana-demo-besar-besaran-buruh-itu-tidak-benar</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/08/purbaya-terima-said-iqbal-1783497478382_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Antisipasi 40 Merek Beras Fortifikasi Ditarik, Bulog Sidak Stok Ritel</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:11:00 +0700</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Perum Bulog antisipasi penarikan beras fortifikasi dan pastikan ketersediaan beras premium di ritel modern. Sidak dilakukan untuk menjaga stok dan kualitas.</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806121009-92-1389241/antisipasi-40-merek-beras-fortifikasi-ditarik-bulog-sidak-stok-ritel</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/bulog-antisipasi-penarikan-40-merek-beras-fortifikasi-1785990406252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>BPS: Belanja Haji 2026 Sumbang Rp8,8 T ke Ekonomi RI</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:50:34 +0700</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>BPS mencatat belanja haji 2026 berkontribusi Rp8,78 triliun ke perekonomian RI. Total pengeluaran seluruh jemaah haji tahun ini mencapai Rp29,25 triliun.</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806120810-532-1389240/bps-belanja-haji-2026-sumbang-rp88-t-ke-ekonomi-ri</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/bps-belanja-haji-2026-sumbang-rp88-t-ke-ekonomi-ri-1785992604155_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Bappenas Ungkap Transisi Ekonomi Hijau Bisa Buka 5 Juta Lapangan Kerja</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:32:33 +0700</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Menteri PPN/ Kepala Bappenas Rachmat Pambudy mengungkapkan transisi ekonomi hijau bisa membuka setidaknya lebih dari 5 juta lapangan kerja pada 2029.</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806121011-532-1389243/bappenas-ungkap-transisi-ekonomi-hijau-bisa-buka-5-juta-lapangan-kerja</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/the-bangun-bangsa-coference-2026-1785988721541_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Danantara Siapkan IPO BUMN, Pegadaian hingga Injourney Masuk Daftar</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:10:43 +0700</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>COO BPI Danantara Dony Oskaria mengatakan penawaran umum perdana saham (IPO) akan menjadi salah satu strategi transformasi BUMN dalam lima tahun ke depan.</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806071341-92-1389138/danantara-siapkan-ipo-bumn-pegadaian-hingga-injourney-masuk-daftar</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/08/dony-oskaria-1780890082276_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>PLTA Punya Umur Panjang, Operasi Bisa Lebih dari 100 Tahun</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:55:48 +0700</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Pembangkit listrik tenaga air (PLTA) memiliki usia operasional yang sangat panjang, bahkan bisa beroperasi lebih dari 100 tahun.</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806114757-85-1389234/plta-punya-umur-panjang-operasi-bisa-lebih-dari-100-tahun</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/03/23/bf02f88f-b454-4740-82e8-3589cf217b1b_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>BRI Consumer Expo 2026 Goes to PIK2 Tawarkan Beragam Promo Menarik</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:44:44 +0700</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>BRI menghadirkan BRI Consumer Expo 2026 Goes to PIK2 bagi masyarakat yang ingin memperoleh berbagai pilihan produk perumahan dengan beragam promo.</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806113500-625-1389228/bri-consumer-expo-2026-goes-to-pik2-tawarkan-beragam-promo-menarik</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/bri-consumer-expo-2026-goes-to-pik2-1785991152789_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Bappenas: Ekonomi Hijau Prioritas Utama Pembangunan Nasional</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:40:59 +0700</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Menteri PPN/ Kepala Bappenas Rachmat Pambudy menegaskan ekonomi hijau merupakan prioritas utama pembangunan nasional.</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806111713-532-1389225/bappenas-ekonomi-hijau-prioritas-utama-pembangunan-nasional</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/the-bangun-bangsa-coference-2026-1785988721625_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Purbaya Bantah Pakai Koramil-Babinsa untuk Dongkrak Penerimaan Pajak</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:20:21 +0700</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan (Menkeu) Purbaya Yudhi Sadewa menegaskan aparat TNI dan Polri tidak akan dilibatkan untuk menagih maupun meningkatkan penerimaan pajak.</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806062004-532-1389111/purbaya-bantah-pakai-koramil-babinsa-untuk-dongkrak-penerimaan-pajak</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/11/purbaya-yudhi-sadewa-1757582339808_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Bangun Bangsa Conference 2026 Usung 3 Isu Utama</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:17:02 +0700</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Bangun Bangsa Conference 2026 resmi dimulai di Menara Bank Mega pada Kamis (6/8) dengan tiga isu utama yang dibahas.</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806104215-532-1389218/bangun-bangsa-conference-2026-usung-3-isu-utama</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/the-bangun-bangsa-coference-2026-1785989754991_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Kemenkeu Siap Ambil Alih Saham Kereta Cepat, Tak Pakai APBN</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:59:05 +0700</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Kemenkeu akan alihkan saham kereta cepat dari konsorsium BUMN ke SMV untuk mengelola tanpa membebani APBN. Target pengalihan selesai September 2026.</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806091953-532-1389169/kemenkeu-siap-ambil-alih-saham-kereta-cepat-tak-pakai-apbn</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/purbaya-danantara-sepakat-alihkan-saham-bumn-di-kcic-1785924066818_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Presiden IBCSD Dorong Investasi Sosial Jadi Strategi Bisnis Perusahaan</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:57:59 +0700</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Indonesia Business Council for Sustainable Development (IBCSD) mendorong dunia usaha menjadikan investasi pada masyarakat sebagai bagian dari strategi bisnis.</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806105240-92-1389220/presiden-ibcsd-dorong-investasi-sosial-jadi-strategi-bisnis-perusahaan</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/the-bangun-bangsa-coference-2026-1785988317226_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>FOTO: Penampakan Harley-Davidson Bekas Asal China yang Diselundupkan</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:35:22 +0700</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Antara Foto</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Bea Cukai Tanjung Priok membeberkan modus penyelundupan sepeda motor Harley-Davidson bekas asal China.</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20250523151901-534-1232477/foto-penampakan-harley-davidson-bekas-asal-china-yang-diselundupkan</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bea-cukai-gagalkan-penyelundupan-harley-davidson-asal-china-1785924745143_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Harga Minyak Dunia Lumer ke US$79,08 Pagi Ini Berkat Sinyal Damai</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:15:57 +0700</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Sementara itu, minyak mentah West Texas Intermediate (WTI) AS terkoreksi 53 sen atau 0,7 persen ke level US$74,69 per barel.</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806095744-85-1389188/harga-minyak-dunia-lumer-ke-us-7908-pagi-ini-berkat-sinyal-damai</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/09/17/41b03f02-9109-4fad-af23-748fb73dc353_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Terbang Rp50 Ribu ke Level Rp2,676 Juta Hari Ini</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:54:46 +0700</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Adapun Logam Mulia mencatat harga buyback emas Antam hari ini naik Rp90 ribu menjadi Rp2,490 juta per gram dibandingkan perdagangan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806094657-92-1389177/harga-emas-antam-terbang-rp50-ribu-ke-level-rp2676-juta-hari-ini</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/04/17/berburu-emas-batangan-meskipun-harga-terus-naik-1744874240153_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Pasokan Aman, BULOG Perluas Distribusi Beras Premium ke Retail Modern</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:45:10 +0700</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Dengan semakin luasnya jaringan pemasaran, masyarakat memiliki lebih banyak pilihan beras premium dengan mutu yang terjamin dan harga yang kompetitif.</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806080148-97-1389148/pasokan-aman-bulog-perluas-distribusi-beras-premium-ke-retail-modern</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/perum-bulog-1785978654130_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Rupiah Gagah ke Level Rp17.913 per Dolar AS Pagi Ini</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:34:20 +0700</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Analis memperkirakan rupiah masih berpeluang menguat pada perdagangan hari ini seiring meredanya tekanan dari harga minyak mentah dunia.</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806085600-78-1389157/rupiah-gagah-ke-level-rp17913-per-dolar-as-pagi-ini</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/09/05/2594c7ac-d6ac-46fd-bf5c-d47017b19b30_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Bos BGN Ancam Tutup Dapur MBG Sebabkan Keracunan</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:05:03 +0700</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono menegaskan SPPG alias dapur program MBG yang menyebabkan kasus keracunan akan langsung disuspensi dan diinvestigasi.</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806070155-92-1389137/bos-bgn-ancam-tutup-dapur-mbg-sebabkan-keracunan</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bos-bgn-ultimatum-dapur-mbg-1785936867518_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Purbaya Buka Suara soal Isu Gaji Manajer Kopdes Merah Putih Rp16 Juta</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:45:43 +0700</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya membantah kabar yang menyebut gaji manajer Koperasi Desa/Kelurahan Merah Putih (Kopdes Merah Putih) akan mencapai Rp16 juta per bulan.</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806063432-532-1389117/purbaya-buka-suara-soal-isu-gaji-manajer-kopdes-merah-putih-rp16-juta</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/14/purbaya-tak-akan-kejar-kejar-orang-kaya-demi-genjot-penerimaan-pajak-rl-1784021265783_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Daftar Jabatan yang Pernah Diemban Sri Mulyani di Bank Dunia</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:31:12 +0700</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Sri Mulyani Indrawati, ekonom Indonesia, ditunjuk sebagai Ketua Bersama IDA Bank Dunia. Dia akan memimpin penggalangan dana untuk negara termiskin dunia.</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805181511-532-1389009/daftar-jabatan-yang-pernah-diemban-sri-mulyani-di-bank-dunia</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/09/sertijab-menkeu-sri-mulyani-ke-purbaya-yudhi-sadewa-1757396049358_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Cerahkan Ekonomi RI, Bangun Bangsa Conference 2026 Digelar Hari Ini</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:02:58 +0700</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Bangun Bangsa Conference 2026 di Jakarta membahas pertumbuhan komunitas berkelanjutan dan ekonomi inklusif. Diskusi melibatkan pemerintah, bisnis dan akademisi.</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260728152549-532-1385772/cerahkan-ekonomi-ri-bangun-bangsa-conference-2026-digelar-hari-ini</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/12/01/kawasan-sudirman_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Membaca Arah Ekonomi RI usai Melaju 5,29 Persen di Kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:30:28 +0700</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Lidya Julita Sembiring</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Ekonomi Indonesia tumbuh 5,29 persen di kuartal II 2026, didorong konsumsi pemerintah dan investasi. Pemerintah dinilai perlu jaga momentum hingga akhir tahun.</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806062053-532-1389113/membaca-arah-ekonomi-ri-usai-melaju-529-persen-di-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/05/13/terowongan-kendal-steril-dari-pedagang-kaki-lima-10_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Airlangga Respons soal Jurang Si Kaya dan Miskin Kian Melebar</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:05:34 +0700</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Menko Airlangga buka suara mengenai kenaikan tingkat ketimpangan di Indonesia setelah rasio gini (gini ratio) pada Maret 2026 tercatat sebesar 0,368.</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805203327-532-1389078/airlangga-respons-soal-jurang-si-kaya-dan-miskin-kian-melebar</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/03/kemenko-perekonomian-1783046333120_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Bank Dunia Tugaskan Sri Mulyani Urus Dana untuk Negara Miskin</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:35:01 +0700</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Bank Dunia menunjuk mantan Menteri Keuangan Sri Mulyani sebagai Ketua Bersama Independen Asosiasi Pembangunan Internasional (IDA).</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806060552-532-1389109/bank-dunia-tugaskan-sri-mulyani-urus-dana-untuk-negara-miskin</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/07/08/rtm-pelaksanaan-sekolah-rakyat-1751972795346_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>IHSG Diproyeksi Lanjut Ngegas Hari Ini</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:15:21 +0700</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>IHSG diproyeksi menguat pada perdagangan Kamis (6/8) dengan potensi di kisaran 6.403-6.420. Analis merekomendasikan saham ADRO, ASII, dan lainnya.</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806060305-92-1389108/ihsg-diproyeksi-lanjut-ngegas-hari-ini</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/05/11/1e656f7c-100b-45e5-b9d3-3d0904b21184_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Respons Mendag soal Temuan 80% Beras Fortifikasi Tak Sesuai Standar</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:45:29 +0700</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Mendag Budi Santoso merespons temuan Mentan Andi Amran Sulaiman yang menyebut sekitar 80 persen beras fortifikasi yang diperiksa diduga tidak memenuhi standar.</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805190549-92-1389041/respons-mendag-soal-temuan-80-beras-fortifikasi-tak-sesuai-standar</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/23/menteri-perdagangan-mendag-ri-budi-santoso-1784802559812_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Mendag Respons Ekspor Nikel Dkk Disetop Efek Aturan Logam Tanah Jarang</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:45:49 +0700</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso buka suara terkait revisi aturan ekspor mineral yang mengandung unsur logam tanah jarang (LTJ).</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805185304-92-1389037/mendag-respons-ekspor-nikel-dkk-disetop-efek-aturan-logam-tanah-jarang</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/13/menteri-perdagangan-mendag-budi-santoso-1778639529234_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>PLN Gaet Swasta untuk Garap 262 Proyek PLTA dan PLTM hingga 2034</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 03:45:18 +0700</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>PLN melibatkan swasta dalam 315 proyek PLTA dan PLTM hingga 2034, dengan kapasitas total 11,7 GW. Kolaborasi jadi kunci sukses pembangunan energi terbarukan.</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260805141937-85-1388898/pln-gaet-swasta-untuk-garap-262-proyek-plta-dan-pltm-hingga-2034</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/pln-ungkap-proyek-pembangkit-hidro-117-gw-butuh-investasi-rp627-t-1785910336593_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>BGN Ungkap Dobel Data Penerima MBG Capai Sekitar 6 Juta Orang</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:37:35 +0700</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kepala Badan Gizi Nasional (BGN) Sudaryono mengungkap adanya data yang tidak akurat pada penerima manfaat program Makan Bergizi Gratis (MBG). Hal itu disampaikannya usai rapat koordinasi terbatas...</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcden423/bgn-ungkap-dobel-data-penerima-mbg-capai-sekitar-6-juta-orang</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/022010200-1785818124-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Lelang Batubara Hasil Penindakan Tambah PNBP Rp 20,97 Miliar, ESDM Kawal Pascalelang</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:16:09 +0700</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kementerian Energi dan Sumber Daya Mineral (ESDM) meraup tambahan Penerimaan Negara Bukan Pajak (PNBP) sebesar Rp 20.976.670.000 dari lelang batubara hasil penegakan hukum di Kalimantan Timur. Tambahan...</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjccex423/lelang-batubara-hasil-penindakan-tambah-pnbp-rp-2097-miliar-esdm-kawal-pascalelang</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/tambang_250804123609-455.jpg</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Galeri 24 Kejar Laba di Atas Rp1,3 Triliun Tahun Ini</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Pegadaian Galeri Dua Empat (Galeri 24) membidik laba lebih dari Rp1,3 triliun pada 2026 seiring pertumbuhan bisnis perdagangan emas yang terus berlanjut. Hingga akhir Juni...</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc6wa416/galeri-24-kejar-laba-di-atas-rp13-triliun-tahun-ini</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/039015800-1761909672-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Berantas Praktik Curang, Amran Perketat Pengawasan Beras Fortifikasi</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:17:19 +0700</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kepala Badan Pangan Nasional (Bapanas) sekaligus Menteri Pertanian Andi Amran Sulaiman memastikan pengawasan beras fortifikasi diperketat melalui pemeriksaan yang lebih luas terhadap mutu, kandungan gizi, perizinan, serta...</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc9ov490/berantas-praktik-curang-amran-perketat-pengawasan-beras-fortifikasi</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/menteri-pertanian-mentan-andi-amran_260730145848-982.jpg</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Banggar DPR Sebut Faktor Musiman Dongkrak Pertumbuhan Ekonomi Kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:54:33 +0700</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Badan Anggaran Dewan Perwakilan Rakyat (Banggar DPR) RI menilai faktor musiman turut mendongkrak perekonomian Indonesia yang tumbuh 5,29 persen pada kuartal II 2026 dibandingkan dengan periode yang...</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc8mx490/banggar-dpr-sebut-faktor-musiman-dongkrak-pertumbuhan-ekonomi-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/ketua-badan-anggaran-banggar-dpr-ri-said-abdullah-menegaskan_220914194552-782.jpeg</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Pengangguran Terbuka di Jateng Capai 960 Ribu Orang per Mei 2026</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:40:13 +0700</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, SEMARANG — Badan Pusat Statistik (BPS) Provinsi Jawa Tengah (Jateng) mengungkapkan, jumlah pengangguran terbuka di Jateng per Mei 2026 mencapai 960 ribu orang. Jika dibandingkan dengan Februari 2026, jumlah...</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc7z1423/pengangguran-terbuka-di-jateng-capai-960-ribu-orang-per-mei-2026</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/096165000-1784736607-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>BI Yakin Ekonomi 2026 Tetap Tumbuh hingga 5,7 Persen</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Bank Indonesia (BI) mempertahankan proyeksi pertumbuhan ekonomi Indonesia pada kisaran 4,9 persen hingga 5,7 persen sepanjang 2026. Optimisme tersebut ditopang oleh kinerja ekonomi semester I yang tumbuh...</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc7jx416/bi-yakin-ekonomi-2026-tetap-tumbuh-hingga-57-persen</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/056307800-1717057747-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Waskita Gandeng ANRI Perkuat Tata Kelola Kearsipan</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:36:38 +0700</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Waskita Karya (Persero) Tbk melakukan serah terima arsip statis kepada Arsip Nasional Republik Indonesia (ANRI). Langkah ini merupakan bentuk kepatuhan sekaligus pemenuhan kewajiban yang diamanatkan undang-undang.
+Dokumen...</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc7t2490/waskita-gandeng-anri-perkuat-tata-kelola-kearsipan</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/waskita-karya-meraih-kontrak-baru-sebesar-rp12-5-triliun-sepanjang_260402121822-688.jpeg</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Komisaris Pertamina Patra Niaga Pastikan Keandalan Energi di Bali</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, DENPASAR – Komisaris Utama PT Pertamina Patra Niaga, Sabar Yudo Suroso, bersama Komisaris PT Pertamina Patra Niaga, Wanti Waranei F. Mamahit, melakukan Management Walkthrough (MWT) di wilayah Bali,...</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc4sh522/komisaris-pertamina-patra-niaga-pastikan-keandalan-energi-di-bali</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/komisaris-utama-pt-pertamina-patra-niaga-sabar-yudo-suroso_260806133123-665.jpeg</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Bittime Dukung Langkah OJK Perketat Industri Aset Kripto</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Otoritas Jasa Keuangan (OJK) memperkuat pengawasan terhadap industri aset kripto dengan menghentikan 228 Pedagang Aset Keuangan Digital (PAKD) ilegal hingga Mei 2026. Langkah tersebut dinilai dapat memperkuat...</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc5q8416/bittime-dukung-langkah-ojk-perketat-industri-aset-kripto</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_250508110733-775.png</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Ekonomi Tumbuh 5,29 Persen, Kemiskinan Turun, Mengapa Daya Beli Masyarakat Belum Pulih?</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:24:20 +0700</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Penurunan angka kemiskinan menjadi kabar menggembirakan di tengah pertumbuhan ekonomi Indonesia yang mencapai 5,29 persen pada kuartal II 2026. Namun, sejumlah indikator menunjukkan perbaikan tersebut belum...</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc78k370/ekonomi-tumbuh-529-persen-kemiskinan-turun-mengapa-daya-beli-masyarakat-belum-pulih</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/009601800-1770627250-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Efek Pemangkasan TKD, Pemkot Cimahi Khawatir TPP ASN Terancam</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:10:38 +0700</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, CIMAHI -- Kebijakan pemangkasan Transfer ke Daerah (TKD) memicu tekanan berkepanjangan terhadap kondisi fiskal Pemerintah Kota (Pemkot) Cimahi. Kondisi ini berpotensi menimbulkan risiko terhambatnya pembangunan serta pembayaran gaji dan...</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc6lq423/efek-pemangkasan-tkd-pemkot-cimahi-khawatir-tpp-asn-terancam</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/003460200-1684833732-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Fesyen Lokal Kian Menguat, Discovery Commerce Perluas Pasar dan Tingkatkan Penjualan</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:44:51 +0700</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Industri fesyen lokal terus menunjukkan peran strategis sebagai penggerak ekonomi nasional. Untuk memperkuat pertumbuhan merek fesyen lokal, TikTok Shop by Tokopedia mengusung kampanye #BeliLokal dalam Indonesia...</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc5er370/fesyen-lokal-kian-menguat-discovery-commerce-perluas-pasar-dan-tingkatkan-penjualan</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260806134433-206.png</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Pemerintah Tunda Pajak Marketplace hingga November 2026 demi Jaga Daya Beli</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Direktorat Jenderal Pajak (DJP) Kementerian Keuangan memutuskan untuk menunda implementasi pemungutan Pajak Penghasilan (PPh) Pasal 22 atas transaksi pada platform lokapasar (marketplace). Hal itu dilakukan demi...</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjc49m370/pemerintah-tunda-pajak-marketplace-hingga-november-2026-demi-jaga-daya-beli</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/004008600-1702393340-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Opsi 3 Sekolah Relokasi Pascainsiden SDN Kebayoran Lama Selatan Roboh</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:00:04 +0700</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Sebelumnya, murid terpaksa belajar dalam kondisi seadanya setelah SDN Kebayoran Lama Selatan 09 roboh.</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263670/opsi-3-sekolah-relokasi-pascainsiden-sdn-kebayoran-lama-selatan-roboh</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/XwmZ5D9e2CMkOo7xdszvvt5nxIw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9303092/original/073670500_1784618204-1000989135.jpg</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Pertanian Hidroganik, Jurus Jitu Ketahanan Pangan dan Urban Farming di Palu</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:41:11 +0700</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Pemkot Palu mengandalkan pertanian hidroganik sebagai solusi urban farming untuk memperkuat ketahanan pangan. Caranya dengan memanfaatkan lahan sempit</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8260825/pertanian-hidroganik-jurus-jitu-ketahanan-pangan-dan-urban-farming-di-palu</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/5P7OXzHKNLew_kUpvgbj1o2ogoA=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9313889/original/050967100_1785721725-watermarked_img_8211827384851360367.jpg</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Jejak Terakhir IWD, Eks Ketua Yayasan Sekolah Swasta Penguasa Bunker Berisi Ratusan Senpi</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:38:39 +0700</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>IWD diberhentikan karena dugaan menyalahgunakan keuangan yayasan untuk kepentingan pribadi.</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263636/jejak-terakhir-iwd-eks-ketua-yayasan-sekolah-swasta-penguasa-bunker-berisi-ratusan-senpi</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Jejak Panjang Masinis Indonesia</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:55:20 +0700</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Sudah lebih dari satu setengah abad, masinis menjadi bagian dalam perjalanan sejarah perkeretaapian Indonesia.</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263645/jejak-panjang-masinis-indonesia</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/XamGwc3sai9XqNzzh5jjtpgD33I=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/1652226/original/028594700_1500379068-_DSC3359.jpeg</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Ramai Isu Pergantian Kapolri, Istana Buka Suara</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:04 +0700</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi menjawab isu pergantian Kapolri.</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263641/ramai-isu-pergantian-kapolri-istana-buka-suara</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/_br72lp4vVWS5CLZakL8R6QgFI4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/7767979/original/011455400_1780578714-IMG_3908__1_.jpeg</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Jakarta Timur Gencarkan Gerakan Pilah Sampah, Ini yang Dilakukan</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:16:29 +0700</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>HBKB Jakarta Timur dimanfaatkan Pemkot Jakarta Timur untuk mengedukasi warga tentang pemilahan sampah dan memperkuat kesadaran lingkungan. (AI Generated).</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8255454/jakarta-timur-gencarkan-gerakan-pilah-sampah-ini-yang-dilakukan</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/upreIj66hI7P3_7dvqcNOAxf_64=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9308336/original/024807300_1785137635-ChatGPT_Image_27_Jul_2026__14.30.04.jpg</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Koperasi Merah Putih Harus Jadi Pendorong Ekonomi Desa Berbasis Potensi Lokal</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:58:06 +0700</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Koperasi harus menjadi penggerak hilirisasi agar hasil laut dan perkebunan diolah, dipasarkan, dan memberikan nilai tambah yang dinikmati masyarakat desa.</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263469/koperasi-merah-putih-harus-jadi-pendorong-ekonomi-desa-berbasis-potensi-lokal</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Jk1Flp5jCFQLRpABkkrcKNbABjI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316200/original/076957300_1785917199-Zulhas_Koperasi.jpeg</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Usai 995 Senjata, Sekolah di Jaksel Kembali Temukan Narkoba, hingga CD Porno</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:37:42 +0700</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Pengurus sekolah juga mengaku masih menemukan satu ruangan menyerupai bunker yang hingga kini belum berhasil dibuka.</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263580/usai-995-senjata-sekolah-di-jaksel-kembali-temukan-narkoba-hingga-cd-porno</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Polisi Kerahkan K-9 Cari Bagian Tubuh Korban Mutilasi di Kali Licin</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:24:55 +0700</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Polda Metro masih mencari potongan tubuh korban mutilasi dengan bantuan anjing pelacak K-9.</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263559/polisi-kerahkan-k-9-cari-bagian-tubuh-korban-mutilasi-di-kali-licin</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/LBt8tXj1_Cz4eJVC5_JOrt1zRdM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317289/original/030834100_1786008290-20260806_133113.jpg</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Ada Bunker Rahasia di Sekolah Jaksel, Tempat Penemuan Ratusan Senjata Api</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:57:40 +0700</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Kuasa hukum yayasan, Hermawanto khawatir masih ada senjata atau barang terlarang lain yang tersimpan di dalamnya.</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263555/ada-bunker-rahasia-di-sekolah-jaksel-tempat-penemuan-ratusan-senjata-api</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Enam Profesor UT Ingatkan Ilmu Pengetahuan Harus Menjawab Kehidupan</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:10:18 +0700</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Pengukuhan Profesor UT tahun ini menjadi bagian penting dari rangkaian Dies Natalis ke-42 UT.</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263531/enam-profesor-ut-ingatkan-ilmu-pengetahuan-harus-menjawab-kehidupan</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/NGGv5gTRKrwwgJYjPWGgOE4fSz4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317232/original/098283800_1786007411-Pengukuhan_profesor_UT.jpeg</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Jelang HUT RI, Prabowo Kumpulkan Menhan sampai Pimpinan TNI</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo kumpulkan pimpinan TNI bahas program pembangunan dan persiapan HUT ke-81 Kemerdekaan RI.</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263523/jelang-hut-ri-prabowo-kumpulkan-menhan-sampai-pimpinan-tni</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/7rezoWnVECUgvzdA-Wav3g5ho-c=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317223/original/030459400_1786006897-IMG_3299.jpg</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Pengelolaan Sampah Mandiri Kurangi Beban TPA Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:04:11 +0700</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Pemkab Gunungkidul mendorong pengelolaan sampah mandiri melalui bank sampah, TPS3R, dan pengolahan sampah rumah tangga untuk mengurangi beban TPA.</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8261612/pengelolaan-sampah-mandiri-kurangi-beban-tpa-gunungkidul</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/NV6ybeIdtOhIw8-jTTfXOLn4_bk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/8407960/original/020894400_1782291107-ChatGPT_Image_24_Jun_2026__15.43.56.jpg</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Nasib Eks Ketua BEM UBK Usai Akui Terima Duit Bayaran Demo</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>M. Abdimaludin, eks Ketua BEM UBK, diskors dua semester usai mengakui terima uang Rp 20 juta terkait demo.</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263510/nasib-eks-ketua-bem-ubk-usai-akui-terima-duit-bayaran-demo</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Q9A2d6FS85ySxjK1TLVYocI0OA8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317201/original/095330200_1786005536-93d5030f-dade-4871-b4f5-9b3c898c7bee.jpg</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Pemotor Tak Berdaya saat Disergap Perampok Bersenjata di Bekasi</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:32:34 +0700</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Pengendara motor di Cibitung dirampok saat parkir, aksi pelaku terekam kamera dan viral.</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263505/pemotor-tak-berdaya-saat-disergap-perampok-bersenjata-di-bekasi</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/TrJZ9UE_uJpRX4gpeLxEJi1GfBk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317199/original/055221900_1786005151-WhatsApp_Image_2026-08-06_at_15.04.03.jpeg</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>PAN Respons Usulan Pilkada Tanpa Wakil: Bagus dan Simpatik</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:22:26 +0700</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>PAN menilai usulan Pilkada tanpa wakil kepala daerah layak dipertimbangkan dan dikaji lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263490/pan-respons-usulan-pilkada-tanpa-wakil-bagus-dan-simpatik</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/JwqYB1obtM3z3pcCP-Qhz1Cm5xY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4532767/original/071716600_1691641578-WhatsApp_Image_2023-08-10_at_11.15.29__1_.jpeg</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Komisi IX DPR: Nakes Jangan Hilang Empati</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:42:45 +0700</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Kecaman muncul setelah viral komentar tenaga kesehatan terhadap pasien BPJS yang kemudian meninggal dunia, memicu sorotan terhadap etika profesi di media sosial.</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263395/komisi-ix-dpr-nakes-jangan-hilang-empati</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ci7Pc-0rF-7Amg_GhMV6r78s5_M=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9315762/original/044264700_1785892339-yurizal_ok.jpg</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Detik-detik Gudang SDN 04 Srengseng Sawah Terbakar</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:46:24 +0700</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Gudang penyimpanan buku SDN 04 Srengseng Sawah terbakar, api cepat dipadamkan sebelum merembet.</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263374/detik-detik-gudang-sdn-04-srengseng-sawah-terbakar</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/5ousgPr5dU4zlrH7YwVTIZCGRjg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316980/original/088687100_1785998781-WhatsApp_Image_2026-08-06_at_13.41.21.jpeg</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Gudang SDN Srengseng Sawah 04 Terbakar Saat Kegiatan Belajar Mengajar</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:45:19 +0700</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Petugas pemadam kebakaran melakukan pendinginan di gudang SDN Srengseng Sawah 04, Kecamatan Jagakarsa, Jakarta Selatan, Kamis (6/8/2026). Gudang yang menyimpan buku dan alat musik tradisional terbakar saat kegiatan belajar mengajar berlangsung. Suku Dinas Penanggulangan Kebakaran dan Penyelamatan Jakarta Selatan mengerahkan 15 unit armada yang terdiri atas delapan unit pompa dan tujuh unit pendukung dengan total 60 personel. Api berhasil dipadamkan sehingga tidak merembet ke ruang kelas maupun bangunan lainnya.</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8263373/gudang-sdn-srengseng-sawah-04-terbakar-saat-kegiatan-belajar-mengajar</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/n-URUsLqJv0DdXeEAzRpCjBLd8I=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316973/original/091365800_1785998707-sreng1.jpg</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>KPK Ungkap Menhut Raja Juli Diduga Tak Cuma Sekali Temui Bupati Kuansing</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:41:38 +0700</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Juru Bicara KPK Budi Prasetyo mengatakan, pertemuan pada 2 Juni bukanlah yang pertama.</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263366/kpk-ungkap-menhut-raja-juli-diduga-tak-cuma-sekali-temui-bupati-kuansing</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/QjqXMyr542XnoOWmkkwylLS7D10=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5616746/original/005533300_1778202507-57316f55-f4f7-455d-9c12-7372ebfd6541.jpeg</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Pramono Siapkan Lift Disabilitas Usai Aksi Pramusapa Viral</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:47:25 +0700</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta menyiapkan lift penyeberangan bagi penyandang disabilitas setelah aksi pramusapa Transjakarta membantu penumpang viral di media sosial.</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263423/pramono-siapkan-lift-disabilitas-usai-aksi-pramusapa-viral</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/zDC9l1ECUUyW7uyCu02aeeYmbN4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317046/original/070177700_1786001581-IMG_3296.jpg</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Roy Suryo Kembali Melawan, Ajukan Praperadilan Baru</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:33:41 +0700</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Roy Suryo menyiapkan praperadilan baru setelah permohonan ganti rugi Rp 200 juta tak diterima hakim.</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263351/roy-suryo-kembali-melawan-ajukan-praperadilan-baru</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/_GaBw5NML_gK5VzT4dzk4u0y0jw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/8673924/original/064756300_1782715045-8b339f5c-5296-40f5-b4c9-ab830a996d58.jpeg</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>PDIP Ingatkan Peran Ibu di Balik Generasi Bangsa Berkualitas</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:27:32 +0700</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>PDIP melalui Sekjen Hasto Kristiyanto mengingatkan pentingnya peran ibu dalam membentuk generasi bangsa berkualitas.</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263344/pdip-ingatkan-peran-ibu-di-balik-generasi-bangsa-berkualitas</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/TVQvkDifQis1Il952UXRStBebA8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316947/original/039573700_1785997631-ee717174-b372-422b-94e1-c05c2257a6e6.jpg</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Polisi Temukan Tersangka Mutilasi di Depok Gabung Komunitas Gay</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:09:06 +0700</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Namun, polisi belum menyimpulkan bahwa keanggotaan tersangka dalam grup itu berkaitan dengan motif pembunuhan.</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263333/polisi-temukan-tersangka-mutilasi-di-depok-gabung-komunitas-gay</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/3_XSuRpVsw7mR1OINb8kGSne_JA=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316566/original/060113700_1785945727-WhatsApp_Image_2026-08-05_at_22.56.47.jpeg</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Fakta Baru Kasus Mutilasi Depok, Pelaku Incar Harta Korban</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:59:52 +0700</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Dalam kasus mutilasi Kunaefi di Depok, polisi menduga Saepullah merencanakan pembunuhan demi menguasai harta korban.</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263321/fakta-baru-kasus-mutilasi-depok-pelaku-incar-harta-korban</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/1iiaomed9-X6pKdh2Bzdunu9-zk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316565/original/074193900_1785945709-WhatsApp_Image_2026-08-05_at_22.56.47__1_.jpeg</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>SD di Jagakarsa Kebakaran</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:42:00 +0700</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Sebanyak 17 unit mobil pemadam dan 68 personel dikerahkan untuk menangani kebakaran tersebut.</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263306/sd-di-jagakarsa-kebakaran</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/kqC2Pq5iVFJVCUAr11Y0occyE6o=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316887/original/070750900_1785994915-WhatsApp_Image_2026-08-06_at_12.00.47.jpeg</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Pramono Punya Cara Baru Ubah Kebiasaan Sampah Jakarta</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung menekankan pentingnya pendidikan pilah sampah sejak usia dini.</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263288/pramono-punya-cara-baru-ubah-kebiasaan-sampah-jakarta</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/NKZ-iWppoys5zkmu912A9CcPrPM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5525274/original/049838400_1773036532-IMG_7709.jpeg</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Kenapa Penduduk Jakarta Berkurang Ribuan Orang, Ternyata Ini Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:31:29 +0700</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Penurunan penduduk Jakarta mencapai 2.838 jiwa.</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263298/kenapa-penduduk-jakarta-berkurang-ribuan-orang-ternyata-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/z92OZyFJKZZuh99qajrMKY8u8yQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/3894535/original/042247000_1641302185-20220104-PPKM_DKI_Jakarta_Naik_ke_Level_2-1.jpg</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>ART Diduga Disekap di Kelapa Gading, KTP Ditahan hingga Diminta Uang</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:20:03 +0700</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Korban lapor polisi melalui layanan Hotline 110 pada Selasa (4/8/2026) siang.</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263281/art-diduga-disekap-di-kelapa-gading-ktp-ditahan-hingga-diminta-uang</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/5Y9N1gb6kifdc0BUtQSeNxb4xKw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/2320245/original/076392300_1533533412-1533533412367325a1f9c9196ede-1512021137-30ae43ad1aa0a416699051b73a3dfcf6.jpg</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Ultimatum untuk Dapur MBG: Urus SLHS atau Ditutup!</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:33:21 +0700</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>SLHS adalah syarat mutlak dalam operasional dapur MBG, bukan sekadar kelengkapan administrasi.</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263237/ultimatum-untuk-dapur-mbg-urus-slhs-atau-ditutup</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/A7I6G7HBNviW-ig563-eBhNqrvc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9315680/original/094273700_1785851037-DSC09754.JPG</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Praperadilan Roy Suryo soal Ganti Rugi Rp 200 Juta Ditolak</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Penolakan karena cacat formil, karena Menteri Keuangan tidak ditarik sebagai pihak.</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263230/praperadilan-roy-suryo-soal-ganti-rugi-rp-200-juta-ditolak</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/hzJpaJXsAW8FgPeiggKTx28aiy8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316811/original/029393100_1785990479-IMG_2697.jpg</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Waspada Kemarau Panjang, Jakarta Siapkan Hujan Buatan 2 Kali Sepekan</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:28:58 +0700</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Puncak musim kemarau diperkirakan terjadi pada akhir September hingga pertengahan Oktober</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263232/waspada-kemarau-panjang-jakarta-siapkan-hujan-buatan-2-kali-sepekan</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/VpvQuWKhOkEi9RmepqMLAF7Vz4Q=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4038725/original/060241700_1653990107-Cuaca_Ekstrem_Melanda_Jakarta-Faizal_Fanani-3.JPG</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>KPK Duga Uang Amplop Raja Juli Belum Dikembalikan Semua</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:17:26 +0700</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>KPK menduga uang amplop yang diterima Menteri Kehutanan Raja Juli Antoni dari Bupati Kuansing nonaktif Suhardiman Amby belum dikembalikan sepenuhnya.</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263213/kpk-duga-uang-amplop-raja-juli-belum-dikembalikan-semua</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/QjqXMyr542XnoOWmkkwylLS7D10=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5616746/original/005533300_1778202507-57316f55-f4f7-455d-9c12-7372ebfd6541.jpeg</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Antusias Murid SD Jalani Imunisasi HPV</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:21:46 +0700</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Pelaksanaan Bulan Imunisasi Anak Sekolah (BIAS) 2026 kembali digelar sebagai upaya memperkuat perlindungan kesehatan anak. Salah satunya berlangsung di SDN Gandul 1, Depok, Jawa Barat, Kamis (6/8/2026), saat murid kelas V menerima vaksin Human Papillomavirus (HPV). Program yang digelar setiap Agustus dan November ini mencakup pemberian vaksin campak-rubella, difteri, tetanus, dan HPV sesuai kelompok usia untuk menjaga kekebalan tubuh serta mencegah penyakit yang masih berpotensi menimbulkan kejadian luar biasa.</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8263209/antusias-murid-sd-jalani-imunisasi-hpv</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/5Kb4bkUBDbrgw2_FEyCpE8JCOv8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316787/original/074153700_1785989436-imu5.jpg</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Said Abdullah Ungkap Catatan di Balik Ekonomi 5,29 Persen</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Said Abdullah menyoroti pertumbuhan ekonomi Indonesia 5,29 persen di Q2 2026 yang patut disyukuri.</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263195/said-abdullah-ungkap-catatan-di-balik-ekonomi-529-persen</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Hj-lOnCTefnRlxsiNSY-JB2QAIU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316775/original/069679200_1785988824-9ad6070e-b741-4ae0-991c-aa0c23294d10.jpg</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>War Tiket HUT ke-81 RI Diserbu 128 Ribu Orang, Peserta dari 14 Negara</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:11:41 +0700</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Besarnya minat tersebut mencerminkan semangat kebangsaan sekaligus antusiasme masyarakat untuk menyaksikan langsung upacara di Istana Merdeka.</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263157/war-tiket-hut-ke-81-ri-diserbu-128-ribu-orang-peserta-dari-14-negara</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/voAM4ERcE1yrvtZEfo8q-McdTWk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5318124/original/057002400_1755424877-WhatsApp_Image_2025-08-17_at_13.49.06_ee2d54dd.jpg</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>KPK Duga Bupati Kuansing Setor Uang ke Pejabat Kemenhut</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:56:00 +0700</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>KPK menduga Bupati Kuansing Suhardiman Amby menyetor uang SGD 12.500 kepada pejabat Kemenhut.</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263149/kpk-duga-bupati-kuansing-setor-uang-ke-pejabat-kemenhut</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/1auyCMIXIPHH1OgTj2VCLd7PBXs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/8793285/original/012088700_1782899757-kpk7.jpg</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Penduduk Jakarta Berkurang Ribuan Orang, Ini Data Terbarunya</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:49:53 +0700</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Selain mencatat data kependudukan terbaru, DKI Jakarta juga menjadi provinsi dengan capaian aktivasi IKD tertinggi secara nasional.</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263147/penduduk-jakarta-berkurang-ribuan-orang-ini-data-terbarunya</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/1Lkc5X5yU7Q9hiKDrL2ooES16SM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4175713/original/091328900_1664458434-Pemprov_DKI_Akan_Dukung_Pencabutan_Status_Pandemi_Covid-19-IQBAL_3.jpg</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Ultimatum Sudaryono Tertibkan Dapur MBG Bermasalah</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Membenahi dapur MBG bermasalah menjadi salah satu fokus utama Kepala BGN Sudaryono usai dilantik.</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263050/ultimatum-sudaryono-tertibkan-dapur-mbg-bermasalah</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/Mp00hKSCi-QazLx9tIXNy9fK2js=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9312420/original/096653700_1785491450-40603f1f-f0f2-4626-9878-f11bfbfc0c16.jpeg</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Jakarta Bakal Diguyur Hujan Buatan Tiap Pekan</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:13:24 +0700</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Hujan buatan itu merupakan strategi Pemprov DKI Jakarta menghadapi dampak dari fenomena el nino.</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263054/jakarta-bakal-diguyur-hujan-buatan-tiap-pekan</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/83vWfF8-EKy0mX3__TbiecrpT10=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4521888/original/068671200_1690882636-20230801-Gelombang-Panas-El-Nino-Jakarta-Faizal-2.jpg</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Ketika Empati Hilang, Coreng Wajah Pelayanan Kesehatan</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:00:59 +0700</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Komentar nirempati terhadap Yurizal memicu sorotan publik soal empati tenaga kesehatan.</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263028/ketika-empati-hilang-coreng-wajah-pelayanan-kesehatan</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/IiOsgxGbLOMN1ZXS3TxNv_P2qTk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9315744/original/019758300_1785885131-yurizal.webp</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Duel Indonesia Vs Singapura Jadi Kans Baker Kembali Pimpin Top Skor Piala AFF 2026</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:05:18 +0700</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Torehan gol Mitchell Baker di Piala AFF 2026 kini disamai oleh penyerang Myanmar eks Borneo FC, Win Naing Tun.</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/06/18044728/duel-indonesia-vs-singapura-jadi-kans-baker-kembali-pimpin-top-skor-piala-aff</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/4LIHxDYmqc4xH7mG_4xbfG6QFFQ=/15x54:1487x1035/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/07/31/6a6c926a5dc0e.png</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Exit Tol Cipayung Depok di Ruas Tol Sawangan-Bojonggede Ditargetkan Rampung 2027</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:05:18 +0700</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Exit Tol Cipayung pada ruas Tol Sawangan-Bojonggede ditargetkan rampung pada 2027. Pemkot Depok mempercepat pembebasan lahan.</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/06/17452281/exit-tol-cipayung-depok-di-ruas-tol-sawangan-bojonggede-ditargetkan</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/QYdgTec7wcwjFLmiyhohZ7vG9Ws=/150x22:750x422/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2022/03/25/623d6fdcbe9b9.jpeg</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Tol Sawangan-Bojonggede Dilanjutkan, Exit Tol Cipayung Depok Akan Dibangun</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:05:18 +0700</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Pembangunan Tol Sawangan-Bojonggede berlanjut. Ruas baru ini akan dilengkapi Exit Tol Cipayung, Depok.</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/06/17291661/tol-sawangan-bojonggede-dilanjutkan-exit-tol-cipayung-depok-akan-dibangun</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/t4-2dioazU0M8LvnJI0_A5YqeHg=/0x0:750x500/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2022/03/25/623d6fdcbe9b9.jpeg</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I725"/>
+  <autoFilter ref="A1:I884"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$884</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1029</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I884"/>
+  <dimension ref="A1:I1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -41986,8 +41986,6823 @@
         </is>
       </c>
     </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Menkum bakal gratiskan tarif PNBP pemberitahuan laporan tahunan RUPS</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:44:45 +0700</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Menteri Hukum Supratman Andi Agtas berencana menggratiskan tarif Penerimaan Negara Bukan Pajak (PNBP) pemberitahuan ...</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683047/menkum-bakal-gratiskan-tarif-pnbp-pemberitahuan-laporan-tahunan-rups</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000473338.jpg</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Pesona Galaxy Z Fold8 berhasil pikat banyak pemilik Z Flip beralih</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:44:09 +0700</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Perusahaan teknologi, Samsung mengatakan setelah Galaxy Z Fold8 debut di pasaran dengan tampilan yang baru ternyata ...</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683043/pesona-galaxy-z-fold8-berhasil-pikat-banyak-pemilik-z-flip-beralih</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/InShot_20260806_191407456.jpg</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>BNPB: 40 ribu liter air didistribusikan untuk 741 KK di Lamongan</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:39:18 +0700</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) memastikan sebanyak 40 ribu liter air bersih telah didistribusikan untuk ...</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683039/bnpb-40-ribu-liter-air-didistribusikan-untuk-741-kk-di-lamongan</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/30/IMG-20260330-WA0008.jpg</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Luksemburg tolak Schengen dijadikan alat tekanan politik</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:38:59 +0700</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri Luksemburg Leon Gloden mengatakan negara-negara Uni Eropa tidak seharusnya menjadikan kawasan ...</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683035/luksemburg-tolak-schengen-dijadikan-alat-tekanan-politik</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Spanyol-Migran-memasuki-Ceuta_1.jpg</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Korut tembakkan rudal balistik, tak ada konfirmasi kerusakan di Jepang</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:38:04 +0700</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Korea Utara pada Kamis menembakkan sedikitnya satu rudal balistik, dan tidak ada proyektil yang diyakini jatuh di dalam ...</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683031/korut-tembakkan-rudal-balistik-tak-ada-konfirmasi-kerusakan-di-jepang</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/04/03/Korut-rudal.jpg</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>KAI Daop 7 Madiun salurkan dana program TJSL sebesar Rp123,126 juta</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:37:12 +0700</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) Daop 7 Madiun menyalurkan dana program tanggung jawab sosial (TJSL) perusahaan dan ...</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683029/kai-daop-7-madiun-salurkan-dana-program-tjsl-sebesar-rp123126-juta</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/tjsl.jpeg</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Orang tua dan anak bisa bermain Roblox bersama lewat fitur Family Zone</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:36:17 +0700</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Gim daring Roblox memperkenalkan fitur Family Zone yang menawarkan pengalaman interaktif untuk membantu orang tua dan ...</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683028/orang-tua-dan-anak-bisa-bermain-roblox-bersama-lewat-fitur-family-zone</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000141766.jpg</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Kemendukbangga salurkan MBG 3B ke 9,6 juta penerima manfaat</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:35:47 +0700</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Kementerian Kependudukan dan Pembangunan Keluarga (Kemendukbangga) Republik Indonesia hingga Kamis (6/8/2026), telah ...</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683025/kemendukbangga-salurkan-mbg-3b-ke-96-juta-penerima-manfaat</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/mendukbangga5.jpg</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Kejari Wonosobo selidiki dugaan penyimpangan bansos PKH</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:33:51 +0700</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>ANTARA - Kejaksaan Negeri Wonosobo, Jawa Tengah, mengungkap dugaan penyimpangan penyaluran bantuan sosial Program ...</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683021/kejari-wonosobo-selidiki-dugaan-penyimpangan-bansos-pkh</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_KEJARI-WONOSOBO-SELIDIKI-DUGAAN-PENYIMPANGAN-BANSOS-PKH.jpg</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>BMKG: Musim kemarau turunkan kualitas udara di Sumsel</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:27:56 +0700</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mencatat kualitas udara di Sumatera Selatan masih berada ...</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683008/bmkg-musim-kemarau-turunkan-kualitas-udara-di-sumsel</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BMKG-MUSIM-KEMARAU-TURUNKAN-KUALITAS-UDARA-DI-SUMSEL.jpg</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Polda Banten kerahkan water cannon atasi krisis air dampak kemarau</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:27:02 +0700</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Kepolisian Daerah (Polda) Banten mengalihfungsikan kendaraan taktis water cannon yang biasa digunakan untuk ...</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683019/polda-banten-kerahkan-water-cannon-atasi-krisis-air-dampak-kemarau</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000876362.jpg</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>IDI: Burnout bukan alasan komentar nirempati ke pasien</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:26:19 +0700</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Ikatan Dokter Indonesia (IDI) mengatakan, burnout bukan alasan bagi tenaga kesehatan dan tenaga medis untuk bersikap ...</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683017/idi-burnout-bukan-alasan-komentar-nirempati-ke-pasien</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000177677.jpg</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Jasa Marga sebut progres pembangunan jalan Jogja-Solo capai 98 persen</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:26:08 +0700</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>PT Jasa Marga (Persero) menyatakan perkembangan proyek strategis nasional (PSN) pembangunan jalan tol Jogja-Solo ruas ...</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683015/jasa-marga-sebut-progres-pembangunan-jalan-jogja-solo-capai-98-persen</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_185719.jpg</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Menperin beri tiga arahan demi perkuat ekosistem startup RI</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:18:42 +0700</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Menteri Perindustrian (Menperin) Agus Gumiwang Kartasasmita memberikan tiga arahan untuk memperkuat ekosistem startup ...</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683005/menperin-beri-tiga-arahan-demi-perkuat-ekosistem-startup-ri</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-18.46.24_edit_306839271755781.jpg</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Basarnas sisir lewat udara lokasi kebakaran KMP Mutiara Sentosa II</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:16:14 +0700</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Badan Nasional Pencarian dan Pertolongan (Basarnas) mengerahkan helikopter HR-1301 untuk melakukan penyisiran lewat ...</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683001/basarnas-sisir-lewat-udara-lokasi-kebakaran-kmp-mutiara-sentosa-ii</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-17.54.30.jpeg</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Prabowo sedih Indonesia tak lolos Piala Dunia, singgung Cape Verde</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:13:51 +0700</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengaku sedih Indonesia belum mampu lolos ke putaran final Piala Dunia sepak bola meski ...</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682997/prabowo-sedih-indonesia-tak-lolos-piala-dunia-singgung-cape-verde</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-2835945.jpg</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Realisasi investasi NTB TW II Rp33T, tembus 51 persen dari target 2026</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:13:17 +0700</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Provinsi Nusa Tenggara Barat mencatatkan ...</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682880/realisasi-investasi-ntb-tw-ii-rp33t-tembus-51-persen-dari-target-2026</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_REALISASI-INVESTASI-NTB-TW-II-RP33T-TEMBUS-51-PERSEN-DARI-TARGET-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Pemprov Lampung: Satelit Lampung-1 dukung pengembangan pertanian</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:11:46 +0700</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Lampung menyatakan bahwa adanya satelit Lampung-1 dapat mendukung pengembangan sektor ...</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682993/pemprov-lampung-satelit-lampung-1-dukung-pengembangan-pertanian</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/VID-20260805-WA0027-1.jpg</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Fajar 2026 digelar perkuat rantai industri halal Jateng</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:07:22 +0700</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Festival Jawa Tengah Syariah (Fajar) 2026 kembali digelar oleh Kantor Perwakilan Bank Indonesia Provinsi Jateng dan ...</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682989/fajar-2026-digelar-perkuat-rantai-industri-halal-jateng</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1002084042.jpg</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Bulog Jabar perluas distribusi beras premium jaga harga sesuai HET</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:06:44 +0700</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Perum Bulog Kantor Wilayah Jawa Barat memperluas jangkauan distribusi 3.000 ton pasokan beras premium hasil produksi ...</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682985/bulog-jabar-perluas-distribusi-beras-premium-jaga-harga-sesuai-het</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1002082362.jpg</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Gubernur Koster ingin jadikan Bali sebagai hub ekspor</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:04:41 +0700</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Gubernur Bali Wayan Koster mulai menggarap tata kelola yang menjadikan Pulau Dewata sebagai hub atau penghubung ekspor ...</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682983/gubernur-koster-ingin-jadikan-bali-sebagai-hub-ekspor</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_144511.jpg</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Lima armada damkar dikerahkan padamkan kebakaran kapal di Indramayu</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:04:08 +0700</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Satuan Polisi Pamong Praja (Satpol PP) dan Pemadam Kebakaran (Damkar) Kabupaten Indramayu mengerahkan lima armada ...</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682979/lima-armada-damkar-dikerahkan-padamkan-kebakaran-kapal-di-indramayu</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001521111.jpg</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Tembus West End, kini rancang koreografi Home Sweet Loan The Musical</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:03:47 +0700</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Film "Home Sweet Loan" diadaptasi menjadi pertunjukan teater musikal lewat kolaborasi Visinema, Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682975/tembuswest-endkini-rancang-koreografi-home-sweet-loan-the-musical</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_113606.jpg</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>BGN percepat pembangunan SPPG 3T targetkan rampung dalam satu minggu</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:03:10 +0700</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) mempercepat pembangunan dan aktivasi Satuan Pelayanan Pemenuhan Gizi (SPPG) di wilayah ...</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682971/bgn-percepat-pembangunan-sppg-3t-targetkan-rampung-dalam-satu-minggu</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0015.jpg</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Presiden: Pengentasan kemiskinan harus dilakukan dengan cara rasional</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:01:47 +0700</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengatakan langkah pengentasan kemiskinan dalam upaya memastikan kebangkitan bangsa harus ...</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682968/presiden-pengentasan-kemiskinan-harus-dilakukan-dengan-cara-rasional</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/27d03785-b673-4948-938e-08b30202c584.jpeg</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Dinkes: Ada 89 SPPG di Tangerang belum miliki SLHS</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:00:51 +0700</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Dinas Kesehatan (Dinkes) Kabupaten Tangerang, Banten, mencatat sebanyak 89 dari total 312 unit Satuan Pemenuhan ...</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682965/dinkes-ada-89-sppg-di-tangerang-belum-miliki-slhs</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000415240.jpg</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Kepala BRIN: Indonesia sedang bangun kapabilitas teknologi nasional</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:58:43 +0700</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Kepala Badan Riset dan Inovasi Nasional (BRIN) Arif Satria menegaskan bahwa Indonesia saat ini sedang berfokus pada ...</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682961/kepala-brin-indonesia-sedang-bangun-kapabilitas-teknologi-nasional</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-2835941.jpg</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Kebakaran di SDN 04 Srengseng Sawah diduga karena korsleting listrik</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:54:55 +0700</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Suku Dinas Pendidikan Wilayah I Jakarta Selatan mengungkap penyebab kebakaran di gudang penyimpanan buku SDN 04 ...</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682959/kebakaran-di-sdn-04-srengseng-sawah-diduga-karena-korsleting-listrik</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001015028.jpg</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>BSSN catat 182 potensi serangan siber tiap detik lewat internet</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:54:34 +0700</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Badan Siber dan Sandi Negara (BSSN) mencatat rata-rata 182 potensi serangan siber per detik terhadap berbagai entitas ...</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682957/bssn-catat-182-potensi-serangan-siber-tiap-detik-lewat-internet</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_171401.jpg</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>KSP: Tol Harbour Road II Elevated dukung kelancaran logistik</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:54:22 +0700</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>ANTARA - Progres pembangunan Jalan Tol Harbour Road II Elevated di Jakarta Utara telah mencapai 44 persen dan ...</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5682879/ksp-tol-harbour-road-ii-elevated-dukung-kelancaran-logistik</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_KSP-TOL-HARBOUR-ROAD-II-ELEVATED-DUKUNG-KELANCARAN-LOGISTIK.jpg</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>KB Bank perkuat kemandirian ekonomi disabilitas melalui pelatihan</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:54:07 +0700</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>PT Bank KB Indonesia Tbk (KB Bank) bekerja sama dengan Terala Foundation memperkuat pemberdayaan ekonomi penyandang ...</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682955/kb-bank-perkuat-kemandirian-ekonomi-disabilitas-melalui-pelatihan</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000177986.jpg</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Fakta-fakta kasus viral Yurizal pasien BPJS yang meninggal dunia</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:52:47 +0700</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Kasus meninggalnya Yurizal Tri Chaerawan menjadi sorotan publik setelah kisahnya viral di media sosial. Sebelum ...</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682951/fakta-fakta-kasus-viral-yurizal-pasien-bpjs-yang-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/07/WhatsApp-Image-2026-02-04-at-14.27.31.jpeg</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Menkes: Nakes sebagai pelayan masyarakat tak boleh nirempati</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:51:36 +0700</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Menteri Kesehatan (Menkes) Budi Gunadi Sadikin menegaskan tenaga kesehatan (nakes) sebagai pelayan masyarakat tidak ...</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682947/menkes-nakes-sebagai-pelayan-masyarakat-tak-boleh-nirempati</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/20260806_142431.jpg</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Realisasi investasi Jakarta capai Rp173,6 triliun pada semester I 2026</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:49:50 +0700</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Realisasi investasi Jakarta mencapai Rp173,6 triliun atau 17,2 persen dari total realisasi investasi nasional, pada ...</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682944/realisasi-investasi-jakarta-capai-rp1736-triliun-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_2438.jpeg</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Bappenas: Peningkatan kesehatan ibu dan anak jadi prioritas nasional</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:49:39 +0700</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Sekretaris Kementerian Perencanaan Pembangunan Nasional/Sekretaris Utama Badan Perencanaan Pembangunan Nasional ...</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682940/bappenas-peningkatan-kesehatan-ibu-dan-anak-jadi-prioritas-nasional</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Teni.jpg</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Polres Nabire libatkan ahli digital forensik usut pembunuhan siswi SMP</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:49:19 +0700</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Polres Nabire melibatkan ahli digital forensik untuk mengekstraksi data dari tiga telepon seluler sebagai bagian dari ...</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682937/polres-nabire-libatkan-ahli-digital-forensik-usut-pembunuhan-siswi-smp</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-20.01.06.jpeg</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>GP Ansor Kalteng kerahkan ratusan personel bantu penanganan karhutla</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:47:16 +0700</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Gerakan Pemuda (GP) Ansor Kalimantan Tengah (Kalteng) mengerahkan ratusan personel untuk berkolaborasi mendukung ...</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682935/gp-ansor-kalteng-kerahkan-ratusan-personel-bantu-penanganan-karhutla</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001727437.jpg</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Sejarah upacara HUT RI 17 Agustus: Awal mula, makna, dan perkembangannya</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:46:06 +0700</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Upacara bendera dalam rangka memperingati Hari Ulang Tahun (HUT) Kemerdekaan Republik Indonesia setiap 17 Agustus ...</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682931/sejarah-upacara-hut-ri-17-agustus-awal-mula-makna-dan-perkembangannya</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/18/WhatsApp-Image-2026-05-17-at-09.18.03.jpeg</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Kuasa hukum sebut eks ketua yayasan simpan senpi dan narkotika di sekolah</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:45:53 +0700</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Kuasa hukum sebuah yayasan sekolah swasta di Jakarta Selatan mengungkapkan mantan Ketua Pengurus Yayasan berinisial IWD ...</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682927/kuasa-hukum-sebut-eks-ketua-yayasan-simpan-senpi-dan-narkotika-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001014987.jpg</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Ekonomi triwulan II-2026 tumbuh 5,29 persen</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Perekonomian Indonesia tumbuh 5,29 persen (year-on-year) pada triwulan II-2026, naik dibandingkan periode sama ...</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5682905/ekonomi-triwulan-ii-2026-tumbuh-529-persen</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/20260806-Ekonomi-triwulan-II-2026-tumbuh-5-29-persen.jpg</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>BRIN ungkap 3 strategi khusus untuk bantu genjot pertumbuhan ekonomi</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:44:54 +0700</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Kepala Badan Riset dan Inovasi Nasional (BRIN) Arif Satria mengungkapkan pihaknya memiliki tiga strategi khusus untuk ...</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682923/brin-ungkap-3-strategi-khusus-untuk-bantu-genjot-pertumbuhan-ekonomi</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-2835945.jpg</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>PT PAL mulai produksi Scorpène Evolved, perkuat kerja sama RI-Prancis</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:43:34 +0700</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>PT PAL akan memulai tahap produksi kapal selam siluman Scorpène Evolved dengan upacara pemotongan pelat baja ...</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682919/pt-pal-mulai-produksi-scorpne-evolved-perkuat-kerja-sama-ri-prancis</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/30/WhatsApp-Image-2026-01-30-at-16.53.05.jpeg</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia percaya diri hadapi Singapura</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:42:45 +0700</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Gelandang tim nasional Indonesia Marc Klok menyebut skuad Garuda percaya diri menghadapi Singapura pada laga ...</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682917/timnas-indonesia-percaya-diri-hadapi-singapura</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/timnas-indonesia-dikalahkan-vietnam-di-piala-aff-2833631.jpg</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Putaran ketujuh negosiasi Lebanon-Israel masuki hari terakhir di Roma</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:38:49 +0700</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Hari ketiga sekaligus hari terakhir putaran ketujuh negosiasi antara Lebanon dan Israel yang dimediasi Amerika Serikat ...</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682913/putaran-ketujuh-negosiasi-lebanon-israel-masuki-hari-terakhir-di-roma</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/thumbs_b_c_44d942499a723724c9911a3f1b4d8b35.jpg</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Perjalanan wisata ke luar negeri meningkat 11,2 persen pada April-Juni</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:37:36 +0700</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Agen perjalanan Golden Rama mengungkapkan bahwa perjalanan internasional yang dilakukan masyarakat Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682901/perjalanan-wisata-ke-luar-negeri-meningkat-112-persen-pada-april-juni</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/photo_6314070532281799045_y.jpg</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Pengamat: Kehadiran kapal PPA tepat untuk kebutuhan pertahanan RI</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:37:18 +0700</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Pengamat Pertahanan Marapi Alman Helvas Ali menilai keputusan Kementerian Pertahanan (Kemhan) menghadirkan kapal ...</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682899/pengamat-kehadiran-kapal-ppa-tepat-untuk-kebutuhan-pertahanan-ri</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/10/kri-brawijaya-320-tiba-di-surabaya-2620345.jpg</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Kemenag terbitkan 40 buku digital PAI dan dapat diunduh gratis</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:36:28 +0700</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Kementerian Agama menerbitkan 39 buku teks utama PAI dan Budi Pekerti untuk jenjang PAUD/TK, SMA/SMK, dan SLB, serta ...</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682897/kemenag-terbitkan-40-buku-digital-pai-dan-dapat-diunduh-gratis</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000176750.jpg</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Kejati Kalteng tetapkan lima komisioner KPU Kotim tersangka</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:34:48 +0700</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Kejaksaan Tinggi (Kejati) Kalimantan Tengah (Kalteng) menetapkan lima komisioner Komisi Pemilihan Umum (KPU) Kabupaten ...</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682893/kejati-kalteng-tetapkan-lima-komisioner-kpu-kotim-tersangka</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001727412.jpg</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Investasi NTB pada semester I 2026 tembus Rp33,73 triliun</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:28:07 +0700</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Nusa Tenggara Barat (NTB) menyebutkan realisasi ...</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682891/investasi-ntb-pada-semester-i-2026-tembus-rp3373-triliun</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/20260806_102535.jpg</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>KKI: Ada 10 nakes yang diduga beri komentar nirempati ke peserta JKN</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:28:04 +0700</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Konsil Kesehatan Indonesia mengatakan, pihaknya mengidentifikasi 10 tenaga kesehatan dan tenaga medis yang diduga ...</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682889/kki-ada-10-nakes-yang-diduga-beri-komentar-nirempati-ke-peserta-jkn</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000177666.jpg</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Prabowo Ingin Investasi Besar di Pendidikan demi Kemajuan Riset-Inovasi</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:42:03 +0700</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo menekankan pentingnya investasi pendidikan untuk kemajuan riset dan inovasi.</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607634/prabowo-ingin-investasi-besar-di-pendidikan-demi-kemajuan-riset-inovasi</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/presiden-prabowo-subianto-saat-memberikan-taklimat-di-depan-para-pimpinan-kamar-dagang-dan-industri-indonesia-kadin-di-istana--1785493704621_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Viral 2 Monyet Diikat di Tiang Lampu Merah, Dinas KPKP DKI Cek ke Lokasi</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:39:02 +0700</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Video viral dua monyet diikat di tiang lampu lalu lintas Jakarta memicu kepedulian warganet. Dinas KPKP DKI Jakarta menyelidiki dugaan eksploitasi satwa.</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607630/viral-2-monyet-diikat-di-tiang-lampu-merah-dinas-kpkp-dki-cek-ke-lokasi</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/monyet-diikat-di-tiang-lampu-merah-jakarta-dok-medsos-1786019911702_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Pakar Bicara Reshuffle untuk Pulihkan Kepercayaan Publik</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:36:16 +0700</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Dwi Rahmawati</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Direktur PPI Adi Prayitno menilai pemerintah perlu merespons hasil survei publik. Reshuffle kabinet bisa jadi opsi untuk tingkatkan kepercayaan publik.</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607626/pakar-bicara-reshuffle-untuk-pulihkan-kepercayaan-publik</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/15/presiden-prabowo-pimpin-sidang-kabinet-paripurna-1765806819168_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Satgas PRR Pacu Penyelesaian Fasilitas Pendukung Huntap di Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:31:56 +0700</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Satgas PRR percepat penyediaan fasilitas umum di huntap Aceh Tamiang. Lahan telah terpenuhi 100%, mendukung pemulihan bagi 4.159 kepala keluarga.</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607622/satgas-prr-pacu-penyelesaian-fasilitas-pendukung-huntap-di-aceh-tamiang</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/lahan-huntap-aceh-tamiang-terpenuhi-satgas-prr-pacu-penyelesaian-fasilitas-pendukung-1786019498077.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Seskab: Pertama Kali Periset BRIN Diundang dan Pamerkan Hasil Riset di Istana</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:30:04 +0700</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto bertemu 150 periset BRIN di Istana, membahas riset dan inovasi. Prabowo menekankan pentingnya sains untuk kemajuan bangsa.</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607618/seskab-pertama-kali-periset-brin-diundang-dan-pamerkan-hasil-riset-di-istana</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/teddy-indra-wijaya-1786019351589_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Rajiv Minta Penyebab Kebakaran Bromo Diusut, Jangan Berhenti di Pemadaman</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:28:05 +0700</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan melanda Taman Nasional Bromo Tengger Semeru, memicu keprihatinan. Anggota DPR Rajiv mendesak investigasi dan pencegahan lebih baik ke depan.</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607617/rajiv-minta-penyebab-kebakaran-bromo-diusut-jangan-berhenti-di-pemadaman</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/rajiv-1786019074067_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Ribka Haluk Cek Langsung Penanganan Dugaan Keracunan MBG di Jayapura</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:19:35 +0700</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Haluk meninjau dugaan keracunan Program Makan Bergizi Gratis di Jayapura. Ia pastikan penanganan korban berjalan cepat dan komprehensif.</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607604/ribka-haluk-cek-langsung-penanganan-dugaan-keracunan-mbg-di-jayapura</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kemendagri-1786018696572.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Skor PISA RI Rendah, Prabowo Beberkan Tantangan Kelola 388 Ribu Sekolah</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:11:33 +0700</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengakui pendidikan Indonesia tertinggal dalam PISA. Ia menekankan tantangan geografis dan meminta perbaikan kualitas pendidikan.</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607594/skor-pisa-ri-rendah-prabowo-beberkan-tantangan-kelola-388-ribu-sekolah</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/presiden-prabowo-subianto-saat-memberikan-taklimat-di-depan-para-pimpinan-kamar-dagang-dan-industri-indonesia-kadin-di-istana--1785493704749_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>RS Pusri Palembang Klarifikasi Dokter Hina Pasien BPJS 'Banyakin Duit Halal'</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:06:07 +0700</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Welly Jasrial Tanjung</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>RS Pusri Palembang klarifikasi komentar dokter Tamara yang menghina pasien BPJS. Manajemen akan sanksi sesuai ketentuan untuk menjaga profesionalisme.</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607588/rs-pusri-palembang-klarifikasi-dokter-hina-pasien-bpjs-banyakin-duit-halal</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/06/21/ilustrasi-dokter-melakukan-operasi_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Daniel Mananta Kagumi Program 'Bangun Rumah Tukangku' Semen Tiga Roda</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:03:42 +0700</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Angga Laraspati</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Mbah Jan, tukang bangunan berusia 68 tahun, merasakan kebahagiaan memiliki rumah baru berkat program Bangun Rumah Tukangku dari Indocement.</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607585/daniel-mananta-kagumi-program-bangun-rumah-tukangku-semen-tiga-roda</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/semen-tiga-roda-1786017701232_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Pihak Sekolah di Jaksel Dukung Polisi Usut Temuan Ratusan Senpi hingga Sabu</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:36:25 +0700</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Sekolah swasta di Jakarta Selatan mendukung penyelidikan polisi terkait penemuan ratusan senjata api dan air gun di ruang mantan ketua yayasan.</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607536/pihak-sekolah-di-jaksel-dukung-polisi-usut-temuan-ratusan-senpi-hingga-sabu</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-sejumlah-senjata-api-di-salah-satu-ruangan-yayasan-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786002238709_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Pemkab Majalengka dan BNN Perkuat Upaya Pencegahan Narkotika</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:28:53 +0700</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Pemkab Majalengka berkolaborasi dengan BNN untuk pencegahan narkotika melalui edukasi dan kurikulum antinarkotika.</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607523/pemkab-majalengka-dan-bnn-perkuat-upaya-pencegahan-narkotika</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bnn-1786015611493_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Ada 'Bunker' di Sekolah Jaksel TKP Temuan Ratusan Senjata, Apa Isinya?</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:25:52 +0700</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Ratusan senjata, termasuk air gun dan senjata api, ditemukan di sekolah swasta di Jakarta. Pihak sekolah minta polisi buka bunker yang masih terkunci.</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607518/ada-bunker-di-sekolah-jaksel-tkp-temuan-ratusan-senjata-apa-isinya</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Prabowo Bicara RI Butuh Orang Pintar, Kutip Ucapan Habibie soal 1% SDM Cerdas</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:16:54 +0700</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menekankan pentingnya SDM unggul di sains dan teknologi untuk kebangkitan Indonesia. Dia mengutip pandangan BJ Habibie.</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607505/prabowo-bicara-ri-butuh-orang-pintar-kutip-ucapan-habibie-soal-1-sdm-cerdas</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/presiden-prabowo-subianto-evadetik-1786014998958_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Prabowo Sedih: Cape Verde ke Piala Dunia, Padahal Penduduk Sumedang Lebih Banyak</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:06:11 +0700</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto kembali mengungkap rasa sedihnya Indonesia tidak bisa masuk Piala Dunia 2026.</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607489/prabowo-sedih-cape-verde-ke-piala-dunia-padahal-penduduk-sumedang-lebih-banyak</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/presiden-prabowo-subianto-evadetikcom-1786014352529_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>DPD Jadi Tuan Rumah Sidang Bersama DPR-DPD pada 14 Agustus</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:03:34 +0700</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Ketua MPR, DPR dan DPD gelar rapat persiapan Sidang Tahunan MPR RI dan Sidang Bersama pada 14 Agustus. Sultan Bakhtiar jadi tuan rumah, fokus pada HUT ke-81 RI.</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607477/dpd-jadi-tuan-rumah-sidang-bersama-dpr-dpd-pada-14-agustus</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/dpd-ri-1786014203443_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Dikejar Warga Bogor, Maling 2 HP di Dashboard Motor Tak Berkutik Diciduk</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:01:35 +0700</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Seorang pria berinisial ISL ditangkap warga setelah mencuri dua telepon seluler di Bogor. Pelaku dikejar dan diamankan Polsek Parung untuk penyelidikan.</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607472/dikejar-warga-bogor-maling-2-hp-di-dashboard-motor-tak-berkutik-diciduk</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/05/30/ilustrasi-kejahatan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Pramono Pastikan Pembelajaran di SDN Srengseng Jaksel Normal Usai Kebakaran</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:57:21 +0700</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung memastikan kegiatan belajar di SDN Srengseng Sawah 04 tetap normal pascakebakaran. Tidak ada kerusakan serius dan korban.</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607463/pramono-pastikan-pembelajaran-di-sdn-srengseng-jaksel-normal-usai-kebakaran</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/pramono-anung-beliadetikcom-1785834009810_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Lestari Moerdijat Dorong Sosialisasi Masif Lindungi Data Pribadi Anak</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:51:41 +0700</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Lestari Moerdijat menyoroti penyalahgunaan data anak dalam PAUD, mendesak peningkatan literasi dan perlindungan data pribadi di masyarakat.</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607452/lestari-moerdijat-dorong-sosialisasi-masif-lindungi-data-pribadi-anak</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/lestari-moerdijat-1785500283118.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Viral Isu Opang Pungli ke Ojol di Stasiun Juanda, Polisi Ungkap Faktanya</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:50:46 +0700</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Kabar pengemudi ojol jadi korban pungli di Stasiun Juanda, Jakpus, beredar di medsos. Polisi memastikan kabar tersebut tidak benar alias hoaks.</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607447/viral-isu-opang-pungli-ke-ojol-di-stasiun-juanda-polisi-ungkap-faktanya</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kabar-pengemudi-ojol-jadi-korban-pungli-di-stasiun-juanda-jakpus-beredar-di-medsos-polisi-memastikan-kabar-tersebut-tidak-bena-1786013272495_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Pernah Dijajal Prabowo, KA Nusantara Explorer Bakal Layani Rute Ini</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:30:36 +0700</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan (Menhub), Dudy Purwagandhi, mengungkap sejumlah rute yang akan dilintasi Kereta Api (KA) Nusantara Explorer.</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8607597/pernah-dijajal-prabowo-ka-nusantara-explorer-bakal-layani-rute-ini</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/melihat-interior-kereta-mewah-nusantara-explore-yang-dijajal-prabowo-1785397124147_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>PNM Dorong Inovasi Usaha Nasabah Mekaar Lewat Program Studi Banding</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:03:20 +0700</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>PNM memberdayakan pelaku usaha ultra mikro melalui program Reward Studi Banding, meningkatkan kapasitas dan inovasi usaha untuk kesejahteraan keluarga.</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607584/pnm-dorong-inovasi-usaha-nasabah-mekaar-lewat-program-studi-banding</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pnm-dorong-inovasi-usaha-nasabah-mekaar-lewat-program-studi-banding-1786017780195.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>BRIN Klaim Teknologi Ini Bisa Hemat Subsidi LPG Rp 26 T</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:00:16 +0700</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) membeberkan sejumlah terobosan riset dan inovasi di sektor energi kepada Presiden Prabowo Subianto.</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607530/brin-klaim-teknologi-ini-bisa-hemat-subsidi-lpg-rp-26-t</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/29/kepala-brin-arif-satria-1785259411523_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Kemarau Panjang Dongkrak Panen Garam Petani Cirebon</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:00:06 +0700</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Tripa Ramadhan</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Kemarau panjang akibat El Nino membawa berkah bagi petani garam di Cirebon. Produksi garam meningkat tajam karena cuaca panas mempercepat proses penguapan.</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8606795/kemarau-panjang-dongkrak-panen-garam-petani-cirebon</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kemarau-panjang-dongkrak-panen-garam-petani-cirebon-1785996501130_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Perpres Ojol Terbit Bulan Ini!</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:56:16 +0700</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan (Menhub), Dudy Purwagandhi, mengatakan Peraturan Presiden (Perpres) tentang ojek online (ojol) akan diterbitkan bulan ini.</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607579/perpres-ojol-terbit-bulan-ini</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/27/menteri-perhubungan-menhub-dudy-purwagandhi-1782539749588_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Industri Tekstil Tumbuh 6,36%, Ditopang Investasi Rp 2,7 T</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:40:40 +0700</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Industri tekstil dan pakaian jadi (TPT) mencatat pertumbuhan sebesar 6,36% secara tahunan (year-on-year/yoy) pada kuartal II-2026.</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8607541/industri-tekstil-tumbuh-6-36-ditopang-investasi-rp-2-7-t</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/03/01/momen-panglima-tinjau-industri-tekstile-ramah-lingkungan-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Tolak Tambang Geothermal, Aktivis Desak ESDM Lindungi Tanah Adat</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:00:24 +0700</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Ari Saputra</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Aktivis WALHI menggelar aksi di depan Kementerian ESDM, Jakarta, menolak proyek geothermal yang dinilai mengancam lingkungan dan tanah adat.</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8607252/tolak-tambang-geothermal-aktivis-desak-esdm-lindungi-tanah-adat</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tolak-tambang-geothermal-aktivis-desak-esdm-lindungi-tanah-adat-1786008665947_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Pengusaha Muda Bahas Peluang Bisnis Hilirisasi Energi dan Minerba</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:23:09 +0700</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Forum MINERS 2026 oleh HIPMI Jakarta Selatan bahas peluang hilirisasi energi dan minerba. Diskusi dan networking untuk kolaborasi bisnis baru.</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607610/pengusaha-muda-bahas-peluang-bisnis-hilirisasi-energi-dan-minerba</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/01/25/6339c310-088e-4568-945d-3eaa5452f0fc_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Irish Bella Umumkan Hamil Anak Pertama dengan Haldy Sabri</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:02:32 +0700</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Irish Bella mengumumkan kabar kehamilannya dengan Haldy Sabri. Ia menunjukkan baby bump-nya.</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607560/irish-bella-umumkan-hamil-anak-pertama-dengan-haldy-sabri</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/irish-bella-1786016686750_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Sidang Mediasi Hak Asuh Anak Ruben Onsu dan Sarwendah Ditunda</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:08:18 +0700</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Sidang lanjutan gugatan hak asuh anak Ruben Onsu dan Sarwendah ditunda. Mediasi tidak dapat dilaksanakan karena kendala dari pihak pengadilan.</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606899/sidang-mediasi-hak-asuh-anak-ruben-onsu-dan-sarwendah-ditunda</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ruben-onsu-dan-sarwendah-1785990957994_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Trump Bantah AS Kekurangan Amunisi, Ancam Penjarakan Pengkhianat</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:45:05 +0700</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump membantah bahwa pasukan militer AS kekurangan amunisi dalam perang melawan Iran.</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806175221-134-1389417/trump-bantah-as-kekurangan-amunisi-ancam-penjarakan-pengkhianat</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/09/donald-trump-1783564607045_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Politikus Muslim El Sayed Respons Kecaman Trump usai Menang Pemilu</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:15:35 +0700</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Politikus Muslim dari Partai Demokrat, Abdul El-Sayed, merespons kritik dan kecaman Presiden AS Donald Trump usai memenangkan pemilu pendahuluan.</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806184109-139-1389442/politikus-muslim-el-sayed-respons-kecaman-trump-usai-menang-pemilu</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/thumbnail-video-1786016616069_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Tokoh Pro Palestina Menang Pemilu Pendahuluan AS, Pelobi Israel Sewot</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:47:03 +0700</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Abdul El Sayed telah memenangkan pemilu pendahuluan (primary) untuk kursi Senat Amerika Serikat di Michigan.</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806182535-134-1389434/tokoh-pro-palestina-menang-pemilu-pendahuluan-as-pelobi-israel-sewot</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/politikus-demokrat-abdul-el-sayed-1785992947567_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Trump Disebut Cekcok dengan Menhan AS Perkara Amunisi-Rudal Menipis</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:11:59 +0700</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Presiden AS Donald Trump dikabarkan cekcok dengan Menteri Pertahanan AS Pete Hegseth gegara menipisnya stok senjata Washington untuk melawan Iran.</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806180424-134-1389422/trump-disebut-cekcok-dengan-menhan-as-perkara-amunisi-rudal-menipis</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/07/08/netanyahu-trump-rapat-rencana-jahat-mau-usir-warga-gaza-1751943457945_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Hanya 12 Kapal Lewati Selat Hormuz dalam 24 Jam Terakhir</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:48:05 +0700</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Hanya 12 kapal yang bisa melintasi rute pelayaran jalur global Selat Hormuz dalam 24 jam terakhir pada Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806171907-120-1389404/hanya-12-kapal-lewati-selat-hormuz-dalam-24-jam-terakhir</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/15/kesepakatan-damai-di-depan-mata-selat-hormuz-segera-buka-1781505172570_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Malaysia Tak Akan Minta Ekstradisi Pilot Pembawa Narkoba di RI</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:06:31 +0700</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Kepolisian Malaysia tidak akan meminta ekstradisi pilot Malaysia yang ditangkap di Indonesia karena membawa narkotika ekstasi seberat 26 kilogram.</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806164815-106-1389393/malaysia-tak-akan-minta-ekstradisi-pilot-pembawa-narkoba-di-ri</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/10/05/bendera-malaysia_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Detik-detik Influencer Meksiko Tewas Ditembak Saat Live Streaming</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:27:10 +0700</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>REUTERS/VIDEO VIRAL</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Influencer media sosial asal Meksiko, Cesar Gastelum, tewas ditembak saat melakukan siaran langsung bersama teman-temannya di luar sebuah restoran cepat saji.</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806145016-139-1389331/detik-detik-influencer-meksiko-tewas-ditembak-saat-live-streaming</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/thumbnail-video-1786002591721_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Mojtaba dan Presiden Iran Diisukan Renggang, Ini Jawaban Pezeshkian</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:46:15 +0700</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>Hubungan antara Pemimpin Tertinggi Iran Mojtaba Khamenei dan Presiden Masoud Pezeshkian diklaim tengah renggang.</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806153122-113-1389351/mojtaba-presiden-iran-diisukan-renggang-ini-jawaban-pezeshkian</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/06/presiden-iran-masoud-pezeshkian-1778042263260_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Abdul El Sayed, Muslim Pertama yang Bakal Jadi Senator AS</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:12:06 +0700</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Abdul El Sayed memenangkan pemilihan pendahuluan (primary) Senat Amerika Serikat (AS) di negara bagian Michigan.</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806145713-134-1389335/abdul-el-sayed-muslim-pertama-yang-bakal-jadi-senator-as</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/politikus-demokrat-abdul-el-sayed-1785992947504_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Dibatalkan MA, AS Kembalikan Tarif Liberation Day Rp1.790 Triliun</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:40:47 +0700</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>AS mengembalikan sekitar Rp1.790 triliun dari tarif Liberation Day yang sebelumnya dipungut Presiden Donald Trump terhadap berbagai negara.</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806140833-134-1389302/dibatalkan-ma-as-kembalikan-tarif-liberation-day-rp1790-triliun</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/01/08/882663ef-b241-4ac9-95cb-da46db5f4dcd_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Israel Beringas, Mau Bangun 2.300 Permukiman Ilegal di Yerusalem Timur</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Otoritas Israel kian menunjukkan kekejaman mereka terhadap warga Palestina dengan berencana membangun 2.300 unit rumah baru untuk memperluas ekspansinya.</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806125406-120-1389264/israel-beringas-mau-bangun-2300-permukiman-ilegal-di-yerusalem-timur</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/25/militer-israel-operasi-besar-besaran-di-tepi-barat-1784981863873_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Kata-kata Rusia soal Disebut Sewa Tentara Bayaran Kolombia di Ukraina</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>tim</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Rusia dilaporkan menggunakan tentara bayaran dari Kolombia untuk membantu mereka dalam perang melawan Ukraina.</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806114740-134-1389233/kata-kata-rusia-soal-disebut-sewa-tentara-bayaran-kolombia-di-ukraina</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/04/20/vladimir-putin-1745116285127_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>FOTO: Teror Objek Misterius Tabrak Pesawat di Bandara Jerman</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Jerman dihebohkan dengan benda melayang misterius yang menabrak pesawat kargo di Bandara Leipzig/Halle, Jerman.</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806101934-136-1389199/foto-teror-objek-misterius-tabrak-pesawat-di-bandara-jerman</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/objek-misterius-di-bandara-jerman-1785986141085_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Jasa Ramalan Tarot Buat Hewan Peliharaan Semakin Laris di Korsel</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>Tren baru ramalan tarot untuk hewan peliharaan tengah melanda melanda di Korea Selatan.</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805181553-113-1389011/jasa-ramalan-tarot-buat-hewan-peliharaan-semakin-laris-di-korsel</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/23/fenomena-tarot-untuk-hewan-peliharaan-di-korsel-1784790517675_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Politikus Muslim Pro-Palestina Menang Pileg AS, Trump Ngamuk</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Politikus Muslim dari Partai Demokrat, Abdul El Sayed, memenangkan pemilu pendahuluan (primary) untuk kursi Senat Amerika Serikat di Michigan, pada Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806115641-134-1389238/politikus-muslim-pro-palestina-menang-pileg-as-trump-ngamuk</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/politikus-demokrat-abdul-el-sayed-1785992947567_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Kanada Gelar Lomba Gendong Istri, Hadiahnya Bir Seberat Badan Istri</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>Kanada baru-baru ini menggelar Ekukonkanto, lomba unik suami gendong istri hadiahnya bir seberat badan pasangannya.</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805200358-134-1389061/kanada-gelar-lomba-gendong-istri-hadiahnya-bir-seberat-badan-istri</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/02/21/a1254691-a0b0-4c28-83bd-5328ae7afa7b_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Isyarat Netanyahu soal Israel Bisa Serang Iran Tanpa Restu AS</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>VIORY/GPO</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Benjamin Netanyahu mengisyaratkan Israel dapat mengambil tindakan militer secara sepihak terhadap Iran.</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806102255-124-1389209/isyarat-netanyahu-soal-israel-bisa-serang-iran-tanpa-restu-as</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/thumbnail-video-1785986747744_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Trump Ultimatum Siapkan Serangan Lebih Dahsyat dari PD II Buat Iran</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Presiden Donald Trump sesumbar Amerika Serikat sudah menyiapkan serangan masif sebelum negosiasi dengan Iran diklaim berjalan.</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806101118-134-1389198/trump-ultimatum-siapkan-serangan-lebih-dahsyat-dari-pd-ii-buat-iran</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/09/donald-trump-1783564607045_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Heli Trump Diduga Langgar Jarak Aman, Terbang Terlalu Dekat Pesawat</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:15:56 +0700</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>AS tengah menyelidiki apakah helikopter militer yang membawa Presiden Donald Trump berada terlalu dekat dengan pesawat penumpang saat terbang di Washington.</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806095237-134-1389190/heli-trump-diduga-langgar-jarak-aman-terbang-terlalu-dekat-pesawat</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/23/trump-kesulitan-lindungi-50-ribu-tentara-as-dari-serangan-iran-1784792922025_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Objek Misterius Tabrak Pesawat Kargo di Bandara Jerman</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:41:03 +0700</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Benda melayang misgterius menabrak pesawat kargo di Bandara Leipzig/Halle, Jerman, pada Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806092904-134-1389172/objek-misterius-tabrak-pesawat-kargo-di-bandara-jerman</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/11/03/c0934cfe-4306-4ae7-b122-bb92dbfd938c_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Malaysia Respons 3 Perempuan Sabah Ditangkap di RI Buntut Bawa Narkoba</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:15:41 +0700</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>Kepolisian Malaysia buka suara soal tiga perempuan asal Kinabalu, Sabah, ditangkap di Bandara Soekarno-Hatta, Tangerang, diduga menyelundupkan narkoba.</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806091354-106-1389166/malaysia-respons-3-perempuan-sabah-ditangkap-di-ri-buntut-bawa-narkoba</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Ogah Manut Trump, Netanyahu Ancam Serang Iran Tanpa Restu AS</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Benjamin Netanyahu mengisyaratkan Israel dapat mengambil tindakan militer secara sepihak terhadap Iran.</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806081434-120-1389153/ogah-manut-trump-netanyahu-ancam-serang-iran-tanpa-restu-as</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/10/16/benjamin-netanyahu_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Polisi Malaysia ke RI Selidiki Rantai Narkoba Pilot Malaysia Airlines</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>Kepolisian Malaysia akan mengirim tim investigasi dan intelijen ke Jakarta untuk menyelidiki jaringan sindikat narkoba yang melibatkan pilot Malaysia Airlines.</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806073234-106-1389144/polisi-malaysia-ke-ri-selidiki-rantai-narkoba-pilot-malaysia-airlines</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/02/17/be21f5ca-953a-4f51-93c2-f3a7ce29da94_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Iran-Oman Sepakat Urusan Selat Hormuz, Wanti-wanti Gelagat AS</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:31:43 +0700</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Iran telah menyepakati rute-rute kapal yang melintasi Selat Hormuz bersama Oman dan tengah menyelesaikan pengaturan untuk mengelola jalur perairan itu.</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806072301-120-1389142/iran-oman-sepakat-urusan-selat-hormuz-wanti-wanti-gelagat-as</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/06/iran-israel-conflict-1775454871064_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Kabinet Anwar Bahas Pilot Bawa Ekstasi sampai Jepang Pangkas Pajak</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>Pilot Malaysia Airlines selundupkan 26 kilogram narkoba ke RI dan Jepang memangkas pajak makanan menjadi sorotan berita internasional.</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806063314-113-1389116/kabinet-anwar-bahas-pilot-bawa-ekstasi-sampai-jepang-pangkas-pajak</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/05/20/740e8805-8262-447e-ae94-b8ce61bf8cd9_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Ini Wilayah yang Bakal Merdeka dari Tetangga RI, Punya 21 Bahasa</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:21:00 +0700</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Terletak di Pasifik Selatan, penduduknya telah memberikan suara 98,3 persen untuk kemerdekaan.</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805185439-113-1389039/ini-wilayah-yang-bakal-merdeka-dari-tetangga-ri-punya-21-bahasa</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/03/20/pulau-bougainville-di-pasifik-selatan-1742445249656_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Digaji Berbulan-bulan, 10 Staf Kantor Polisi India Ternyata Fiktif</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 05:30:42 +0700</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Kepolisian Mumbai, India, menggaji 10 karyawan yang ternyata fiktif selama berbulan-bulan.</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805103632-113-1388795/digaji-berbulan-bulan-10-staf-kantor-polisi-india-ternyata-fiktif</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/03/31/eddce0de-1a16-4f3a-ae16-e6a8831fb8ec_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>FOTO: Pemakaman 112 Jenazah yang Baru Ditemukan di Reruntuhan Gaza</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:30:03 +0700</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>REUTERS</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Warga Palestina menggelar pemakaman 112 warga yang baru ditemukan di balik reruntuhan di Gaza City, Palestina.</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805083257-122-1388740/foto-pemakaman-112-jenazah-yang-baru-ditemukan-di-reruntuhan-gaza</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/warga-gaza-menguburkan-112-jenazah-yang-ditemukan-dari-reruntuhan-perang-1785893554035_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Horor Drone Teror Pria di Ukraina Sebelum Meledak</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 03:30:03 +0700</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>Rekaman video menunjukkan sebuah drone terbang mengitari seorang pria di Kherson, Ukraina, sebelum meledak di dekatnya.</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805104327-139-1388798/horor-drone-teror-pria-di-ukraina-sebelum-meledak</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/thumbnail-video-1785901555516_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>8 Tewas Kena Rudal Rusia di Stasiun KA Kvitnevyi Ukraina</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 03:00:30 +0700</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>Delapan jenazah ditemukan di Stasiun Kereta Api Kvitnevyi setelah serangan rudal Rusia di wilayah Kyiv, Ukraina, pada Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805192723-139-1389052/8-tewas-kena-rudal-rusia-di-stasiun-ka-kvitnevyi-ukraina</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/penampakan-8-jenazah-akibat-serangan-di-stasiun-kereta-api-kvitnevyi-1785933157058_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Potret Tenda Bermain Hiburan Anak-anak di Kala Perang Gaza</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 02:00:53 +0700</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Viory</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>Sebuah tenda bermain di Gaza, dipenuhi anak-anak yang asyik bermain trampolin, gim realitas virtual hingga melukis wajah.</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260805131402-124-1388850/potret-tenda-bermain-hiburan-anak-anak-di-kala-perang-gaza</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/thumbnail-video-1785910382515_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Toyota Indonesia Perkuat Peran Pelajar dalam Upaya Dekarbonisasi</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:47:06 +0700</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>Wakil Presiden Direktur TMMIN I Nyoman Winaya mengatakan, emisi karbon adalah tantangan bersama yang tidak mengenal batas wilayah.</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7864928/toyota-indonesia-perkuat-peran-pelajar-dalam-upaya-dekarbonisasi</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wVt4cfmVDD54GyPvPk7quYnqat0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bos-TMMIN-Nyoman-Winaya-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Hitungan CELIOS soal Omzet KDMP: Wajib Rp182 Juta per Bulan, tapi Cuma untuk Bayar Gaji-Cicil Utang</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:44:52 +0700</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>CELIOS membeberkan hitung-hitungan terkait omzet yang harus dicapai KDMP tiap bulannya hanya untuk sekedar bayar gaji pegawai dan cicil utang.</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7864927/hitungan-celios-soal-omzet-kdmp-wajib-rp182-juta-per-bulan-tapi-cuma-untuk-bayar-gaji-cicil-utang</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1vtBXWzn08S1n85rzXfKEqYKbfw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Gerai-Koperasi-Desa-Merah-Putih_20260402_205200.jpg</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Not Pianika Lagu Hymne Satya Darma Pramuka 'Kami Jadi Pandumu' Lengkap Lirik</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:41:19 +0700</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>Simak not angka pianika lagu Hymne Pramuka ciptaan H. Mutahar yang dapat dijadikan panduan berlatih memainkan salah satu lagu wajib Gerakan Pramuka.</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7864926/not-pianika-lagu-hymne-satya-darma-pramuka-kami-jadi-pandumu-lengkap-lirik</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/X1h1lKU-82bejSHNCJUDpkt1Iso=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pramuka-tuna-netra-sd.jpg</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Gelar Pelatihan Yoga, WN Australia Dideportasi dari Bali</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:41:14 +0700</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>PJ menjadi instruktur meditasi dalam kegiatan bertajuk "7 Day Inner Growth" yang berlangsung di Villa Boreh, Kecamatan Tejakula, Kabupaten Buleleng</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7864925/gelar-pelatihan-yoga-wn-australia-dideportasi-dari-bali</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3YOOYjVvGkYB-_iQQ5fLCjcVfG0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-deportasi_1.jpg</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Warisan Pemikiran HOS Tjokroaminoto Tetap Hidup, Menjadi Spirit Generasi Muda Sambut HUT Ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:39:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>PB SEMMI gaungkan semangat nasionalisme warisan H.O.S. Tjokroaminoto dengan instruksi pengibaran Merah Putih jelang HUT RI ke-81.</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7864924/warisan-pemikiran-hos-tjokroaminoto-tetap-hidup-menjadi-spirit-generasi-muda-sambut-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2wm17HtXvfPZRKi9tkHDkpSDsvQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Berkunjung-ke-Rumah-HOS-Tjokroaminoto-di-Momen-Sumpah-Pemuda_20251028_191722.jpg</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Kalteng Jadi Wilayah Penyangga IKN, Pemerintah Pusat Perkuat Penanganan Karhutla dan Tambang Ilegal</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:30:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Kalimantan Tengah dinilai memegang peran strategis sebagai wilayah penyangga Ibu Kota Nusantara (IKN).</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7864923/kalteng-jadi-wilayah-penyangga-ikn-pemerintah-pusat-perkuat-penanganan-karhutla-dan-tambang-ilegal</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/aUCiJemGBhv1ZwrIk0HDPhSaQ7M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penyangga-ikn-a.jpg</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Bukan Sekadar Penggembira, Ai Ogura Mulai Disejajarkan dengan Marc Marquez dalam Perburuan Gelar</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:30:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>Ai Ogura kini dianggap sebagai salah satu kandidat serius dalam perebutan gelar juara dunia MotoGP 2026 berkat konsistensinya.</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7864922/bukan-sekadar-penggembira-ai-ogura-mulai-disejajarkan-dengan-marc-marquez-dalam-perburuan-gelar</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/UsI9oYnnwxf6u4tv7YWSapbdS84=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ai-Ogura-MotoGP-Spanyol-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Pevoli Asal Bantul Kembali Perkuat Timnas, Ada Cerita Lama dengan Reidel Toiran sebelum Proliga 2022</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:26:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Fahry Septian Putratama mengaku tak memiliki masalah adaptasi dengan pelatih Timnas Voli Putra Indonesia Reidel Toiran karena sudah mengenal baik.</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7864921/pevoli-asal-bantul-kembali-perkuat-timnas-ada-cerita-lama-dengan-reidel-toiran-sebelum-proliga-2022</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/KzT4NuPGehPNjNBaX3j1ZWhIVnU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/outside-hitter-jakata-lavani-allo-bank-fahry-septian-putratama.jpg</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Jelang HUT ke-81 RI, Balai TNGR Tingkatkan Pengawasan Kebersihan Kawasan Rinjani</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:26:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Balai TNGR memperketat pengawasan kebersihan kawasan konservasi menjelang peringatan HUT ke-81 RI.</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7864920/jelang-hut-ke-81-ri-balai-tngr-tingkatkan-pengawasan-kebersihan-kawasan-rinjani</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZL3a7GJYGNIFZZdzjU4qKPPDTkA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Taman-Nasional-Gunung-Rinjani-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>UMPB Komitmen Perkuat Dakwah dan Perkaderan Muhammadiyah Lewat Baitul Arqam</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:24:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>Pelaksanaan Baitul Arqam (BA) di Universitas Muhammadiyah Papua Barat (UMPB) kini telah memasuki minggu ketiga Rencana Tindak Lanjut (RTL).</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7864919/umpb-komitmen-perkuat-dakwah-dan-perkaderan-muhammadiyah-lewat-baitul-arqam</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/urMCe4jUnzD92aIKipXENK_s0So=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/BAITUL-ARQAM-di-UMPB.jpg</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>John Herdman Akui Finishing Timnas Indonesia Belum Maksimal, Minta Pemain Bermain Lepas</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:21:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>Meski mengakui masih ada kekurangan, John Herdman menilai penampilan Indonesia saat menghadapi Vietnam juga menyimpan banyak hal positif.</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864918/john-herdman-akui-finishing-timnas-indonesia-belum-maksimal-minta-pemain-bermain-lepas</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1a7ILPPDpySjbwe7SeQea4Z15Rg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Timnas-Indonesia-Dicukur-Timnas-Vietnam-3-0_20260804_065849.jpg</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>Eddy Soeparno: MPR Masih Kaji Tiga Opsi Produk Hukum PPHN</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:14:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Eddy Soeparno mengungkapkan, MPR masih mengkaji tiga opsi produk hukum yang akan digunakan untuk menetapkan PPHN.</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864917/eddy-soeparno-mpr-masih-kaji-tiga-opsi-produk-hukum-pphn</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/q1nMottqy22Xp111dsjXXdFgUx8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Eddy-Soeparno-audit-ponpes-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 10 SMA Kurikulum Merdeka Halaman 104 Edisi Revisi: Pengayaan</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:13:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban kelas 10 SMA Kurikulum Merdeka Halaman 104 Edisi Revisi: Pengayaan.</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7864916/kunci-jawaban-ips-kelas-10-sma-kurikulum-merdeka-halaman-104-edisi-revisi-pengayaan</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DSga7wM08_0kQh0WIsFqhAjs6F8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Simak-kunci-jawaban-Informatika-Kelas-5-Halaman-139.jpg</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Pertumbuhan Kinerja PTPN Group Tetap Terjaga pada Semester I 2026</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:13:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>kinerja Semester I 2026 menunjukkan konsistensi PTPN Group dalam menjalankan agenda transformasi perusahaan</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7864915/pertumbuhan-kinerja-ptpn-group-tetap-terjaga-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lJOFY1zYXJfLeRJgzlBMh_OOgag=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kinerja-PTPN-agresif-di-kuartal-II.jpg</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Temuan Senjata, Amunisi, dan Narkotika di Sekolah Jaksel, Polisi Diminta Prioritaskan Penyidikan</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:06:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>Ratusan senjata, narkotika, dan materi pornografi ditemukan di sekolah swasta Jaksel, kuasa hukum minta pengusutan menyeluruh.</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7864914/temuan-senjata-amunisi-dan-narkotika-di-sekolah-jaksel-polisi-diminta-prioritaskan-penyidikan</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/l3nMzdlh6bQ2dVHe2SVZe-4J9-4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kasus-penemuan-995-senjata-di-sekolah-swasta-Jaksel-bergulir-dengan-bukti-baru.jpg</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Doa agar Hati Dipenuhi Rasa Syukur dan Tidak Lalai Beribadah</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:04:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Setiap Muslim sangat dianjurkan untuk tidak melalaikan ibadah. Selain itu, sebaiknya mensyukuri setiap karunia yang diberikan oleh Allah SWT.</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7864913/doa-agar-hati-dipenuhi-rasa-syukur-dan-tidak-lalai-beribadah</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9jgbau4aMlWu2j3LNGCv-D5024I=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DOA-SELALU-BERSYUKUR-3456345636363.jpg</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Yayasan Minta Polisi Usut Serius Temuan Senjata Api dan Amunisi di Sekolah Kawasan Pondok Pinang</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:02:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Temuan pertama barang-barang tersebut terjadi pada tanggal 10 dan tanggal 11 Juli 2026 atau hampir satu bulan lalu.</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864912/yayasan-minta-polisi-usut-serius-temuan-senjata-api-dan-amunisi-di-sekolah-kawasan-pondok-pinang</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/bPxfHYKl5htC2rCNea9Sm57Mesw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/temuan-senpi-di-sekolah-as.jpg</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Banyumas, Jumat 7 Agustus 2026: Berawan hingga Cerah</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:02:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Pada hari Jumat, 7 Agustus 2026, sebagian besar daerah Kabupaten Banyumas, Jawa Tengah, diperkirakan akan berawan.</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7864911/prakiraan-cuaca-banyumas-jumat-7-agustus-2026-berawan-hingga-cerah</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0B9mub8oylx1rbLZSyydzRAQUPo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Cuaca-Berawan-2.jpg</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>Efek Domino Transfer Dimulai, Victor Osimhen Bisa Buka Jalan Barca Boyong Junior Lionel Messi</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:01:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>Drama transfer striker top Eropa mulai memanas. Barcelona mengincar Julian Alvarez, Atletico Madrid mempertimbangkan Victor Osimhen.</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864910/efek-domino-transfer-dimulai-victor-osimhen-bisa-buka-jalan-barca-boyong-junior-lionel-messi</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/IatpTp7ocCbKx7l-AGGWPoZLGdM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Victor-Osimhen-tengah-bersama-pemain-Galatasaray-melakukan-selebrasi.jpg</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Laga Hidup-Mati Timnas Indonesia, John Herdman Yakin Garuda Bisa Jadi Pemenang</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:58:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Pelatih Timnas Indonesia, John Herdman, menegaskan timnya tidak akan mengubah pendekatan meski menghadapi pertandingan menentukan.</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864909/laga-hidup-mati-timnas-indonesia-john-herdman-yakin-garuda-bisa-jadi-pemenang</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iP_P_SP0LLpWUqXvqwDcAe20vcY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/TELAN-KEKALAHAN-Pelatih-TImnas-Indonesia-John-Herdman-bersama-sang-kapten-Rizky-Ridho.jpg</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Perluasan Pasar Bisa Perkuat Investasi Industri Protein Nasional</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Perluasan akses pasar dinilai menjadi salah satu langkah penting untuk memperkuat investasi di sektor protein nasional. Pasar yang lebih luas diyakini mampu mendorong masuknya investasi baru, mempercepat...</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcamt522/perluasan-pasar-bisa-perkuat-investasi-industri-protein-nasional</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/082500800-1778423980-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Mentan Pastikan Stok Beras Aman Meski 30 Ribu Hektare Terdampak Kekeringan</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:59:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Pertanian Amran Sulaiman mengatakan sekitar 30 ribu hektare lahan pertanian di berbagai daerah telah terdampak kekeringan. Meski demikian, Amran memastikan kondisi tersebut belum mengganggu ketersediaan...</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcjzi416/mentan-pastikan-stok-beras-aman-meski-30-ribu-hektare-terdampak-kekeringan</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/016359700-1784823606-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Mentan: Kerugian Rakyat Akibat Mafia Beras Capai Rp 100 Triliun</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:51:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, SEMARANG -- Menteri Pertanian Amran Sulaiman mengatakan kerugian rakyat Indonesia akibat praktik culas mafia beras mencapai Rp 100 triliun. Menurut dia, hingga kini sudah ada sedikitnya 38 tersangka dalam...</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcjlt423/mentan-kerugian-rakyat-akibat-mafia-beras-capai-rp-100-triliun</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/menteri-pertanian-mentan-andi-amran_260730145848-982.jpg</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Impor Barang Konsumsi Naik, Menperin Minta Kebijakan Perlindungan Industri Lokal Diperkuat</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:24:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Ichsan Emrald Alamsyah</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Perindustrian (Menperin) Agus Gumiwang Kartasasmita meminta kebijakan perlindungan terhadap industri dalam negeri, terutama industri penyedia bahan baku, terus diperkuat. Langkah itu dinilai penting agar kapasitas industri...</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcicv349/impor-barang-konsumsi-naik-menperin-minta-kebijakan-perlindungan-industri-lokal-diperkuat</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/038443400-1761379188-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Penjelasan eks Ketua Yayasan Soal 995 Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:49:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>Seluruh airsoft gun tersebut disebut bukan senjata ilegal.</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263767/penjelasan-eks-ketua-yayasan-soal-995-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Fl_NzWIZKKZEWAlAQ_ZHoXsZU5g=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317547/original/022307300_1786020542-WhatsApp_Image_2026-08-06_at_19.28.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>Prabowo: Fakta Menyakitkan Pendidikan Indonesia di Bawah Thailand dan Vietnam</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:24:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Prabowo menyinggung soal survei Programme for International Student Assesment (PISA).</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263746/prabowo-fakta-menyakitkan-pendidikan-indonesia-di-bawah-thailand-dan-vietnam</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/YrVtnOghfnGhiMGOoOcxcQ6XGg0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9312462/original/075432400_1785494670-email-attachment_2026_07_31_ariefhakim-at-klyid_prabowo-subianto-sebut-semua-negara-gagal-karena-elitnya-ribut_1000393889.jpg</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Kronologi Temuan 995 Senjata di Sekolah Swasta Jaksel</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:06:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>Kronologi penemuan 995 senjata di sekolah Jaksel, berlanjut hingga temuan narkoba dan CD porno.</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263733/kronologi-temuan-995-senjata-di-sekolah-swasta-jaksel</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ETTDU2qEXOzAfRQOJ_Mo1H87TaE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317518/original/012310700_1786017988-Bungker.webp</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Misteri Pemilik Ratusan Senjata dalam Bunker Sekolah di Jaksel</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:47:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>Dari dalam ruangan, ditemukan 995 pucuk senjata beserta amunisi dan aksesori senjata.</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263713/misteri-pemilik-ratusan-senjata-dalam-bunker-sekolah-di-jaksel</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Kasus SPG GIIAS, Menkum Tegaskan Merekam Tanpa Izin Langgar Hukum</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:15:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>Pelaku dapat dijerat sejumlah aturan, termasuk UU ITE, KUHP, dan UU TPKS.</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263687/kasus-spg-giias-menkum-tegaskan-merekam-tanpa-izin-langgar-hukum</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/unOjCO0HHwFqey7fEv8Rwqhw04I=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5319810/original/091948000_1755575616-1000526552.jpg</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Viral Nakes Nirempati ke Pasien BPJS, Pramono Langsung Minta Dinkes Bertindak</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:03:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Pramono Anung meminta Dinkes DKI dalami dugaan tenaga kesehatan (nakes) yang mencibir pasien BPJS.</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263672/viral-nakes-nirempati-ke-pasien-bpjs-pramono-langsung-minta-dinkes-bertindak</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/iD71y1YMtoY3T2vY7z2TnGw24Xo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317472/original/091873000_1786014229-IMG_3312.jpg</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>Indonesia Dorong Hutan Jadi Solusi Krisis Iklim Dunia</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:59:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>Indonesia memiliki modal besar untuk memainkan peran strategis di tingkat internasional, mulai dari luas hutan tropis, ekosistem mangrove terbesar di dunia, hingga kekayaan keanekaragaman hayati.</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263723/indonesia-dorong-hutan-jadi-solusi-krisis-iklim-dunia</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CKrKeExR0aD3E8gGtZcQV00qL0I=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9316529/original/042654800_1785937869-Indonesia_Dorong_Penguatan_Tata_Kelola_Perhutanan_Sosial_di_Kawasan_ASEAN.jpg__1_.jpeg</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Cahaya</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Doa Qunut Subuh: Bacaan Arab, Latin, Arti, dan Tata Cara Membaca untuk Imam dan Makmum</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:55:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Simak cara membaca doa qunut shalat Subuh yang benar bagi imam dan makmum, lengkap dengan bacaan Arab, latin, arti, serta waktu membacanya.</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>https://cahaya.kompas.com/doa-dan-niat/26H06195227890/doa-qunut-subuh-bacaan-arab-latin-arti-dan-tata-cara-membaca-untuk-imam-dan</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/r8-Ts2ermPjEHvLMVFYEhbnxfUw=/0x79:5882x4000/1200x675/data/photo/2026/07/31/6a6b861dec8c7.jpg</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Sengketa Lahan Ponpes Minhajut Tholibin, Pemkab Purworejo Minta Eksekusi Ditunda</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:55:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Pemkab Purworejo minta PN pertimbangkan penundaan eksekusi Ponpes Minhajut Tholibin karena ahli waris ajukan gugatan perdata.</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/06/193548978/sengketa-lahan-ponpes-minhajut-tholibin-pemkab-purworejo-minta-eksekusi</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/bNPL6dz-UPx0jj9YHijkH89wWYg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a74715f0740c.jpg</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Prabowo: Saya Suka Memimpin dengan Fakta, Meski Kadang Terlihat Tidak Enak</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:55:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menekankan pentingnya memimpin dengan fakta dan realita lapangan, meskipun terkadang kenyataannya pahit.</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/06/19182891/prabowo-saya-suka-memimpin-dengan-fakta-meski-kadang-terlihat-tidak-enak</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/oXyBAST46TU9HDJW7FDqWtrsfF8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a747754344fc.jpg</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I884"/>
+  <autoFilter ref="A1:I1029"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1029</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1029"/>
+  <dimension ref="A1:I1138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -48801,8 +48801,5131 @@
         </is>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>MPR dorong perlindungan data anak usai dugaan pencatutan untuk dapodik</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:05:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR RI Lestari Moerdijat mendorong penguatan upaya perlindungan data pribadi anak merespons dugaan ...</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683316/mpr-dorong-perlindungan-data-anak-usai-dugaan-pencatutan-untuk-dapodik</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/27/WhatsApp-Image-2025-11-27-at-19.17.09.jpeg</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Real Madrid rampungkan transfer Yan Diomande dari RB Leipzig</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:04:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Real Madrid resmi merampungkan transfer pemain sayap (winger) muda Pantai Gading, Yan Diomande dari RB Leipzig pada ...</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683315/real-madrid-rampungkan-transfer-yan-diomande-dari-rb-leipzig</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000042720.jpg</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Berikut roster Dewa United Esports untuk MPL ID musim ke-18</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:00:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Dewa United Esports mengumumkan enam nama yang masuk daftar (roster) pemain yang akan tampil pada Mobile Legends: Bang ...</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683308/berikut-roster-dewa-united-esports-untuk-mpl-id-musim-ke-18</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000474548.jpg</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Bandara Mutiara resmi layani penerbangan internasional Palu-Guangzhou</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:58:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>Bandar Udara Internasional Mutiara SIS Al-Jufri di Palu, Sulawesi Tengah, resmi melayani penerbangan internasional ...</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683307/bandara-mutiara-resmi-layani-penerbangan-internasional-palu-guangzhou</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0046.jpg</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Gubernur Sumut siapkan RSUD Thomsen jadi rumah sakit regional di Nias</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:57:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution menyiapkan RSUD dr M Thomsen Nias Gunungsitoli menjadi rumah sakit ...</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683303/gubernur-sumut-siapkan-rsud-thomsen-jadi-rumah-sakit-regional-di-nias</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001033845.jpg</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>RANS Simba Bogor rekrut Zulfahrizal, perkuat jajaran pelatih</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:56:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>RANS Simba Bogor merekrut Zulfahrizal sebagai asisten pelatih untuk memperkuat jajaran pelatih tim yang ...</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683301/rans-simba-bogor-rekrut-zulfahrizal-perkuat-jajaran-pelatih</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000474514.jpg</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>BRIN pastikan data satelit Lampung-1 di bawah otoritas Indonesia</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:54:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) memastikan keamanan data dalam proyek satelit Lampung-1 tetap berada di bawah ...</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683299/brin-pastikan-data-satelit-lampung-1-di-bawah-otoritas-indonesia</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000034864.jpg</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Presiden tinjau langsung terobosan hasil inovasi anak bangsa</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:52:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>ANTARA -  Presiden Prabowo Subianto berinteraksi langsung dengan para periset Badan Riset dan Inovasi Nasional ...</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683241/presiden-tinjau-langsung-terobosan-hasil-inovasi-anak-bangsa</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-TINJAU-LANGSUNG-TEROBOSAN-HASIL-INOVASI-ANAK-BANGSA.jpg</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Kemendagri apresiasi Peta Cinta Jember pangkas waktu layanan adminduk</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:52:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Kependudukan dan Pencatatan Sipil (Dirjen Dukcapil) Kementerian Dalam Negeri (Kemendagri) Teguh ...</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683296/kemendagri-apresiasi-peta-cinta-jember-pangkas-waktu-layanan-adminduk</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/crd2z4dAfbOEvRGJGHtcAekXHC0327Bq8szMRx02.jpg</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia butuh cara menyerang yang lebih variatif</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:46:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Senin lalu, Stadion Pakansari, Kabupaten Bogor, Jawa Barat, dipenuhi lautan merah. Namun, di balik padatnya tribun, ...</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683292/timnas-indonesia-butuh-cara-menyerang-yang-lebih-variatif</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/timnas-indonesia-dikalahkan-vietnam-di-piala-aff-2833631.jpg</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Wamendagri minta daerah wujudkan pembangunan berkeadilan ekologis</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:44:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Dalam Negeri (Wamendagri) Bima Arya Sugiarto menegaskan pentingnya peran anggota Dewan Perwakilan Rakyat ...</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683288/wamendagri-minta-daerah-wujudkan-pembangunan-berkeadilan-ekologis</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000581498.jpg</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>IESR: PLTS 100 GW harus jadi program nasional bukan kementerian</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:44:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer Institute for Essential Services Reform (IESR) Fabby Tumiwa mengatakan, program pembangunan ...</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683284/iesr-plts-100-gw-harus-jadi-program-nasional-bukan-kementerian</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_213459.jpg</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>BGN beri "deadline" bagi SPPG belum bersertifikat sampai 10 Agustus</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:41:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono memberi tenggat waktu kepada seluruh Satuan Pelayanan ...</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683261/bgn-beri-deadline-bagi-sppg-belum-bersertifikat-sampai-10-agustus</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BGN-BERI-22DEADLINE-22-BAGI-SPPG-BELUM-BERSERTIFIKAT-SAMPAI-10-AGUSTUS.jpg</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Kemenkum akan latih paralegal khusus tangani kekerasan pada perempuan</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:38:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Kementerian Hukum (Kemenkum) berencana akan melatih paralegal yang khusus menangani kekerasan pada perempuan, bekerja ...</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683280/kemenkum-akan-latih-paralegal-khusus-tangani-kekerasan-pada-perempuan</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000473346.jpg</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Prabowo dorong BRIN perkuat riset untuk kemandirian nasional</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:37:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mendorong Badan Riset dan Inovasi Nasional (BRIN) memperkuat riset di berbagai bidang ...</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683276/prabowo-dorong-brin-perkuat-riset-untuk-kemandirian-nasional</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-2835941.jpg</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>CEO logistik Australia sebut pembangunan hijau China sebagai "contoh nyata"</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:31:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>China mencatatkan "kemajuan pesat dalam peralihan ke energi bersih" dan "secara nyata memimpin ...</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683272/ceo-logistik-australia-sebut-pembangunan-hijau-china-sebagai-contoh-nyata</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/CjkinzN000031_20260806_CBMFN0A001_2.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>TP PKK ajak pelajar cintai tanah air lewat potensi wisata bahari</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:30:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>Ketua Umum (Ketum) Tim Penggerak Pemberdayaan dan Kesejahteraan Keluarga (TP PKK) Tri Tito Karnavian mengajak para ...</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683269/tp-pkk-ajak-pelajar-cintai-tanah-air-lewat-potensi-wisata-bahari</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000581454.jpg</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Dillon Brooks perpanjang kontrak tiga tahun di Suns</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:28:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>Forward Dillon Brooks memperpanjang kontraknya di Phoenix Suns dengan durasi tiga tahun, sehingga dia akan ...</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683265/dillon-brooks-perpanjang-kontrak-tiga-tahun-di-suns</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000474467.jpg</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Sambut lima abad Jakarta, DKI cetak 1.000 mushaf Al Quran</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:27:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) DKI Jakarta berencana mencetak 1.000 mushaf Al Quran edisi khusus untuk diberikan kepada ...</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683257/sambut-lima-abad-jakarta-dki-cetak-1000-mushaf-al-quran</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000315801.jpg</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>BI Lampung: Ekonomi Lampung di 2026 diperkirakan tumbuh 5,0-5,6 persen</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:26:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan Bank Indonesia (BI) Lampung menyatakan bahwa ekonomi Lampung di 2026 diperkirakan tumbuh 5,0-5,6 ...</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683256/bi-lampung-ekonomi-lampung-di-2026-diperkirakan-tumbuh-50-56-persen</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/20260718_155833-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Rekor pertemuan di Piala AFF, Singapura ungguli Indonesia</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:22:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia akan berhadapan dengan timnas Singapura di Stadion Jalan Besar, Singapura, Jumat (7/8), pada laga ...</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683253/rekor-pertemuan-di-piala-aff-singapura-ungguli-indonesia</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/Piala-AFF-Indonesia-Lawan-Kamboja-270726-bay-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Lima desa di Muara Enim dilanda karhutla</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:22:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Sebanyak lima desa di Kabupaten Muara Enim, Sumatera Selatan dilanda kebakaran hutan dan lahan (karhutla) akibat musim ...</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683249/lima-desa-di-muara-enim-dilanda-karhutla</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_211515.jpg</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo: "Saya ingin investasi besar di bidang pendidikan"</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:21:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengungkap rencananya ingin berinvestasi dalam jumlah besar pada sektor pendidikan karena ...</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683248/presiden-prabowo-saya-ingin-investasi-besar-di-bidang-pendidikan</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-18.34.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Komisi XIII: RUU Sistem Perbukuan jamin akses ilmu pengetahuan setara</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:20:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XIII DPR RI Willy Aditya mengatakan Rancangan Undang-Undang (RUU) Sistem Perbukuan disusun untuk menjamin ...</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683245/komisi-xiii-ruu-sistem-perbukuan-jamin-akses-ilmu-pengetahuan-setara</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001222615.jpg</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Utusan Khusus Presiden: Proteksi UMKM jadi agenda bangsa</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:20:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Utusan Khusus Presiden Bidang Usaha Mikro, Kecil dan Menengah (UMKM), Ekonomi Kreatif dan Digital Ahmad Ridha Sabana ...</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683240/utusan-khusus-presiden-proteksi-umkm-jadi-agenda-bangsa</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_195323.jpg</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo belum padam, area terbakar capai 120 hektare</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:18:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemadaman kebakaran di kawasan Taman Nasional Bromo Tengger Semeru (TNBTS) memasuki hari keempat. Meski titik ...</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683065/kebakaran-bromo-belum-padam-area-terbakar-capai-120-hektare</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_KEBAKARAN-BROMO-BELUM-PADAM-AREA-TERBAKAR-CAPAI-120-HEKTARE.jpg</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>407 Mal di Indonesia hadirkan program diskon Agustus hingga 80 persen</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:16:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 407 pusat perbelanjaan di berbagai daerah mulai menggelar Indonesia Shopping Festival (ISF) 2026 pada ...</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683156/407-mal-di-indonesia-hadirkan-program-diskon-agustus-hingga-80-persen</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-06-202356_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Wamendagri: Pemerintah cek dugaan keracunan makanan di Jayapura</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:15:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Dalam Negeri (Wamendagri) Ribka Haluk menyatakan pemerintah pusat memberikan perhatian serius terhadap ...</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683239/wamendagri-pemerintah-cek-dugaan-keracunan-makanan-di-jayapura</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/IMG_20260206_115658.jpg</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Muktamar ke-35 NU: medan pertarungan para “menak”</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:14:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>Ketika Nabi Musa As menyampaikan hasratnya untuk ikut dan berguru kepada Nabi Khidir As, putra Imron itu diberi ...</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683236/muktamar-ke-35-nu-medan-pertarunganpara-menak</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/1292340.jpg</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>BRIN sebut teknologi ANG dapat hemat subsidi LPG hingga Rp26 triliun</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:13:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>Kepala Badan Riset dan Inovasi Nasional (BRIN) Arief Satria menyebut teknologi adsorbed natural gas (ANG) yang ...</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683233/brin-sebut-teknologi-ang-dapat-hemat-subsidi-lpg-hingga-rp26-triliun</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-2835941.jpg</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Rekomendasi 12 game anak yang edukatif dan cocok untuk semua usia</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:11:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>Bermain game telah menjadi salah satu aktivitas yang akrab dengan kehidupan anak-anak. Mulai dari smartphone, tablet, ...</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683231/rekomendasi-12-game-anak-yang-edukatif-dan-cocok-untuk-semua-usia</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/03/16/Minecraft_Trails_and_Tales_.Net_600x360_copy_4030x2418-01.jpeg.jpg</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Mendagri siapkan tiga langkah solusi gaji pegawai pemda</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:09:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri (Mendagri) Muhammad Tito Karnavian mengatakan pemerintah telah menyiapkan tiga langkah guna ...</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683228/mendagri-siapkan-tiga-langkah-solusi-gaji-pegawai-pemda</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000580145.jpg</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Khofifah bebaskan denda PKB pengemudi ojol hingga akhir Agustus</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:07:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa membebaskan denda dan pokok tunggakan Pajak Kendaraan Bermotor (PKB) para ...</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683224/khofifah-bebaskan-denda-pkb-pengemudi-ojol-hingga-akhir-agustus</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001403504.jpg</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Huawei MateBook Pro S resmi, laptop premium bobot cuma 798 gram</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:05:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>Huawei kembali meramaikan pasar komputer jinjing dengan memperkenalkan Huawei MateBook Pro S, notebook premium terbaru ...</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683220/huawei-matebook-pro-s-resmi-laptop-premium-bobot-cuma-798-gram</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/InShot_20260805_181445598.jpg</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Freeport-ANTARA gelar wokshop untuk perkuat kapasitas jurnalis Gresik</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:04:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia bersama Lembaga Pendidikan ANTARA menggelar Workshop Jurnalis Gresik pada 6-8 Agustus 2026 untuk ...</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683219/freeport-antara-gelar-wokshop-untuk-perkuat-kapasitas-jurnalis-gresik</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-20.36.24.jpeg</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Tito minta pejabat baru Kemendagri laksanakan tugas semaksimal mungkin</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:02:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>Menteri Dalam Negeri (Mendagri) Muhammad Tito Karnavian meminta para pejabat baru di lingkungan Kementerian Dalam ...</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683217/tito-minta-pejabat-baru-kemendagri-laksanakan-tugas-semaksimal-mungkin</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000581215.jpg</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Pramono: Pembuang sampah akan diumumkan ke publik sebagai efek jera</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:02:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung menginstruksikan jajaran di Dinas Lingkungan Hidup dan Dinas Komunikasi, Informatika ...</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683215/pramono-pembuang-sampah-akan-diumumkan-ke-publik-sebagai-efek-jera</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000315791.jpg</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Wings Air buka rute penerbangan dari Bandung-Lampung</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:58:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Maskapai Wings Air membuka rute penerbangan langsung dari Bandara Husein Sastranegara, Kota Bandung ke Bandara ...</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683211/wings-air-buka-rute-penerbangan-dari-bandung-lampung</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/d0cf3f51-de6f-4192-883c-ccdb5f1a7b14.jpeg</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Pemerintah prioritaskan penguatan program MBG di daerah 3T</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:57:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator (Menko) Bidang Pangan Zulkifli Hasan menegaskan pemerintah menargetkan sejumlah langkah strategis ...</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683208/pemerintah-prioritaskan-penguatan-program-mbg-di-daerah-3t</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/perbaikan-tata-kelola-program-mbg-2835712_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Komisi XIII DPR dan BPIP perkuat-pemahaman nilai Pancasila di Medan</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:56:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>Komisi XIII DPR RI bersama Badan Pembinaan Ideologi Pancasila (BPIP) memperkuat pemahaman nilai-nilai Pancasila kepada ...</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683207/komisi-xiii-dpr-dan-bpip-perkuat-pemahaman-nilai-pancasila-di-medan</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0125.jpg</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Menekraf dukung RIKIN jadikan KI aset ekonomi berkelanjutan</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:54:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>Menteri Ekonomi Kreatif/Kepala Badan Ekonomi Kreatif (Menekraf), Teuku Riefky Harsya, menegaskan dukungannya pada ...</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683204/menekraf-dukung-rikin-jadikan-ki-aset-ekonomi-berkelanjutan</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000454941.jpg</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Pemadaman karhutla di Palangka Raya terkendala minimnya sumber air</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:53:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>ANTARA - Kebakaran hutan dan lahan (karhutla) yang melanda sejumlah wilayah di Kota Palangka Raya, Kalimantan Tengah, ...</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683185/pemadaman-karhutla-di-palangka-raya-terkendala-minimnya-sumber-air</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-06-203549.jpg</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Alur cerita GTA 6: Kisah Lucia, Jason, dan dunia baru Leonida</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:52:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>Setelah penantian lebih dari satu dekade sejak perilisan Grand Theft Auto V, Rockstar Games akhirnya siap menghadirkan ...</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683203/alur-cerita-gta-6-kisah-lucia-jason-dan-dunia-baru-leonida</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/03/rockstargames-website-wide-gtavi-banner-mobile.jpg</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Komnas HAM usulkan badan khusus perkuat pemulihan korban HAM berat</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:52:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>Komisi Nasional Hak Asasi Manusia (Komnas HAM) mengusulkan pembentukan badan khusus untuk memperkuat pelaksanaan ...</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683199/komnas-ham-usulkan-badan-khusus-perkuat-pemulihan-korban-ham-berat</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001222469.jpg</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Kejagung periksa sembilan saksi terkait kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:50:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>Tim Penyidik Kejaksaan Agung (Tim 9) memeriksa sembilan saksi dalam proses penyidikan kasus dugaan tindak pidana ...</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683196/kejagung-periksa-sembilan-saksi-terkait-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087161_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Polisi bongkar dua kasus narkoba di Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:50:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>Polsek Kembangan membongkar dua kasus narkoba di wilayah Cengkareng Timur dan Jelambar, Jakarta Barat, pada akhir Juli ...</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683195/polisi-bongkar-dua-kasus-narkoba-di-jakarta-barat</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_203119.jpg</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Bappenas: Platform ZIS-DSKL integrasikan data mustahik dan DTSEN</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:48:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Kementerian Perencanaan Pembangunan Nasional/Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) mengungkapkan ...</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683193/bappenas-platform-zis-dskl-integrasikan-data-mustahik-dan-dtsen</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Pungkas-Kamis-6-8.jpg</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Menperin beri penjelasan soal isu PHK garmen di Cimahi</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:48:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>Menteri Perindustrian (Menperin) Agus Gumiwang Kartasasmita memberi penjelasan terkait isu pemutusan hubungan kerja ...</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683192/menperin-beri-penjelasan-soal-isu-phk-garmen-di-cimahi</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-20.04.43_edit_307803995922300.jpg</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Di hadapan 150 peneliti BRIN Prabowo janji tambah anggaran riset</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:46:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto dalam taklimatnya di hadapan 150 peneliti Badan Riset dan Inovasi Nasional (BRIN) di halaman ...</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683191/di-hadapan-150-peneliti-brin-prabowo-janji-tambah-anggaran-riset</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/WhatsApp-Image-2026-08-06-at-19.00.40.jpeg</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>1.700 SPPG di daerah stunting beroperasi di pekan kedua Agustus</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:45:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono di Jakarta, Kamis (6/8), mengatakan sebanyak 1.700 Satuan ...</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683120/1700-sppg-di-daerah-stunting-beroperasi-di-pekan-kedua-agustus</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_1.700-SPPG-DI-DAERAH-STUNTING-BEROPERASI-DI-PEKAN-KEDUA-AGUSTUS.jpg</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>Prabowo ingin pimpin pemerintahan berlandaskan fakta</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:53:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menegaskan dirinya ingin memimpin pemerintahan dengan berlandaskan fakta dan ...</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683060/prabowo-ingin-pimpin-pemerintahan-berlandaskan-fakta</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-2835937.jpg</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>10 tips beli mobil di GIIAS 2026, jangan mudah tergiur promo</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:30:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Pameran GAIKINDO Indonesia International Auto Show (GIIAS) 2026 resmi digelar pada 30 Juli hingga 9 Agustus 2026 di ICE ...</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5683148/10-tips-beli-mobil-di-giias-2026-jangan-mudah-tergiur-promo</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.51.jpeg</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>RS Pusri Palembang Pecat Dokter Viral Hina Pasien BPJS 'Banyakin Duit Halal'</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:06:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Welly Jasrial Tanjung</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>RS Pusri Palembang akhiri kerja sama dengan dr Tamara Dewi setelah komentarnya yang menghina pasien BPJS viral. Rumah sakit tegaskan komitmen profesionalisme.</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607744/rs-pusri-palembang-pecat-dokter-viral-hina-pasien-bpjs-banyakin-duit-halal</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/rs-pusri-palembang-1786024777376_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Marak Narkoba dari Malaysia ke Indonesia</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:02:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>Pilot Malaysia ditangkap di Soetta bawa 26 kg ekstasi. Tiga wanita Malaysia juga diamankan.</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607742/marak-narkoba-dari-malaysia-ke-indonesia</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rekaman-cctv-menunjukkan-gerak-gerik-kopilot-malaysia-airlines-sebelum-ditangkap-di-soetta-dok-instagram-bea-cukai-1785729571253_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Dokter yang Hina Pasien BPJS 'Banyakin Duit Halal' Minta Maaf: Mohon Ampun</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:58:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Irawan</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>Dokter Tamara Dewi Jasmine viral setelah komentar menghina pasien BPJS. Ia meminta maaf atas pernyataannya yang menyinggung banyak pihak.</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607738/dokter-yang-hina-pasien-bpjs-banyakin-duit-halal-minta-maaf-mohon-ampun</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tangkap-layar-video-permintaan-maaf-salah-satu-tenaga-kesehatan-palembang-di-media-sosial-1786003592111_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>BM PAN Sebut Narasi Zulhas soal Tanam Sawit Disalahpahami</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:39:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Zulhas tidak mendorong petani meninggalkan padi. Pernyataannya menekankan komitmen pemerintah untuk swasembada pangan dan ketahanan nasional.</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607728/bm-pan-sebut-narasi-zulhas-soal-tanam-sawit-disalahpahami</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/16/menko-pangan-zulhas-saat-peresmian-1061-koperasi-desa-merah-putih-di-nganjuk-jatim-sabtu-1652026-1778908699079_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Komnas HAM Usul Bentuk Badan Pemulihan Korban Pelanggaran HAM Berat</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:28:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>Komnas HAM mendesak pemerintah untuk membentuk badan khusus pemulihan hak korban pelanggaran HAM berat, menekankan pentingnya pertanggungjawaban negara.</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607724/komnas-ham-usul-bentuk-badan-pemulihan-korban-pelanggaran-ham-berat</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/anggota-komnas-ham-amiruddin-al-rahab-1784704292091_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Rudy Tanoesoedibjo Absen Lagi, KPK: Jangan Tunda-tunda Penyidikan!</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:19:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Rudy Tanoesoedibjo mangkir dari panggilan KPK terkait kasus korupsi bansos 2020. KPK imbau agar Rudy kooperatif dan tidak menunda proses penyidikan.</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607722/rudy-tanoesoedibjo-absen-lagi-kpk-jangan-tunda-tunda-penyidikan</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/03/02/gedung-baru-kpk-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>KPK Usut Dugaan Staf Peras Bupati Pemalang Bukan Kasus Pertama</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:18:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Adhfar Aulia Syuhada</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>KPK mengusut staf administrasi Setya Budi terkait pemerasan Bupati Pemalang. Proses penyidikan berlanjut, termasuk kemungkinan keterlibatan pihak lain.</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607721/kpk-usut-dugaan-staf-peras-bupati-pemalang-bukan-kasus-pertama</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/30/staf-admin-kpk-ditahan-1785384064541_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Ungkap Prabowo Tertarik Sepatu Buatannya, Diminta Kembangkan</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:03:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Arif Satria mengungkap ketertarikan Presiden Prabowo pada sepatu karet lokal. Sepatu ini murah dan dikembangkan dari limbah sawit.</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607708/kepala-brin-ungkap-prabowo-tertarik-sepatu-buatannya-diminta-kembangkan</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/arif-satria-dan-prabowo-subianto-1786024963610_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Wajah Bopeng Trotoar Sentul gara-gara Diterabas Pemotor</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:59:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Trotoar di Jalan Alternatif Sentul, Desa Cijujung, Kecamatan Sukaraja, Bogor, Jawa Barat, menjadi bopeng.</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607705/wajah-bopeng-trotoar-sentul-gara-gara-diterabas-pemotor</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/trotoar-di-jalan-alternatif-sentul-bogor-sering-dilewati-motor-sampai-rusak-rizkydetikcom-1785980261197_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Temui Wamensos, 4 Bupati Siap Bangun Sekolah Rakyat Permanen</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:51:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Empat kepala daerah siap dukung Sekolah Rakyat untuk memutus rantai kemiskinan melalui pendidikan. Program ini menyasar anak-anak dari keluarga miskin.</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607701/temui-wamensos-4-bupati-siap-bangun-sekolah-rakyat-permanen</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temui-wamensos-4-bupati-siap-bangun-sekolah-rakyat-permanen-1786024259848_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Warga Binaan Ketahuan Umpetin Sabu Usai Diminta Jongkok Petugas Rutan Salemba</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:43:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Seorang warga binaan berinisial FK ditangkap saat mencoba menyelundupkan sabu dan inex ke Rutan Kelas I Jakarta Pusat.</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607691/warga-binaan-ketahuan-umpetin-sabu-usai-diminta-jongkok-petugas-rutan-salemba</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/barang-bukti-dipamerkan-dalam-konferensi-pers-terkait-warga-binaan-mencoba-menyelundupkan-narkotika-ke-rutan-salemba-dok-istim-1786023754017_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>BRIN Ungkap Progres Perkembangan Teknologi Nuklir Pangan hingga Kesehatan</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:38:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>BRIN mempresentasikan riset teknologi nuklir kepada Presiden Prabowo. Teknologi nuklir yang dipresentasikan fokus pada nuklir damai untuk energi hingga pangan.</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607688/brin-ungkap-progres-perkembangan-teknologi-nuklir-pangan-hingga-kesehatan</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/brin-presentasi-hasil-riset-teknologi-nuklir-cahyo-biro-pers-media-dan-informasi-sekretariat-presiden-1786023463743_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Kebakaran di SDN 04 Srengseng Sawah Diduga Akibat Korsleting Listrik</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:38:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Kebakaran di gudang buku SDN 04 Srengseng Sawah diduga akibat korsleting listrik. Evakuasi siswa berjalan lancar, tidak ada korban jiwa.</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607687/kebakaran-di-sdn-04-srengseng-sawah-diduga-akibat-korsleting-listrik</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kebakaran-di-sdn-di-srengseng-sawah-jagakarsa-jakarta-selatan-telah-padam-kebakaran-terjadi-di-gudang-penyimpanan-buku-dok-dam-1786000554849_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Setelah Don Ritto, Kejagung Geledah Rumah Nurman Herin Terkait TPPU Febrie</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:29:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Rumondang Naibaho</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung menggeledah rumah tersangka Nurman Herin dalam kasus pencucian uang yang melibatkan mantan Jampidsus Febrie Adriansyah. Bukti ditemukan.</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607683/setelah-don-ritto-kejagung-geledah-rumah-nurman-herin-terkait-tppu-febrie</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Sempat Gagal Dua Kali, Ramdhan Raih Predikat Lulusan Terbaik IPDN</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:08:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Muhammad Ramdhan, lulusan terbaik IPDN, berhasil setelah dua kali gagal. Dukungan orang tua dan tekadnya membawanya meraih prestasi gemilang.</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607664/sempat-gagal-dua-kali-ramdhan-raih-predikat-lulusan-terbaik-ipdn</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sempat-gagal-dua-kali-ramdhan-raih-predikat-lulusan-terbaik-ipdn-1786021687636.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Menkes soal Viral Nakes Hina Pasien BPJS: Nggak Boleh Nirempati</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:07:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Menkes Budi Gunadi Sadikin menyesalkan tindakan nakes yang menghina pasien BPJS, Yurizal. Ia menekankan pentingnya empati dalam pelayanan kesehatan.</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607662/menkes-soal-viral-nakes-hina-pasien-bpjs-nggak-boleh-nirempati</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/24/menkes-budi-gunadi-sadikin-1782280281551_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Kala Proyek Trotoar Lebar di Depok Diprotes Warga</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:05:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Pembangunan trotoar di Jalan Pemuda menuai sorotan. Pasalnya lebar trotoar dinilai terlalu luas hingga membuat jalan utama semakin sempit.</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607661/kala-proyek-trotoar-lebar-di-depok-diprotes-warga</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/proyek-trotoar-di-jalan-pramuka-depok-1785988778760_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Sudaryono Copot Kepala SPPG di Papua Buntut Kasus Keracunan MBG</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:50:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono mencopot kepala SPPG di Jayapura setelah kasus keracunan program MBG. Investigasi sedang dilakukan untuk mencegah kejadian serupa.</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607643/sudaryono-copot-kepala-sppg-di-papua-buntut-kasus-keracunan-mbg</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Wamendagri Minta Tata Kelola MBG Dievaluasi usai Kasus Keracunan di Papua</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:45:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Haluk evaluasi Program MBG di Jayapura. Fokus pada keamanan pangan dan perbaikan proses distribusi untuk kesehatan penerima manfaat.</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607616/wamendagri-minta-tata-kelola-mbg-dievaluasi-usai-kasus-keracunan-di-papua</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/wamendagri-dorong-evaluasi-menyeluruh-tata-kelola-mbg-usai-keracunan-papua-1786019051110_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Viral 2 Monyet Diikat di Lampu Merah Kalibata Siang-siang Bikin Iba</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:39:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>Video viral dua monyet diikat di tiang lampu lalu lintas Jakarta memicu kepedulian warganet. Dinas KPKP DKI Jakarta menyelidiki dugaan eksploitasi satwa.</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607630/viral-2-monyet-diikat-di-lampu-merah-kalibata-siang-siang-bikin-iba</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/monyet-diikat-di-tiang-lampu-merah-jakarta-dok-medsos-1786019911702_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Proyek Koperasi Desa Merah Putih di Yahukimo Dimulai</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:57:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>Kemenkop bersama Pemerintah Kabupaten Yahukimo melakukan peletakan batu pertama pembangunan Koperasi Desa Merah Putih di Yahukimo, Papua Pegunungan.</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607736/proyek-koperasi-desa-merah-putih-di-yahukimo-dimulai</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kopdes-merah-putih-yahukimo-1786028188459_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>LRT  Kelapa Gading-Manggarai Diresmikan 26 Agustus!</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:14:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam, Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi menyampaikan LRT Jakarta Kelapa Gading-Manggarai akan diresmikan pada 26 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8607718/lrt-kelapa-gading-manggarai-diresmikan-26-agustus</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/stasiun-lrt-kelapa-gading-1785919858797_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Istana Putuskan Calon Gubernur BI Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:23:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi menyampaikan calon Gubernur Bank Indonesia (BI) akan diputuskan pada pekan ini.</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607676/istana-putuskan-calon-gubernur-bi-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/mensesneg-prasetyo-hadi-1784627991634_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>China dan Rusia Berminat Bangun Kereta Trans Kalimantan</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:00:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi mengungkapkan minat investor China dan Rusia untuk membangun jalur kereta Trans Kalimantan. Proposal resmi sedang ditunggu.</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8607603/china-dan-rusia-berminat-bangun-kereta-trans-kalimantan</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/01/04/pembangunan-jembatan-layang-di-jalan-trans-kalteng_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Cerita di Balik Praperadilan Febrie Adriansyah, Polri Sempat Tak Dipertimbangkan Jadi Pihak Termohon</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:47:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Namun situasi itu berubah ketika tim hukum Febrie Adriansyah mendapat berbagai masukan dari ahli yang saat itu mereka libatkan.</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864974/cerita-di-balik-praperadilan-febrie-adriansyah-polri-sempat-tak-dipertimbangkan-jadi-pihak-termohon</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vnA3GyrBpxMBzqqmAaE7LxF8zBw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Febri-Diansyah-Kuasa-Hukum-Eks-Jampidsus-Podcast-di-Tribunnews_20260806_170759.jpg</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi IV DPR Pertanyakan Rendahnya Serapan Anggaran Pemulihan Bencana di Sumbar</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:44:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Alex menilai, minimnya serapan anggaran ini menyisakan tanda tanya besar yang harus dijawab secara jujur, baik oleh pemerintah daerah.</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864973/wakil-ketua-komisi-iv-dpr-pertanyakan-rendahnya-serapan-anggaran-pemulihan-bencana-di-sumbar</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/_OCGsDuw1aWEsBMzjs38MxF8sI4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wakil-Ketua-Komisi-IV-DPR-RI-Alex-Indra-Lukman-2310.jpg</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Gus Salam Ziarah dan Silaturahmi ke Kediaman Rais Syuriyah PWNU Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:42:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Bagi Gus Salam, perjalanan silaturahmi ke Sulawesi Tengah memberikan banyak inspirasi mengenai model dakwah yang dibangun Guru Tua.</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864972/gus-salam-ziarah-dan-silaturahmi-ke-kediaman-rais-syuriyah-pwnu-sulawesi-tengah</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/gQPS5uAVCzw1Q4CfpmoOyE6bYEs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/silaturahmi-gus-salam-asd.jpg</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Kasus Mutilasi Depok, Polisi Perlu Dalami Dugaan Kekerasan Seksual Sebelum Pembunuhan</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:41:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Saepullah akui bunuh dan mutilasi korban di kontrakan Depok. Polisi dalami dugaan pelecehan fisik sebelum peristiwa terjadi.</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/tribunners/7864971/kasus-mutilasi-depok-polisi-perlu-dalami-dugaan-kekerasan-seksual-sebelum-pembunuhan</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hbY1aZw_KZ28iXykvBfi1MWNxDo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Reza-Indragiri-Amril-soroti-kasus-Taufik-Hidayat-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Temuan Ratusan Senjata di Pondok Pinang Masih Diselidiki Polisi, Dua Pihak Saling Klaim</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:34:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>995 senjata yang ditemukan di sekolah swasta di kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan, diklaim merupakan barang legal.</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7864970/temuan-ratusan-senjata-di-pondok-pinang-masih-diselidiki-polisi-dua-pihak-saling-klaim</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/C0lT2Y0zI_MxSjs7s2qkRNylM8s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Benda-berbentuk-senjata-yang-ditemukan-di-sebuah-ruangan-321.jpg</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Lokta Perbakin Klaim 995 Airsoft Temuan di Kebayoran Lama Jaksel Bukan Senjata Ilegal</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:30:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>995 senjata adalah legal sesuai Surat Izin SI/5483-XII/2008 diterbitkan Polri milik dari PT Lokta Karya Perbakin</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7864969/lokta-perbakin-klaim-995-airsoft-temuan-di-kebayoran-lama-jaksel-bukan-senjata-ilegal</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c23bmk4PHY76ZCmOECtNP5j3wK4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ratusan-senjata-api-di-sekolah-swasta-Pondok-Pinang-Kebayoran-Lama-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Momen di Balik Podcast Sarwendah, Ada Peringatan Keras Denny Sumargo Sebelum Kamera Menyala</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:29:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Densu membongkar percakapan emosional serta peringatan yang ia sampaikan langsung kepada Sarwendah sebelum proses rekaman dimulai.</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7864968/momen-di-balik-podcast-sarwendah-ada-peringatan-keras-denny-sumargo-sebelum-kamera-menyala</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ik23waLzTdDpWPovuqWu3mZdce4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Denny-Sumargo-1-03082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Buntut Komentar Nirempati ke Pasien BPJS, 10 Nakes Bisa Terancam Sanksi hingga Pencabutan STR</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:28:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Anggota Pimpinan KKI  Mohammad Syahril menanggapi kasus komentar nirempati yang diberikan nakes kepada pasien BPJS bernama Yurizal Tri Chaerawan.</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864967/buntut-komentar-nirempati-ke-pasien-bpjs-10-nakes-bisa-terancam-sanksi-hingga-pencabutan-str</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/p0kXUyCR8fnZZnvbSAImBeiibE4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KOMENTAR-PASIEN-BPJS-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Trump Murka, Ancam Penjarakan Pembocor Isu Krisis Amunisi AS di Tengah Perang Lawan Iran</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:25:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Trump murka usai isu krisis amunisi AS mencuat. Pembocor informasi militer diancam hukuman penjara, sementara stok rudal Pentagon jadi sorotan</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7864966/trump-murka-ancam-penjarakan-pembocor-isu-krisis-amunisi-as-di-tengah-perang-lawan-iran</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zAJrXAtbprOaJvloF4HTWYbFg8I=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DONALD-TRUMP-SAAT-BERPIDATO-DI-MICHIGAN-27072026.jpg</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPAS Kelas 6 SD Kurikulum Merdeka Hal 164 Edisi Revisi: Sistem Tata Surya</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:25:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Simak berikut merupakan kunci jawaban buku pelajaran IPAS kelas 6 SD/MI Kurikulum Merdeka (Edisi Revisi) halaman 164 bab 6: : Sistem Tata Surya</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7864965/kunci-jawaban-ipas-kelas-6-sd-kurikulum-merdeka-hal-164-edisi-revisi-sistem-tata-surya</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/reTJ9u7n0HNj2tEhsGGySd0oe-w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Siswa-Tetap-Semangat-Masuk-Sekolah-Setelah-Libur-Lebaran-2026_20260330_122954.jpg</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Soal Respons Saksi Ditanya ‘Dapat Duit dari Doktif?’, Richard Lee Curiga Kebohongan Disembunyikan</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:17:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Richard Lee menilai ada ketidaksesuaian antara mimik wajah saksi dan jawaban lisan yang disampaikan kepada majelis hakim.</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7864964/soal-respons-saksi-ditanya-dapat-duit-dari-doktif-richard-lee-curiga-kebohongan-disembunyikan</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1uynxN2bOm-vhlWElEhMtM3x7QM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sidang-richard-lee-22.jpg</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Perbaikan Operasional dan Akses Pasar Dorong Prospek Ekspor Garmen Indonesia</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:16:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Peningkatan daya saing industri tidak hanya ditentukan oleh biaya tenaga kerja, tetapi juga efektivitas pengelolaan operasional di tingkat produksi.</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7864963/perbaikan-operasional-dan-akses-pasar-dorong-prospek-ekspor-garmen-indonesia</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7P-hvz4qtc1lfnh5p-2mvNEa8P4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kiri-ke-Kanan-Muhammad-Hendrian-Analis-Kebijakan-di-Lingkungan-Kementerian-Perindustrian.jpg</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Jadwal Tayang MotoGP Inggris 2026 Mulai Besok: Marc Marquez Cs Coba Pecahkan Tradisi Silverstone</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:15:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Marc Marquez cs beraksi di MotoGP Inggris 2026 dengan publik menanti apakah tradisi selalu melahirkan juara berbeda kembali berlanjut.</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7864962/jadwal-tayang-motogp-inggris-2026-mulai-besok-marc-marquez-cs-coba-pecahkan-tradisi-silverstone</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/MEy9iIAnegjypjQBfgLWO7TUHFo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Balapan-sprint-race-MotoGP-Valencia-2025.jpg</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Penasihat Presiden Sebut Makalah MBG Untuk Nobel Perdamaian Bukan dari Pemerintah</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:06:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Hasan Nasbi menegaskan makalah  terkait program MBGyang disebut untuk dinominasikan dalam ajang Nobel Perdamaian 2026, bukan dari pemerintah</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864961/penasihat-presiden-sebut-makalah-mbg-untuk-nobel-perdamaian-bukan-dari-pemerintah</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iZ4zuJPH-8FlSDDMiNuidK8nQf4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penasihan-Khusus-Presiden-Bidang-Komunikasi-Hasan-Nasbi-123654.jpg</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Sosok Indra Wargadalem, Eks Ketua Yayasan Sekolah Swasta Jaksel yang Dikaitkan Temuan 995 Senpi</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:05:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Indra Wargadalem tengah menjadi sorotan setelah dikaitkan dengan penemuan 995 senpi di sebuah sekolah swasta di Jaksel. Ini profilnya.</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864960/sosok-indra-wargadalem-eks-ketua-yayasan-sekolah-swasta-jaksel-yang-dikaitkan-temuan-995-senpi</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vW0d_IgDKBzXm1gs4Ywv9pSzyic=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sosok-Indra-Wargadalem.jpg</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Rekam Jejak Respati Ardi, Wali Kota Solo Digugat Bar Ruang Bahagia Buntut Razia Miras di Lokananta</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:02:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Wali Kota Solo, Respati Ardi, digugat oleh Bar Ruang Bahagia terkait razia minuman keras di kawasan Lokananta.</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7864959/rekam-jejak-respati-ardi-wali-kota-solo-digugat-bar-ruang-bahagia-buntut-razia-miras-di-lokananta</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hRa4HibmH-qJUUALGVQo5tfcmAo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wali-Kota-Solo-Terpilih-2024-Respati-Ardi.jpg</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Desiree Tarigan Puji Buku EPIC Vershome, Ajak Anak Muda Berbagi Ilmu Lewat Karya Literasi</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:02:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Desiree Tarigan berharap generasi muda berani membagikan ilmu dan pengalaman mereka kepada masyarakat luas melalui karya literasi.</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7864958/desiree-tarigan-puji-buku-epic-vershome-ajak-anak-muda-berbagi-ilmu-lewat-karya-literasi</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vq1Mn_LBwqj5anBdXwsN2Jt5KXw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Desiree-1-05082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Hasil Babak Pertama Persib vs Persebaya: Skor 1-1, Sananta dan Matricardi Saling Balas Gol</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:59:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Persib Bandung dan Persebaya Surabaya bermain imbang 1-1 pada babak pertama final Piala Presiden 2026. Sananta dan Matricardi sama-sama mencetak gol.</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864957/hasil-babak-pertama-persib-vs-persebaya-skor-1-1-sananta-dan-matricardi-saling-balas-gol</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/HAgsthoY5Rw5MnXwygZ-TgqFSME=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Aksi-penyerang-Persib-Bandung-Uilliam-Barros-saat-cetak-gol-melawan-Arema-FC.jpg</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>John Herdman Puji Permainan Singapura, Tetapi Tegaskan Garuda Datang untuk Menang</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:52:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>John Herdman menilai Singapura merupakan tim yang memiliki karakter permainan positif dan tidak sekadar mengandalkan strategi bertahan.</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7864956/john-herdman-puji-permainan-singapura-tetapi-tegaskan-garuda-datang-untuk-menang</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5--Pv7tebNEyl0mxHHmRV8UW3WE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pelatih-Timnas-Indonesia-John-Herdman-saat-diwawancarai.jpg</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Ekonomi Tumbuh, Ketimpangan Melebar: DPR Desak Pemerintah Perkuat Perlindungan Pekerja Informal</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:49:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Said berharap program afirmasi tersebut mencakup pemberian beasiswa, kemudahan akses BPJS, hingga perluasan lapangan kerja.</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7864955/ekonomi-tumbuh-ketimpangan-melebar-dpr-desak-pemerintah-perkuat-perlindungan-pekerja-informal</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5usl4QaobnTw6Cy-zE3pr7If0q0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ketua-banggar-said-abdullah-rapur-dpr-rabu-20-mei.jpg</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Transaksi QRIS Meroket, Jalin-BACenter Dukung Digitalisasi Pembayaran</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:12:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Erik Purnama Putra</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Jalin Pembayaran Nusantara (Jalin) yang menjadi bagian ekosistem Danantara Indonesia dan Yayasan Bina Astacita Center (BACenter) saling berkolaborasi. Kedua institusi tersebut pun menandatangani nota kesepahaman...</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcq5k484/transaksi-qris-meroket-jalinbacenter-dukung-digitalisasi-pembayaran</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260806204634-115.png</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Eks Ketua Yayasan Bantah Narkoba dan CD Porno di Sekolah Jaksel Miliknya</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:33:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>Eks Ketua Yayasan justru meminta polisi menelusuri pihak yang menguasai lingkungan sekolah sejak April 2026.</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263833/eks-ketua-yayasan-bantah-narkoba-dan-cd-porno-di-sekolah-jaksel-miliknya</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ETTDU2qEXOzAfRQOJ_Mo1H87TaE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317518/original/012310700_1786017988-Bungker.webp</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Sengketa Yayasan Antara 3 Pembina di Balik Temuan 995 Senjata</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:33:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>Perkara sengketa jelang putusan di PN Jakarta Pusat.</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263831/sengketa-yayasan-antara-3-pembina-di-balik-temuan-995-senjata</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>TelkomGroup Tanam 20 Ribu Mangrove untuk Perkuat Ketahanan Ekosistem Pesisir Indonesia</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:12:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>TelkomGroup menanam 20 ribu mangrove sebagai upaya memperkuat ketahanan ekosistem pesisir, mengurangi abrasi, dan mendukung keberlanjutan lingkungan.</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263824/telkomgroup-tanam-20-ribu-mangrove-untuk-perkuat-ketahanan-ekosistem-pesisir-indonesia</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/7iNINKuyrfgCTaVJirgAATQtWwU=/0x169:6000x3551/673x379/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317607/original/092401400_1786025430-Foto_1__2___1_.jpg</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Prabowo Sedih Indonesia Tak Lolos Piala Dunia: Masa Cape Verde Masuk</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:06:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>Dia kemudian membandingkan jumlah penduduk Cape Verde dengan Kabupaten Sumedang, Jawa Barat.</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263821/prabowo-sedih-indonesia-tak-lolos-piala-dunia-masa-cape-verde-masuk</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/YrVtnOghfnGhiMGOoOcxcQ6XGg0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9312462/original/075432400_1785494670-email-attachment_2026_07_31_ariefhakim-at-klyid_prabowo-subianto-sebut-semua-negara-gagal-karena-elitnya-ribut_1000393889.jpg</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Kejagung Kembali Periksa 9 Saksi dalam Kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:48:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>Penyidikan kasus TPPU FA berlanjut, Kejagung memeriksa 9 saksi dan menggeledah rumah di Bandung.</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263811/kejagung-kembali-periksa-9-saksi-dalam-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/w_GeOd-UYoIvUQ2hdbIaeIz-tIY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5512712/original/018042200_1771992094-WhatsApp_Image_2026-02-25_at_10.59.24.jpeg</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Pemadaman Terus Dilakukan Setelah Karhutla Melanda Gunung Bromo</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:18:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan masih melanda kawasan Taman Nasional Bromo Tengger Semeru (TNBTS), Kabupaten Probolinggo, Jawa Timur, Kamis (6/8/2026). Berdasarkan laporan Badan Nasional Penanggulangan Bencana (BNPB), sekitar 60 hektare lahan telah terbakar. Petugas terus melakukan pemadaman dengan mengerahkan berbagai peralatan, termasuk drone water spray untuk menjangkau titik api di medan yang sulit diakses. Upaya pengendalian dilakukan agar kebakaran tidak meluas ke kawasan konservasi lainnya.</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8263799/pemadaman-terus-dilakukan-setelah-karhutla-melanda-gunung-bromo</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/wK2gPH1_-8IdGpx1ZrBKthC7qKE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317570/original/070568800_1786022249-br1.jpg</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>Prabowo Sebut Indonesia Tak Kekurangan Orang Pintar, Tapi Butuh Dibina</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:02:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>Prabowo juga sempat mengutip pernyataan Presiden ke-3 RI, BJ Habibie.</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263779/prabowo-sebut-indonesia-tak-kekurangan-orang-pintar-tapi-butuh-dibina</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/FoiefrwGe4QDCRwl2XNxoHsJAeY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5386433/original/064295900_1761008005-8.jpg</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Wamendagri Minta Pengelolaan MBG Segera Dibenahi</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:05:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>Evaluasi dilakukan menyusul dugaan keracunan yang dialami ratusan penerima manfaat, mulai dari sanitasi, penyimpanan makanan, hingga mekanisme distribusi.</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263778/wamendagri-minta-pengelolaan-mbg-segera-dibenahi</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/v_NpJVDUKp0ETTvYa7z3v-B3ioM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317562/original/012874000_1786021313-WhatsApp_Image_2026-08-06_at_19.30.27.jpeg</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Awal Mula Terbongkarnya Temuan 995 Senjata di Sekolah Versi Yayasan</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:00:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Guru Mengeluh Gaji Tak Pernah Naik, Pengurus Baru Bongkar Dugaan Penyimpangan hingga Temukan Ratusan Senjata</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263776/awal-mula-terbongkarnya-temuan-995-senjata-di-sekolah-versi-yayasan</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ETTDU2qEXOzAfRQOJ_Mo1H87TaE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317518/original/012310700_1786017988-Bungker.webp</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Pemkot Bogor Bakal Adakan Lagi CFD Tiap Minggu, Lokasinya Masih Dicari</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:11:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>Pemkot Bogor berencana menghidupkan kembali CFD setelah vakum sejak pandemi. Namun, lokasi baru masih dikaji agar tak mengganggu aktivitas warga.</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/06/22110461/pemkot-bogor-bakal-adakan-lagi-cfd-tiap-minggu-lokasinya-masih-dicari</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/XSCUirIk4rikiEE1Xkb0J02qWzM=/0x0:954x636/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2023/10/19/653114e6ba96f.jpg</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Ibu Pengidap Stroke Tewas Diduga Dibunuh Anaknya di Ngawi</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:11:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Seorang perempuan di Ngawi tewas dengan luka di kepala. Diduga, perempuan itu dibunuh oleh anaknya</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/06/213631178/ibu-pengidap-stroke-tewas-diduga-dibunuh-anaknya-di-ngawi</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/17MHzoDbReBTJFot9g6e0SCG9do=/0x2:897x600/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2019/05/18/1478721438.jpg</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Diskon Grab sampai 81 Persen Sepanjang Agustus, Ojol hingga Pesan Makan</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:11:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Momentum Hari Kemerdekaan menjadi kesempatan bagi kami untuk menghadirkan manfaat yang dapat dirasakan seluruh ekosistem Grab.</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/06/210120826/diskon-grab-sampai-81-persen-sepanjang-agustus-ojol-hingga-pesan-makan</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/wgv26sn0fHSaqevNqXFfvZMqIDc=/0x0:534x356/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/03/24/69c1d5bf5fb9b.webp</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1029"/>
+  <autoFilter ref="A1:I1138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1138"/>
+  <dimension ref="A1:I1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -53924,8 +53924,2029 @@
         </is>
       </c>
     </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>KPK dalami pemberian Blueray Cargo kepada pegawai Bea Cukai</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:59:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) mendalami pemberian sejumlah uang dari PT Blueray Cargo kepada pegawai Direktorat ...</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683435/kpk-dalami-pemberian-blueray-cargo-kepada-pegawai-bea-cukai</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/pemeriksaan-iskandar-sitorus-sebagai-saksi-2835524.jpg</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>KPK dalami selisih uang yang dikembalikan Menhut dari Suhardiman Amby</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:54:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>ANTARA - Komisi Pemberantasan Korupsi (KPK) mendalami selisih uang yang dikembalikan Menteri Kehutanan Raja Juli Antoni ...</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683413/kpk-dalami-selisih-uang-yang-dikembalikan-menhut-dari-suhardiman-amby</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KPK-DALAMI-SELISIH-UANG-YANG-DIKEMBALIKAN-MENHUT-DARI-SUHARDIMAN-AMBY.jpg</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Warga keluhkan dampak revitalisasi Kali Cakung Lama di Kelapa Gading</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:54:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Warga Kampung Rawa Indah, RT 04/03, Kelurahan Pegangsaan Dua, Kecamatan Kelapa Gading, Jakarta Utara, mengeluhkan ...</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683433/warga-keluhkan-dampak-revitalisasi-kali-cakung-lama-di-kelapa-gading</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_4288.jpeg</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks perpanjang kontrak Naji Marshall</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:47:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks memperpanjang kontrak forward Naji Marshall setelah pemain berumur 28 tahun itu mencatatkan musim ...</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683429/dallas-mavericks-perpanjang-kontrak-naji-marshall</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000474637.jpg</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Hoki putra-putri Indonesia segrup dengan Jepang pada Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:43:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>Tim nasional hoki lapangan Indonesia, baik putra maupun putri, berada satu grup atau pul dengan tuan rumah Jepang pada ...</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683423/hoki-putra-putri-indonesia-segrup-dengan-jepang-pada-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/Tim-hoki-putri-Indonesia-kalahkan-Singapura-260626-fzn-12.jpg</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Komunikasi ATR/BPN baik dan meraih Popular Government Institutions</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:42:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Kementerian Agraria dan Tata Ruang (ATR)/Badan Pertanahan Nasional (BPN) meraih Popular Government Institutions Award ...</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683420/komunikasi-atr-bpn-baik-dan-meraih-popular-government-institutions</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_232006.jpg</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>PB SEMMI respons isu Surpres ganti Kapolri: Kinerja Listyo Sigit baik</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:37:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Serikat Mahasiswa Muslimin Indonesia (PB SEMMI) merespon isu adanya Surat Presiden (Supres) tentang ...</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683419/pb-semmi-respons-isu-surpres-ganti-kapolri-kinerja-listyo-sigit-baik</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1000087296.jpg</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Pemkot memetakan potensi kerawanan tawuran dan konflik sosial di Jakut</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:34:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Utara (Jakut) memetakan potensi kerawanan tawuran dan konflik sosial lewat forum ...</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683416/pemkot-memetakan-potensi-kerawanan-tawuran-dan-konflik-sosial-di-jakut</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1771904152_ae8bf4453e35621f9af3-2.jpeg</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>KPI ajak masyarakat kritis atas informasi tak valid di media sosial</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:32:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Komisi Penyiaran Indonesia (KPI) mengajak kepada masyarakat untuk bersikap kritis terhadap maraknya informasi tidak ...</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683415/kpi-ajak-masyarakat-kritis-atas-informasi-tak-valid-di-media-sosial</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001299202.jpg</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Warga Jakbar diimbau lakukan deteksi dini kanker payudara</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:20:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Jakarta Barat (Pemkot Jakbar) menegaskan pentingnya deteksi dini sebagai upaya preventif dan ...</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683409/warga-jakbar-diimbau-lakukan-deteksi-dini-kanker-payudara</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG_20260806_224733.v1.jpg</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Menkum menargetkan kerja sama dengan 1.000 LBH di 2027</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:19:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Menteri Hukum (Menkum) Supratman Andi Agtas menargetkan kerja sama dengan 1.000 lembaga bantuan hukum (LBH) atau ...</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683408/menkum-menargetkan-kerja-sama-dengan-1000-lbh-di-2027</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000473336.jpg</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Menang dramatis, Persebaya Surabaya juara Piala Presiden 2026</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:16:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Pesepak bola Persebaya Surabaya Ramadhan Sananta berselebrasi setelah mencetak gol ke gawang Persib Bandung pada final ...</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5683407/menang-dramatis-persebaya-surabaya-juara-piala-presiden-2026</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Final-Piala-Presiden-2026-060826-rzl-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Pemerintah sasar cakupan 5G nasional 2029 optimalkan pemanfaatan AI</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:13:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>Kementerian Komunikasi dan Digital (Kemkomdigi) menyasar agar cakupan 5G nasional bisa terwujud di 2029, sehingga ke ...</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683401/pemerintah-sasar-cakupan-5g-nasional-2029-optimalkan-pemanfaatan-ai</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/InShot_20260806_230301926.jpg</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Diego Forlan jadi pelatih interim timnas Uruguay</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:10:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Legenda sepak bola Uruguay, Diego Forlan ditunjuk sebagai pelatih interim tim nasional Uruguay setelah Marcelo Bielsa ...</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683400/diego-forlan-jadi-pelatih-interim-timnas-uruguay</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1000042734.jpg</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Gubernur Khofifah lepas kontingen Pramuka Jatim ke Jambore Nasional</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:08:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>ANTARA - Gubernur Jawa Timur, Khofifah Indar Parawansa, menanamkan semangat heroisme bagi kontingen Pramuka asal ...</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5683381/gubernur-khofifah-lepas-kontingen-pramuka-jatim-ke-jambore-nasional</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/GUBERNUR-KHOFIFAH-LEPAS-KONTINGEN-PRAMUKA-JATIM-KE-JAMBORE-NASIONAL.jpg</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Realisasi investasi Jakarta serap 289 ribu tenaga kerja</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:30:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Realisasi investasi Jakarta pada semester I 2026 yang mencapai Rp173,6 triliun menyerap 289 ribu tenaga kerja, terdiri ...</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683152/realisasi-investasi-jakarta-serap-289-ribu-tenaga-kerja</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/bursa-kerja-di-jakarta-2817824.jpg</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Kronologi temuan 995 pucuk senjata api di sekolah swasta Jaksel</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:00:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Tim kuasa hukum sekolah swasta di kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan mengungkap kronologi temuan ...</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5682835/kronologi-temuan-995-pucuk-senjata-api-di-sekolah-swasta-jaksel</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001014922.jpg</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Pria di Jakut Tersengat Listrik Saat Mau Curi Kabel Gardu, Alami Luka Bakar</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:42:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Seorang pria berinisial SD tersengat listrik saat mencoba mencuri kabel di gardu, mengalami luka bakar parah dan dirawat di RS Polri Kramat Jati.</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607786/pria-di-jakut-tersengat-listrik-saat-mau-curi-kabel-gardu-alami-luka-bakar</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/07/tangan-tersengat-listrik-1746608472483_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Pemerintah Renovasi Sekretariat LVRI, Bedah Rumah Veteran di 19 Provinsi</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:42:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Kementerian Pertahanan merenovasi 9 sekretariat LVRI dan 52 rumah veteran di 19 provinsi. Program ini wujud penghormatan negara kepada pejuang bangsa.</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607785/pemerintah-renovasi-sekretariat-lvri-bedah-rumah-veteran-di-19-provinsi</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pemerintah-renovasi-sekertariat-lvri-dan-rumah-veteran-di-19-provinsi-dok-istimewa-1786034404798_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Geger Mayat dalam Bagasi Mobil di Grobogan, Diduga Bos Konter HP yang Hilang</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:16:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Ardian Dwi Kurnia</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Warga Gubug, Grobogan, dikejutkan penemuan mayat dalam bagasi mobil. Diduga korban merupakan bos konten HP yang hilang di Ambarawa</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607777/geger-mayat-dalam-bagasi-mobil-di-grobogan-diduga-bos-konter-hp-yang-hilang</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/08/23/penemuan-mayat-wanita-duduk-di-melaya_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>BRIN: Presiden Beri Atensi Riset Pengelolaan Sampah hingga Genteng dari Limbah</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:41:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto apresiasi inovasi BRIN, termasuk teknologi pengelolaan sampah dan genteng ramah lingkungan. Kerja sama uji coba juga sedang dibangun.</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607760/brin-presiden-beri-atensi-riset-pengelolaan-sampah-hingga-genteng-dari-limbah</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/presiden-prabowo-melihat-hasil-riset-brin-cahyo-biro-pers-media-dan-informasi-sekretariat-presiden-1786030862950.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Penjaga hingga Pembuang Sampah di TPS Liar Jaktim Didenda Rp 5 Juta</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:29:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Rolando Fransiscus Sihombing</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Jakarta menindak tegas penimbunan sampah ilegal di Kramat Jati. Tiga pelaku dikenai sanksi denda administratif untuk mencegah pelanggaran serupa.</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607751/penjaga-hingga-pembuang-sampah-di-tps-liar-jaktim-didenda-rp-5-juta</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pemprov-dki-periksa-tps-liar-di-jaktim-1786030130768_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Mobil Terbakar di Tol Dalam Kota, Lalin Arah Cawang Macet Malam Ini</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:08:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Sebuah mobil Toyota Rush terbakar di Tol Dalam Kota arah Cawang, menyebabkan kemacetan. Api sudah padam, namun proses pendinginan masih berlangsung.</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607745/mobil-terbakar-di-tol-dalam-kota-lalin-arah-cawang-macet-malam-ini</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/13/ilustrasi-api_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Jurus Bank Jago Genjot Nasabah</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:39:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Amanda Christabel</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Bank Jago menggandeng Bibit &amp; Stockbit sejak 2021, untuk memberikan opsi investasi di dalam layanan perbankan digital.</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8607783/jurus-bank-jago-genjot-nasabah</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/04/15/bank-jago_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Pedestrian Deck Dukuh Atas: Ketika Kota Dibangun dari Langkah Kaki</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:00:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Shafira Cendra Arini</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Salah satu wujudnya di kawasan Dukuh Atas yang dirancang sebagai simpul transportasi terpadu dengan enam moda transportasi publik.</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8607770/pedestrian-deck-dukuh-atas-ketika-kota-dibangun-dari-langkah-kaki</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pedesterian-deck-dukuh-atas-1786031934340_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Batu Bara Hasil Sitaan Laku Dilelang Rp 20,97 Miliar</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:29:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM menyampaikan PNBP hasil lelang Barang yang Dikuasai Negara berupa batu bara hasil penegakan hukum di Kalimantan Timur sebesar Rp 20,97 miliar.</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607752/batu-bara-hasil-sitaan-laku-dilelang-rp-20-97-miliar</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/batu-bara-hasil-penindakan-hukum-laku-dilelang-1786030053576_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Wajah Musdalifah Basri Iritasi Akibat Totalitas saat Bikin Konten</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:09:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Komika Musdalifah Basri berbagi pengalaman buruk setelah menggunakan pewarna wajah berbahaya untuk konten. Kini, ia lebih berhati-hati dalam berkreasi.</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606916/wajah-musdalifah-basri-iritasi-akibat-totalitas-saat-bikin-konten</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/musdalifah-basri-1786000069978_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Klarifikasi Sarwendah Minta Tambah Tiket Konser BLACKPINK kepada Ruben Onsu</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:01:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Permintaan Sarwendah tambah tiket konser BLACKPINK jadi salah satu pemicu masalah dengan Ruben Onsu. Pihak Sarwendah klarifikasi soal ini.</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607627/klarifikasi-sarwendah-minta-tambah-tiket-konser-blackpink-kepada-ruben-onsu</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ruben-onsu-dan-sarwendah-1785990958073_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>MUA Bubah Alfian Cerita Detik Menegangkan Kecelakaan Mobil</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:25:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Makeup Artist Bubah Alfian menceritakan kecelakaan mobil setelah Jember Fashion Carnaval. Kelelahan dan kecepatan diduga jadi penyebab utama insiden tersebut.</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606994/mua-bubah-alfian-cerita-detik-menegangkan-kecelakaan-mobil</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/bubah-alfian-1785990698424_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Trump Serang Kandidat Senat Muslim Michigan: Dia Penuh Omong Kosong</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:30:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat menyerang kandidat Senat Michigan, Abdul El-Sayed yang merupakan seorang Muslim pada Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806121802-139-1389244/trump-serang-kandidat-senat-muslim-michigan-dia-penuh-omong-kosong</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/thumbnail-video-1785993732321_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>JD Vance Akui Negosiasi dengan Israel Amat Sulit</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:56:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Wakil Presiden Amerika Serikat JD Vance mengakui pembicaraan dengan Iran amat sulit.</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806201629-134-1389493/jd-vance-akui-negosiasi-dengan-israel-amat-sulit</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/11/wapres-as-jd-vance-1775872516501_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Pelobi Israel 'Siram' Rp536 M Demi Jegal Kandidat AS Pro Palestina</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:18:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Kelompok pelobi pro Israel yang sudah aktif sejak tahun 1950-an ini, disebut telah menggelontorkan dana hingga setara kurang lebih Rp536 miliar.</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806200347-134-1389490/pelobi-israel-siram-rp536-m-demi-jegal-kandidat-as-pro-palestina</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/05/07/menlu-as-antony-blinken-beri-sambutan-di-acara-aipac_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Bank-Bank Diminta Siaga Hadapi Petaka Besar, Korbannya Sudah Banyak</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Teknologi AI canggih membawa ancaman serius, dengan insiden pembobolan perusahaan. JPMorgan pimpin aliansi untuk mitigasi risiko.</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806124358-37-757098/bank-bank-diminta-siaga-hadapi-petaka-besar-korbannya-sudah-banyak</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/21/jp-morgan-chase-1784617169554_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Bunga di China Ternyata Makan Daging, Bentuknya Mengejutkan</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Penemuan mengejutkan, bunga liar Saxifraga candelabrum di China barat daya adalah tumbuhan karnivora pertama di genusnya.</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806061231-37-757111/bunga-di-china-ternyata-makan-daging-bentuknya-mengejutkan</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/rambut-kelenjar-yang-lengket-pada-spesies-tanaman-saxifraga-candelabrum-terlihat-sedang-memerangkap-serangga-mangsa-dalam-foto-1785997193512_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Ternyata Monyet Punya Binatang Peliharaan Seperti Manusia</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Penelitian Universitas Oxford mengungkap kera dan monyet juga merawat hewan dari spesies berbeda.</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806134904-37-757131/ternyata-monyet-punya-binatang-peliharaan-seperti-manusia</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/20/seekor-bayi-monyet-bernama-punch-menjadi-pusat-perhatian-di-media-sosial-punch-merupakan-bayi-monyet-di-kebun-binatang-ichikaw-1771567865691_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Raja Ojol Tutup di RI, Sekarang Menggila Ancam Driver Online</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Uber siapkan lebih dari Rp180 triliun untuk ekspansi taksi robot tanpa sopir. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806162635-37-757195/raja-ojol-tutup-di-ri-sekarang-menggila-ancam-driver-online</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/01/26/9d2fddd0-0e40-4370-a7f5-57170fa82b49_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Perusahaan China Bangkrut, Bos Besar Langsung Dihukum Mati</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Pengadilan China menjatuhkan hukuman mati kepada Zhao Weiguo, mantan Komisaris Utama Tsinghua Unigroup.</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260806162050-37-757192/perusahaan-china-bangkrut-bos-besar-langsung-dihukum-mati</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/05/15/ketua-tsinghua-unigroup-zhao-weiguo-terlihat-selama-wawancara-dengan-reuters-di-beijing-tiongkok-15-november-2015-1747293725188_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Said: Ekonomi Tumbuh 5,29 Persen Patut Disyukuri, Tapi Industri dan Pertanian Harus Diwaspadai</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Nashih Nashrullah</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Ketua Badan Anggaran (Banggar) DPR RI Said Abdullah mengapresiasi capaian pertumbuhan ekonomi Indonesia yang mencapai 5,29 persen secara tahunan (year on year/yoy) pada triwulan II 2026, di...</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcezx320/said-ekonomi-tumbuh-529-persen-patut-disyukuri-tapi-industri-dan-pertanian-harus-diwaspadai</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/ketua-dpp-pdip-yang-juga-ketua-badan-anggaran-banggar_220906182440-582.jpg</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>NCC 2026 Dorong Kolaborasi Perkuat Keamanan Siber dan Ekonomi Digital</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:48:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Penguatan keamanan siber dinilai menjadi prasyarat utama untuk menjaga laju pertumbuhan ekonomi digital Indonesia di tengah semakin masifnya adopsi kecerdasan buatan (artificial intelligence/AI). Tanpa sistem keamanan...</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjcmg2370/ncc-2026-dorong-kolaborasi-perkuat-keamanan-siber-dan-ekonomi-digital</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260806195140-854.png</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>Siasat Agar Tak Antre di SPBU Berjam-jam</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:03:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Antrean panjang di SPBU membuat pengendara menyusun strategi. Ada yang rela mengisi bensin tengah malam, sementara yang lain memilih membayar lebih mahal demi menghemat waktu.</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263527/siasat-agar-tak-antre-di-spbu-berjam-jam</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/B5vF_oqPo37pI7NMT6YfNm-drvQ=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317227/original/083215400_1786007013-IMG_20260806_100057_766.jpg</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Detik-Detik 2 Remaja Nyambi Kurir Sabu Tak Berkutik saat Dibekuk</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:06:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Keduanya sempat dikepung warga.</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263876/detik-detik-2-remaja-nyambi-kurir-sabu-tak-berkutik-saat-dibekuk</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/FgsrshL7R0LyFPttCAwrj8fdd8k=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317637/original/064591800_1786032367-IMG-20260806-WA0019.jpg</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Eks Ketua DPRD Ponorogo Jadi Tersangka Dugaan Korupsi Tunjangan Perumahan</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:55:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>SN kini ditahan di Rumah Tahanan Kelas IIB Ponorogo selama 20 hari untuk kepentingan penyidikan.</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263871/eks-ketua-dprd-ponorogo-jadi-tersangka-dugaan-korupsi-tunjangan-perumahan</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/iqwEsRApikkILHu3rLmVdAtxFKI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317631/original/047526200_1786031385-462812.jpg</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Kasus Mutilasi di Depok, Pelaku Resign dari Tempat Kerja Saat Hari Kejadian</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:21:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Redaksi Liputan6</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Sehari sebelum peristiwa pembunuhan, pelaku minta libur dengan alasan mengikuti wawancara kerja di sebuah food court mal.</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263859/kasus-mutilasi-di-depok-pelaku-resign-dari-tempat-kerja-saat-hari-kejadian</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/jk0mg0oz_NYTomVposjWMV7bOa4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317152/original/097817700_1786004215-email-attachment_2026_08_06_dicky-agung-prihanto_polisi-lakukan-pencarian-potongan-tubuh-korban-mutilasi-disepanjang-kali-licin-depok_IMG-20260806-WA0016.jpg</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1138"/>
+  <autoFilter ref="A1:I1181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1181"/>
+  <dimension ref="A1:I1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -55945,8 +55945,55 @@
         </is>
       </c>
     </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Lima Klaster Budidaya Rumput Laut, Mesin Penggerak Ekonomi Pesisir NTT</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:43:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Pemprov NTT menyiapkan lima klaster budidaya rumput laut  untuk memperkuat ekonomi pesisir melalui industri rumput laut yang terintegrasi dari hulu hingga hilir.</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8258000/lima-klaster-budidaya-rumput-laut-mesin-penggerak-ekonomi-pesisir-ntt</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/BEMmzSbMbghDJkycArhbEohHXRE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/557605/original/100505bfoto_petani-laut.jpg</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1181"/>
+  <autoFilter ref="A1:I1182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1310</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1182"/>
+  <dimension ref="A1:I1310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -55992,8 +55992,6024 @@
         </is>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>idEA Respons Keputusan Purbaya Tunda Pajak Marketplace Jadi 1 November</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:30:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>pajak marketplace 1 november</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806151229-92-1389338/idea-respons-keputusan-purbaya-tunda-pajak-marketplace-jadi-1-november</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/09/12/tanah-abang-sepi-pembeli-online-maupun-offline-9_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>OJK Tutup 1.220 Entitas Keuangan Ilegal, Mayoritas Pinjol</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:48:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Satuan Tugas Pemberantasan Aktivitas Keuangan Ilegal (Satgas PASTI) OJK menindak 1.220 entitas keuangan ilegal sepanjang periode Januari hingga 31 Juli 2026.</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806144051-78-1389322/ojk-tutup-1220-entitas-keuangan-ilegal-mayoritas-pinjol</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/12/06/perlindungan-konsumen-ojk_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>Buruh Desak Pemerintah Penuhi 4 Tuntutan Paling Lambat September</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:23:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>KSPI dan Partai Buruh meminta pemerintah segera menuntaskan empat tuntutan utama di bidang ketenagakerjaan paling lambat September 2026.</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806150420-92-1389336/buruh-desak-pemerintah-penuhi-4-tuntutan-paling-lambat-september</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/08/said-iqbal-1780909168706_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>VinFast Indonesia dan Danamon Jalin Kemitraan Pembiayaan Dealer</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:21:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>VinFast</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>VinFast Indonesia dan Bank Danamon menjalin kerja sama pembiayaan dealer di GIIAS 2026, dukung ekspansi jaringan dan ekosistem kendaraan listrik di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806200023-625-1389481/vinfast-indonesia-dan-danamon-jalin-kemitraan-pembiayaan-dealer</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/vinfast-1786022311078_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>BGN Minta Guru Edukasi Siswa agar MBG Tak Dibawa Pulang</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:02:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono meminta guru ikut mengedukasi siswa agar makanan dari program Makan Bergizi Gratis (MBG) dikonsumsi di sekolah dan tidak dibawa pulang.</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806184050-92-1389441/bgn-minta-guru-edukasi-siswa-agar-mbg-tak-dibawa-pulang</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bos-bgn-ultimatum-dapur-mbg-1785936867370_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Pesantren dengan 1.000 Santri atau Lebih Boleh Punya Dapur MBG Sendiri</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:47:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Pondok pesantren dan sekolah berbasis keagamaan dengan sistem asrama yang memiliki sedikitnya 1.000 santri atau siswa diperbolehkan membangun dapur MBG sendiri.</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806192930-92-1389470/pesantren-dengan-1000-santri-atau-lebih-boleh-punya-dapur-mbg-sendiri</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/15/libur-telah-usai-mbg-kembali-dsalurkan-ke-sekolah-1784084515012_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Purbaya soal Ekonomi RI Tumbuh 5,29 Persen Kuartal II: Cukup Baik</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:30:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya Yudhi Sadewa menilai pertumbuhan ekonomi Indonesia sebesar 5,29 persen pada kuartal II 2026 masih tergolong baik meski melambat.</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806062717-532-1389114/purbaya-soal-ekonomi-ri-tumbuh-529-persen-kuartal-ii-cukup-baik</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/28/purbaya-yudhi-sadewa-1782630196255_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Bos BGN Klarifikasi Isu 13 Ribu Dapur MBG Baru Segera Dibuka</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:23:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono meluruskan kabar soal pembukaan 13 ribu SPPG baru untuk dapur program Makan Bergizi Gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806190606-92-1389458/bos-bgn-klarifikasi-isu-13-ribu-dapur-mbg-baru-segera-dibuka</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/bgn-tutup-833-dapur-sppg-bermasalah-1785317578257_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>PNM Ajak Nasabah Mekaar Studi Banding, Buka Jalan Inovasi Usaha</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:13:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>PNM mengajak nasabah Mekaar studi banding untuk meningkatkan kapasitas dan pengetahuan nasabah untuk menciptakan produk bernilai tambah dan kesejahteraan.</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806191041-625-1389460/pnm-ajak-nasabah-mekaar-studi-banding-buka-jalan-inovasi-usaha</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/pnm-1786015572796_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Airlangga Ungkap Serapan Tenaga Kerja RI Naik 15% saat Marak Isu PHK</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:12:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Menko Perekonomian Airlangga mengungkapkan penyerapan tenaga kerja meningkat 15 persen di semester I 2026, meski ada isu PHK.</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806111120-92-1389224/airlangga-ungkap-serapan-tenaga-kerja-ri-naik-15-saat-marak-isu-phk</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/28/airlangga-hartarto-1777372147383_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Airlangga Sebut China Sambut Saham Kereta Cepat Diambil Alih Kemenkeu</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:52:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Menko Airlangga mengungkap pihak China telah menerima informasi terkait langkah Kemenkeu yang mengambil alih saham kereta cepat dari konsorsium BUMN KCIC.</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806142609-92-1389314/airlangga-sebut-china-sambut-saham-kereta-cepat-diambil-alih-kemenkeu</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/menteri-koordinator-bidang-perekonomian-airlangga-hartarto-1785934139213_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Prabowo Bakal Ajukan Nama Calon Gubernur Bl Baru Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:34:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto akan mengajukan nama calon Gubernur Bank Indonesia (BI) baru kepada Dewan Perwakilan Rakyat (DPR) RI pekan ini.</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806182525-78-1389433/prabowo-bakal-ajukan-nama-calon-gubernur-bl-baru-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/21/mensesneg-prasetyo-hadi-1784621820728_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>EWINDO: Warga Harus Diajak Rancang Program Sosial, Tak Hanya Menerima</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:27:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Corporate Secretary EWINDO Faisal Reza menilai pelibatan masyarakat dalam merancang program pemberdayaan demi menjaga keberlanjutan program.</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806175936-92-1389420/ewindo-warga-harus-diajak-rancang-program-sosial-tak-hanya-menerima</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/faisal-reza-1786001952964_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Lampung Financial Festival 2026 Bakal Hadir, Pendaftaran Segera Dibuka</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:17:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Lampung Financial Festival 2026 akan digelar pada 5-6 September, memperkuat literasi dan inklusi keuangan, libatkan berbagai pemangku kepentingan.</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806181145-83-1389423/lampung-financial-festival-2026-bakal-hadir-pendaftaran-segera-dibuka</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/lampung-financial-festival-2026-1786012678379_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Wali Kota Malang Ungkap 3 Syarat UMKM Bisa Naik Kelas</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:12:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Wali Kota Malang Wahyu Hidayat mengungkap tiga syarat agar para pelaku usaha mikro, kecil, dan menengah (UMKM) bisa naik kelas.</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806174600-92-1389414/wali-kota-malang-ungkap-3-syarat-umkm-bisa-naik-kelas</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/wahyu-hidayat-wali-kota-malang-di-the-bangun-bangsa-conference-1786012004254_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Negara di Ambang Perang, Presiden Dievakuasi Kendaraan Lapis Baja</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Presiden Taiwan, Lai Ching-te, memimpin latihan perang Han Kuang untuk memperkuat pertahanan menghadapi ancaman China.</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806151620-4-757159/negara-di-ambang-perang-presiden-dievakuasi-kendaraan-lapis-baja</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/para-tentara-berjalan-melewati-kendaraan-militer-saat-latihan-militer-tahunan-han-kuang-di-taipei-taiwan-6-agustus-2026-1786005288358_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Persiapan Perang! Pentagon Susun Strategi Nuklir Lawan Rusia-China</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Pentagon menyusun strategi nuklir untuk presiden AS, fokus pada senjata nuklir taktis.</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806151419-4-757158/persiapan-perang-pentagon-susun-strategi-nuklir-lawan-rusia-china</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/11/29/b-21-raider-angkatan-udara-amerika-serikat-pembom-siluman-jarak-jauh-yang-dapat-dipersenjatai-dengan-senjata-nuklir-lepas-land-6_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Kejar Ekonomi 11%, Bank-Bank Milik Tetangga RI Terancam-Diberi Warning</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Vietnam berambisi mencapai pertumbuhan ekonomi dua digit pada 2026, namun Fitch Ratings peringatkan bank-bank akan menghadapi tekanan signifikan</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806163456-4-757197/kejar-ekonomi-11-bank-bank-milik-tetangga-ri-terancam-diberi-warning</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/02/bank-central-vietnam-1782973836311_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Senjata AS Disebut "Sakaratul Maut", Trump dan Pentagon Pasang Kuda-Kuda</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Pejabat AS bantah laporan kekurangan amunisi.</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806063959-4-756949/senjata-as-disebut-sakaratul-maut-trump-pentagon-pasang-kuda-kuda</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/30/usa-trump-1785371156663_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Presiden Turun Tangan, Suhu 39 Derajat Bikin Negara Siaga</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Presiden Korsel Lee Jae-myung perintahkan kementerian siaga hadapi gelombang panas ekstrem. Suhu di Seoul diperkirakan mencapai 39°C, mendekati rekor tertinggi.</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806162145-4-757193/presiden-turun-tangan-suhu-39-derajat-bikin-negara-siaga</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/13/para-peserta-berjalan-di-sekitar-halaman-kuil-naksansa-selama-program-perjodohan-kuil-buddha-untuk-pria-dan-wanita-lajang-di-y-1783939121123_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>China Balas Dendam, Perusahaan Teknologi-Drone AS Kini Kena Getahnya</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:20:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>China membalas tekanan dagang dan teknologi dari Amerika Serikat (AS)</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806180523-4-757248/china-balas-dendam-perusahaan-teknologi-drone-as-kini-kena-getahnya</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/15/presiden-china-xi-jinping-memperlihatkan-suasana-kompleks-bersejarah-zhongnanhai-kepada-presiden-amerika-serikat-donald-trump--1778835485412_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Berumur 4 Dekade, Rusun Klender Bakal Disulap Sampai Punya 10.000 Unit</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi DKI Jakarta berencana akan merevitalisasi Rusun Klender sebagai bagian dari upaya menyediakan hunian yang lebih layak.</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806170805-7-757220/berumur-4-dekade-rusun-klender-bakal-disulap-sampai-punya-10000-unit</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/suasana-aktivitas-warga-di-kawasan-rumah-susun-rusun-klender-jakarta-kamis-682026-pemerintah-provinsi-dki-jakarta-berencana-ak-1786010808375_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Tak Cuma Taruh Dana di Bank, DPR Bocorkan Cara Purbaya Dorong Ekonomi</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:55:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XI DPR RI Mukhamad Misbakhun menilai pemerintah memiliki amunisi menggerakkan roda ekonomi di semester kedua tahun ini</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806202810-4-757269/tak-cuma-taruh-dana-di-bank-dpr-bocorkan-cara-purbaya-dorong-ekonomi</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/02/menteri-keuangan-ri-purbaya-yudhi-sadewa-berbincang-dengan-ketua-komisi-xi-dpr-ri-m-misbakhun-cnbc-indonesiatri-susilo-1767328515504_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Smelter Raksasa Bahan Baku Baterai EV Mulai Beroperasi di Sulteng!</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:50:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>PT Vale Indonesia Tbk menjadwalkan operasional atau startup proyek High Pressure Acid Leaching (HPAL) raksasa di Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806175304-4-757242/smelter-raksasa-bahan-baku-baterai-ev-mulai-beroperasi-di-sulteng</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/01/29/vale-reuterswashington-alvesfile-photo_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Purbaya Datangi Korban Montara, Bawa Pesan Khusus Prabowo</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:47:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa tengah melakukan kunjungan kerja ke Nusa Tenggara Timur, Kamis (6/8/2026)</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806204141-4-757270/purbaya-datangi-korban-montara-bawa-pesan-khusus-prabowo</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/menteri-keuangan-purbaya-melakukan-kunjungan-kerja-ke-ntt-untuk-menemui-korban-tumpahan-minyak-montara-1786027999931_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>DPR Ungkap Deretan Subsidi Pemerintah untuk Jaga Daya Beli Masyarakat</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:45:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XI DPR Mukhamad Misbakhun menjelaskan, pemerintah telah menggelontorkan subsidi untuk menjaga daya beli masyarakat</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806202044-4-757268/dpr-ungkap-deretan-subsidi-pemerintah-untuk-jaga-daya-beli-masyarakat</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/09/coffe-morning-cnbc-indonesia-berjudul-kupas-tuntas-aturan-penyeragaman-kemasan-produk-tembakau-1783565508612_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Guncangan Baru Dunia, Negara Ini Larang Ekspor Tembaga-Kobalt</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Republik Demokratik Kongo larang ekspor konsentrat tembaga dan kobalt untuk dorong pengolahan dalam negeri. Kebijakan ini berpotensi guncang industri global.</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806173927-4-757232/guncangan-baru-dunia-negara-ini-larang-ekspor-tembaga-kobalt</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/30/kobalt-1767071954540_169.gif?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Pikap Produksi Karawang Diekspor ke 27 Negara, Filipina Pasar Utama</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:35:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>PT Isuzu Astra Motor Indonesia tengah memperluas pasar ekspor kendaraan niaga buatan dalam negeri</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806201412-4-757267/pikap-produksi-karawang-diekspor-ke-27-negara-filipina-pasar-utama</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/07/24/isuzu-traga-di-ajang-gaikindo-indonesia-international-auto-show-giias-2025-cnbc-indonesiatri-susilo-1753347554725_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Kendaraan 4x4 Isuzu Siap untuk Daerah Bencana, Dari D-Max hingga Elf</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:25:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Kebutuhan kendaraan berpenggerak empat roda masih menjadi perhatian PT Isuzu Astra Motor Indonesia</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806195859-4-757266/kendaraan-4x4-isuzu-siap-untuk-daerah-bencana-dari-d-max-hingga-elf</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/isuzu-d-max-dikenalkan-di-ajang-gaikindo-indonesia-international-auto-show-giias-2026-yang-berlangsung-di-ice-bsd-tangerang-ra-1785912291851_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Proyek LRT Jakarta Velodrome-Manggarai Diresmikan 26 Agustus</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:15:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi memastikan peresmian LRT Jakarta Fase 1B bakal diresmikan 26 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806195325-4-757265/proyek-lrt-jakarta-velodrome-manggarai-diresmikan-26-agustus</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/27/suasana-pengerjaan-proyek-jalur-lintas-raya-terpadu-lrt-jakarta-rute-velodromemanggarai-fase-1b-di-kawasan-rawamangun-jakarta--1785140790098_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>China dan Rusia Minat Garap Proyek Rel Trans Kalimantan</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:05:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi membeberkan potensial investor yang akan ikut membangun jaringan kereta Trans Kalimantan</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806194722-4-757264/china-dan-rusia-minat-garap-proyek-rel-trans-kalimantan</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/04/menteri-perhubungan-menhub-dudy-purwaghandi-saat-ditemui-di-kompleks-parlemen-jakarta-kamis-462026-1780568570837_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Trump Tutup Kantor Konsulat AS di RI, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Amerika Serikat (AS) berencana menutup lima konsulat dan misi diplomatik di sejumlah negara, termasuk Konsulat AS di Medan, Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806172914-4-757217/trump-tutup-kantor-konsulat-as-di-ri-ada-apa</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/gedung-konsulat-jenderal-amerika-serikat-di-jerman-1786011390197_169.webp?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Ini Bocoran Menhub Kapan KA 'Orient Express' RI Beroperasi dan Rutenya</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:55:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Pemerintah bakal segera meresmikan kereta wisata mewah Nusantara Explorer</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806193901-4-757263/ini-bocoran-menhub-kapan-ka-orient-express-ri-beroperasi-rutenya</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/25/pt-kereta-api-indonesia-persero-melaksanakan-uji-statis-dan-uji-dinamis-terhadap-dua-kereta-nusantara-explorer-luxury-sleeper--1784953390022_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Tetap Waspada, Hal Ini Masih Jadi Ancaman Bagi Ekonomi RI</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:50:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Gejolak global masih menjadi tantangan besar bagi perekonomian Indonesia ke depan.</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806173758-4-757233/tetap-waspada-hal-ini-masih-jadi-ancaman-bagi-ekonomi-ri</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/17/api-berkobar-di-jembatan-yang-rusak-akibat-serangan-udara-di-bandar-khamir-provinsi-hormozgan-iran-16-juli-2026-dalam-cuplikan-1784262899518_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Prabowo Akan Terbitkan Aturan Baru Ojol, Ini Bocoran Menhub</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:45:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Emir Yanwardhana</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Pemerintah akan segera menerbitkan Peraturan Presiden (Perpres) yang mengatur soal ojek online (ojol).</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806193532-4-757262/prabowo-akan-terbitkan-aturan-baru-ojol-ini-bocoran-menhub</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/11/menteri-perhubungan-dudy-purwagandhi-saat-tiba-di-istana-negara-jakarta-kamis-1162026-1781158490961_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Ungkap Permintaan Prabowo Soal BBM B100-E100 Buat RI</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:35:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Arif Satria mengaku diminta Presiden Prabowo mengkaji dampak implementasi mandatori biodisel campuran 100% bahan nabati</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806192553-4-757261/kepala-brin-ungkap-permintaan-prabowo-soal-bbm-b100-e100-buat-ri</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/10/rektor-ipb-university-arif-satria-di-istana-kepresidenan-jakarta-pusat-senin-10112025-1762760175703_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Blusukan di Aceh, Wapres Gibran Cek Pembangunan Jembatan Pasca Bencana</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Wapres Gibran meninjau pembangunan Jembatan Krueng Tingkeum di Kita Blang, Kab. Bireuen, Aceh.</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806171747-7-757210/blusukan-di-aceh-wapres-gibran-cek-pembangunan-jembatan-pasca-bencana</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/wakil-presiden-gibran-rakabuming-meninjau-pembangunan-infrastruktur-di-aceh-1786011580022_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Misbakhun Bocorkan Sosok yang Tepat Jadi Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:25:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>Komisi XI DPR RI Mukhamad Misbakhun membeberkan kriteria sosok yang cocok untuk menjadi Gubernur Bank Indonesia (BI) baru</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806191450-4-757254/misbakhun-bocorkan-sosok-yang-tepat-jadi-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/09/coffe-morning-cnbc-indonesia-berjudul-kupas-tuntas-aturan-penyeragaman-kemasan-produk-tembakau-1783565508758_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Makin Banyak Warga RI Pasang Charger EV: 6 Bulan Tambah 21.865 Rumah</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:15:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>PT PLN (Persero) mencatat tambahan sebanyak 21.865 pelanggan baru yang menggunakan layanan pengisian daya kendaraan listrik</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806185224-4-757253/makin-banyak-warga-ri-pasang-charger-ev-6-bulan-tambah-21865-rumah</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/ilustrasi-petugas-pln-melakukan-pengecekan-kwh-meter-untuk-home-charging-kendaraan-listrik-meningkatnya-jumlah-pengguna-kendar-1786011138627_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Bos Ritel Benarkan Warga RI Kini Marak Belanja Pakai Paylater</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:05:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Hippindo anggap tren penggunaan layanan belanja sekarang bayar nanti atau buy now pay later (BNPL) di masyarakat masih tergolong wajar.</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806184702-4-757252/bos-ritel-benarkan-warga-ri-kini-marak-belanja-pakai-paylater</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/18/ketua-umum-hippindo-budihardjo-iduansjah-saat-menghadiri-opening-ceremony-bina-indonesia-great-sale-di-pusat-perbelajaan-kota--1766035998753_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Pengakuan Bos Ritel: Harga Barang Sudah Naik 5-10% Akibat Dolar Tinggi</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:55:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Hippindo mencatat harga sejumlah barang, khususnya produk impor, sudah naik beberapa waktu terakhir</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806183054-4-757251/pengakuan-bos-ritel-harga-barang-sudah-naik-5-10-akibat-dolar-tinggi</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/11/15/ketua-umum-himpunan-peritel-dan-penyewa-pusat-perbelanjaan-indonesia-hippindo-budihardjo-iduansjah_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Pesantren-Sekolah Asrama Boleh Bikin Dapur SPPG Sendiri, Ini Syaratnya</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>Pemerintah izinkan pondok pesantren dan sekolah berasrama dengan lebih dari 1.000 santri membangun dapur untuk program MBG dengan standar SPPG.</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806164415-4-757199/pesantren-sekolah-asrama-boleh-bikin-dapur-sppg-sendiri-ini-syaratnya</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/konferensi-pers-terkait-program-mbg-usai-rapat-koordinasi-terbatas-di-kantor-kemenko-bidang-pangan-jakarta-kamis-682026-1786004294635_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Prabowo Tak Risau Skor PISA RI Kalah dari Singapura, Ungkap Fakta Ini</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menganggap tidak fair jika skor PISA Indonesia dibandingkan dengan Singapura</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806182200-4-757249/prabowo-tak-risau-skor-pisa-ri-kalah-dari-singapura-ungkap-fakta-ini</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pertemuan-presiden-ri-dengan-150-periset-dari-badan-riset-dan-inovasi-nasional-6-agustus-2026-1786010089825_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>APBN 2027 Sudah Ancang-Ancang Hadapi Harga Minyak di Atas US$100/Barel</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:40:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Pemerintah telah menyiapkan skenario antisipasi dalam RAPBN 2027 apabila harga minyak mentah kembali melonjak di atas US$100 per barel.</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806164637-4-757200/apbn-2027-sudah-ancang-ancang-hadapi-harga-minyak-di-atas-us-100-barel</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/14/menteri-keuangan-menkeu-purbaya-yudhi-sadewa-menyampaikan-pokok-pokok-tanggapan-pemerintah-terhadap-pandangan-fraksi-fraksi-dp-1784007403180_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Ternyata Ini Alasan Isuzu Belum Boyong Truk dan Pikap Listrik ke RI</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>Tren elektrifikasi kendaraan listrik di Indonesia menghadapi tantangan di segmen komersial.</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806180442-4-757247/ternyata-ini-alasan-isuzu-belum-boyong-truk-dan-pikap-listrik-ke-ri</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/communication-management-department-head-pt-isuzu-astra-motor-indonesia-puti-annisa-moeloek-di-booth-isuzu-giias-kamis-682026-1786014840434_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Video:Gaspol di GIIAS, Geely Hadirkan Suv Ice Sporty Beperforma TinggI</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:30:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Gaspol di GIIAS 2026, Geely Hadirkan Suv Ice Sporty Beperforma Tinggi</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806130239-8-757115/videogaspol-di-giias-geely-hadirkan-suv-ice-sporty-beperforma-tinggi</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/gaspol-di-giias-2026-geely-hadirkan-suv-ice-sporty-beperforma-tinggi-1785997618123_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Bodong! Ada 6 Juta Data Ganda Penerima MBG, Sudaryono Bakal Bertindak</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Pemerintah temukan 6 juta data ganda dalam pemutakhiran penerima manfaat program Makan Bergizi Gratis. Diperkirakan, penerima manfaat tahun depan 63 juta orang.</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806162040-4-757191/bodong-ada-6-juta-data-ganda-penerima-mbg-sudaryono-bakal-bertindak</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/05/makan-bergizi-gratis-mbg-cnbc-indonesiafiasal-rahman-1775372467831_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Lewat Perpres, DPR Dorong Aktivitas Tambang di Pulau Belitung</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:05:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Ketua Komisi XII DPR RI, Bambang Patijaya, dukung penerbitan Perpres untuk legalitas timah di Belitung.</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806180056-4-757245/lewat-perpres-dpr-dorong-aktivitas-tambang-di-pulau-belitung</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/23/ketua-komisi-xii-dpr-bambang-patijaya-saat-menyampaikan-paparan-dalam-cnbc-indonesia-coffee-morning-di-queens-head-kemang-jaka-1761188752713_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Harga Biodiesel Naik Rp 14.924/L - Trump Kembalikan Uang "Pungli"</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:00:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>CNBC INDONESIA</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Harga Biodiesel Naik Rp 14.924/L - Trump Kembalikan Uang "Pungli"</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806143708-8-757147/harga-biodiesel-naik-rp-14924-l--trump-kembalikan-uang-pungli</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/harga-biodiesel-naik-rp-14924l-trump-kembalikan-uang-pungli-1786011978326_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Chery Q Tantang Mobil Listrik Murah di RI, Diskon Rp10 Juta di GIIAS</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>PT Chery Sales Indonesia luncurkan mobil listrik Chery Q di GIIAS 2026. Tersedia dua varian dengan harga promosi mulai Rp 239,9 juta.</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806145838-4-757154/chery-q-tantang-mobil-listrik-murah-di-ri-diskon-rp10-juta-di-giias</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/chery-q-menjalani-test-drive-di-area-sekitaran-ice-bsd-saat-event-giias-2026-kamis-682026-1786003152960_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Eks Pejabat Pertahanan Masuk Bui, Terima Suap Rp127 Miliar</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:56:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Mantan pejabat dijatuhi hukuman 10 tahun penjara karena kasus suap senilai 55 juta yuan. Ia mengakui kesalahan dan mengembalikan aset ilegal.</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806170317-4-757204/eks-pejabat-pertahanan-masuk-bui-terima-suap-rp127-miliar</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pengadilan-di-provinsi-sichuan-china-1786011233913_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Pemerintah Prioritaskan Daerah 3T dan Kelompok Prioritas untuk MBG</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:55:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Pangan Zulkifli Hasan memimpin rapat untuk memperkuat Program Makan Bergizi Gratis, fokus pada daerah 3T dan kelompok prioritas.</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806175101-4-757234/pemerintah-prioritaskan-daerah-3t-dan-kelompok-prioritas-untuk-mbg</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/dok-kementerian-dalam-negeri-1786013677319_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>BPS Resmi Rilis Indeks Kepuasaan Layanan Haji, Nilainya 83,28 di 2026</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) resmi merilis Indeks Kepuasan Layanan Haji Indonesia (IKLHI) pada 2026</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806161747-4-757190/bps-resmi-rilis-indeks-kepuasaan-layanan-haji-nilainya-8328-di-2026</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/02/infografis-layanan-umrah-bandara-soekarno-hatta-resmi-dipusatkan-di-terminal-2f-secara-bertahap-1782993817460_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>RI Punya Potensi 89.000 Ton Uranium Buat 'Nuklir', Ini Penjelasan BRIN</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Indonesia menyimpan potensi 89.000 ton uranium untuk bahan baku pembangkit listrik tenaga nuklir (PLTN)</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806161056-4-757188/ri-punya-potensi-89000-ton-uranium-buat-nuklir-ini-penjelasan-brin</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pertemuan-presiden-ri-dengan-150-periset-dari-badan-riset-dan-inovasi-nasional-6-agustus-2026-1786005466292_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>ClientEarth dan CPI Kolaborasi Perkuat Transisi Energi Berkeadilan</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:40:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>ClientEarth dan CPI Indonesia tandatangani MoU untuk dukung transisi energi berkeadilan dan net-zero 2060. Kolaborasi ini fokus pada kebijakan dan pendanaan.</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806173334-4-757231/clientearth-cpi-kolaborasi-perkuat-transisi-energi-berkeadilan</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/cpi-1786012625537_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Thailand Heboh Aktor Drama Gay Dikejar Fans Wanita, Bandara Minta Maaf</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Bandara Suvarnabhumi meminta maaf setelah insiden kericuhan penggemar drama Double Helix. Video diskriminatif petugas keamanan viral, memicu perhatian luas</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806160911-4-757187/thailand-heboh-aktor-drama-gay-dikejar-fans-wanita-bandara-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/11/01/turis-asing-tiba-di-bandara-suvarnabhumi-di-hari-pertama-pembukaan-pariwisata-thailand-7_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Bos BGN Minta MBG Jangan Dibawa Pulang-Dihabiskan di Sekolah, Kenapa?</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) imbau siswa tidak bawa pulang makanan dari program Makan Bergizi Gratis (MBG) untuk mencegah keracunan.</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806155510-4-757179/bos-bgn-minta-mbg-jangan-dibawa-pulang-dihabiskan-di-sekolah-kenapa</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/sudaryono-saat-dilantik-sebagai-kepala-badan-gizi-nasional-bgn-oleh-presiden-prabowo-subianto-di-istana-merdeka-jakarta-rabu-2-1784713821615_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>TASPEN Proaktif Salurkan Manfaat kepada Pejabat Negara dan Ahli Waris</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:30:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>PT TASPEN menyalurkan manfaat pensiun dan asuransi kepada pejabat negara dan ahli waris, memastikan hak peserta terpenuhi dengan layanan proaktif dan responsif.</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806172626-4-757216/taspen-proaktif-salurkan-manfaat-kepada-pejabat-negara-ahli-waris</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/taspen-1786012200149_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Aturan Program Bedah Rumah Baru Terbit, Ini Isi Lengkapnya</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:22:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Wiji Nur Hayat</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Pemerintah terbitkan aturan baru BSPS untuk mempermudah bantuan bedah rumah bagi MBR. ini isi aturan lengkapnya.</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806171355-4-757206/aturan-program-bedah-rumah-baru-terbit-ini-isi-lengkapnya</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/04/07/pembongkaran-rumah-di-kebon-pala-untuk-dijadikan-rumah-panggung-cnbc-indonesia-muhammad-sabki-3_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Ibadah Haji Ikut Gerakkan Ekonomi RI, Nilainya Rp 8,78 T</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Kontribusi penyelenggaraan ibadah haji pada 2026 mencapai Rp8,78 triliun atau sebesar 0,13 persen terhadap perekonomian Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806154605-4-757176/ibadah-haji-ikut-gerakkan-ekonomi-ri-nilainya-rp-878-t</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/03/21/kepala-badan-pusat-statistik-bps-amalia-adininggar-widyasanti-tiba-di-istana-negara-jakarta-jumat-2132025-cnbc-indonesiatri-su-1742541970128_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Video:Ekspansi Klinik Gigi, Ketersediaan Dokter dan Nakes Jadi Hambatan</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:10:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Ekspansi Klinik Gigi, Ketersediaan Dokter dan Nakes Masih Jadi Hambatan</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806164941-8-757201/videoekspansi-klinik-gigi-ketersediaan-dokter-nakes-jadi-hambatan</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/ekspansi-klinik-gigi-ketersediaan-dokter-nakes-masih-jadi-hambatan-1786010563832_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Ekonom Soroti Kredit UMKM Lesu di Tengah Pertumbuhan Ekonomi 5,29%</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:05:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Pengamat ekonomi menyoroti rendahnya kredit untuk UMKM meski pertumbuhan ekonomi baik. UMKM penting untuk serapan tenaga kerja dan perekonomian Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806150024-4-757155/ekonom-soroti-kredit-umkm-lesu-di-tengah-pertumbuhan-ekonomi-529</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/policy-and-program-director-prasasti-piter-abdullah-1785996188301_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>PNBP ESDM Dapat Tambahan Rp20 M dari Lelang Batu Bara Hasil Penindakan</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>ESDM dapat tambahan sebanyak Rp20,9 miliar untuk PNBP dari lelang batu bara hasil penindakan</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806153617-4-757172/pnbp-esdm-dapat-tambahan-rp20-m-dari-lelang-batu-bara-hasil-penindakan</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/24/tambang-batu-bara-tanjung-enim-pt-bukit-asam-tbk-ptba-dok-ptba-1784862117166_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>AHY: Rapat Dewas Danantara Sepakat Whoosh Diambil Alih Kemenkeu</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:45:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>AHY: Rapat Dewas Danantara Sepakat Whoosh Diambil Alih Kemenkeu</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806142640-8-757145/ahy-rapat-dewas-danantara-sepakat-whoosh-diambil-alih-kemenkeu</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/ahy-rapat-dewas-danantara-sepakat-whoosh-diambil-alih-kemenkeu-1786008874826_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Penampakan Kali Bekasi Hari Ini Usai Viral Menghitam Seperti Oli Bekas</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>(CNBC Indonesia/Muhammad Sabki)</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Kondisi aliran Kali Bekasi yang sebelumnya sempat berubah warna menjadi hitam kini berangsur normal.</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806160247-7-757181/penampakan-kali-bekasi-hari-ini-usai-viral-menghitam-seperti-oli-bekas</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/kondisi-air-kali-bekasi-di-sekitar-jembatan-jalan-m-hasibuan-kecamatan-bekasi-timur-kota-bekasi-jawa-barat-kamis-682026-1786006764553_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Negara Ini Tambal Kas Negara-Hindari Defisit, BUMN Dijual-jual</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Pemerintah India, di bawah PM Modi, kini agresif menjual sahamnya di perusahaan-perusahaan negara (BUMN). Ada Apa?</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806124602-4-757100/negara-ini-tambal-kas-negara-hindari-defisit-bumn-dijual-jual</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/seekor-burung-terbang-melintasi-logo-life-insurance-corporation-of-india-lic-di-salah-satu-kantornya-di-new-delhi-india-pada-3-1785995976565_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Lantik Pejabat, Mendagri Minta ASN Tingkatkan Kinerja</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:39:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Mendagri Tito Karnavian melantik pejabat baru di Kemendagri, Jakarta. Pelantikan ini diharapkan meningkatkan kinerja dan motivasi pegawai dalam organisasi.</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806161449-4-757194/lantik-pejabat-mendagri-minta-asn-tingkatkan-kinerja</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/dok-kementerian-dalam-negeri-1786009154274_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Video: Jaga Daya Beli Warga Miskin dan Menengah, Bansos-Subsidi Dilanjut</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:33:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Jaga Daya Beli Warga Miskin dan Kelas Menengah, DPR Sebut Bansos dan Subsidi Berlanjut</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806152632-8-757166/video-jaga-daya-beli-warga-miskin-menengah-bansos-subsidi-dilanjut</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/jaga-daya-beli-warga-miskin-kelas-menengah-dpr-sebut-bansos-subsidi-berlanjut-1786006095906_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Latihan Militer Buat Tragedi, Pesawat Jatuh dan Hantam Gunung</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Empat orang tewas dalam kecelakaan pesawat ambulans udara di New Mexico. NTSB kaitkan insiden dengan gangguan sinyal GPS akibat latihan militer AS.</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806142704-4-757143/latihan-militer-buat-tragedi-pesawat-jatuh-hantam-gunung</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/05/30/petugas-pemadam-kebakaran-bekerja-di-reruntuhan-pesawat-patroli-maritim-milik-angkatan-laut-korea-selatan-yang-jatuh-di-sebuah-1748563140651_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Soal Ramai Mal Bangun Pagar Tinggi Lalu Dibongkar, Ini Kata Bos Ritel</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:20:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Ketua Hippindo, Budihardjo, menjelaskan fenomena pemasangan pagar di mal lalu dibongkar. Apa katanya?</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806143711-4-757148/soal-ramai-mal-bangun-pagar-tinggi-lalu-dibongkar-ini-kata-bos-ritel</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/pagar-besi-tinggi-yang-sempat-terpasang-di-depan-pusat-perbelajaan-kota-kasablanka-kokas-menteng-dalam-tebet-jakarta-selatan-p-1785735121923_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Pantau Peta Ekonomi RI, BPS Siap Data Seluruh Rumah Tangga dan Usaha</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:16:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Sensus Ekonomi 2026 akan mendata seluruh rumah tangga dan usaha di Indonesia untuk menghasilkan peta perekonomian terbaru dan terlengkap.</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806161414-4-757189/pantau-peta-ekonomi-ri-bps-siap-data-seluruh-rumah-tangga-usaha</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/02/01/833adaa3-d4ca-4e79-9076-b9e052c4476c_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Doyan Belanja, Jemaah Haji RI Habiskan Rp1,96 T Buat Oleh-Oleh</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:15:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Peserta Haji Indonesia belanja Rp1,96 triliun untuk oleh-oleh pada 2026, mencakup 46,1% dari total pengeluaran pribadi. Belanja ini penting bagi jamaah.</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806144739-4-757151/doyan-belanja-jemaah-haji-ri-habiskan-rp196-t-buat-oleh-oleh</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/26/para-peziarah-muslim-menggunakan-payung-untuk-melindungi-diri-dari-terik-matahari-setelah-salat-zuhur-di-luar-masjid-nimrah-di-1779801326900_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Pengangguran RI Terbanyak Lulusan SMA, Tapi Porsi Sarjana Terus Naik</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:05:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Komposisi pengangguran makin banyak berasal dari pemegang gelar sarjana, meski dari sisi jumlah pengangguran terus turun</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806141512-4-757138/pengangguran-ri-terbanyak-lulusan-sma-tapi-porsi-sarjana-terus-naik</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/05/06/infografis-sebaran-pengangguran-di-indonesia-lulusan-smk-terbanyak_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Video: Mencari Pengganti Perry Warjiyo, DPR Sebut Kriteria Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:03:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Mencari Pengganti Perry Warjiyo, DPR Sebut Kriteria Gubernur Bank Indonesia</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806152637-8-757168/video-mencari-pengganti-perry-warjiyo-dpr-sebut-kriteria-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/mencari-pengganti-perry-warjiyo-dpr-sebut-kriteria-gubernur-bank-indonesia-1786006160165_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Potret Pilu Pemakaman Massal 112 Jenazah di Gaza</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Warga Gaza menggelar pemakaman jenazah 112 anggota satu keluarga besar yang tewas dalam agresi Israel.</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260805185933-7-756912/potret-pilu-pemakaman-massal-112-jenazah-di-gaza</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/warga-gaza-menggelar-pemakaman-jenazah-112-anggota-satu-keluarga-besar-yang-tewas-dalam-agresi-israel-hampir-tiga-tahun-lalu-s-1785925831443_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Video:Misbakhun: DPR RI Dukung Purbaya Suntik Dana SAL di Himbara</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:55:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Jaga Ekonomi RI Tumbuh di Atas 5%, DPR RI Dukung Purbaya Suntik Dana SAL di Himbara</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806152637-8-757165/videomisbakhun-dpr-ri-dukung-purbaya-suntik-dana-sal-di-himbara</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/jaga-ekonomi-ri-tumbuh-di-atas-5-dpr-ri-dukung-purbaya-suntik-dana-sal-di-himbara-1786006006914_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Ekspor Nikel RI di 2026 Diramal Hilang 5 Juta Ton Gegara Hal Ini</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Kadin mencatat ketidak pastian RKAB bisa memangkas ekspor nikel hingga 5 juta ton</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806143615-4-757146/ekspor-nikel-ri-di-2026-diramal-hilang-5-juta-ton-gegara-hal-ini</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/31/pengolahan-nikel-1774927170384_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Prabowo Panggil Pimpinan BRIN, Bahas Riset Untuk Program Prioritas</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:45:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Prabowo Panggil Pimpinan BRIN, Bahas Riset Untuk Program Prioritas</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806135014-8-757130/prabowo-panggil-pimpinan-brin-bahas-riset-untuk-program-prioritas</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/prabowo-panggil-pimpinan-brin-bahas-riset-untuk-program-prioritas-1786001727121_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Sudaryono Copot Pengelola Dapur MBG di Jayapura Usai Keracunan Massal</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:42:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>BGN telah menyelidiki keracunan Makan Bergizi Gratis di Jayapura. Pengelola dapur dipecat dan dapurnya disuspend.</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806153904-4-757173/sudaryono-copot-pengelola-dapur-mbg-di-jayapura-usai-keracunan-massal</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/sudaryono-saat-dilantik-sebagai-kepala-badan-gizi-nasional-bgn-oleh-presiden-prabowo-subianto-di-istana-merdeka-jakarta-rabu-2-1784713821615_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Rosan Lapor Prabowo: Danantara Ditawarkan Jadi Pemilik Bandara Madinah</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:41:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>CEO Danantara, Rosan Roeslani, memberikan laporan kepada Presiden Prabowo Subianto terkait kunjungan kerjanya ke Arab Saudi.</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806153939-4-757174/rosan-lapor-prabowo-danantara-ditawarkan-jadi-pemilik-bandara-madinah</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/11/rosan-roeslani-dalam-tasyakuran-hut-ke-1-danantara-indonesia-jakarta-11-maret-2026-1773226499236_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Zulhas dan Sudaryono Kerahkan 1.700 Dapur MBG di 3T, Ini Tujuannya</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:36:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Pemerintah percepat penyelesaian dapur Makan Bergizi Gratis (MBG) di wilayah 3T. Ini tujuannya.</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806152202-4-757169/zulhas-dan-sudaryono-kerahkan-1700-dapur-mbg-di-3t-ini-tujuannya</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/konferensi-pers-terkait-program-mbg-usai-rapat-koordinasi-terbatas-di-kantor-kemenko-bidang-pangan-jakarta-kamis-682026-1786004294635_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Ditanya Purbaya, Fuso Ungkap Canter Lulus Uji B50 Sejauh 40.000 Km</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Mitsubishi Fuso uji truk Canter dengan biodiesel B50 hingga 40.000 km. Hasilnya positif, tanpa dampak negatif pada performa mesin.</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806135158-4-757133/ditanya-purbaya-fuso-ungkap-canter-lulus-uji-b50-sejauh-40000-km</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/menteri-keuangan-menkeu-purbaya-yudhi-sadewa-saat-menghadiri-gaikindo-indonesia-international-auto-show-giias-di-ice-bsd-tange-1785999095652_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Indonesia Gandeng China Bangun Kawasan Industri Madura</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:30:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Indonesia Gandeng China Bangun Kawasan Industri Madura</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806135001-8-757129/indonesia-gandeng-china-bangun-kawasan-industri-madura</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/indonesia-gandeng-china-bangun-kawasan-industri-madura-1786001661520_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Gerak Cepat, Satgas Pangan Dalami Dugaan Pengoplosan Beras Fortifikasi</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:24:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Tim Satgas Pangan intensifkan penyelidikan dugaan manipulasi beras fortifikasi. Pengawasan diperkuat untuk memastikan keamanan dan mutu gizi bagi masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806151856-4-757161/gerak-cepat-satgas-pangan-dalami-dugaan-pengoplosan-beras-fortifikasi</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/satgas-pangan-1786004626371_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Bank Dunia Tugaskan Sri Mulyani Urus Dana Untuk Negara Miskin</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:20:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Bank Dunia Tugaskan Sri Mulyani Urus Dana Untuk Negara Miskin</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806134950-8-757128/bank-dunia-tugaskan-sri-mulyani-urus-dana-untuk-negara-miskin</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/bank-dunia-tugaskan-sri-mulyani-urus-dana-untuk-negara-miskin-1786001520443_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Media Asing: Perang Tarif Trump Berkah ke RI, Pulau Ini Jadi "Surga"</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Media asing menyebut kebijakan tarif Trump membawa berkah bagi RI. Pulau ini bahkan menjadi "surga" manufaktur.</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806125535-4-757104/media-asing-perang-tarif-trump-berkah-ke-ri-pulau-ini-jadi-surga</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/09/08/bendungan-sei-gong-di-kepulauan-riau-batam-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Putin Resmi Legalkan Kripto di Rusia, Izinkan Bitcoin hingga USDT</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Presiden Rusia Putin menandatangani undang-undang yang melegalkan perdagangan kripto, membentuk pasar teregulasi di bawah pengawasan pemerintah mulai 2026.</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806171430-17-757207/putin-resmi-legalkan-kripto-di-rusia-izinkan-bitcoin-hingga-usdt</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/09/ww2-anniversaryrussia-parade-1778317771696_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>TUGU Pimpin Konsorsium Asuransi Proyek Offshore Terbesar di Dunia</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:00:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Tugu Insurance memimpin konsorsium asuransi untuk proyek gas Lapangan Abadi Blok Masela senilai US$20,9 miliar, mendukung perlindungan aset strategis nasional.</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806173701-17-757230/tugu-pimpin-konsorsium-asuransi-proyek-offshore-terbesar-di-dunia</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/25/dok-tugu-insurance-1745598853308_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Prabowo Putuskan Nama Calon Gubernur BI Pekan Ini</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:25:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto akan memutuskan nama calon Gubernur Bank Indonesia (BI) pada pekan ini.</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806180240-17-757246/prabowo-putuskan-nama-calon-gubernur-bi-pekan-ini</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/01/12/bc650501-ec7c-48aa-8760-3a5bd7df914d_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Konsolidasi BUMN, Danantara Gandeng Kemenkeu</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:15:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>BP BUMN dan BPI Danantara bersinergi dengan Kementerian Keuangan untuk mendukung proses konsolidasi dan streamlining perusahaan pelat merah.</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806175638-17-757244/konsolidasi-bumn-danantara-gandeng-kemenkeu</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/31/kepala-bp-bumn-sekaligus-coo-danantara-indonesia-dony-oskaria-saat-ditemui-di-istana-merdeka-jakarta-jumat-3172026-1785502950718_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>BP BUMN Dan Danantara Susun Strategi Untuk 5 Tahun Ke Depan</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:05:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>BP BUMN dan BPI Danantara menyusun arah transformasi perusahaan pelat merah melalui peta strategi lima tahun ke depan.</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806175323-17-757243/bp-bumn-dan-danantara-susun-strategi-untuk-5-tahun-ke-depan</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/05/wisma-danantara-1772701258048_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Pengganti Skor Kredit, Nomor HP Aktif 10 Tahun Bisa Dapat Pembiayaan</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:34:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Pinjaman daring (Pindar) memudahkan akses keuangan bagi masyarakat menengah bawah. AFPI ungkap potensi dan tantangan dalam pembiayaan ini di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806172545-17-757218/pengganti-skor-kredit-nomor-hp-aktif-10-tahun-bisa-dapat-pembiayaan</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/07/29/ilustrasi-sim-card-dok-pixabay_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Didorong Danantara Untuk IPO, Ini Kata Bos Pegadaian</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:10:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Zefanya Aprilia</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>PT Pegadaian mempertimbangkan IPO di BEI.</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806152907-17-757171/didorong-danantara-untuk-ipo-ini-kata-bos-pegadaian</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/02/pegadaian-1756789199443_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>IHSG Terkoreksi Tipis, Turun 0,12% ke Level 6.343</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:50:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>IHSG melemah tipis 0,12% di level 6.343,71 pada 6 Agustus 2026. Sentimen positif dari pertumbuhan ekonomi dan penurunan kemiskinan mendukung pasar.</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806161456-17-757198/ihsg-terkoreksi-tipis-turun-012-ke-level-6343</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893110839_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Dewas Danantara Bahas Perubahan RKAT hingga Pembentukan DSI</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:07:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>BPI Danantara menggelar rapat koordinasi untuk membahas perubahan RKAT dan pembentukan DSI serta DDMF.</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806152217-17-757162/dewas-danantara-bahas-perubahan-rkat-hingga-pembentukan-dsi</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/30/danantara-indonesia-cnbc-indonesiamuhammad-sabki-1751266532126_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Airlangga Bocorkan Format Anggaran dan Susunan Direksi PT DSI</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:45:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Menko Airlangga Hartanto membahas format anggaran dan susunan komisaris PT Danantara Sumberdaya Indonesia dalam rapat Dewan Pengawas.</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806140150-17-757137/airlangga-bocorkan-format-anggaran-susunan-direksi-pt-dsi</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/aimenteri-koordinator-bidang-perekonomian-airlangga-hartarto-pada-konferensi-pers-di-jakarta-rabu-582026-1785971442706_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Bos JPMorgan Bunyikan Alarm 'Bom Waktu', Ada Krisis Mirip 2008?</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>CEO JPMorgan Jamie Dimon memperingatkan risiko tinggi di pasar keuangan global. Ada masalah apa?</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806133545-17-757119/bos-jpmorgan-bunyikan-alarm-bom-waktu-ada-krisis-mirip-2008</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/26/jamie-dimon-di-world-economic-forum-reuters-1769400735415_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>BEI Sambut Baik Inisiatif Danantara Dorong BUMN IPO</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:30:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia menyambut rencana IPO BUMN. Empat perusahaan siap melantai, termasuk Pelindo dan Angkasa Pura, untuk meningkatkan kapitalisasi pasar.</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806151918-17-757160/bei-sambut-baik-inisiatif-danantara-dorong-bumn-ipo</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/15/direktur-utama-bursa-efek-indonesia-jeffrey-hendrik-saat-menyampaikan-pemaparan-dalam-investment-forum-2026-di-bursa-efek-indo-1784106053873_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Airlangga Beberkan Respons China Usai Kemenkeu Ambil Alih Utang Whoosh</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:15:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Menteri Airlangga Hartarto mengungkap respons positif konsorsium China terkait pengambilalihan utang Whoosh oleh Kemenkeu.</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806133459-17-757122/airlangga-beberkan-respons-china-usai-kemenkeu-ambil-alih-utang-whoosh</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/aimenteri-koordinator-bidang-perekonomian-airlangga-hartarto-pada-konferensi-pers-di-jakarta-rabu-582026-1785971442706_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Asing Diam-Diam Kompak Serok Bank BUMN</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:10:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Saham perbankan BUMN jadi incaran investor asing, sementara BBCA mengalami aksi jual terbesar. IHSG stagnan di level 6.351,22 pada sesi I hari ini.</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806141053-17-757149/asing-diam-diam-kompak-serok-bank-bumn</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893110839_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Rupiah Menang Lawan Dolar AS, Ditutup Menguat ke Rp17.910</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:07:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah kembali ditutup menguat terhadap dolar Amerika Serikat (AS).</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806145335-17-757156/rupiah-menang-lawan-dolar-as-ditutup-menguat-ke-rp17910</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342314_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Video: Intip Kinerja Terkini MTEL dan KAEF</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:00:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Intip Kinerja Terkini MTEL dan KAEF</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806135712-19-757136/video-intip-kinerja-terkini-mtel-kaef</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pt-kimia-farma-persero-tbk-akhirnya-mencatat-laba-yang-dapat-diatribusikan-kepada-pemilik-entitas-induk-sebesar-1032-miliar-ru-1786001358289_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Jualan ke Uniqlo-Adidas Laris, PBRX Kok Malah Rugi dan Kas Menipis?</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:20:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>PT Pan Brothers Tbk (PBRX) mencatat rugi US$ 5,19 juta di semester I-2026 meski pendapatan tumbuh 12%. Ketergantungan pada Uniqlo dan Adidas masih tinggi.</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806134217-17-757134/jualan-ke-uniqlo-adidas-laris-pbrx-kok-malah-rugi-kas-menipis</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/02/03/pan-brothersdok-spnorid_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Video: Dihajar Kanan-Kiri, Harga Batu Bara Ambruk-Harga Minyak Melunak</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:31:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Dihajar Kanan-Kiri, Harga Batu Bara Ambruk hingga Harga Minyak Melunak</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806125751-19-757105/video-dihajar-kanan-kiri-harga-batu-bara-ambruk-harga-minyak-melunak</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/dihajar-kanan-kiri-harga-batu-bara-ambruk-hingga-harga-minyak-melunak-1785997253189_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Saham Emiten Grup Djarum (BACH) ARB 3 Hari Beruntun, Ambles 38%</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Saham PT Bach Multi Global (BACH) tertekan, terkunci di ARB selama tiga hari berturut-turut. Penjualan asing meningkat, dengan penurunan 37,9% dari puncak.</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806125706-17-757107/saham-emiten-grup-djarum--bach--arb-3-hari-beruntun-ambles-38</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019552_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Asing Net Sell Rp339 Miliar di Sesi I, Ini Daftar Sahamnya</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:15:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>IHSG stagnan di level 6.351,22 pada sesi I, dengan nilai transaksi Rp10,36 triliun. Investor asing mencatat net sell Rp339,05 miliar.</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806124048-17-757097/asing-net-sell-rp339-miliar-di-sesi-i-ini-daftar-sahamnya</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/04/pengunjung-mengamati-layar-digital-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-jakarta-kamis-462026-1780551448532_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Rehat Dulu, IHSG Sesi Pertama Stagnan di Level 6.351</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:47:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>IHSG stagnan di level 6.351,22 pada perdagangan Kamis. Sentimen positif didorong pertumbuhan ekonomi dan penurunan tingkat kemiskinan di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806120725-17-757095/rehat-dulu-ihsg-sesi-pertama-stagnan-di-level-6351</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019809_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Gap Kredit RI Capai Rp1.650 T, Pindar Bersaing dengan Pinjol Ilegal</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:20:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Asosiasi Fintech Pendanaan Indonesia (AFPI) mencatat gap kredit masyarakat Indonesia mencapai Rp1.650 triliun, membuka peluang dan tantangan bagi pinjaman daring.</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806114636-17-757063/gap-kredit-ri-capai-rp1650-t-pindar-bersaing-dengan-pinjol-ilegal</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/11/15/pinjol-paling-banyak-utangi-warga-ri_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Ekonomi Tumbuh 5,29%, Capaian Positif di Tengah Gejolak Dunia</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:17:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Robertus Andrianto</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Ekonomi Indonesia tumbuh 5,29% pada kuartal II-2026, menunjukkan ketahanan di tengah gejolak global. Piter Abdullah optimis pertumbuhan akan berlanjut.</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806115814-17-757069/ekonomi-tumbuh-529-capaian-positif-di-tengah-gejolak-dunia</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/08/17/warga-mengikuti-upacara-peringatan-hut-ke-79-republik-indonesia-ri-di-kawasan-bundaran-hotel-indonesia-hi-jakarta-sabtu-178202_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>BP BUMN dan Danantara Beri Sinyal Boyong BUMN IPO, Ini Daftarnya</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:32:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>BP BUMN dan BPI Danantara rencanakan IPO sejumlah perusahaan pelat merah, termasuk Pelindo dan Angkasa Pura, untuk tingkatkan kapitalisasi pasar.</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806112632-17-757047/bp-bumn-dan-danantara-beri-sinyal-boyong-bumn-ipo-ini-daftarnya</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/31/kepala-bp-bumn-sekaligus-coo-danantara-indonesia-dony-oskaria-saat-ditemui-di-istana-merdeka-jakarta-jumat-3172026-1785502950718_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Purbaya Buka-bukaan Soal Kemenkeu Ambil Alih 60% Saham Whoosh</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 11:11:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya Yudhi Sadewa bertemu BP BUMN untuk percepatan pengelolaan KCJB dan penyempurnaan regulasi perpajakan demi transformasi BUMN yang lebih efisien.</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806110743-17-757041/purbaya-buka-bukaan-soal-kemenkeu-ambil-alih-60-saham-whoosh</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/14/kereta-cepat-whoosh-dok-kcic-1768369144432_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>15 Pialang Asuransi Diduga Ilegal, Ketua Apparindo Ingatkan Hal Ini</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:45:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Apparindo imbau perusahaan asuransi tidak bekerja sama dengan pialang ilegal. OJK menindak 15 perusahaan pialang tanpa izin untuk perbaikan ekosistem industri.</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260805174410-17-756885/15-pialang-asuransi-diduga-ilegal-ketua-apparindo-ingatkan-hal-ini</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/03/23/e0eb91d8-e067-4072-9c51-e4170bd1a817_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Dukung Proyek Strategis, WIKA Bukukan Kontrak Baru Rp 6,91 T</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:22:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Khoirul Anam</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>PT Wijaya Karya raih kontrak baru Rp6,91 triliun hingga Juni 2026, didorong proyek strategis di sektor konstruksi dan energi.</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806101124-17-757015/dukung-proyek-strategis-wika-bukukan-kontrak-baru-rp-691-t</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/wika-1785986471838_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Sebulan Naik 56,84%, BEI Pantau Ketat Pergerakan Saham TRUK</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:20:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia (BEI) memantau ketat pola pergerakan Unusual Market Activity (UMA) atas emiten logistik PT Guna Timur Raya Tbk. (TRUK).</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806094352-17-756999/sebulan-naik-5684-bei-pantau-ketat-pergerakan-saham-truk</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019966_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Harga Naik 132,2%, BEI Gembok Perdagangan Saham DOOH</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:00:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia (BEI) menghentikan sementara perdagangan (suspensi) saham PT Era Media Sejahtera Tbk (DOOH) karena mengalami peningkatan harga.</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806094057-17-756998/harga-naik-1322-bei-gembok-perdagangan-saham-dooh</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019625_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Video: Pasar Semringah,IHSG Menghijau dan Rupiah Menguat ke Rp17.900/USD</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:54:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Pasar Modal RI Semringah, IHSG Menghijau dan Rupiah Menguat ke Rp 17.900 per USD</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806094701-19-757000/video-pasar-semringahihsg-menghijau-rupiah-menguat-ke-rp17900-usd</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pasar-modal-ri-semringah-ihsg-menghijau-rupiah-menguat-ke-rp-17900-per-usd-1785984608257_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Harga Minyak Naik ke US$80, Pasar Khawatir Gangguan Pasokan</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:25:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Harga minyak dunia bergerak sedikit menguat pada perdagangan Kamis (6/8/2026) pagi waktu Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806085301-17-756982/harga-minyak-naik-ke-us-80-pasar-khawatir-gangguan-pasokan</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/04/usa-oilproduction-1767530216300_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>OJK Tindak 15 Pialang Asuransi Ilegal, Ketua Asosiasi Beri Imbauan Ini</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:10:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Apparindo mengimbau perusahaan asuransi untuk tidak bekerja sama dengan perusahaan pialang (broker) tanpa izin.</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806085524-17-756985/ojk-tindak-15-pialang-asuransi-ilegal-ketua-asosiasi-beri-imbauan-ini</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/03/ketua-umum-dai-dewan-asuransi-indonesia-yulius-bhayangkara-menyampaikan-pemaparan-dalam-acara-market-outlook-2026-di-bursa-efe-1772514199286_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Rekomendasi Saham Hari Ini: Ada ATNM hingga KBLF</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:05:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Rekomendasi saham hari ini termasuk ANTM, BRMS, dan KLBF. Cek target harganya.</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806083357-17-756971/rekomendasi-saham-hari-ini-ada-atnm-hingga-kblf</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/market-1785980036-1785980037057_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Pagi Ini Rupiah Dibuka Menguat, Dolar AS Turun ke Rp17.900</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:02:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Momentum penguatan rupiah masih berlanjut pada pembukaan perdagangan hari ini.</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806082552-17-756980/pagi-ini-rupiah-dibuka-menguat-dolar-as-turun-ke-rp17900</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342884_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>IHSG Dibuka Naik 0,5%, Mayoritas Saham Masih Belum Bergerak</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 09:02:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>IHSG dibuka menguat pada 6 Agustus 2026, didorong sentimen positif global dan domestik. Ekonomi Indonesia tumbuh 5,29%, mendukung optimisme pasar.</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806084736-17-756981/ihsg-dibuka-naik-05-mayoritas-saham-masih-belum-bergerak</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893111052_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Pan Brothers Balik Rugi, Laba Tahun Lalu Tinggal Kenangan</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:50:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Pan Brothers (PBRX) mencatat rugi bersih US$5,19 juta di semester I-2026 meski penjualan naik 12,1%.</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806081247-17-756969/pan-brothers-balik-rugi-laba-tahun-lalu-tinggal-kenangan</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/02/03/pan-brothersdok-spnorid_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Bursa Asia Dibuka Variatif, Nikkei-Kospi Koreksi</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Pasar Asia-Pasifik bervariasi pada 6 Agustus 2026, dengan Nikkei 225 turun dan Kospi anjlok. Dow Jones mencapai rekor tertinggi, didorong laporan laba dan AI.</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806080153-17-756965/bursa-asia-dibuka-variatif-nikkei-kospi-koreksi</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/04/japan-financial-markets-1743746448303_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>OJK Cabut Izin BTPN Syariah Ventura, SMBC Buka Suara</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:20:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>OJK mencabut izin usaha BTPN Syariah Ventura.</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806050557-17-756938/ojk-cabut-izin-btpn-syariah-ventura-smbc-buka-suara</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/03/26/ilustrasi-ojk-cnbc-indonesiafaisal-rahman-2_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Purbaya Bebaskan Pajak Konsolidasi BUMN hingga 2028</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:15:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengungkap potensi pajak Rp500 triliun dari konsolidasi BUMN.</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806074710-17-756964/purbaya-bebaskan-pajak-konsolidasi-bumn-hingga-2028</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/menteri-keuangan-purbaya-yudhi-sadewa-saat-konferensi-pers-hasil-rapat-berskla-kssk-iii-tahun-2016-di-jakarta-senin-382026-1785748274270_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Perlahan Asing Geser Haluan Lagi, Incar Saham Ini</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:50:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Investor asing mencatat net sell Rp182,8 miliar, namun saham komoditas seperti ANTM dan TINS menarik perhatian dan mencatat net buy.</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806043226-17-756936/perlahan-asing-geser-haluan-lagi-incar-saham-ini</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/10/06/karyawan-melintas-di-dekat-layar-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-jakarta-rabu-61020-6_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Ada Tiga Emiten Baru Masuk Daftar Saham HSC, Ini Daftar Lengkapnya</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:20:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia menambah tiga emiten baru ke daftar High Shareholding Concentration (HSC), total kini menjadi 54 saham.</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806044135-17-756937/ada-tiga-emiten-baru-masuk-daftar-saham-hsc-ini-daftar-lengkapnya</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797018973_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>IHSG Lanjut Reli, Asing Malah Kabur Lagi</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:50:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Investor asing mencatat net sell Rp182,8 miliar pada 5 Agustus 2026, namun IHSG tetap menguat 0,50% ke level 6.351,14. Saham TLKM paling banyak dijual.</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260806042743-17-756935/ihsg-lanjut-reli-asing-malah-kabur-lagi</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019625_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1182"/>
+  <autoFilter ref="A1:I1310"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1311</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1310"/>
+  <dimension ref="A1:I1311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -62008,8 +62008,55 @@
         </is>
       </c>
     </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Buruh Tetap Kawal Pembahasan RUU Ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 13:28:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Buruh menegaskan tetap berada dalam status siaga untuk mengawal pembahasan Rancangan Undang-Undang (RUU) Ketenagakerjaan di DPR RI.</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8606831/buruh-tetap-kawal-pembahasan-ruu-ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/01/ilustrasi-kepadatan-lalin-saat-demo-buruh-1777601372612_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1310"/>
+  <autoFilter ref="A1:I1311"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1311</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1311"/>
+  <dimension ref="A1:I1337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -62055,8 +62055,1230 @@
         </is>
       </c>
     </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Menkum Tunggu DPR soal Penggantian Nama RUU Perampasan Aset</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:55:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Menkum Supratman menunggu kabar DPR tentang usulan penggantian nama RUU Perampasan Aset. RUU ini sudah masuk prolegnas dan mendapat masukan dari para ahli.</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806213936-12-1389511/menkum-tunggu-dpr-soal-penggantian-nama-ruu-perampasan-aset</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/09/dpr-setujui-ruu-polri-jadi-undang-undang-1780995987689_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Prabowo: Investasi RnD Indonesia Masih Sedikit, Kita Perbaiki</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:50:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengakui rendahnya investasi RnD di Indonesia dan berkomitmen untuk meningkatkannya. Ia menekankan pentingnya kualitas pendidikan.</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806192627-20-1389473/prabowo-investasi-rnd-indonesia-masih-sedikit-kita-perbaiki</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-1786016567897_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Keluarga Korban KMP Mutiara Sentosa yang Masih Hilang Diminta Melapor</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:45:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Keluarga korban KMP Mutiara Sentosa II yang hilang diminta melapor ke Polres Tanjung Perak atau KSOP untuk mendukung proses pencarian oleh Basarnas.</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806204344-20-1389507/keluarga-korban-kmp-mutiara-sentosa-yang-masih-hilang-diminta-melapor</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/62-korban-kmp-mutiara-sentosa-ii-tiba-di-surabaya-dari-masalembu-1785831912067_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Polresta: Bripda RF Diduga Rencanakan Pembunuhan Lansia Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:30:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Bripda RF ditetapkan sebagai tersangka pembunuhan berencana nenek Nurlis di Deliserdang. Tersangka merusak CCTV sebelum kejadian dan melarikan diri setelahnya.</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806201531-20-1389492/polresta-bripda-rf-diduga-rencanakan-pembunuhan-lansia-deli-serdang</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/09/14/5cf965a3-c769-46ef-a4b8-ca0c095cfd58_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Pakar Hukum soal RUU Perampasan Aset: Lebih Tepat Istilah Pemulihan</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:18:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Guru Besar Hukum Unissula usulkan istilah 'pemulihan aset' dalam RUU Perampasan Aset agar lebih restoratif.</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806203332-12-1389505/pakar-hukum-soal-ruu-perampasan-aset-lebih-tepat-istilah-pemulihan</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/10/31/57bd5113-e11c-46b7-948b-d8a96adbc8eb_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Menkum Bakal Gratiskan Tarif PNBP Pemberitahuan Laporan Tahunan RUPS</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:11:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Menteri Hukum Supratman Agtas mengaku sedang mengusulkan ke Menkeu untuk penggratisan tarif PNBP pada laporan tahunan RUPS.</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806215103-20-1389512/menkum-bakal-gratiskan-tarif-pnbp-pemberitahuan-laporan-tahunan-rups</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/11/18/dpr-setujui-ruu-kuhap-menjadi-undang-undang-1763445439624_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>1 Tahun Kasus Dana CSR BI dan OJK, KPK Belum Tahan 2 Anggota DPR</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:07:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>KPK terus menyelidiki kasus korupsi dan pencucian uang terkait program sosial di BI dan OJK. Dua anggota DPR telah ditetapkan sebagai tersangka.</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806204652-12-1389508/1-tahun-kasus-dana-csr-bi-ojk-kpk-belum-tahan-2-anggota-dpr</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/05/ilustrasi-gedung-kpk-7_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Korupsi Pesawat Fiktif, Eks Pegawai BUMN Tersangka Kejari Tangerang</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:58:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Kejari Tangerang menetapkan FA, eks VP PT Angkasa Pura Cargo, sebagai tersangka korupsi pesawat fiktif. Proyek gagal, penyidikan masih berlanjut.</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260805105021-12-1388801/korupsi-pesawat-fiktif-eks-pegawai-bumn-tersangka-kejari-tangerang</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/09/08/ilustrasi-tindakan-kriminal-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Tragedi Kebakaran Maut di Bombana Sultra, Ibu dan 4 Anak Tewas</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:45:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Kebakaran di Bombana, Sulawesi Tenggara, mengakibatkan tewasnya seorang ibu dan empat anak.</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806194611-20-1389489/tragedi-kebakaran-maut-di-bombana-sultra-ibu-dan-4-anak-tewas</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/12/24/ilustrasi-kebakaran-pabrik_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Usai Don Ritto, Tim 9 Kejagung Juga Geledah Rumah Nurman Herin</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:17:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung menggeledah rumah Nurman Herin di Bandung terkait kasus TPPU emas 74 kg dan Rp543 miliar.</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806202827-12-1389504/usai-don-ritto-tim-9-kejagung-juga-geledah-rumah-nurman-herin</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/31/kejagung-tahan-nurman-herin-terkait-kasus-tppu-mantan-jampidsus-1785471654529_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Usai Imbauan Walkot, Pengelola Mal Surabaya Kini Pendekkan Pagar</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:16:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Pengelola mal di Surabaya, Pakuwon Group, memendekkan pagar di Tunjungan Plaza dan Pakuwon Mall untuk menjaga estetika kota, sesuai imbauan Walkot Eri Cahyadi.</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806202621-20-1389503/usai-imbauan-walkot-pengelola-mal-surabaya-kini-pendekkan-pagar</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/usai-tinggikan-pengelola-mal-surabaya-kini-pendekkan-pagar-karena-imbauan-walkot-1786019976304_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>FOTO: Kebakaran Hutan Gunung Bromo, Kemenhut Kerahkan Operasi Terpadu</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:09:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan seluas 70 hektare melanda Gunung Bromo hingga Kamis (6/8). Akibatnya, tiga akses masuk wisata kawasan Gunung Bromo.</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806190958-22-1389459/foto-kebakaran-hutan-gunung-bromo-kemenhut-kerahkan-operasi-terpadu</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/kebakaran-hutan-kawasan-gunung-bromo-1786018084811_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>FOTO: Karhutla dan Kekeringan Landa Boyolali Imbas Kemarau</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:00:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan (karhutla) serta kekeringan melanda wilayah Boyolali, Jawa Tengah.</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806070138-22-1389129/foto-karhutla-dan-kekeringan-landa-boyolali-imbas-kemarau</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/pemadaman-kebakaran-kawasan-hutan-di-boyolali-1785974493169_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>KPK Lakukan Penggeledahan di Kota Bengkulu</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:40:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>KPK menggeledah lokasi di Kota Bengkulu terkait dugaan korupsi suap pengelolaan limbah kesehatan.</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806202244-12-1389495/kpk-lakukan-penggeledahan-di-kota-bengkulu</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/05/ilustrasi-gedung-kpk-8_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Pemilik soal Ratusan Airsoft Gun di Sekolah Jaksel: Buat Ekskul Nembak</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:36:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Direktur Utama PT Lokta Karya Perbakin menjelaskan bahwa 995 senjata airsoft yang ditemukan di sekolah Jaksel untuk ekstrakurikuler menembak.</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806200454-12-1389491/pemilik-soal-ratusan-airsoft-gun-di-sekolah-jaksel-buat-ekskul-nembak</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>TNI AD soal Wacana Sertifikat Pramuka Garuda Tanpa Tes: Tetap Seleksi</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:16:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>TNI AD menegaskan sertifikat Pramuka Garuda tidak menjamin penerimaan tanpa seleksi.</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806194631-12-1389477/tni-ad-soal-wacana-sertifikat-pramuka-garuda-tanpa-tes-tetap-seleksi</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/06/pengibaran-serentak-bendera-merah-putih-1754479814794_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Mangkir Lagi, KPK Ingatkan Rudy Tanoe Kooperatif</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:11:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>KPK mengingatkan Rudy Tanoe untuk kooperatif setelah mangkir dari panggilan. Dia penting dalam kasus dugaan korupsi bansos beras 2020.</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806194924-12-1389478/mangkir-lagi-kpk-ingatkan-rudy-tanoe-kooperatif</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/12/14/bambang-rudijanto-tanoesoedibjo_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Buntut Penebangan Pohon, Videotron di Padel Cihapit Bandung Disegel</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:05:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Satpol PP Bandung segel videotron di SixNine Padel setelah penebangan 10 pohon tanpa izin. Penyelidikan masih berlanjut untuk mengungkap pihak terlibat.</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806144153-20-1389332/buntut-penebangan-pohon-videotron-di-padel-cihapit-bandung-disegel</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/penyegelan-videotron-sixnine-padel-buntut-penebangan-10-pohon-secara-ilegal-di-bandung-1786001631954_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Prabowo Tes Langsung Kekuatan Genteng Buatan BRIN</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:31:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto uji coba ketahanan genteng inovasi BRIN berbahan sabut kelapa. Kunjungan ini melibatkan 150 peneliti yang memamerkan temuan mereka.</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806183730-20-1389439/prabowo-tes-langsung-kekuatan-genteng-buatan-brin</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-1786016568023_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Pihak Sekolah di Jaksel Ungkap Momen Temukan Ratusan Senpi</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:23:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Kuasa hukum mengungkap 995 senjata ditemukan di ruang mantan ketua yayasan sekolah di Jakarta Selatan. Temuan ini termasuk senjata api dan narkoba.</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806184026-12-1389443/pihak-sekolah-di-jaksel-ungkap-momen-temukan-ratusan-senpi</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Hasan Nasbi Duga Makalah MBG untuk Nobel Bukan dari Pemerintah</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:13:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Penasihat Presiden Prabowo buka suara soal makalah program Makan Bergizi Gratis yang diajukan jadi Nobel Perdamaian 2026.</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806185935-32-1389450/hasan-nasbi-duga-makalah-mbg-untuk-nobel-bukan-dari-pemerintah</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/27/hasan-nasbi-1777279292814_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Selain Senpi, CD Porno-Narkoba Juga Ditemukan di Yayasan di Jaksel</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:10:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Ratusan senjata api, narkoba, dan CD porno diduga ditemukan di ruangan mantan ketua yayasan sekolah di Pondok Pinang, Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806181924-12-1389432/selain-senpi-cd-porno-narkoba-juga-ditemukan-di-yayasan-di-jaksel</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Dukung MBG di Wilayah 3T, Mendagri Siap Kerahkan Ditjen Dukcapil</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:05:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Kemendagri</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Menurut Mendagri, masyarakat di wilayah 3T seperti Papua, NTT, dan Malukumerupakan kelompok yang paling membutuhkan perhatian pemerintah.</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806184637-25-1389444/dukung-mbg-di-wilayah-3t-mendagri-siap-kerahkan-ditjen-dukcapil</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/kemendagri-1786016909695_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Selain Senpi, Ada Ruang Diduga Bunker di Yayasan Sekolah Pondok Pinang</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:04:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Selain 995 senjata api, alat pembuat peluru, dan narkoba, gedung yayasan sekolah di Pondok Pinang Jaksel juga ditemukan ruang diduga bunker.</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806183504-12-1389448/selain-senpi-ada-ruang-diduga-bunker-di-yayasan-sekolah-pondok-pinang</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Menkes Sedih Respons Banyak Nakes Cibir Pasien BPJS di Medsos</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Menkes Budi Gunadi Sadikin menanggapi komentar menghina pasien BPJS oleh tenaga kesehatan. Ia menekankan pentingnya empati dalam profesi kesehatan.</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806174644-20-1389415/menkes-sedih-respons-banyak-nakes-cibir-pasien-bpjs-di-medsos</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/07/pemerintah-pulihkan-pelayanan-kesehatan-di-wilayah-terdampak-bencana-1767781411341_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Prabowo Antusias Cermati Perkembangan Teknologi dan Hasil Riset BRIN</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:05:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengunjungi pameran riset BRIN di Istana, melihat inovasi untuk program prioritas seperti ketahanan pangan dan energi.</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806175333-20-1389418/prabowo-antusias-cermati-perkembangan-teknologi-dan-hasil-riset-brin</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/31/pertemuan-presiden-prabowo-dengan-pengusaha-kadin-1785486310599_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1311"/>
+  <autoFilter ref="A1:I1337"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-06.xlsx
+++ b/data/berita_2026-08-06.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1338</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1337"/>
+  <dimension ref="A1:I1338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -63277,8 +63277,55 @@
         </is>
       </c>
     </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Smelter Raksasa Bahan Baku Baterai EV Mulai Beroperasi di Sultra!</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:50:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>PT Vale Indonesia Tbk menjadwalkan operasional atau startup proyek High Pressure Acid Leaching (HPAL) raksasa di Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806175304-4-757242/smelter-raksasa-bahan-baku-baterai-ev-mulai-beroperasi-di-sultra</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/01/29/vale-reuterswashington-alvesfile-photo_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1337"/>
+  <autoFilter ref="A1:I1338"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>